--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E647"/>
+  <dimension ref="A1:E659"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11398,9 +11398,213 @@
         <v>08-09-2026 09:13:51 pm</v>
       </c>
     </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>6aac3e7e25ff80deb19c23e6</v>
+      </c>
+      <c r="B648" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C648" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D648" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E648" t="str">
+        <v>18-09-2026 12:54:46 am</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>6aa02d38bc28a15fc89bd2d6</v>
+      </c>
+      <c r="B649" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C649" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D649" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E649" t="str">
+        <v>08-09-2026 09:13:52 pm</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
+        <v>6aac3e7e25ff80deb19c23e8</v>
+      </c>
+      <c r="B650" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C650" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D650" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E650" t="str">
+        <v>18-09-2026 12:54:46 am</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>6aac3e8825ff80deb19c24e2</v>
+      </c>
+      <c r="B651" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C651" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D651" t="str">
+        <v>Started Playing game and Debited "10" and Balance "400"</v>
+      </c>
+      <c r="E651" t="str">
+        <v>18-09-2026 12:54:56 am</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>6aac3e8925ff80deb19c24e8</v>
+      </c>
+      <c r="B652" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C652" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D652" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E652" t="str">
+        <v>18-09-2026 12:54:57 am</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>6aac3ea625ff80deb19c2533</v>
+      </c>
+      <c r="B653" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C653" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D653" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E653" t="str">
+        <v>18-09-2026 12:55:26 am</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>6aac3ea625ff80deb19c253a</v>
+      </c>
+      <c r="B654" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C654" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D654" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E654" t="str">
+        <v>18-09-2026 12:55:26 am</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>6aac3ec625ff80deb19c2633</v>
+      </c>
+      <c r="B655" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C655" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D655" t="str">
+        <v>Started Playing game and Debited "10" and Balance "390"</v>
+      </c>
+      <c r="E655" t="str">
+        <v>18-09-2026 12:55:58 am</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>6aac3ec625ff80deb19c2639</v>
+      </c>
+      <c r="B656" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C656" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D656" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E656" t="str">
+        <v>18-09-2026 12:55:58 am</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>6aac3f2325ff80deb19c2662</v>
+      </c>
+      <c r="B657" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C657" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D657" t="str">
+        <v>Answered incorrectly for Qst ID: 6aac3ec725ff80deb19c2644, Qst: How many colour names match their text colour out of 12?, Submitted Answer: 7, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nO3dd3wUdf748df2zaaS0EvoLYICCgICAgI27AUbHiLnnXI/7JyoX08P9Sxn4RBExAJ3Koh6h9gBqdKR3pQuhCRAerLJtvn98clmd7O7SZgECPh+Ph772JnPfOYzZbPznk+ZjUHTNA0hhBDiJBnP9A4IIYQ4O0kAEUIIoYsEECGEELpIABFCCKGLBBAhhBC6SAARQgihiwQQIYQQukgAEUIIoYsEECGEELpIABFCCKGLBBAhhBC6SAARQgihiwQQIYQQukgAEUIIoYsEECGEELpIABFCCKGLBBAhhBC6SAARQgihiwQQIYQQukgAEUIIoYsEECGEELpIABFCCKGLBBAhhBC6SAARQgihi7mmBRzPux+Pdw8mYyMaJM0iOCZ5vPs5nncfAHExo7Fb+3I8b0yl5SXFPYPd2h+n60eKnHMwGZOpF/+PqPkLimdQ6l6HzdKTeEflZYOPIuenFJZ8gtvzC2huzKaWOOzXEO+4D4PBUVbmexSVzMZsakn9xBnlaxc6P6TQ+REACY5xOOzXlJebmX0NGi6S4p7Cbh1YxX7UfX/8Ixw4EJqWmAhxcXDRRXDPPRAbq9LXrYMnn6y8vLfego4d4bXX4LvvAulWKzRqBKmpcMstcN55tXoYZ4fNm2HqVFizBgoKoHFjSEuDsWOhW7dAvu++UycwmN0OMTHQpg3ceiv06BFYNmYMHDwYfbsDB8JTT6k8Y6r47jzzDPTvD7Nnw3vvqT+Ejz9W2/Z77z21/Ior4NFHq334Z8LXX8PMmbB9O5SUQNOmarfHjoWkpEC+kz3lwSZOhGXLwGyGzz4LfF/8Nm2Cxx9X01OnQvv2gWUrVsBzz0GrVvDuu6Hr7dmjvk8rVkBODtSvDx06wH33qY/I72S+l7ppNVRcslDbl27Q9qWj5RdNC1mWmX2jti8d7VBmS83rK9Bc7u3avnQqfRU652qapml5hZPK1k2tdPuZObdp+9LRMnNuqzSfT3OX70+k129ZaZrbc0jTNE0rdH6u7UtH259u0Xy+ovIyjh4fXJ4/K+fu8vRS97bydLdn30mdv7qqSxdNg+ivbt00zelUeb/9tvK8oGlr1qi8o0dHz2M2a9o775y5Yz4jJk/WNIsl8gmxWjXt++8Ded97r/KTbDRq2vz5gfxpaZXnv63sO7N9e9Uf4Fz1vdT+8Y9A2lNPhR7LE0+o9NGjT+05q6EHHoh+mC1aaNq2bYG8J3vK/fLzNS02NpBvxozwPIsWBZYPHRq67PPPVXqXLqHpc+aElhv8Mhg0bdasQN6T+V7qVeMaSIztMuJiRlLonEV2wVPE2m/GaEzBWbqIopIvAEhJnILREIc3aL0GSR9gMjYPK89qOb+muxRRbsGzZftjIMFxP3GO0RgNCThdC8jJfwK3ZwfHcm+jScoK7NZ+gAENN6Xu9ditA9C0YkrcK8vLK3EtKZ8uda0GwGxqgdnU+pTs/5kyahTceWdgfulSeP55dff0+eehy0Dd2Vmt4eV06hQ636cP/P3v4PNBVpa6eV2yRN0B9u4N55+aP4O65ccf4cEH1Um4/HKYMEHd1m7dCg8/DL/8AnfdBYcPh57U+Hj44ovAfH4+jB8Pe/fC3/4Gw4eHbmf0aLj99vDtN2oUnvbBB9A8/HsZ8QN59VW1fxU/3Dps2jR1tw8wYgQ89BA0aAArV8Jjj8Fvv8H118O2bWCzBdY72VM+ezYUFQXmp0+He++Nvl8LFsCcOWqfotm2TX0fnU64+GL1/enUCfbtUzWZ9etVy8GVV6paSbDqfi9PVo0DCEBywms4S7/B6ztOdsHTpCROJjv/IQBiY0bgsF0dto7N0heLuUNtbL5KmuYkr+hNABJjHyI54fXyZRZzeyymdmRkX06JayXO0kXE2IZgMXfE7dlFqXsNdusASlwr0LQSLOYOeLwH8XgP4fHuw2xqQ6l7FQB264DTcjynU9u2MGRIYH7IEHWNOXIEfv01PP/gwaqKX5UGDULLveUW6NpVlfnWW+oLd86bOFEFj2HD4NtvwWBQ6S1aqLaLu+6CCy6Ao0ehZcvAehZL6MkD2L9fXQH37AnfTsUPsTJ9+6r2kOpwuVTEX7gwsO913EsvqfdbblEXeb+2baF7d3W69+yBTz5RF2u/kz3lM8pavu+9F95/H9auVTddwS2SFT3yiLr4JyREXv7yyyp4XHCBahrzB4TUVBUgrrwSOndWfy4VA0h1v5cnq1YCiMlYn+SE1zmWezcFxe8CHlyebRiN9UhJeDPiOm7PdnxaQUiaAcspqYGUuFaiaep2IM4RfhsQYxuGydQMr/cITtcCYmxDsFv7qQDiWg2x4CxdCIDDdjWl7k2UuBbjLF1CvKNNeQ3kXAwgFa1fr/5AIfJ1ZuPG8Dud2Niq73RsNrjhBnjlFfXlOOfl5qrqHKgaQsULcFoa/Pxz9coqKYEfflDTwQ3pfunpsGFDeHrHjqovI9j27aofJpjFEl4D6dBB3X7/+KPqC6lYFa2Ddu8OdAlFqg106QI9e6quqIULQwNIRZWd8q1bVcAwGuHZZ2HHDli1St0U+Ws/wZKT1SlOT4f/+z+YNCnyNufNU+8jR4Z/xxo2jPwR++n9XlalVgIIUNaM9W+cpQsoKFbhNzn+FUzGxhHzZ+bcGJZmMjUlteGR2tqlcl7f4bIpA5YoTUwWU1u83iN4vIcAsFv7U1A8gxKXql04XSqA2G1DMBpTKHEtpsS1lNiYm3B5dpatc+4FkDfeUDUOrxeyswPXll691F1cRX37hqf17q2+QFVp1ky9+wPUOe3QIdUMDer212/9+vDA0bOnuj32y80NrFNQoHpSPR4VhZ9/PnxbU6aoV0U//RT+gd0Y/r2kaVNV5QzWpYvqdf7Xv9Rt+NXhrQx1TfAhBJ/yYG3bqgBScezByZzy995T74MHq9bAP/xB/f1/9JFq9avYme5wqJrRXXepjylS4Ar+7rVrF0jfuROWLw/Nm5YG/fqFptXke1mZWgsgACmJb3PkWFc0zYndOoD4CHf7fnZr3/JRT35GY0pt7k45TQvufYlW1dZC3u1WNZzB6ztKqXsDLvdmDFiwWwdgMtYnp+BpSlyLKXWtBXyYjA2xmGsynKFuys5WL7+WLVVT/ahR6q6posGD1Z1XsM6dq7et0lL17vVWnu+c43YHpufPV43bwV54ITSA+Hyq4dvPYID771fNSZGGsbVrp5rEKgoebuTXt6+6ogVLifK9nDhRdYQdOaJGc0Vre6kjPJ6q8/hjuv/dr7qnvLQU/vMfNX3XXerd39eSn6+axiINeLvzTnWjtmiRKvexx6Lvo8sVmF6+HP70p9DlDzwQHkBq8r2sTK0GEIupLRZTW1yebcTYLif6xRrqJ35w2vpAzKayW1s03N69WM1dwvK4vXtVXmOLsnVaYzY1x+M9TF7hi4APm/USjIY4bJYLMRrr4fH+RqHzY8Bf+zg72oFPxsSJ6o95zhzV0nLokHoFdzAG+/pr/W2th8sqipH6ds85qanqG+3zqUb0Pn1Uer9+8Ne/qunp09WtbkXJyXDihOowuv121XaxZInq1Y3knnuqHs/p98EH1e8DSUiAN99UVdF33lHDguswfw0X1CkPvpMPTgfVDRWsuqf8v/9V+UDVNiZPVtP+i/f06dFHTE+dqloK16wJH7qbnKxOd35+aJ9Lt26BP5dPPlHfzUhq8r2szO/iQUKbtQ8GgxqvXlD8XthyZ+m3eL3pAMTYBpen+2shRSX/K1vm70UzEWMdpJaVPRfiz3susttVNXzCBHVn9uKLqtm7NmmaalGB0LHs56ykJBhQ1uQ5Y4YKJABDh6r2jJdein7n79e+Pcydqx7Q2blTXdmqc5tdm26+WfXeer3q9rkO69xZPWIDgWamYFu2BPoRBg8OXw5Vn/LgcrdvV+Vt2ADFxSpt3TrVHxFJhw7wxBNq2t+/Euzaa9X7rFmB2nqvXoE/lzZtIpd7Kp2xAOL2bKfUvSHs5fEeDsmnaa4o+Q6E5PP5siPm8/qOYTQkkOC4H4D8okmcyB+H27MTj/cwBcXvkpVzGwBWS/eympNiKw8K6sttt15WvsxeFkw03GXLzr3+j4qefVY1x4Oquh8+HJ5n48bAlyb4lZUVmi83N7BswYLAXZ3JBOPGnfJDqRueeUa1hSxbBlddpXpes7LU/O23q07qqrRuHbjNXb1aRfeK/J3oFV9bt4bnDb7qBb8ifdh+b70V3uxVBxmNgRrDZ5+pZqPNm1Wf2+zZKnb7fKr2UdmYgGinfP9+NaYAVG1g797Ql38gXWUjDJ94IvI4CP8ymw127YJLL1V/JllZah/+/Gf1YGE01f1enrSaPUYS7nBWF21fOlpOwQthy6rzIOGJvMc0TQs8SBjt5X+Qz/8gYbRXftHbmqZpms9XomWcuCpqvkOZrTWX+9eQ/S11by1ffuBogubTXEHH8ktgWUaSpmne2j6VZ5T/QcKJE0PTt2/XNLtdLbv+epVWnQeWJk1SeSt7kNBo1LQ33ji9x3nGTZqknqCMdlI6dw482eZ/qi05Obyc665Ty2w2Tdu5U6VV9SBhq1YqX3UeJHxMfS/LHyS88cbQ7b/4YiBvHX6Q0OvVtFGjoh9mw4aatm5dIP/JnPKnn1bzTZtqmscTnv9vf1PLExI0raAg8CBh8+ah+RYsCOxPxQcJZ8/WNIej8gchf/pJ5T2Z76VetdoHAmCz9sZkahzxgTqDITaoGSgyi1mFX7MptdK8VvN5Ze9d8FWSz2RqXrZtG42Sv6TQ+TGFzv/g8mwn+KdMEmLHYTQkVthGGg7bcDRKsFp6YCDQa2wxtyfWfjM+LRerpQfnWmtg796qut+6wseYlqZGZn3+ORQWqhvWlJSqHzNITQ2sXzGvzaaq7yNHhvYV/y6MG6easqZNU214GRmqwbt7dzUi6qabVLUM1GioIUPUU20VTZum2jU8Hvj0U1W76dNHrRONv7MpNrbqD9B/W9yqlcpbcVjvo4+q29ycHPUh11FGo+rmuf569XzGxo3q2YpmzdSgsocfDu2DO5lTfviwyjt8eOAjCzZqVKCZdsMG9TEPGRL+zMaQIapfY8OG8LEPI0aon06ZOlX1waSnq5HYXbvCddfBHXcE+idP5nupl0HTKo43EEIIIap2bt02CyGEOG0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF3MNS4hayNoPrDGQ70Oocs0n1oOEJMCjsZwYnvl5SW2AXs9KM2DkhNgMENCavT8xVngLgRLHDgaVmOHNcjaBNm7wOeG+FRo2hdM1kCW/EPgPAaWWEjuFLStTCg4XLafrcGeHFh2bDP4PJDQEmLqV2M/ToPt26GkJDAfEwNJSerlcATSnU7YsUNNd+kCNltgWXY27N8PRiN0767SDh6E48fDt1evHrRoARZLIM3rhU2bQvPFxwf2wxp03ouKIDNTTbdpE/24om3fz2qFrl2jL6/rduxQn0kwhwMSE6Fp09D00lI4ckRNt2wJJlPkMo8cgYwMiI2FTp1Cl+3ZA3l5UL++KgNg40bw+aLvY+PG0KxZ9Y/pHOP27MCnhX5GBkwYjcmYTS0AQ3m6T8vH7fm10vKs5k4YDLF4vAfx+kL/tk3GRphMjTBgibL2GaTV1MKxmvZPNO1Nu6bl7AldtmWGWvZPg6b9tkTTjm8vm6/ktXuuWnfDJDU/PbXy7X91m8r31W1V7+uRnzTt/U7h25zaUNO2fRjIt/71svRGoet/Pyawzk/PBNKd2eoY/4mmHVpc9X6cLmlpmgbhL4tF08aO1TS3W+XbvDmwbO/e0DL+/W+VHhcXSLvvvsjlgqbZ7Zr2+OOa5vOpvHl50fMmJmralCmBcj//XKUbjZUf15gx0csETUut4m+mruvSJfqx9eihaTt3BvKuWhVYdvRo9DKffFLl6dUrfNnw4WrZmDGBtLi4ys/x+PG1d7xnocNZXbR96UR8HcyorxUUzyzPW1zybdS8/leJa42maZp2LHd0lDwmLTPnNs3rPX6mDjmimtdA+r8Ie+epO/PFD8EN81V6aR6seEpNd70Xml8KJ3YE1mvaFyyO8PIcjWq8SxFlboDPhoK7WNWWWgxUtZb0lZB/EL4bpWoy3cZC8/5qneJMyNuvahsABxcGyvttSWA6Yw2ggckGTS4+NftfE+3aQatWUFgIhw5BejpMmaLuZp98Un+59etDt25q2udTd7KHDsGrr0LHjnDvvaH5e/SA5GTIzYVff1V3vWPHqjviwYNrtv1gDatTEz0LtG0Lrcv+9nw+2LABfv4ZrroKdu8OremdKl26qNpGRe3anfptnwUspraYzeoz0jQ3Ls9WvL7jHMsdjdXSA6u5S0j+GOtgMIT3HBgNiSHzJmMDrJYL8PkK8WnZuD2/UOScjduzm6YpqzAYbGFlnAk1DyDWBBg8GebdAPu+gn1fQ5urYdXf1QXY0QgGvBK+3hUfhDd5nUoLH1DBo14HuOlb1VQG4HHCd/fA7jmw9HHocDM06KaCjKsA0lepAJK7B/IPqCDhLYWja9S65hhIX63KatxTzdc199wTCBRut7oALVwIs2fXLID06gVffx2Y93igTx9Yvx7mzQsPIK++GggUJ07ABReoppXZs/UFkN69Yf58/ftf140aBU8/HZjfuFEF4f37VQBOSzv1+/DXv8Jdd5367Zyl4hyjSIoLfEZeXxa/ZbVB04ooLvkKa1xoAGmU/DUGg73Kcm3WPjSqN6983ln6A5nZw3G5N1LgfJ8Ex/21dxA1UDud6O2uh/Y3qOnFD6n+gI2T1fzgSapP40zK3QMZa9X0pa8GggeoC/7QaWC2q4Cwey4YzdC0j1p+tCw4+Gsfra9Q/RzeUhVcgvM0H3Dqj6WmLBa4uKyWdOxY7ZZtNqtagX+6Mikpgbb42t6Pc53NFt4XIuoEkzEFg0H16xkMUfqjdIixDcNhvx6AYudntVZuTdW8BuI3eDIcXKQu1nMGqg7q1ldBxxGR8393T3gTlj0Fhs+utV0qd2xzYLpxr/DltiRVMzm2BY6Vdfg26w8HflA1DQgEkNQhqpN863uqGSt1UCA41eUAommqg3rXLpg1S6V17FizMo8ehblzVUd9To66K16wQC279trI67jdkJUFS5bAihU124/Vq2Ho0PD0++6DW27RV2ZdMmcObNmipt1udc6MRnjxRTUA4XR4+WWYOTM8/ZNPAjcLv2Muz3aKSuaWNTXlUOJajs+XgwEzDtvVYfkzs68Oa8KymDuTkvCvKrdls1xIUclcXJ4qBiKdRrUXQOKaQf9/wKKxUJqr+heGTI2eP31lhDJO0V1VSY56Nxijj9SKbawCSEmumvf3gxzbBO4i+G2xmm95WSCAHF6iRnOV5JTVWvqemv2vqaeeUq9gJlPNmq9ANancemtoWlwcPPYY3H13eP7LLgtPS0lR/SB6HD+umuIquvxyfeXVNdu2qVewBg1UP9KZ3AcIHd33O1bknE2RM/Sm12RsQkriv7CYw5sYna4fw9J8vsJqbctgUDfcPi1Px56eGrUXQAAu+DOse0V1Sne7XzX1RHPtF+HDc42nqFPQEqveNZ/ql4ltEp6n8Kh6tyWo98a9Av0dW2dASbYKksmdy4bpGuDoWjhUFlgadlf9JnVRTAzY7WooaL16qnP2scegXz+1PLgz1uUKXdftVu+xseHlduwIt90Gy5fDjz+q7cybF70/Iz5eNW0lJKj9uPBCmDBBDf3Vo39/eOON8PTmzfWVV9eMGgV33qk60I8fV8OhX39d9WnZbHD77dUvy9+kWPHzhco/44kT4corw9PPlYEKNRRjG4bN0oOiki9xe3ZgNrWkScpSzKbI176mKSvBYA1JMxoinPcIvL4sAAzVzH861G4AMRgDF1FbFVXs+uedvk70BucHpo+uUX02wUqyIbdsnHaDC9S7OQYaXwRHfoJ1r6q0lkPUe0wDaHiBep7k50kqrVn/U7f/NfX005XXNoKfCSkqCl1WUKDe60Xox2rbFp59Vk3ffrvqDL/iChVM/MEp2P/+p6+zPJrERBWEzlVt28KQIYH5O+6AzZvhhx/g449PLoD4P+PCCHe7+fnqPVKzWKtW5/Y5riG7tT9JcU+TFPc0R473xO3ZSfrxPjRrsAmTMTzIWi3dq9WJHonHu0+VYe5co32uTb+PJ9FT0gKBYdl4NTTXz1MCC+9X7yarGoXl16zsIlhY9qBWalATTGrZFzvnF/Vel/s/qtKsWeCBvoqjmlaWNTWmpFRexrRpasip2w0jR6ohuqJ2eTyBAQdVDVKoyD8ceP9+9YCpX06O6heDqj9jEZXBEEvDpE8wGGx4fUc5nnsvoNVa+S7PVopLvgQg1l53+vdqtwZyMn58MHKTT9trIG1kYN55HObfGp6v+QDo/pfA/JGfIuc7/4/Qcqjqj/l0EOT8CrO6qdFUtkTV8Z+nIjt9nlXNVH7N+gMvl80YAjUQUNPr/1m2yBjoMzkbmc1w442qBvH3v8O6ddChA2zdCosWqTzROsX9EhPh/fdVP8eBAzB+PLzzjr790bTwvhVQzyQ880xgfsOGyPlAbTtSrelsEtyJnpsL+/bB3r1qPlLt4777VFNlsGbNVDPf0KHqfOTkwCWXwE03qVrJV1+pNIslclPV5Mnw5Zfh6Z07w3PP1ez4zjFWywUkxT1LTsEEiku/otA5i7iYP4TkOZZ7JxA+OivecQ8xtsD5L3WvJyvnVjTc+HzHKHWtQcOD1dyFeMeYU30o1XbmAsiB7yKnV+w3cRfDL3PD81V83qLgN/WqKHWwCiBN+8LNP8AP96law+5PA3lsiXDJROj+/0LXbXaJCg6aT9VigvtOmvUP9JGknBf6syZnoylT1CitxYvhm2/UC8BgUDWKhx6quoyBA1WH+OTJMGOG6kjX85MimqZGd1V04kTovH8UWCRvvnn2B5BIHdg2mwrOkQJnpGdiOnVSAaRePfj8c9UMlpGhgr1ffDxMnRr54cC1a9WrogFncY37FEqKe5zikv9S6l5Ldv5jxFQYiVVU8kXE9ezWfiEBxOtNp8gb/LdtxGG/gfoJb5V3ptcFBk3Taq+eBeqZCFch1GsHCa1Cl7mLAs9ORJPQEuq1V8Ege3f0fHFN1IX7+FYoyoyeL7kTxAd1qmpe1fmdvVM995HYWtVmLHGR1z+8XAWJ2EZQv8LFMH2VOqZIy+qCVatUn4b/SfTq2LhRtbMXFqoLS58+qjYSbOdO9QBgpCfBi4sDzV5Nm6p1lyxR8/4n0aPJygrccUeSnKzK8G+/Mv37h/6m19lk9erQvgqrVXVwG43qfAZ3duflqRpjNLGx6jP0czrV8On9+1WHerNmKvBXDLaLF6vfMYsmKQkuuuikDutcUupejc9XiMXcFrOpdcgyrzcdl0f96obV3BmDwU6pe2Ol5VnMHTGbWuD27MDjTQ9ZZjTWw2Jqi9F4moZun4TaDyBCCCF+F34fnehCCCFqnQQQIYQQukgAEUIIoYsEECGEELpIABFCCKGLBBAhhBC6SAARQgihiwQQIYQQukgAEUIIoYsEECGEELpIABFCCKGLBBAhhBC6SAARQgihiwQQIYQQukgAEUIIoYsEECGEELpIABFCCKGLBBAhhBC6SAARQgihiwQQIYQQukgAEUIIoYsEECGEELpIABFCCKGLBBAhhBC6SAARQgihiwQQIYQQukgAEUIIoYsEECGEELpIABFCCKGLBBAhhBC6SAARQgihiwQQIYQQukgAEUIIoYsEECGEELpIABFCCKGLBBAhhBC6SAARQgihiwQQIYQQukgAEUIIoYsEECGEELpIABFCCKGLBBAhhBC6SAARQgihiwQQIYQQukgAEUIIoYsEECGEELpIABFCCKGLBBAhhBC6SAARQgihi7lWS/thDOQfLJsxgC0J7PUgtjGk3Q1JbdWivH2w4E9q+spZENskUMahRbD2JTDHwPVfqrQNb8L+r0O3ZYkFswNS0uC8URDfXKW7i2HedYF8RovaD1uS2n6X0WqfALI2wuZpal+HTot+XBteh/3fRl/uaAhXfVTJiTkD9n0N22fCie3gKYG4ptD6Cug2Vp0LvwPfwfrXQtc12dX5T2oDHW6FRj0ib2P1RDi8DAxmuPYz9ZkEy9oEyx5X05dNhXrtA8uOrIBVz0FCKxj2buh6uXtg41sqT0kOxNSHeh3g/Pugef9Avox1sOLJys/D4LcguWPlec60zZth6lRYswYKCqBxY0hLg7FjoVu3QL7vvoPXKnxWdjvExECbNnDrrdAj6LMaMwYOHiSqgQPhqadUnjFjKt/HZ56B/v1h9mx47z2Ii4OPP1bb9nvvPbX8iivg0Uerffin0/G8+/F492AyNqJB0iyC76E93v0cz7sPgLiY0ditfTmeV/l5SYp7Bru1P07XjxQ552AyJlMv/h9R8xcUz6DUvQ6bpSfxjirOOT6KnJ9SWPIJbs8voLkxm1risF9DvOM+DAZHWZnvUVQyG7OpJfUTZ5SvXej8kEKnui4lOMbhsF9TXm5m9jVouEiKewq7dWAV+xFd7QaQ9FVwYkfkZRvehBFLoaxy3VMAAB2YSURBVGE3cBXCwYUq3eMMzVd0VC2zxAXSsncG8kcs+w24c60KEJqn8rxbpsMdq1UQyduv5g3GygPIiSq2n5AafdmZsGgsbJoampa3T12QN78DN30LKeep9ML0yo9t3atw/TxoMzw03VUAa18Gd5Ga3zUbut4bmqckO1D2orFw8w+BZcVZaln9LqHr7P4Uvh8dKNe/7xlrYedHcOVMSBtZVv6JyvcdwJVX+fIz7a234JFHwO0OpO3bBytXwqxZMH8+DBum0tPTYWElx/vqqzBvHgwv+6xWrYIdUb6PAPXrq/eiosrLBfhT2Q3fgQOBvC+8AM8/H8izZ49allrHvg9BYu03k5E9FNCwW/sT7/hT+bLs/Mdwli4sv0h7vYdwllZ+Xvzru93bKCiejtmUWmkAcboWUeScjS8mv9IAouHhWM4Iikq+CEl3e/fidP1IfvG7NE7+DrOpBUZjPZylCzFgISXhX+WBpbD43zhdPwJgMjYtDyAuz06KS78BoH7i9EqPryq1G0D8uoyGTrer6eyd8NP/QWkerPybuhjp1bgX9HshMJ9/ABY/pC5UG16Hy6aE5r/0VWjQTQWVwytgzYuQ8wtsfhsuruLONZImveGSieHpZvvJl3WqbJ4WCB4dR8CFD0FMA0hfCUsfg4Lf4H/Xw6htYLIF1rPGw7VBf6yufFg2HnL3qs+tYgDZNTv0Ir9lengACXZwAeyeo/YpmuPb4LtR6qaiycXQ9++Q3EkFkKWPQ+Z6+OGP0PpKVSsJduPXYLSGl5ncKfr2zrQff4QHHwSfDy6/HCZMUDWJrVvh4Yfhl1/grrvg8GGwBh1bfDx8EfRZ5efD+PGwdy/87W+BAOI3ejTcfnv49hs1Ck/74ANo3jw8/fzzw9NefVXtX6c6fI4riLFdRlzMSAqds8gueIpY+80YjSk4SxeVX6xTEqdgNMThDVqvQdIHmIzh58VqiXBeakFuwbNl+2MgwXE/cY7RGA0JOF0LyMl/ArdnB8dyb6NJygrs1n6AAQ03pe712K0D0LRiStwry8srcS0pny51rQbAbGqB2dS6Rvt5agJIUltoOURNtxyiahVr/gFZP9es3Jj6gXL9DnwPv3wGOb+G52/YA1IHq+lWV6iL6G+LVdNVbW2/rln7knrvcAsMnx1IT2oLDbvDrAtUE9GuT1TTn5/REn5seftV0MnZE76drWVV5a73wtb3VQ0ha5OqYUaz5BF18bcmRNn3l1XwaHABjFgGprKLZkKqChBfXAnJndXfU8UA0mJw3Qrk1TFxogoew4bBt9+CwaDSW7SAVq3UxfmCC+DoUWjZMrCexQJDKnxW+/fDY4+pWkBFbduG54+mb1/o0KF6eV0u1cy2cGFg388CyQmv4Sz9Bq/vONkFT5OSOJns/IcAiI0ZgcN2ddg6NktfLOZqnpca0jQneUVvApAY+xDJCa+XL7OY22MxtSMj+3JKXCtxli4ixjYEi7kjbs8uSt1rsFsHUOJagaaVYDF3wOM9iMd7CI93H2ZTG0rdqwCwWwfUeF9PTQCpyH9xN9XyF7woQ7WDg2ojr4y3FAoOle2HrfK80bjyIHNDeHp8c3BEuJs73bJ3B/qgItUG6neBxj3h6BrV9BMcQCrylMDBsian4L4LgONbVcAwGKHPs6rZMn2VqoUMmRpWFPZkFaAK01VtdNCkyNvcW1Y7TRsZCB5+joZwV4Rz75e1MXwdS2zdrYHk5sLSpWp69OjwC3BaGvxczRuukhL4oeyzat8+fHl6OmyIcO46dlR9GcG2b1f9MMEslvAaSIcOqsbz44+qL+TOO6u3r3WAyVif5ITXOZZ7NwXF7wIeXJ5tGI31SEl4M+I6bs92fFroeTFgOSU1kBLXSjRN1e7jHOHf4xjbMEymZni9R3C6FhBjG4Ld2k8FENdqiKW86c1hu5pS9yZKXItxli4h3tGmvAZSdwPIge9VE0hpvrq4HC77orQdXvl6VTm8BGaUdcSX5qgOVlAX756Pheff+q66CBYfU4Emd2/ZflwTnrda218O/7koPP3SV+GiCNs/3QqPBKb9AxYqSmqrAkh+hc7V0tzAuXUVqPPr86hg2+/50Lxb31PvqYNV8DzvDyqA7PxInYuKnekWB/R/Cb65CzZOiRy4SrLVdgGS2gXSs3eq8x4sJQ2a9QtN+6RveJlNesMdq8LT64JDh0DT1HTboM9q/frwwNGzJ3TvHpjPzQ2sU1AAOTng8YDNFton4TdlinpV9NNPqsYR7MYbw/M1bQpHjoSmdemiOsv/9S9V87k6/K69LlPNWP/GWbqAgmJVm06OfwWTsXHE/Jk54efFZGpKasMjEXLXjNd3uGzKgCVKE5PF1Bav9wger7optlv7U1A8gxKX+nt3ulQAsduGYDSmUOJaTIlrKbExN+Hy7Cxbp64GkMPL1CtYqytUmzaoO1c//5eo4rwxwq65i1V7uJ85Bno/BV3HRK4B7JodOm8wQfe/QMdbq3ccFcXUj9xEk9AyPO1M8HmqzlN+viued1/oucUAF9wP3ccGOtxB1eR2/kdNd75LvXccofqiXPmqaaxrhM7BznfCtg/UKLuF91cecH2uwPTh5YERe37dHggPIKmDQ/+uQDV3nQ2CO9Dnz4e//z10+QsvhAYQn091tPsZDHD//ao56bzzCNOunWoSqygpKTytb19wOELTUlIi7/fEifD55yq4PPUUJERpmqyjUhLf5sixrmiaE7t1APER7vb97Na+5Z3TfkZjlPNSQ5oW3PsSrWkw9Htst6rRiV7fUUrdG3C5N2PAgt06AJOxPjkFT1PiWkypay3gw2RsiMVc89GJpyaAtLtetXUbjGq0U1J7aBBU1QtuavAUh67rn7clhpfb+irVCX90Ncy7EZzH4MhKuPCRyPtx4SNqCKfRoppRGnar2cW+SW+4Yb7+9U+1+GaB6dw9oXfywekA8S1C0+3JMPaEam78+nbVVPfbEug1PjTfr/8F5wk1ve5V2DhZTfsv3lumRw4goJq3Zp6vakBbKwzdtServhFXfmifS8Nu0OuvanrXJ5B/KHLZN3x9dvWBpKaC0aiCwZ490KePSu/XD/5adrzTp6vaRUXJyXDiBPz6q+oc37ABlixRHemR3HMPPFnNQSMffFD9PpCEBHjzTbjlFnjnHTUs+CxiMbXFYmqLy7ONGNvlRL9YQ/3ED05bH4jZ5P8ea7i9e7Gau4TlcXtVa4rZ2KJsndaYTc3xeA+TV/gi4MNmvQSjIQ6b5UKMxnp4vL9R6PwY8Nc+at5vdWoeJGzcU43Z7zoG2t8UGjwgtAO0sEIVsPiYevc/q1GR0azuPq/4ADDA/m/UaKFI2lyt9qPLPdDuurpTUzhVkjurZ24g0MwU7NiWQB9Oi8GRy6jXHq6ZqwJ49k746vbQms22oHJPbFflZW5QtUNQTYXRBinU6wC9nlDTB34IX972WvW+Y5aq6YAaedf/JfVKbBO53LNRUhIMKGtCmDFDBRKAoUPhpZfUK9qdv1/79jB3LiQmws6dKph4qlELrU033wxXXgleLyxadHq3fY6yWftgMKjnawqKw7/HztJv8XrTAYixBb7H/lpIUcn/ypb5B06YiLEOUsvKngvx562p09OJXpE9GRJbl43yGa/m63VQF7jNZc9jVNUp3uZq1ZSxaYpqV28zHFpdrn+fInWOW+ND9yNaJzqoIGm06N9+bTAYoed4Ndrpl8/gmzvVvKMh/LYUFj+omqriW6gmpWgSW8PgyfDt3aq2t+ZF6POM+rwOqXHlXP0JNOkVut6ng1XfypbpMOTtyGX3egJ2fRx51NzFT8AvcyF7F8y5FAa8EhjGu+1D9RxLNJE60UEdq6Nh9PXOpGeeUR3py5bBVVeppqtWrWDXLnj7bdVJXZXWrWHyZLj7bli9Gl58UZUbLFonutUKXbuGpkXqRAc15DfS8F5Qz7J07QrFxZGXnwMidaIDmIyNMJsC50XTXJS6w8+1yZiC2dSqfN7ny46Yz2xKxWRsQILjfvKKXie/aBLgJcFxPwZDPM7Sb8nOV82/Vkv3spqTYrP2p9D5CaBuRuzWy8qX2W1DKCr5Ag132bKa93/AmQogAANehq9uUyN6Pro4dJklNnCnWlUZ+79VF5iF98MftunbF80XuXM8dTDcEnRXFa0THeBPR9TT3mdajwdVIN7+Iez8WL2CORrCdV+oju3KpI2EXz+HPfNUAOl4q+ok13zqODveovqUgp03Sj1dvvNj1Zkeidmunkr/bGj4spTz1IOC349WzVxzLg3PEy34RepEBzXiq8e4Sg/1jBk0SDUBPfoofP+9elXUuTNcd114erCRI1VfxLx5KoDcemvosxnROtFbtVLDf4NF6kQH1VH+apTPtE0bePrp6jeTnYUidaIDJMY+RnJC4Lx4fRmkHw+/RsTF3E2DpJnl887SH3CWhtfC6ye+Tbzjz9SLfxG3ZxfFpd+QXzSZ/KLJIfnMptY0TPqU4Eak4FqF0ZCAzRq4wYuxBoZxG41JtTZ6rHYDSNM+6uKSWI2HUzrcArfUh58nQdZmdXdvqwdNe0OvCaFPKCd3Vs8oVOzAtsTCFR/C6rJOx/1fQ+urA88z2JMr3wdHw8qf62hQtr2UzlU//6F3aHBtMxhV816762Hb++rO3OOEuGbqp0wufDh0wEFcU3Vs1vjwsoZMA0+pehBz96dQcFjlbTM8PHgAdBkF6T+p6cwN6vy3HBL+zEbLIapfI3OD+imTYB1HqOd3Nk9VfTCF6epXCRp0hbbXQec7AufanlL151LXfiWgonHjVFPWtGlqVFRGhurj6N5dXcxvuglMZee6aVP1PEd8hM9q2jQoLVVNWJ9+qmohffqodaLxP0gYG1v1cyL+4cGtWqm8FYf1PvoobNyo+mzS0qp16HWBzdobk6lxxAfqDIbYoGagyCxmdV7MptRK81rN55W9d8FXST5TWW3GYLDRKPlLCp0fU+j8Dy7P9pCfMkmIHYfRENpPbDWn4bANR6MEq6UHBgItIhZze2LtN+PTcrFaelBbvRcGTas4DEoIIYSomvwarxBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF3Mp2tDh3MPs/HIRnKKc2gc35jOjTvTIqlFSJ7jRcc5lHMobN04WxxNE5oSZ4sLSd+RsYMST0nUbdZz1KN1cmtKPCXsyNhR6f61TmlNvZh6ZBRkkJ6Xjt1sJ61xWkieI3lHyCzIJCU2hZb1WlZ1yEIIcU475QHkRNEJ/vL5X/h88+f4NF95usFg4OYLbub9298nxhIDwPxt8/njnD9GLMdkNHF12tV8eMeHJNgTALht5m3syIweGEZ0H8FHIz9i34l99Hq9V6X7OecPc7jpgpuYuXYmT339FEaDkeXjlnNxy4vL80xdMZWXF73MPRffw7sj3q32ORBCiHPRKQ0gRa4iBr41kJ2ZOzEZTQxsO5BWya3YkbmDtQfXMnfTXAwY+Pjuj0PWs5gsDGg7oHz+aP5RdmTs4MttXzL+y/FMu3VaSP529dvRMjm8RnBek/PC0vq06oPD6ghLbxTfKGTep/l44LMHWPPwGszG01ZRE0KIs8YpvTJO/H4iOzN3khSTxLwx87ik9SXly57/4Xme/e5Z5m6ey3PHnqN9g/bly+Jt8Xz/5+9Dynpg7gNMXzWdedvmhQWQP/T6AxOGTKjWPr13+3t0aNChWnk3H9nMlBVTeHDAg9XKL4QQvyenLIB4fB5mrZsFwKODHg0JHgCPD36c85uez/lNz6dVcqsqy2uc0BjgtNUGzEYzHp+H5757jlu63ULThKanZbtCCHG2OGVX48O5h8kqzAKgV2p4/4PNbOPaLtdGXNfldfHZ5s/weD1kF2dzrPAYk5ZNAuCa864Jyz9z7UyW7FkSlv7GDW+Q1ii0I/zeT+4Na8JKcaSENaMN6zSMvcf3sjtrN4/+71E+ufuT6AcrhBC/Q6csgBwvPF4+3TCuYfn0pGWTmLJ8SkjeRwY9wp/7/rl8vrC0kNtm3haSx2w0c+eFd/LSNS+FbWvP8T3sOb4nLD3PmReWturAqrC0SLULm9nGWze9xbBpw5i7aS739LonLI8QQvyenbIAkhKXUj59JO8IXZt2BSC3OJd9J/aF5M0pzgmZd1gd/PWyv7IrcxdzNs7Bp/l46ZqXeOjShyJu64F+DzCq16iw9Eh9HZ/d8xmp9VJD0ixGS8RyB7UfxB097uCjDR8x7otxXJ12dcR8Qgjxe3TKAkhqUiqN4xuTUZDB6oOruaLzFQCMv2w84y4dB0Cv13qxP3t/2Lp2s52nhj4FQM/Unjzyv0d4bN5jGA1Gxg0YF5a/SUITejTvUa39SmucVu1OdIBXrn2Fb3Z8w57je/hw7YfVXk8IIc51p+xJdJPRxF0X3QXAm0vfZMW+FQDEWGKoF1OPo3lHyS/Nr7Kc/9f//3Fl5ysBmPDVBLambz1VuxxRo/hGvDD8BQDySsKbxIQQ4vfqlA5penrY03y57Ut+OfYLl029jKEdh9ImpQ07MnawfN9yvD4vACmxKVHLMBgMTB8xnQteuYDs4mxGzx7NqodWhYzGmv3zbDYf2Ry2boO4Bky+aXJI2sP/fZh4W3xY3uHnDS8PeBWN6T2GWetmsfrA6modtxBC/B6c0gASZ4tj+bjl3D/3fuZtm8d3O78LWZ7WKI0nhz7JbT1ui1KC0iShCZNunMTI/4xk4+GNvLX8rZD+kO0Z29mesT1svUjDg7/f9X1YGhDxQUQ/o8HI1Jun0uv1Xnh8nkr3VQghfi8MmqZpp2NDh3MPs+7QOjIKMkiwJ3Bhiwvp1LBTSJ70/HR2ZuwMexLdb9neZbi9bmKtsfRu1ZvVB1ZT5CqKuk27xc4lrS+hyFVUZe0htV4q7Ru050D2AfYe30vDuIblHf9+6w+tJ68kjyaJTcKGBwshxO/NaQsgQgghzi3yc+5CCCF0kQAihBCnwNq1a/nTffdFXLZp0yb+cPfdtbq9N994gxG33sqB/YFHI154/nlefeWViPnXrVvHyLvuorCwkJ9WrODOO+446W1KABFCiLNcQUEB69evp3v37ixctKg8fdDgwWzatInCwsKwdZYtXcrFvXsTFxcXtqy6JIAIIc4aHo+HrVu34na7Wb16NUuXLiU7Ozss3759+1iyZAlbtmzB43YDkJuby84dgf8fpGkaW7duJT8/8DzaoUOHyMjIKJ/fs2cPS5cuZceOHQR3Fx8+fJisrCx2797NqlWrcLlcABw5coTFixezdWv1nldzOp2sWbOGDevX43Q6AXC5XGzdurV83u/XX3/lxIkTEctZsWIFzZo358qrrmLF8uXl6/bq2ZOYmBhWrVwZkj8/P5+ff/6ZywYPrtZ+RiP/6EIIcdYoLi7m+YkTSUtLw+FwYLVamfHuuzw+fjznn38+Ho+HKVOmsH3bNrp07cpvh9R/OH18/Hg8Hg/PPfcc0955h6SkJPbt28fzEydy5513cu111wHw+muvMeK226hfvz5T3nqLXbt20aVLF/bt20dCQgLj//pXYmJi+Gr+fI4dO8aePXvQNI1/vvYamzdtYubMmVx00UVkZmbi9fkqOxQ8Hg/P/N//0bRpU06cOMH06dOZOHEiDRo2ZNrbb3Pdddcx7PLLASgsLOS5Z5/lhRdeICUl/Lm5xYsX07dvX7p06YLNZmPF8uUMHTYMs8VC//79WbFiBUOHDSvPv3LlSho0aECnzp1r9HlIDUQIcdZp07Ytj48fz4MPPcQNN97IjBkz0DSNZUuXsnnTJl5+5RXGjRvHSy+/TFJSEjM//JCmTZvSuHFjtmzZAsCWLVuIT0hg+3b1DFlGRgbHjh+nW7duLFy4kN27d/PqP//J2L/8hZdfeQWPx8N///vf8n04ePAg/5o8mfc/+ACHw8GsWbMY+5e/8NDDD/PiP/5Bcr16lR6Dx+Phuuuu4+FHHmHi88/Tuk0b5nz6KQaDgQEDBrB8+fLyvKtXraJps2a0bNUqrJz9+/fz26FD9O/fH5PJRP8BA1iwYEH58kGDB7N7926ysrLK05YuWcKgQYMwGAy6zr+fBBAhxFlnyJAh5dP9+vUjMyODzMxMNm/ezEUXXUS9sou3yWRiyNCh7Nq1C4CLevZk82b1qxVbNm/mmuHD2blzJx6Phw0bNtC1a1diYmLYuWMHTZo0YevWraxatYp169bRoGFDdpeVA9CufXsSExMxm83l5ffu3RtQv6Bx6cCBlR5DTEwMl/TrV55/wIABbCtr+rp04EB+/fVXMsua05YtW8all14asZzFP/5I27Zt8Xo8ZGVmkta5MwcPHmT37t0ApKam0rZtW1asUD8n9dtvv3Ho0CEGDhpUzbMdnQQQIcRZJz4+8HNEDof6/z7FxcWUlJQQn5AQlrewsBCPx8NFF17Ils2bcTqd7Nmzh6HDhhETE8OePXv4ecMGevXsCUBOTg55eXmsWb26/OXzemnZMvCLFfWSksqni4uLcTgcIXf0SYmJVR5DcP7Y2FgKi9SD0Y0bN6ZT584sW76cjIwM9u7dS//+/cPKcLvd/PTTTxw+fJgJEyYwYcIEpkyZgtliYWFwLWTQIFaU1WiWLl1Kjx49SKxi/6pD+kCEEGed48eOlY8eyszMxGAwUL9+fRo0bFh+1+539OhR4hMSMJvNdOjYEYDvvvuO1q1b43A46NK1K+vWrmX37t2Me1D9++r6DRpgMhoZ+5e/lJdz5MiR8g55IOTi36B+ffLz83E6ncTExABE7fD2y8vLw+PxYDary3BmRgYNGzQoXz5w4EC+mj8fi8VCt27dSKgQGAHWrlmD2+1m+rvvYrfby9MXLljAhx9+yMi77yYhIYFL+vVj5syZHNi/n59WrOC+KMOLT5bUQIQQZ525c+fi8XhwuVzM/fRTLrzwQhISErj44ov5+eefy5upTpw4wZfz5tHvEvUvtY1GI927d2f+l1/SpUsXALp27cr3339PmzZtyu/KL774YlauXFneP5Kbm8srL7/M8rJmoIo6dOxIw4YN+fjjj9E0jcLCQuZ/9VWlx1BaWsp/v/gCTdPIycnh66+/5pJLAv/6u3fv3hw7doyFCxZEbQ5bvHgxPXv1CgkeAH0vuQSDwcDSJUsA1VzWp08f/v3vf2MwGLigW7dK9626pAYihDjrWK1W/nTffXg8Htq1a8cDY8cCKhj88b77+NekSZjNZoqKiujXrx933Hln+boX9ezJ0qVL6dq1a/k6brebnmXNV6ACyMi77+bVV14hJiaGgoICevfpw4gRIyLuj8lk4rHHH+f1115jzL33AtCzZ0825uREzA+QkpJC+tGj/HHMGEpKShg4aBDX33BD+XK73U6fPn3YsGEDPXqE/7+jrKwstm3bxoQnnwxb5nA46N27NwsWLmT4NddgMBgYPHgwf/vb37j55psxGmun7iC/hSWEOGvk5+fzxzFjeOPNN0lOTqa0tDRiW76maWRnZ+NwOMqblPTwlxMbGxt2l19Zfn/nenUUFhZisViw2Wxhy6a9/TaxsbGMrOWn1muL1ECEEGclu90e9aJuMBgiPi9xsk62HD3bjfQk+P79+zlw4ACrV6/mpZdfPqnyTicJIEKIs4bJZKJNmzZYLJYzvSun1M8//8yCH35g1D330Lhx4zO9O1FJE5YQQghdZBSWEEIIXSSACCGE0EUCiBBCCF0kgAghhNBFAogQQghdJIAIIYTQRQKIEEIIXSSACCGE0EUCiBBCCF3+P0KBoJ1NU8DjAAAAAElFTkSuQmCC</v>
+      </c>
+      <c r="E657" t="str">
+        <v>18-09-2026 12:57:31 am</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
+        <v>6aac3f2725ff80deb19c2677</v>
+      </c>
+      <c r="B658" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C658" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D658" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E658" t="str">
+        <v>18-09-2026 12:57:35 am</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
+        <v>6aac3f2825ff80deb19c267e</v>
+      </c>
+      <c r="B659" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C659" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D659" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E659" t="str">
+        <v>18-09-2026 12:57:36 am</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E647"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E659"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E659"/>
+  <dimension ref="A1:E733"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11602,9 +11602,1267 @@
         <v>18-09-2026 12:57:36 am</v>
       </c>
     </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>6aac3f2e25ff80deb19c2778</v>
+      </c>
+      <c r="B660" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C660" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D660" t="str">
+        <v>Started Playing game and Debited "10" and Balance "380"</v>
+      </c>
+      <c r="E660" t="str">
+        <v>18-09-2026 12:57:42 am</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>6aacd18fda7ccce74a649bf7</v>
+      </c>
+      <c r="B661" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C661" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D661" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E661" t="str">
+        <v>18-09-2026 11:22:15 am</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>6aacd190da7ccce74a649bfd</v>
+      </c>
+      <c r="B662" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C662" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D662" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E662" t="str">
+        <v>18-09-2026 11:22:16 am</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>6aacd1a3da7ccce74a649cf8</v>
+      </c>
+      <c r="B663" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C663" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D663" t="str">
+        <v>Started Playing game and Debited "10" and Balance "370"</v>
+      </c>
+      <c r="E663" t="str">
+        <v>18-09-2026 11:22:35 am</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>6aacd3a363a1ab8fce86c577</v>
+      </c>
+      <c r="B664" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C664" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D664" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E664" t="str">
+        <v>18-09-2026 11:31:07 am</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>6aacd3a463a1ab8fce86c57e</v>
+      </c>
+      <c r="B665" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C665" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D665" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E665" t="str">
+        <v>18-09-2026 11:31:08 am</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>6aacd3ac63a1ab8fce86c67a</v>
+      </c>
+      <c r="B666" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C666" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D666" t="str">
+        <v>Started Playing game and Debited "10" and Balance "360"</v>
+      </c>
+      <c r="E666" t="str">
+        <v>18-09-2026 11:31:16 am</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>6aacd3ed859274c346d9bdf8</v>
+      </c>
+      <c r="B667" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C667" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D667" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E667" t="str">
+        <v>18-09-2026 11:32:21 am</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>6aacd3ee859274c346d9bdff</v>
+      </c>
+      <c r="B668" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C668" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D668" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E668" t="str">
+        <v>18-09-2026 11:32:22 am</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>6aacd3fcc47303ebe44266f0</v>
+      </c>
+      <c r="B669" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C669" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D669" t="str">
+        <v>Started Playing game and Debited "10" and Balance "350"</v>
+      </c>
+      <c r="E669" t="str">
+        <v>18-09-2026 11:32:36 am</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
+        <v>6aacd45ddf2e9020d657d949</v>
+      </c>
+      <c r="B670" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C670" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D670" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E670" t="str">
+        <v>18-09-2026 11:34:13 am</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v>6aacd45edf2e9020d657d94f</v>
+      </c>
+      <c r="B671" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C671" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D671" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E671" t="str">
+        <v>18-09-2026 11:34:14 am</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v>6aacd466df2e9020d657da4d</v>
+      </c>
+      <c r="B672" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C672" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D672" t="str">
+        <v>Started Playing game and Debited "10" and Balance "340"</v>
+      </c>
+      <c r="E672" t="str">
+        <v>18-09-2026 11:34:22 am</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v>6aacd4b506e2c50da97210d4</v>
+      </c>
+      <c r="B673" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C673" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D673" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E673" t="str">
+        <v>18-09-2026 11:35:41 am</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v>6aacd4b506e2c50da97210da</v>
+      </c>
+      <c r="B674" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C674" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D674" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E674" t="str">
+        <v>18-09-2026 11:35:41 am</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v>6aacd4be06e2c50da97211d9</v>
+      </c>
+      <c r="B675" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C675" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D675" t="str">
+        <v>Started Playing game and Debited "10" and Balance "330"</v>
+      </c>
+      <c r="E675" t="str">
+        <v>18-09-2026 11:35:50 am</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v>6aacd4da1e81e388547cdbfa</v>
+      </c>
+      <c r="B676" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C676" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D676" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E676" t="str">
+        <v>18-09-2026 11:36:18 am</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v>6aacd4db1e81e388547cdc00</v>
+      </c>
+      <c r="B677" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C677" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D677" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E677" t="str">
+        <v>18-09-2026 11:36:19 am</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v>6aacd4e21e81e388547cdd00</v>
+      </c>
+      <c r="B678" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C678" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D678" t="str">
+        <v>Started Playing game and Debited "10" and Balance "320"</v>
+      </c>
+      <c r="E678" t="str">
+        <v>18-09-2026 11:36:26 am</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>6aacd4fb1e81e388547cdd2d</v>
+      </c>
+      <c r="B679" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C679" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D679" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E679" t="str">
+        <v>18-09-2026 11:36:51 am</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>6aacd4fb1e81e388547cdd34</v>
+      </c>
+      <c r="B680" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C680" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D680" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E680" t="str">
+        <v>18-09-2026 11:36:51 am</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>6aacd5364317469e09f845c9</v>
+      </c>
+      <c r="B681" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C681" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D681" t="str">
+        <v>Started Playing game and Debited "10" and Balance "310"</v>
+      </c>
+      <c r="E681" t="str">
+        <v>18-09-2026 11:37:50 am</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>6aacff2dde1f98600405f1a9</v>
+      </c>
+      <c r="B682" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C682" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D682" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E682" t="str">
+        <v>18-09-2026 02:36:53 pm</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>6aacff2ede1f98600405f1af</v>
+      </c>
+      <c r="B683" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C683" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D683" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E683" t="str">
+        <v>18-09-2026 02:36:54 pm</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>6aacff36de1f98600405f2b1</v>
+      </c>
+      <c r="B684" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C684" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D684" t="str">
+        <v>Started Playing game and Debited "10" and Balance "300"</v>
+      </c>
+      <c r="E684" t="str">
+        <v>18-09-2026 02:37:02 pm</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>6aacffaeda591da363146150</v>
+      </c>
+      <c r="B685" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C685" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D685" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E685" t="str">
+        <v>18-09-2026 02:39:02 pm</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>6aacffaeda591da363146156</v>
+      </c>
+      <c r="B686" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C686" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D686" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E686" t="str">
+        <v>18-09-2026 02:39:02 pm</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>6aacffb8da591da363146259</v>
+      </c>
+      <c r="B687" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C687" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D687" t="str">
+        <v>Started Playing game and Debited "10" and Balance "290"</v>
+      </c>
+      <c r="E687" t="str">
+        <v>18-09-2026 02:39:12 pm</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>6aacffb8da591da36314625f</v>
+      </c>
+      <c r="B688" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C688" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D688" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E688" t="str">
+        <v>18-09-2026 02:39:12 pm</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>6aacffe1e4b42bb351611ee9</v>
+      </c>
+      <c r="B689" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C689" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D689" t="str">
+        <v xml:space="preserve">Created Question Number : 0, Rupees : 10, Qst ID : 6aacffe0e4b42bb351611edc , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E689" t="str">
+        <v>18-09-2026 02:39:53 pm</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>6aacffe1e4b42bb351611eee</v>
+      </c>
+      <c r="B690" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C690" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D690" t="str">
+        <v xml:space="preserve">Created Question Number : 0, Rupees : 10, Qst ID : 6aacffe0e4b42bb351611edc , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E690" t="str">
+        <v>18-09-2026 02:39:53 pm</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>6aacffe6e4b42bb351611f03</v>
+      </c>
+      <c r="B691" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C691" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D691" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E691" t="str">
+        <v>18-09-2026 02:39:58 pm</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>6aacffe7e4b42bb351611f0a</v>
+      </c>
+      <c r="B692" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C692" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D692" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E692" t="str">
+        <v>18-09-2026 02:39:59 pm</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
+        <v>6aacffeee4b42bb35161200e</v>
+      </c>
+      <c r="B693" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C693" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D693" t="str">
+        <v>Started Playing game and Debited "10" and Balance "280"</v>
+      </c>
+      <c r="E693" t="str">
+        <v>18-09-2026 02:40:06 pm</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>6aad0005e4b42bb35161203a</v>
+      </c>
+      <c r="B694" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C694" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D694" t="str">
+        <v>Answerd Correctly to Qst ID : 6aacfff0e4b42bb351612019, Reward : 10, Qst No : 2 ,Question : How many boxes are unbroken in total?</v>
+      </c>
+      <c r="E694" t="str">
+        <v>18-09-2026 02:40:29 pm</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>6aad000ae4b42bb35161205d</v>
+      </c>
+      <c r="B695" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C695" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D695" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aad000ae4b42bb35161204e , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E695" t="str">
+        <v>18-09-2026 02:40:34 pm</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>6aad000ae4b42bb351612060</v>
+      </c>
+      <c r="B696" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C696" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D696" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aad000ae4b42bb35161204e , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E696" t="str">
+        <v>18-09-2026 02:40:34 pm</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>6aad0325854c7a62eaa04168</v>
+      </c>
+      <c r="B697" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C697" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D697" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E697" t="str">
+        <v>18-09-2026 02:53:49 pm</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>6aad0019e4b42bb351612070</v>
+      </c>
+      <c r="B698" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C698" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D698" t="str">
+        <v>Answered incorrectly for Qst ID: 6aad000ae4b42bb35161204e, Qst: How many boxes are unbroken in total?, Submitted Answer: 10, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nO3df0BUdb7/8eeZHwyCiKKG+AMkMpMVEX+Vmpqb/TBTWdY0vZtuP7auX23b623v99u2d/febq21W3Yra7cfW+ruUmtGWqFrtouOiamgCGJmKGIqooIiogzMzPn+MZ5ZVH4Mw8wcZng//mmU85nzRuK853U+53yOoqqqihBCCNFGBr0LEEIIEZykgQghhPCKNBAhhBBekQYihBDCK9JAhBBCeEUaiBBCCK9IAxFCCOEVaSBCCCG8Ig1ECCGEV6SBCCGE8IpJ7wJEcHpn3gZd9vtI5lRd9iuEuJYkENFmejUPvfcthLiSJBDhNW/SQEOdHQBzeNv/15PmIUTHIglEBNSRXRWU7arQuwwhhA9IAxEBdSi3nEPby/UuQwjhA3IKSwRMXU09J/adcb8OjwrTuSIhRHtIAhEBU7rjJE6HitOhUrrjpN7lCCHaSRqICJhDuScavZbTWEIEO2kgIiBqq+qo+OYcpjAjpjAjFd+cpbaqTu+yhBDtIA1EBMTh3HJUVSV+xHUMSOuNqqoclsl0IYKaNBAREIe2u05fJY2LI2lcX9ffyWksIYKaXIUl2qW6vJaGOjt2mwOHXQXAaXditzkAUFWV2qo6zpSeJyzCRP/U3gCERZg4U1pN0fpSImPCURQFAJPFiMHk+lxjNCmYLEbM4Sai4yJ1+O6EEC2RBiLazfqHIqq+q2l1u4GjYjGaDe7XB63H2fHnAy2OiRkQxe0/S/NJnUII35IGItolOi6SGc+MJXfFfg5uOeb6SwUGDO+NKcyIoiiERbj+Nxs8eYB73JA7EtxJo/6iHVVVsdc7+K7gNLiCDDdO6s+4HydjshgD+j0JITwjDUS0m8liZOJjKcQlx7Dt3WLsNgc1py5x+xNp9OjftckxvZOi6Z0U7f5zdXktf39lD6hgNBsYuyCZm74/oMmxQoiOQRqI8JlBE/rR+/po/v7KHs4eu8Anv8rl1kdSSBoX1+K4I7sqsL5ZSP1FO9Fxkdz+RBox8VEBqloI4S25Ckv4VPd+XZnxzFiSxsXRUOcgZ3kBue8V47Q7r9nWaXeS+14xX7y8m/qLdpLGxZH+3DhpHkIECWkgwufM4SYmLx7O6PsHA3DQehxVvXY7VXV9DWD0/YOZvHi4V8u8CyH0IQ1E+I0l0gxAv5Re7quvGjOaDfRL6XXFtkKI4CENRPhNWb7ruR8JI68DoP5iA5tf38vf/3cPdTX1rq+NcH2tbLc8I0SIYCPnC4Rf2G0OyvdXoSgKA4b35tje01jfLOLiORsAFQfPMvGxFAak9UZRFMqLq7DbHHLJrhBBRBqIF1Lzl+iy370jl+myX28c33cGe72DmIQo9mSVsP+Lo6BCn5tiADh5oIq//TaP5Cnx9IjvSlVZDcf3nSFhZKzOlQshPCUNpI30ah7avoOliRzNPwVAVVkNVWU1GM0GRt53IynTBgJQlH2E/A8Psn/T0SvGSAMRInhIA/FSoA/kejautlJVlaN7Trv/HDMgitsWpV5xee6wexPpP6wXm1/f614G5eie06iq6l4XSwjRsckkuvC504equVRtQ1EUUqYlMvPZpu/tiImPYuaz40iZloiiKFyqtnH6ULUOFQshvCEJRPhcWf4puvbqwqR/TSEuuWeL2xrNBm7+l5sYODqWLb8v5Gj+Ka67oXuAKhVCtIckEOFzlkgzGc/f2mrzaCz2xh6kPzeeMLkfRIigIQkkgI7ZKgHob/H8wBqMht2b6NW4sAiT12OFEIEnCSSA3j75BW+f/ELvMoQQwiekgQTIMVsln1Xm8VllnjuJCCFEMJNTWAHy9skvsKsO9+v/Tpijc0Xt9868DXqXIITQkSSQANDSh0kxYlKMQZ9CHsmc2in3LYS4kiSQANDSR3qvmwFYe2ZH0KcQOZALISSB+JmWPgyKgYf7fJ+f9JmCSTHySeUujtpOt/4GQgjRQUkD8TMtfczoOZp4S2/6W3pyb89ROFUnfzz5D73LE0IIr0kD8aOr04dGUogQIhTIHIgfNZ77iLf0dv+9lkLWntnBH0/+I6jnQjqy2bNn+/T9Vq9e7dF7N95OiFAmCcRPmksfGkkh/uXr5hEs+xYikCSB+Elz6UMjKSQw/JUGmntfaR6iM5EE4getpQ+NpBAhRDCTBOIHraUPjaQQ0Zhe6UXmbIS3JIH4mKfpQyMpRIDM2YjgJAnExzxNHxpJIaKxQKcBaR7t48t/P0+v8rt6Wz1JA/EhLX0AmBUj73p4o6BZMQLwWWUeP+kzJeSfF9JRnTt3juLiYs6ePYuiKHTv3p2hQ4cSHR2td2miA9I7NXaEJiINxIcar7j74encNo+3q46gXyMrGJWWlpKZmUlhYSGqql7xNUVRSE1NZe7cuSQmysOuxLX8cSBv6T07UmqUBuIjdtXBdeZuPOTBvEdLTIoRu+rAdDmVCP9av349q1atwul0YrFYSElJoU+fPgCcPHmSoqIiCgoKKCoqYv78+UydKotICqGRBuIjJsXIor5ycAkm69evZ8WKFSiKwvTp08nIyCAyMvKKbWpra/noo4/Izs7mvffeA+hwTaSiogKA2NhYnSsRnY1chSU6pdLSUlatWoWiKCxevJgHHnjgmuYBEBkZyfz581m8eDGKorBq1SqOHDkS+IJbkJWVRVZWlt5liE5IGojolDIzM3E6ndx7771MmDCh1e0nTJjAPffcg8Ph4P333w9AhZ6pqKjAarVitVrdSUR0fBUVFSHx85IGIjqdc+fOUVhYiMViISMjw+Nxs2bNIiwsjIKCAqqrq/1YoeeysrJwOBw4HA5JIUEkVFKjNBDR6RQXF6OqKikpKU2etmpOZGQkQ4cORVVV9u/f78cKPaOlD6PRiNFolBQSJEIpNcokupdS85foXYLwUlVVFQBxcXFtHtu3b192797NmTNnfF1Wm2npY/LkyQDk5OSQlZXFwoULda5MtET7uWmvg/nnJQmkjfaOXNYp9y1ctPtEFEXRtQ7tU6zBYCA9PZ2MjAyMRiNbtmyhvLxc19pE80ItNUoC8YIcyINbz56uO/1PnDjR5rHawVl7D700Th9akpo4cSI5OTmsXbvW40+1HeFu5s4k1FJjmxuIN3dBtmWNF0/eQ4j2SE5ORlEU9u3bR21trcfzIBcuXGDfvn0oikJycrKfq2ze1elDk5GRgdVqZcuWLaSnp3t1ik74z9U/N4PBEPQ/rzadwtJ77RchfKF79+6kpqZis9n46KOPPB63Zs0a6uvrGT58uK7rY2mfYidNmnTFQSc2NpaJEyfidDpZu3atbvWJpl39cwuFn5dXp7C8SQOXLl3yeqw0D+Frc+fOpaioiOzsbBITE1u9F8RqtbJhwwaMRiPz5s0LUJXXai59aNqaQrTfLUn4/hWqqTFgk+g7d+5k165dgdqdEC1KTExk/vz5qKrK8uXLWblyJbW1tddsd+HCBVasWMHrr7+OqqrMnz+fhIQEHSp2aS59aELhU20oCtXUGLBJ9G3btqEoChMnTgzULoVokbam1apVq8jOzmbTpk1NLqZYX1+P0WhkwYIF3H333brV21r60AT7p9pQ4+vU2JEEJIHU1NRQVFREYWEhNTU1gdilEB6ZOnUqS5cuJS0tjYaGBvLz88nOziY7O5v8/HwaGhpIS0vj+eef17V5QOvpQxPsn2pDTSinxoAkkO3bt7tvnPnqq6+44447ArFbITwycOBAnnrqKaqrq9m/f7/7RsOYmBiSk5M7xAOlPE0fmmD+VBtKQj01BiSBbNu2zf36yy+/DMQuhWiz6Ohoxo4dy7Rp05g2bRpjx47tEM0DPE8fmmD+VBtKQj01+j2BVFZWcuDAAcLCwgA4cOAAlZWVut+IJUSw0D7FAphMJtatW+fROJPJ9etttVrJyMiQ54UEWGdIjX5vILm5uaiqysiRIwHX6azc3FymT5/u710LERIar520adOmNo/XVuoN1rudg1VTqwW0REshbV1NQE9+byDaKatbb70VVVXZvn0727ZtkwYihAccDgcxMTHMnDmzXe9jMplwOBwYjfKo5EDoLKnR6wZy4sQJ6urqsNls2O12AOx2O3V1de5tKisrKS0tJSIiguHDhwMQERHB4cOH+eyzz644jRUeHu7+xzOZTFgsFsLDw+nbt6+3JQoR9IxGI3PmzNG7DNFGnSU1tiuBvPHGGxw9erTV7caMGYPZbHa/3rx5M6tWrWpxTHx8PEuWyJLpon1kFQMRaJ0pNXrdQPr27ctzzz3Hu+++S05ODuBa4jotLQ2LxQLgXqTu9ttvd4+766673ElDu/PXZrOxZ88e91LZkydP5qGHHnK/jxBttXr1at2ahywL0rl1ptTYrgRisVhYuHAhycnJvPPOO9hsNioqKliyZAkDBgxockxSUhJJSUnuP5eXl7Ns2TJUVcVsNvPggw8yZcqU9pQlBCAHciH8zSf3gUyaNInnn3+eAQMGcPz4cZ5++ukr7v1ozs6dO3nqqacoKysjLi6O3/zmN9I8hBAiSPjsKqx+/frx7LPP8tZbb7Ft2zZeeeUVDhw4wIIFC9ynrDR2u52VK1eyceNGAMaPH8+jjz5Kly5dfFWOEEFJ5mxEMPHpnehdunThiSeecC93vXnzZve8RmOqqrJ582YA5s2bxxNPPCHNQ3Rqep5uk1N9wlt+uQ9EmzwfNmyY++qrxsxmM8OGDWPXrl0ePw1OiFAnB/Lg1JlTo1/WwsrLywNg1KhRgOtqq9dee42XXnrJvRqv9rX8/Hx/lCCEEH4lqdEPCcRms1FcXIyiKIwYMYKCggJ+//vfc/bsWQAOHjzIwoULGTFihPu51DabTS7ZFUIEnY5yINeLzxtIYWEh9fX1JCQksGbNGj7//HNUVWXIkCEAfP311yxdupQ777yT+Ph4ysrKKCwsZPTo0b4uRQghhB/5vIFop6TKysooKyvDbDYzZ84c99pXn376KX/961/dV2BpY6SBCCFEcPFpA1FV9Yo5jfj4eB5//PErniE9Y8YMUlNTee2119zLoOTn56OqKoqi+LIcIYQQfuTTSfSSkhKqq6tRFIXp06ezdOnSK5qHJiEhgaVLlzJ9+nQURaG6upqSkhJfliKEEMLPfJpA8vLy6NWrF4sWLeJ73/tei9uazWYeeOABxowZw/Lly8nLy2PQoEG+LEcIIYQf+TSBREZG8uKLL7baPBobPHgwL7zwgtwPIoQQQcanCWTGjBlejYuIiPB6rBBCCH345UZCIYQQoc/vj7QVojORZ5CIzsSrBtKZ134Rojl6/l7Mnj1bmogIuDY1EHnKmxCt8+b/1UuXLgF4tSq1fKALvNH3LNBlv7vWr9Rlv81pcwIJ1QN5U7+Ejb9Xf/2Shuq/p2ibnTt3oigKEydO1LsU0Qq9moe2747URGQOBDn1IPS3bds2aSBBxpsD+cVLdQBEdAlv81g9G1dzpIE00tKB3B8HeTn1IABqamooKipyv46KitK5IuEvObn5KArc8/3xepfiE3IZrxA62759Ow6HA4fDwVdffaV3OcKPNm7ezsbNofMzlgYihM62bdvmfv3ll1/qWInwp3Pna9i1dz87C4o5d75G73J8QhqIEDqqrKzkwIEDhIWFERYWxoEDB6isrNS7LOEHX2zdhd3uwG538Pcvd+ldjk9IA2mniooKKioq9C5DBKnc3FxUVWXkyJGMHDkSVVXJzc3VuyzhB59v+eepq1A5jSUNpJ2ysrLIysrSuwwRpLRTVrfeeivjx7smVhuf0hKh4dSZKvYWH8QSFoYlLIy9xQc5daZK77LaTa7CaoeKigqsVisAGRkZxMbG6lyR6ChOnDhBXV0dNpsNu90OgN1up66uzr1NZWUlpaWlREREMHz4cMC1sOjhw4f57LPP6Nmzp3vb8PBwTCbXr6vJZMJisRAeHk7fvn0D+F0Jb32+ZQdOVWXCza6f8xdbd/K5dQc/ypiqc2XtIw2kHbKysnA4HO7XCxcu1Lki0ZG88cYb7qdutmTMmDGYzWb3682bN7Nq1aoWx8THx7NkyRKf1Cn8b+Pl01d33XYLqJcbyOavpIF0Vlr6MBqNAFitVkkhwq1v374899xzvPvuu+Tk5ACgKAppaWlYLBYA9zNwbr/9dve4u+66y500amtrAbDZbOzZswdVVQGYPHkyDz30kPt9hH7KjpVzsc5GXZ2NhgZX0myw27lUZ3NvU3GmigMlR+ga2YVxI4cB0DWyC1+XHOEvH/+N2F4x7m27hFswX/75m80mwsMtRIRbSOgfF8DvynPSQLykpY/JkycDkJOTIylEXMFisbBw4UKSk5N55513sNlsVFRUsGTJEgYMGNDkmKSkJJKSktx/Li8vZ9myZaiqitls5sEHH2TKlCmB+haEB55Z9jYlR461ut1t40YRFmZ2v/5s01b+9+33Wxxzw8D+PP+LxT6p0x+kgXhBSx8Gg4H09HQMBgNWq5UtW7aQnp5OXFzH/LQg9DFp0iRuuOEGli1bxnfffcfTTz/NY4895p40b87OnTt54403uHjxInFxcSxZsoSEhIQAVS08kdA/jvde/jW/fWMVn27aCriS5vjRwwi/nBCjukYAkH7Xbe5x9027HbPJdfai5sJFAOpsNrbtKnQnzel3TOA//s98wi1hgfp22kwaiBcapw+tWUycOJGcnBzWrl0rKURco1+/fjz77LO89dZbbNu2jVdeeYUDBw6wYMEC9ykrjd1uZ+XKlWzcuBGA8ePH8+ijj3q1Uq8vyMqzLQu3hPGrf3uEkcOG8MLrK7lUZ+N4+Wme/8Virk/o1+SY5BsTSb4x0f3no8dP8v9+sxxVVQkLM/PkYz/iB1NvC9B34D25jLeNrk4fmoyMDIxGI1u2bKG8vFzHCkVH1aVLF5544gnmzZsHwObNm92fNhtTVZXNmzcDMG/ePJ544okWm8fq1av9tiCn3ivPBpNpt49n5Sv/xfUJ/Sj97gQPLnnGo/s9Nufms+Bn/8W3pd8R368PK17+dVA0D5AE0mZNpQ+A2NhYSSHCI9rk+bBhw9xXXzVmNpsZNmwYu3btcm+rt0CngWBrHprEAX15b9mv+M1r77Fx81f88re/p2D/QZY8Os89Oa5psNtZ9lYmaz77O+C6QusXjz/o1Uq9epEE0gbNpQ+NpBDhiby8PABGjRoFuK62eu2113jppZeoqam54mv5+fn6FCm8FtElnGf/YyGLfnwfANlffInqbCJpOlWyv3DdSLrox/fx7H8sDKrmAdJA2kRLH5MmTWpyolxLIU6nk7Vr1+pQoejobDYbxcXFKIrCiBEjKCgoYMmSJWzdupUdO3bw5JNPUlBQwIgRI1AUhX379mGz2Vp8z9mzZ8ujATqgbl1d6fHmtKHuq68aCwszc3Pa0Cu2DTbSQDzUWvrQSAoRLSksLKS+vp74+HjWrFnD0qVLOXv2LEOGDGHIkCGcPXuWpUuXsmbNGuLj46mvr6ewsFDvsoUXrDv2ADDxljQAamov8p+/+wP/97nX3Kvxanemb925R58i20nmQDzU3NzH1WQuRLREOyVVVlZGWVkZZrOZOXPmMH36dAA+/fRT/vrXv7qvwNLGjB49Wpd6hXcu1dnI2/s1hsuX9G7PL+KZl9/hTNU5AAq/LuFX//YIt45JxaAo7Cr4mkt1NrqEB9fNodJAPOBp+tBkZGTIfSHiGqqqXjGnER8fz+OPP37FvR0zZswgNTWV1157zb0MSn5+PqqqoihKwGv2RuXZavILv+Z01TkUFHrFRDMqdQgx3aP1Li1gdhYUY6uvZ9D18byduY6Psv+BqqqkDR0MwJ593/DEr17ih9O+T1LiAL49fJSdBcVMumWEzpW3jTQQD3iaPjSSQkRTSkpKqK6uRlEU7r33Xu6///4mr8JKSEhg6dKlfPDBB3z22WdUV1dTUlLCoEGDdKjacwdKjvD6ig/ZuacY51WXJxsUhZtHDGXRj+9jcFLo3wy5dUcBAN8ePsq3h48SZjbxrw/8kH/5oWvtq798tIE//Okj9xVY2hhpICGm8Yq7JpOJdevWeTROuzlM1sgSmry8PHr16sWiRYv43ve+1+K2ZrOZBx54gDFjxrB8+XLy8vI6dAP5YN3nvPz2+zidTsItYYxJ+x4D4lz/z39XXsHOPcVszy9iZ8F+fvbIXO6feYfOFfuPU1XdDQRcy5E88/N/ZVDiP5eveWDWPdwyMoVf/e4P7mVQtu4owKmqGIIkaYI0kFY1XnF306ZNbR7vcDhkjSwBuO7/ePHFF4mIiPB4zODBg3nhhRf44osv/FhZ+3yw7nNeevMvKIrCjzKm8tDcGURFXvk91tRe5I+Z68hcu5GX3vwzQMg2keJvDlN1rhqDojDvB3ezcMEswszXHmoHJQ5g5Sv/ze9XriHz479Rda6a4m8Ok3JTUhPv2jFJA2mBw+EgJiaGmTNntut9TCYTDofDvXKv6JxmzJjh1biIiAivx/rbgZIjvPz2+yiKwjNPPsbdk8c2uV1UZAQ/+8lcBicl8OuX3uJ/33mfESmDufH6+ABX7H/Wr3bTp3dPfv3vP2HUsCEtbhtmNvHEI/czefxIfv3iW2zdsUcaSKgwGo3MmTNH7zKE6LDeWLkGp9PJjzKmNts8Gpv6/XEcOHSEzI838vqKD3nlmX8PQJWB1a1rJO+/8RxdIz1fu2zYkEH86dVn+HhDjh8r8z25D0QI4ZXKs9Xs2L2PcEsYD831PCE9PHcmlrAwvsovoupctR8r1McDs+5pU/PQdI3swgOz7vFDRf4jCUQIH+ssd4XnF36NU1UZk/a9a+Y8WtKtaySjhw/hy5172V30DVMmjPFjlcKfJIEI4SP+WhG3o+771JmzAMT369PmsQn9XJfDnzxd6dOaRGBJAhHCh/RsIgGnXW167TqBrVIvDwqWmyObEqwrBvuSNJBGOsupByF8QXuWd9nxk20ee/TymMbPAw8Wu9avlIdsXSYNBNenRr2aR6f6xCpCyoiUmy6v41RMTe1Fj+dBztfUsqvAtU7UiJSb/Fylf3S0A7lepIFcJgdyIdqmZ49obh4xlO35Rfwxcx0/+8lcj8a9nbkWW30940enEtO9m5+rFP4kk+hCCK8t+vF9GI1GMtduZMM/clvdfv0/tvHXTzZhNBpZtGBWACoU/iQJxAPlv9bnztC4/z6ky36F8NTgpAR+9shcXnrzz/z6pbc4cOgID8+dec0Dks7X1PJ25lr++skmVFXl334yl0EheBd6ZyMNpBV6NQ9t39JEREd3/8w7UBR4+e33yfx4Ix9l5zB6eDLx/VyLKR49XsGugv3Y6usxGo0seXQes6dP0blq4QvSQDwU6AO5no1LiLaaM+MO0oYO5vUVH/JVfhFf7iy44uuuByulsmjBLEkeIUQaiBDCJ268Pp5Xnvl3qs6dZ3fRAfeNhtf16sGIlJtkwjwESQMRQvhUTPdusjxJJyFXYQkhhPCKNBAhhBBekVNYfuC8cBpb6Q6cNRWgKBi6Xocl8RYMXXvpXZoQQviMNBAfaigvpmbT77Ad3gaq88ovKgYsSbcSNeXnmOOS9SlQCCF8SBqIj9R+tYLzG38DTgeKuQuW68dj7JkAgKOyDNvhbdhKrNgOb6PbXU8TeYus5CmCh6w865Kav0SX/e4duUyX/bZGGogP1H61gvMb/gcUhchxj9B10iIM4VdesuisO8+FLcup3f4u5zc8AyBNRHR4svLsP+nVPLR9d8QmIg2knRrKi13JQ1HonvESXYbNbHI7Q3g3ut31C8x9kjn38ZOc3/gcYQNHY+4jp7NEx9bRDuR6C/SBXM/G1Rq5Cqudar54EZwOIsc+3GzzaKxLajqRtzwITodrrBBCBClJIO3gvHAa26EvUcxd6Dppkcfjuk5azMW8TGwlW3FeOCNXZ4mQ1O/vf9Rlv8dvf1iX/XZGkkDawVa6A1QnluvHXzPn0RJDl2jCEseC6qT+yA4/ViiEPvRqHnrvu7ORBNIOzvPlABh7JbZ5rKnX9dgO5uC4/B5ChKJApwFpHoElDaQ9FMX1X1Vt+1j3GMVn5QghOpYzDTXk1ZRwuuE8AL3N3RgddQM9zVE6V+Yb0kDawdAtDgBHZWmbx9ovjzF26+PTmoQQ+vv64jFeOZ7NjvMHcXLlB0wDCmO7Dean/aZxU0Q/nSr0jaBpIO/M26DLfqcNav5rloFjQDFgO5yLs+68x/MgzkvnqC/dDoqBsMRbfFSpEKIj+MspKy8e+wSn6iTcEMYt3QYxwOK6UOY72xm+Ov8t284f4KuagzzZfybzrpugc8XeC4oGolfzAMj+djnTBi1u8muGrr2xJN2KrcTKhS3L6XbXLzx6zwubX0NtqMMy6DYMkT19Wa4QQa/sUg0ACV2C7zTPX05Z+e13a1FQmB97G4/G3UGUscsV29Q4LvFm+ef8ucLKC999DBC0TSQoGojmkcypAd2fJ40rasrPsR3eRu32dzH3SaZLanqL21/a+zG1O1aCwUjUlCd9VaoQIePVI66nGb40JLgOql9fPMaLxz5BQeG5xHlMixnZ5HZRxi482X8mQyL683RpJi8eW8fIrtczOAhPZ8llvO1kjkum211Pg6q67jD/23M4L1Vfs53z0jnOb/gfzn38c1BVut39S8x9huhQsRAdV9mlGtaUl7CmvMSdRILFq8fX41SdPBA7qdnm0di0mJH8KHYiDtXJqyfWB6BC3wuqBNJRRd6yABSF8397ltrt73IxL5OwxHGYeg4EwF55hPrSXNSGOjAY6Tb1l0TePF/fooXogF49UoD98krWrx4pCJoUcqahhq/Of0O4IYxH4+7weNyjcXey+nQuudUHqGyoCbqrs6SB+EjkzfMJSxhFzRcvYivZiu3gP7A13kAxYBl0G1FTnpTkIUQTtPRhUlwnRtaUl/DTgcODYi4kr6YEJyq3dBt0zZxHS7oZuzAmahBbq/eTf+EQd/YY7scqfS/kG0jNqWp0zRYAABGfSURBVIsARF0X4fd9mfskE/Ojd3HWVlJf+hWOmgoAjFGxhCXeIhPmQrRASx/3970RgA9OHAyaFFLRcA6ABMt1bR47MLw3W6vhZP05X5fldyHfQPasPQTAxEdTArZPQ2RPwodOC9j+ROcye/ZsXfa7evVqv723lj6MisLihFQMisKa8hI+LP+WxQmpJEZ4vlSQHpTLNwSreHFT8VXvEUxCehK95tRFSrYep2TrcXcSESKY6dU8/L1vLX3cFzeIxIhuJHSJYlbcDThUleVle/22X1+JDesOQFnd6TaPPXJ5TGxYtE9rCoSQTiB71h7C6VDdrwOZQoTwJ3+mgab4s3lcnT40Px04PGhSyMiuSRhQ2FHzLTWOSx7Pg1TbL7Kz5lsMKIyKusHPVfpeyCYQLX0YjAoGoyIpRIgO6ur0oQmmFNLLHMXYboOpc9bzZvnnHo97s/xzbM4GxkffRIypqx8r9I+QbSBa+rhhQj9umNAPp0N1z4cIITqG5tKH5qcDh2NSDHxY/i2lF8/rUKHnftpvGkbFwJ8rrGRX5be6/WeVeWSe2opRMfB4v+CcMw3JU1ha+lAMCqkzrsdgcCWQb63HSZ1xPdF9Itv8nuW/TvJDpQLkwUOdWeMrr5o6RaWlkA9OHGR52d4OfUXWTRH9eLL/TF747mOeLs3k64vHeDTuTrpddTqr2n6RN8s/J/PUVlRUft4/ncFd+upUdfuEZAPR0seNt/V3N4sbJvTj4OZj7P3kcNDMhcT9d+gnJr0fPNSZmkhFheuy8tjYWJ0rcWktfWiCaS5k3nUTUIDfHVvHnyq2sPp0LjdHDSIhvDfgmmTfUfMtNmcDRsXAz/v/gLnX3apv0e0Qcg3k6vShSUtP8jqFdIYDud7kwUP+l5WVBcDChQt1rsSltfShCaYUAjD3ugmM6Ho9r55YT271AazV+6HR6kYGFCZED+HxftOCNnloQq6BNJU+wHUjYTCmECF8oaKiAqvVCkBGRobuKcTT9KEJphQCMDiiH6/f8BOq7BfIqymhot7VQWLDohkVdUNQTpg3JaQm0ZtLH5q09CQMRoVvrcepPlmrQ4VC6CMrKwuHw4HD4XAnET01d+VVc4LpiqzGYkxdubPHcB6IncQDsZO4s8fwkGkeEGIJpLn0oZEUIjojLX0YjUYArFarrilESx8AZsXA62WFHo0zB+EaWaEuZBpIa+lD0565ENGxBPODhwJJSx+TJ08GICcnh6ysLN3mQhqvuPun4wfaPN6uOoNmjaxQFzINpLX0oZEUEjqC9cFDgaSlD4PBQHp6OgaDAavVypYtW0hPTycuLi6g9dhVJ7GWCBYlDGvX+5gMBuyq071yr9BHSDQQT9OHRlJI8Gt8GkROZzSvcfrQmsXEiRPJyclh7dq1AU8hJsXAf1zf+sOWRHAIiQbiafrQSAoJfsH64KFAujp9aDIyMnRNIcEuNX+J3iV0GEHfQLT0AWA0Gdj76WGPxhlNruhbsvU4aelJAXleiPCNYH7wUCA1lT7AdSOhnikkWO0duUy35rF35DJd9tuaoG8gjVfc/fqLo20er62RJSkkeATzg4cCpbn0oZEU4p2OeiDXS1A3EKdDJbKHhdTprc97tMRgUnA6VAzG4HugS2cT7A8eCpTm0odGUojwhaBuIAajwsj7btS7DBFATS1/EUzLXARCa+lDE4gU0hmXjOlM5Bo4ETRaevBQsCz5HQha+pg0aVKLTUFLIU6nk7Vr1/q0Bj0XqexMC2TqLagTiOhcmlt8L9gW2/MnT9OHxp8pRA7koU8SiAgKofTgIX/yNH1o/JlCROiTBCKCQig9eMhfGq+4azKZWLdunUfjTCbXYUDvNbJE8AmqBvLOvA16lyB0EIoPHvLW6tWrm/2alj4ANm3a1Ob31lbqlSuyhKeCooE8kjlVt+bxSOZUXfYr/ilUHzzkSw6Hg5iYGGbOnNmu9zGZTDgcDvfKvUK0JCgaCMiBvLMK9QcP+YrRaGTOnDl6lyE6GZlEFx1aZ3nwkKdmz57N7Nmz9S5DCCCIEojofOTBQ0J0bNJARIclDx4SomOTBiI6JHnwkBAdnzQQ0SHJg4daJvMgoiOQj2VCBJGW7gMJ5X2LjkkSiBBBRg7koqOQBCKEEMIrkkCEEEFLr7kgSYEuiqqqqt5FiM5L7wcOyZLjwUvvCwmkiUgCETo7fvvDujURaR6hIdAHcr0bV0ciDUToTg7kQgQnmUQXQgjhFWkgQgghvCKnsERAnZyuz7pUfT7dqst+hQhl0kBEwOjVPLR9SxMR586do7i4mLNnz6IoCt27d2fo0KFER0frXVpQkgYiAi7QB3I9G5foGEpLS8nMzKSwsJCr71xQFIXU1FTmzp1LYmKiThUGJ2kgQgiv+Ppy1saX47b03tp2nl6+u379elatWoXT6cRisZCSkkKfPn0AOHnyJEVFRRQUFFBUVMT8+fOZOlWefuqpTtNA5JnqQviOnvdCzJ49u03NY8WKFSiKwvTp08nIyCAyMvKKbWpra/noo4/Izs7mvffeA5Am4qFO0UD0ah7avqWJiFDlr5v4mnvftjSu0tJSVq1ahaIoLF68mAkTmj6VGRkZyfz580lMTGT58uWsWrWKIUOGMHDgQG9K71Q6RQPReHMgb6izA2AOb/s/lZ6NS4hQpzWT5ppNZmYmTqeT6dOnN9s8GpswYQKHDx8mOzub999/n6eeesqn9YaiTtVAvHFkVwUKcMOEfnqX0ik5z1ZRX7QHR9UZUBSMPXoSNiwNQ/cYvUsTHdi5c+coLCzEYrGQkZHh8bhZs2axadMmCgoKqK6ulquzWiENpBWHcstRFGkggdZw6CAXVr6JrSAPLj8X3U0xYBkxmq7zH8N8/SB9ChQdWnFxMaqqkpKScs2cR0siIyMZOnQou3fvZv/+/YwdO9aPVQY/aSAtqKup58S+M+7X4VFhOlfUOVz85EPO/3E5OJ0olnDCho/CFOdq4Pby49QX5GHL34GtII9uDy8mYvosnSsWbVFRUQFAbGys3/ZRVVUFQFxcXJvH9u3bl927d3PmzBlflxVypIG0oHTHSZwO1f16yJR4nSsKfRc/+ZDzb78KikLkD+4ncs4CDJFdr9jGWXuB2g9WULtuNeffegVAmkgQycrKAmDhwoU6V9I07T4RRVF0rqTjk7WwWnAo90Sj1+U6VtI5NBw66EoeikL0kl8S9dCia5oHgCGyK1EPLyb6334JisL5Py6n4fC3OlQs2qqiogKr1YrVanUnEX/o2bMnACdOnGhly2uVl5df8R6iedJAmlFbVUfFN+cwhRkxhRmp+OYstVV1epcV0i6sehOcTiLT59Dltjtb3b7L5DuJnHEfOBxcWPVWACoU7ZWVlYXD4cDhcLiTiD8kJyejKAr79u2jtrbW43EXLlxg3759KIpCcnKy3+oLFdJAmnE4txxVVYkfcR0D0nqjqiqHt0sK8Rfn2Spse/JQLOFEzlng8bjI+3+MEmbBtnsnznNVfqxQtJeWPoxGI0aj0a8ppHv37qSmpmKz2fjoo488HrdmzRrq6+sZPny4XIHlAWkgzTi03RV9k8bFkTSur+vv5DSW39QX7QHVSdjwUU2etmqOoWsUYakjQHVSv6/AjxWK9tLSx8SJE5k4caLfU8jcuXMxGo1kZ2ezdWvr669ZrVY2bNiA0Whk3rx5fqsrlHS6SfTq8loa6uzYbQ4cdtdkmdPuxG5zAK4JtNqqOs6UnicswkT/1N4AhEWYOFNaTdH6UiJjwt0TbCaLEYPJ1YeNJgWTxYg53ER0nOeXDgpwVJ4CwNR3QJvHmvrFY9u1HcfpU74uS/iIlj4MBgPp6ekYDAasVitbtmwhPT3dq6ulWpOYmMj8+fN57733WL58OYcPH2bWrFnXXNZ74cIF1qxZw4YNG1BVlfnz55OQkODzekJRp2sgANY/FFH1XU2r2w0cFYvRbHC/Pmg9zo4/H2hxTMyAKG7/WZpP6uxctCte1Ba3apK2uqpcNdNhaelj8uTJ7mYxceJEcnJyWLt2rd+uyNLWtFq1ahXZ2dls2rSpycUU6+vrMRqNLFiwgLvvvtsvtYSiTtdAouMimfHMWHJX7OfglmOuv1RgwPDemMKMKIpCWITrn2Xw5H9+Gh5yR4I7adRftKOqKvZ6B98VnHYf826c1J9xP07GZDEG9HsKBcZerqRnP/5dm8faT3x3xXuIjuXq9KHJyMjwewoBVxMZMmQI77//PgUFBeTn51/xdUVRSEtLY968eZI82qjTNRBwnXaa+FgKcckxbHu3GLvNQc2pS9z+RBo9+jd9/r13UjS9k/45qVZdXsvfX9kDKhjNBsYuSOam77f99ItwCRuaBoqB+r35OGsveDwP4qw5T/3e3aAYCEuR5NcRNZU+wHUjYSBSCMDAgQN56qmnqK6uZv/+/e4bDWNiYkhOTpYJcy916kn0QRP6kf7sOHr078q54xf45Fe5Hk2UH9lVwbr/zKXqaA3RcZHM/J9x0jzaydAjBsuI0ai2Omo/WOHxuAsfrECtt2EZeTOG6B7+K1B4pbn0ocnIyMBoNLJlyxb3/Rf+FB0dzdixY5k2bRrTpk1j7Nix0jzaoVM3EIDu/boy45mxJI2Lo6HOQc7yAnLfK8Zpd16zrdPuJPe9Yr54eTf1F+0kjYsj/blxxMRH6VB56Ok6/zEwGqldt5pLOZ+3uv2lnI1c/HQNGI1EzX80ABWKttLSx6RJk5o8RaWlEKfTydq1a3WoULRHp28g4FqqffLi4Yy+fzAAB63HUZuYy1VV19cARt8/mMmLh3u1zLtomvn6QXR7eDGoKtUvP0vNO6/hvHDtxQ7OmvOcf/tVql9+DlSVbg8/jinxBh0qFi1pLX1oAp1ChO/I0a8RS6QZgH4pvdxXXzVmNBvol9KLsrwK97bCt1xrWimc/+Nr1K5bzcUN6whLHYmpb38A7CeOUb83H7XeBkYj3R55nIh7f6hv0aJJzc19XC2QcyHCtySBNFKW77orNmHkdQDUX2xg8+t7+fv/7qGupt71tRGur5Xt9t86Pp1dxPQf0nPZ21hG3oLa0IBtVy6161ZTu241tl25qA0NWEaNpdfL70jz6KA8TR8aSSHBSRLIZXabg/L9VSiKwoDhvTm29zTWN4u4eM4GQMXBs0x8LIUBab1RFIXy4irsNodcsusn5usH0eO/foez+qzrgVKVrqW1jT17EZaSJhPmHZyn6UPTnhSi5/PZOztpIJcd33cGe72DmIQo9mSVsP+Lo6BCn5tcT747eaCKv/02j+Qp8fSI70pVWQ3H950hYaT/nmkgwBDdg/Bbv693GaINtPQBYDKZWLdunUfjTCbX4chqtZKRkdHq80JWr16tW/Pw17Pgg400kMuO5ruWwagqq6GqrAaj2cDI+24kZdpAAIqyj5D/4UH2bzp6xRhpIEJcSUsfAJs2bWrzeG2NLE9SiBzI9SUNBNf6V0f3nHb/OWZAFLctSr3i8txh9ybSf1gvNr++170MytE9p1FVVR48I8RlDoeDmJgYZs6c2a73MZlMOBwOjEY5RdyRSQMBTh+q5lK1DUVRGHrPQEbNvrHJq7Bi4qOY+ew48lYfZN/6I1yqtnH6UDXX3dBdh6qF6HiMRiNz5szRuwwRINJAgLL8U3Tt1YVJ/5pCXHLLTyEzmg3c/C83MXB0LFt+X8jR/FPSQIQQnZI0EFz3f2Q8f6t7EUVPxN7Yg/TnxnPgH21f/K+zOzl9gt4lCCF8QO4DwTW/0ZbmoQmLMDHs3kQ/VBSa+nza+kN9QnHfQoQqSSAioORALkTokAYihPCa3MTXuXWqBvLOvA16lyBESJCb+ASAoqpNrTsbevRqHo9kTtVlv0II4W+dpoEIIYTwLbkKSwghhFekgQghhPCKNBAhhBBekQYihBDCK9JAhBBCeEUaiBBCCK9IAxFCCOEVaSBCCCG8Ig1ECCGEV6SBCCGE8Io0ECGEEF6RBiKEEMIr0kCEEEJ4RRqIEEIIr0gDEUII4RVpIEIIIbwiDUQIIYRX/j+XdoWvbyTB7AAAAABJRU5ErkJggg==</v>
+      </c>
+      <c r="E698" t="str">
+        <v>18-09-2026 02:40:49 pm</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>6aad0325854c7a62eaa0416c</v>
+      </c>
+      <c r="B699" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C699" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D699" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E699" t="str">
+        <v>18-09-2026 02:53:49 pm</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
+        <v>6aad0333854c7a62eaa04273</v>
+      </c>
+      <c r="B700" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C700" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D700" t="str">
+        <v>Started Playing game and Debited "10" and Balance "270"</v>
+      </c>
+      <c r="E700" t="str">
+        <v>18-09-2026 02:54:03 pm</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>6aad038846969a25aa03baca</v>
+      </c>
+      <c r="B701" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C701" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D701" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E701" t="str">
+        <v>18-09-2026 02:55:28 pm</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>6aad0334854c7a62eaa04279</v>
+      </c>
+      <c r="B702" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C702" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D702" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E702" t="str">
+        <v>18-09-2026 02:54:04 pm</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>6aad038946969a25aa03bacf</v>
+      </c>
+      <c r="B703" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C703" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D703" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E703" t="str">
+        <v>18-09-2026 02:55:29 pm</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>6aad039046969a25aa03bbd7</v>
+      </c>
+      <c r="B704" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C704" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D704" t="str">
+        <v>Started Playing game and Debited "10" and Balance "260"</v>
+      </c>
+      <c r="E704" t="str">
+        <v>18-09-2026 02:55:36 pm</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
+        <v>6aad040120f5fd5cf0e810d1</v>
+      </c>
+      <c r="B705" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C705" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D705" t="str">
+        <v xml:space="preserve">Created Question Number : 0, Rupees : 10, Qst ID : 6aad040120f5fd5cf0e810c1 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E705" t="str">
+        <v>18-09-2026 02:57:29 pm</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
+        <v>6aad039046969a25aa03bbdd</v>
+      </c>
+      <c r="B706" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C706" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D706" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E706" t="str">
+        <v>18-09-2026 02:55:36 pm</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
+        <v>6aad040120f5fd5cf0e810d3</v>
+      </c>
+      <c r="B707" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C707" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D707" t="str">
+        <v xml:space="preserve">Created Question Number : 0, Rupees : 10, Qst ID : 6aad040120f5fd5cf0e810c1 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E707" t="str">
+        <v>18-09-2026 02:57:29 pm</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="str">
+        <v>6aad041820f5fd5cf0e810e5</v>
+      </c>
+      <c r="B708" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C708" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D708" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E708" t="str">
+        <v>18-09-2026 02:57:52 pm</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="str">
+        <v>6aad041820f5fd5cf0e810ec</v>
+      </c>
+      <c r="B709" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C709" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D709" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E709" t="str">
+        <v>18-09-2026 02:57:52 pm</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="str">
+        <v>6aad046360a6f32eb9070888</v>
+      </c>
+      <c r="B710" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C710" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D710" t="str">
+        <v>Started Playing game and Debited "10" and Balance "250"</v>
+      </c>
+      <c r="E710" t="str">
+        <v>18-09-2026 02:59:07 pm</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="str">
+        <v>6aad048b60a6f32eb90708bf</v>
+      </c>
+      <c r="B711" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C711" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D711" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E711" t="str">
+        <v>18-09-2026 02:59:47 pm</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="str">
+        <v>6aad048b60a6f32eb90708c5</v>
+      </c>
+      <c r="B712" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C712" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D712" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E712" t="str">
+        <v>18-09-2026 02:59:47 pm</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="str">
+        <v>6aad0842f3da7c8551314c67</v>
+      </c>
+      <c r="B713" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C713" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D713" t="str">
+        <v>Started Playing game and Debited "10" and Balance "240"</v>
+      </c>
+      <c r="E713" t="str">
+        <v>18-09-2026 03:15:38 pm</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="str">
+        <v>6aad0842f3da7c8551314c6d</v>
+      </c>
+      <c r="B714" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C714" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D714" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E714" t="str">
+        <v>18-09-2026 03:15:38 pm</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="str">
+        <v>6aad08a4052542ee778a5d2e</v>
+      </c>
+      <c r="B715" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C715" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D715" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aad08a3052542ee778a5d1e , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E715" t="str">
+        <v>18-09-2026 03:17:16 pm</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="str">
+        <v>6aad0852f3da7c8551314c9c</v>
+      </c>
+      <c r="B716" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C716" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D716" t="str">
+        <v>Answerd Correctly to Qst ID : 6aad0844f3da7c8551314c7b, Reward : 10, Qst No : 2 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E716" t="str">
+        <v>18-09-2026 03:15:54 pm</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="str">
+        <v>6aad08a4052542ee778a5d30</v>
+      </c>
+      <c r="B717" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C717" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D717" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aad08a3052542ee778a5d1e , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E717" t="str">
+        <v>18-09-2026 03:17:16 pm</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="str">
+        <v>6aad08bb052542ee778a5d69</v>
+      </c>
+      <c r="B718" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C718" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D718" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6aad08ba052542ee778a5d59 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E718" t="str">
+        <v>18-09-2026 03:17:39 pm</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="str">
+        <v>6aad08b6052542ee778a5d43</v>
+      </c>
+      <c r="B719" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C719" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D719" t="str">
+        <v>Answerd Correctly to Qst ID : 6aad08a3052542ee778a5d1e, Reward : 40, Qst No : 3 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E719" t="str">
+        <v>18-09-2026 03:17:34 pm</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="str">
+        <v>6aad08bb052542ee778a5d6b</v>
+      </c>
+      <c r="B720" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C720" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D720" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6aad08ba052542ee778a5d59 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E720" t="str">
+        <v>18-09-2026 03:17:39 pm</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="str">
+        <v>6aad08cd052542ee778a5da4</v>
+      </c>
+      <c r="B721" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C721" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D721" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6aad08cc052542ee778a5d94 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E721" t="str">
+        <v>18-09-2026 03:17:57 pm</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="str">
+        <v>6aad08c7052542ee778a5d7e</v>
+      </c>
+      <c r="B722" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C722" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D722" t="str">
+        <v>Answerd Correctly to Qst ID : 6aad08ba052542ee778a5d59, Reward : 30, Qst No : 4 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E722" t="str">
+        <v>18-09-2026 03:17:51 pm</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="str">
+        <v>6aad08cd052542ee778a5da6</v>
+      </c>
+      <c r="B723" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C723" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D723" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6aad08cc052542ee778a5d94 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E723" t="str">
+        <v>18-09-2026 03:17:57 pm</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="str">
+        <v>6aad08d0052542ee778a5db6</v>
+      </c>
+      <c r="B724" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C724" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D724" t="str">
+        <v>Answered incorrectly for Qst ID: 6aad08cc052542ee778a5d94, Qst: How many broken boxes are there?, Submitted Answer: 13, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nOzdd2BUVdr48e+dPqkkoYUQQuihV0GQFUFlgbWgiKLYsazgWlb9ue6+uPKqr7oq6oorYi+ogAUWQRCk14BJpARCCyUJIb1Pv78/JjO0kEySmbkzk/P5xwHumXmQ3Hnuc+85z5FkWZYRBEEQhEZSKR2AIAiCEJxEAhEEQRCaRKN0AMJZU6dOPe/XixYtqvP3vc31OYIgCI0hEkiA8HWSaOizRRIRBP8p39JK0c+PGlXqlfcRCSTA1PVF7ssvdyUTlyAIwU0kEEE4hy8Sqie3IkUF2DJ5qxLwlLcrH/EQXRBqKX0bURCCjahABOECvqoGLvW+InkIwUpUICHAfjoX++lcpcMQBKGFEQkkBFQu+pzKRZ8rHYYgCH7gMGXjMGUrHQYgEkjQs5/OpWbdKmrWrRJViCC0AOZTr2M+9brSYQAigQS9ykWfg80GNpuoQhR0vKaC4zUVSochhDiHKRvrmW+xnvk2IKoQkUCCmKv6QKMBjUZUIQp6Jzudd7LTlQ5DCHHmU6+DbAXZGhBViEggQcxVfRivGo/xqvGiClHI8ZoKluQdZkneYVGFCD7jqj6QtCBpA6IKEQkkSLmrD5WKiCnTiZh6l7MKWbsSe+4ppcNrUd7JTscmO7DJDlGFCD7jqj60bW9F2/bWgKhCRAIJUu7qY9wE1B06om7fwVmFOBxULvlS6fBaDFf1oZFUaCSVqEIEnzhbfajRJzyBvuNTtVXI1zhqjigWl0ggQejC6sNFVCH+56o+psR3Y0p8N1GFCD5xtvqYhsrYFZWhc20VYsecM1exuEQCCUIXVh8uogrxL1f1oZYkZiUN4C+dB6KRVCzOO8Sx6nKlwxNCxIXVh0sgVCEigQSZS1UfLqIK8R9X9XFLfHeSw6JIMkYyJb4bdlnm3eMZSocnhIgLqw+XQKhCRAIJMpeqPlxEFeIfF1YfLqIKEbzpUtWHi9JViEggQaSh6sNFVCG+d2H14SKqEMGbLlV9uChdhYgEEkQaqj5cRBXiW5eqPlxEFSJ4Q0PVh4uSVYhIIEHC0+rDRVQhvnOp6sNFVCGCNzRUfbgoWYWIBBIkPK0+XEQV4hsNVR8uogoRmsPT6sNFqSpEbCgVBNzVByBptFQt+cqjcZJGC0DNulVETL0LdfsOPouxpXBVH7d16FFn9eHiqkK+yc3i3eMZvJEy2o9RCsHOXX20m15v9eHiqkKs+V9izpmLsdu7fohSJJCg4O64C1Sv/LHxb1DbIyv6L896ObKWxdPqw+UvnQeyJO8wi/MOMStpQL0JRxBc3NUHIEk6zKfe8micJOkAsJ75Fn3Hp1AZOvsqRDeRQAKdzYY6tjXhU+5o1ttIao0zCWnEP3lTeVp9uIgqRGgKd8ddwHL648a/QW2PLH9UIeLbJNBpNERMn6F0FC2eq/oA0Eoq5h3/3aNxWsn5mHFJ3mH+0nkgScZIn8UohADZikoXj77j4817H0nrTEKS1jtxXYJIIILgAVf1AfBFzoFGj3f1yBJViFAvSYu+09+VjsJjIoEIQgNssoN2+jBmJvVv1vtoVCpssgONJCY/CqFBJBDB6xLWfqTo5+eMu9+r76eRVDzTZYhX31MQQoG4FBIEQRCaRFQgAWbq1KlKh+A13q4EGqJ05SMILY3fE0je8w0vivGl+BeU272rPosWLVIseSxatEiRzxV8T5xvga18SyulQ2iWFl+BKP0PGDWq1P1afJELghBMFEsgTbkykc1VAEj68EaPVfpKTAgeoXQb0UWcb4Hl3AvHYBZUFYgpczVIYBww2evv3ZR/UNleCYCkjmj0WKUrH+Fi4jbi+Xx5vnlK/HsEtqBKIDV7loEkKfoDfS5b0XIAtG1vUziS4HfGUsO2kjzyzdVIQFt9GCNj4mmjM/o1DvHFcZbS55uSleDUqVPFz4IHgiaBOKpLMB/b6n6tCotROCKwFi4BJJFAmmFPRRH/dziVTSW5OGT5vD9TSRJXxibwbNeh9I2MUyjClimQzjd/f5ErkbiGTbzb7595rtQVnzVpXNAkENO+FWC31b5eSdiw2xWNR7YWYSvd4H4tacUXXGN9eHIfcw7twC7LGNUaRsd0oHNtk8Ls6nI2leSyrugUm4pzmd39Mu5P7KNwxC1HoJ1vQmAKmgRSs+e/571W+gfaWvSju2OmtWgpuvb3KRpPsPnw5D6ez9qOBDzUqR+PJw8kSqM775hym4W5x9JYcGIvs7O2A4gk4ieBdr61FE2pBKprTACEGQ2NHtvcyicoVqLby09jObEbSWtA0hqwnNiFvfy0ojFZC5bU+Vpo2J6KIuYc2oEEvNNnDLO7X3ZR8gCI0uh4vvtw3u5zJRIw59BO9lUU+T3eliYQzzfh0tZt3c36bbsV+eygqEBMe/4LsgN9z3Egy5j2rcC0dznhI5Vpc+6w5GIv3wEqZ8a3l2/HYclFpRM7/nnilSO7sMsyD3Xqx03tG57ueXP7buypKGLBib28cmQXXwwc74coG0fpVfDeXPUfaOebUL9V67chSRITx47y+2cHRQXiKqeN/a7D2O+6835PCbaC7wAH2tgJaGP/CDiwFXyvWDzB5Iylho3FORjVGh5PHujxuCeSB2JQqVlfnEOBpcaHEQqBdr41RlFJGas3bOerH35m4Q+rWL1hO8WlZUqH5TOl5RWkZuxnZ/o+Sssr/P75ilYgtsKjyJZqZGs1st35PAG7FdlS7Xwty9jLT2PN24dkiETf7Q8ASIZIrLl7qdr6Eeqo9iBJzt/XhYHauYGKpNYiacOQdGFoWnfxatzO2VegbT0FkLEW/oi1cAm6hFle/ZxQtK0kD4csMzqmQ523rS4lWqNnVGwH1haeZHvJaa5rl+zDKJuuKZVAZe3PfoS68Zv/NKbyCdbzzRMHDmcz79PF7EzbV+dsvuGD+zLznlvo2TXJ77H50ppNqdhsdgDWbk7l5olj/fr5it/CKv3xGWz5Bxs8zpByLZJG735dk/Yd5aterneMpl1PYqZ6vq2jo+YQsr0KHNXIDovzN2ULsr32BENGtuRir8xAUkehiRkHgKSOwl6ZjiV3HpKuA1B7gqnDoHafYkmlA1UYkjoclbG7R/EovdjQF6tl82pXN3cJi2702K5h0azlJLnmSm+HpaifzxwHCaa07+bzzwqk881bvlm6mrkLvsbhcGDQ67hsUB8S49sBcDIvn51p+9i2ew870/fz+Ixp3HbDNX6P0VdWb9jufr1q/faWlUA0rbvQ+oHvKP/pn1Sn1T6IliT03ccgaY0gSagMzi1Awwbf6h4XPmw6Uu2Vj8NUAbKMbK3BfGg91F59hA2aQtSkfzrfpxFqDj2Co3p/w7HH/cn9DEQT9yesZxZiOlb/TmKqsN6E9WrafOtQIdX+V673qLq5xkjudwkNP+YfQcL3CSQQz7fm+mbpat6Y/xWSJDH9pgncN+16IsPDzjumoqqajxYuZeGPq3hj/pcAIZFEzhQWk7EvC73OeZGasS+LM4XFtG0d67cYFK9AJK2R6BtfRdd5BGU/zUa2VGMvOUnM1HfRtK37Sl2b0J/ohLO7w9mKjlH67SyQZSSNnqgJswkb2vjFfSpjd8IHrMV05CmsZ75yRYgm5loktRGQkDTOK2dtu7vc43TxM5wVBiDbygAZ2V6DrWQ1rq89bds7MHR9HUnV+BMslNqsxNf2VTpa3fj70q4x8U3ozRSoiq0mNhXnul/Hahs/FbMxAul8a64Dh7OZu+BrJElizlMP8cerLq/zuMjwMB5/YBo9uybx/Bsf8NaHXzO4X096dOnk54i9a/WGHc7bwcOdzxLXbNrJ6o07mH7TBL/FEDAP0Y0DJ9P6wR/QtO2OreAwhQtu8ujBnSlzNYUfTMaafwBNXDJxD37frB9mSWXE2H0exu7vO29BIeMwZaNPfBZjz08wdH0LQ9e3UEcMdo9RRwx2/76x5yfoO/0D2XIKkEFlcP5+93lNSh5NZSta7m61EkhGxMSjkiQ2l+RSbrN4PK7UamZLcS4qSeLymPY+jNC/lucfwyY7sMkOfjqT7bfPDZTzrTne+2wJDoeDOyb/8ZLJ41wTxo5k2o3XYrfbmffpYj9E6Furam9fjR8zgvFXjgBg9frt9Q3xOsUrkHNp2nSj9YzvKPvv36nZ819KlzyO5cQuov74D3cJ7SLbrZT//CLVO50lqbHfdURf91KTOofWRdv2NtSRg6g+cDeO6gNU/T4OQ9e30baZUu84W9Fyag49gmwvR2XshrHnZ6jD/b/4LVDbrLTVGbkyNoF1RaeYeyyN57sP92jc3GNpmBx2xsYl0trP/bF86cf8o2dfnz7CnQm9/PbZgXS+NVZRSRk7ftuLQa/jvmnXezzu/mk38N1P69i+ew/FpWXEtmr8szhfO34qj2qTGZPJjNXq7AZgtdmoMZndx+QXFnPgcDYR4UZGDnFWhxHhRjIPZ/PVDz/T7pzbWEaDHq3G+VWv1WowGPSEGfQkdYxvdqwBlUDA2Tq61ZS30LTrRcWaf1GT/j1R45+7+EDZQU26c+ps5NVPEzH6Ya/HojL2JLz/GkxHHsdasISarBnYK7ZjSH7Z/XD8bDwWTMeew5L3IQDaNlMwdH2rSbeQmivQ26w823Uom4pzWXBiL30j47i5gXv/S04f5qOT+9BIKv7WbaifovS9PHMVqWX5GFRqAHaW5ZNnrvLrLbpAOt8aY/fvmThkmcsG9bnomUd9oiLCGTYwhc07M/htz0GuHn2ZD6NsujlvLuBw9qkGjxszcig6ndb9evkvm3hrwdf1junWuSOvPOedGaMBl0BcVEbnlYG+yyj3bJBzSRo9+i6jMB34xX2sL0jqCIw9PkQV1gfz8RewnlmIofOLXPQcV3ZgPbPQGXPS8+g7PuGzmBoS6G1W+kbGMbv7ZczO2s5j+zawp6KIJ5IHEn3Bv3Op1czcY2l8dHIfMvB89+H0jvDfA0JfW5p/FIcsc03bTsgyLD9zjGX5R3moUz+/xxIo55unzhSWANApofG3M5MS4tlMBqcLArOrQVLHeD6Z+zyvvfc5//1lEwCSJDFqWH8Meue/TWSEM2neOH6Me9wtk8ah1TgvRioqnTNHTWYzW1J/R66d7HDdNaN55pG7MOg9n0Jfn4BNIKYDawDQ97oaAIepnPKf/olsMxN93YuowmLQ9xyH6cAvmA6uJWzoNJ/GI2mcD5bVra5yz746j8qAutVV2Ip+ch+rlAvbrARaAgFnTysJiRcO7WDBib18cSqTK2ITSK5tpnisupzNxTmYHHY0kop/9hjOvR17Kxy1d/142rnJ043tuiLjTCA/nlYmgQTa+dagZkznk2sHSVLgzuYz6HXMfmIGQ/qn8Oq8z6gxmcnJK+CV52bRJSmhzjG9eyTTu8fZ9VEnck7z7MvvIssyOp2Wpx6azuQJY7waZ0AmENlSjSV7O0gqDN3HYD68kdIf/x+OijMAWE7+RqsbX8XQ4yrKJBWWY9uQLdXOhU0+YiteCYA2dqIzRlsZpqNPg8OEoetcJG0c2pgJ2Ip+wlb8M7r29/oslvoEU5uV+xJ7M7xVO145sov1xTmsKTxx3p+rJImxcYn8rdvQoKo8jlSXUWW3Um23YXU4ALDKdqpru9vKsvP21Z6KIiI1Oq6K6whApEbH7xWFfHBiL/H6cNd6PcLUGrSS88pSq1IRptYQrtbStQlraeoSiOdbQ1z3+I/nNL5H14naMe38ON21qSaNG0XvHsk8+/K7HD2ew71PzuG5R+9l/JgR9Y5bv3U3L8xdQGVVDZ0S2vPKc7Ponpzo9fgCMoGYj25FtprQtk+hYsO/qU79CmQZXZLzfqXl+E6Kv7yPsGF3oG3XE+vpTMxHt2KovXryNtleja1sI6BCE3MNtpI11ByehWxx/iDaKnZi7PYumthrARW2sg3I9uraWVz+dW6bFdcqeVvB9wG7Sr5PZBxfDBxPoaWGbSWnOV270LC9PpzLY9oH7QPzJ/Zv5EBlSYPHTWiThL72GciENkksyjvEC4d21DumV0QMH/Qb55U4IfDON08M7tcLlSSRmr6Piqpqj5+DlFdUkZqeiUqSGNzPfxMWmiM5sQOfvDmbl//9CavWb+cfr/2H9P1ZPPng7e6H4y5Wm403P1jIkuVrAecMrecevbdJnXo9EZgJ5KDzL289nYn1dCaSRkfk2CcJH+lsE1G19SMqfn3TPSPENcZXP9D2svXgMKEO74v55GtY8j4CZNRRI51/Xr6V6v23oIu/H3V4b+xVe7GXrUdTW634U7C2WWmtMwZse5LG6hoWzfKh1/P3g9v4Ni8LcN5xGds6EaNKgyThft4zrUMP97i7O6agq00mZTYzsgw1Dhu/Fp5036m5Nb4HL/W8HKPae6duoJ1vnoiLiWb44L5s272HjxYu5fEHPLultmDhj5gtFkYNG0BsqygfR+k9YUYDLz7zZ7p1TmTep4v5ac1mnphx8d9Zdsj8tGYzADPvuYV7pv7Jp3EFXgKRHZiyfnX/UtOuJ61ufhNtu7NXC+GjHkDXbTSl3z3pbstgyvqVaNkBkveXtlhrb1/Zq/Zir9oLKj2GTn93fylbct7FdOIl9wws1xhvJpBAa7Mi1M+o1vBm79GMjInnbwe3UG23caKmgvn9xtIzvO7d/QZGtWFgVBv3r49Wl/Hgnl+RAb1KzZweI5ju7Wm+AXi+eWrmPbewM30/C39cRc+uSUwYO7Le41f8uoVvl/2CWq1m5t31T8cPVFERzhl6wwf1dc++OpdOp2X4oL6s37bbfawvBVwCseZk4KgsBElF+OX3ETnur0h1NN3TtutF6wd/pGLtG1Rt+xhHZSHWnAy0HQd5OSIHtuJV7l+pwnpj7LHgvLUduoS/oG41jpqsB9xtUJxjHHhzraZosxJ8psR3Y0BUax7a8ysHq0q4LvW/vJYyihvb1d/GfmXBcZ7Yv5EKm4UuYdF80G8sKT54DhR455vnenZN4vEZ03hj/pc8/8YHHDiSzf3Tbrjoi7O8oooFC3/k22W/IMsyTzwwje5Bugp94440AP4wwvn/vaKqmtfe+xyLxcrfHr2HVlGRjB4+kPXbdrNpZxo3TbzKp/EEXAIxHViLOroDrSb/C11y/Q+KJI2OqPF/w9B7PKXf/xXTwV+9/gNtr9iNbD0DqNAlPIKh0/+A6uJpjurwPkQMWIfpxP9iyXkP2XoGe8Vu1JHDvBJHoLZZERrWPbwVy4Zdx//L3MKP+UeYuXc9O0vzeaH7CLSq8y8wrA4Hzx/azmenMgHnDK1XU0Y1qVOvJwLtfGus2264BkmCuQu+ZuEPq/jup3UMG9ibTgnOZooncvJJTd+P2WJBrVbz5IO3M/U65W69NUeNycyuDOfzm1HD+rNt9x7mzP2QwmJnq6PfMw8z+4kZXHHZgNrnQ5nUmMwYDRd/X3lLwCUQlTGaNo+sQKpt6uYJXeJg2jy0jOrd33g9HlvxSlT6jhi6/wdN9Oj6D1bpMXR+EW3cddRkPYyt+GevJRA422ZFEz0a09Enke3VOEzZhPX6DFVY3bc21BGDz2u74qg5TM3Bu3G3WUl+BV37e7wWo1C3CLWWeX3HkBIRw/8d2cXivEN1rsJ3ILM47xAAf+s6lFmdB/g0rkA73861aNEij4679fprGNS3J/M+Xcz23XvYvDP9vD93fuEOYObdU4K28gDYmb4Ps8VC9y6dWLBwKd/99CuyLDOob08A0vYe5LHZb3DzpLF0TU7k0NET7Ezfx5UjBjfwzk0XcAkkfNQDTRonGSKbPLbe99W0InzQViS15w/c1JHDCR+4AevpT70eDwRPmxWld+kLRNFa59XgH2IT3LOvzqVXqflDbAI/Fxx3H+tLgXa+NVWPLp14e85fKS4t57c9B9wLDdu2jmFwv15B9cD8UjbtcCbGQ0dPcOjoCXRaDQ/feTN33OxsnvjVdyt5/4vv3DOwXGNaVAIJNLqEvzRpnKSOavJYTwRrm5WWbnWBc63LtW2cV8LlNgt/P7gVs8POK71GEas1cE3rTvxccJxfCk/4tTdWoJk6dSrgeSUCENsqKmDbkzSHQ5bdCQSc7UjmPP3weWs77pwykRFD+jH7X++726Bs2pGOQ5ZR+WjRpEggQSxQ26x4c3/uUFJtt7G1JNe9QHJd0SmezNzEGbNzJl1q2RneTBnNuNaJqCSJLcW5VNtthHlxyq4QnPYdPEpxaRkqSeL2yX/kz3dPQae9+Oeie3Iin739Av/5bAkLf/iZ4tIy9h08Sr9e9U/aaCrFfjLznvfNX6glCqY2Ky3ZptrWLL0jYpl7LI3PT2UiAyNaOfs5bS89zZ3pq7irYwq9wmPYX1nMpuIcxrdp/jas4nwLbhu3/0b7NnE8/9cHGNo/pd5jdVoNj824jatGDeH51z9g04600EsggUbp7WObI1jarLR0v9S2atlfWcz+ymJ0KjXPdBnCQ536AjD/xF5eO7rbPQPLNcYbCUQIblER4Xz93ktEhHs+U7J/Sne+eGcOP6xc57O4/J5A4l844u+PDGnB1GalJXPIMmsKT7p/3Ssihnf7jDlvbcefk/oxJi6BWfvWu9ugrCk82ax72OJ8Cw13TmnaouSIcGOTx3qixVcgTdkuNpAEU5uVliy9vIACSw0qSeKBxL4823WIu23JuVIiYlk57AZeObKbBSf3UmCpIb28gMHRbRWIOjC4HqYLgSdgtrQVmubcNiuWvA9BpcPQeQ7h/ZYT3m85hs5zQKXDkvehsw3LOWME/1ldeIIEQwTfDprA7O6X1Zk8XHQqNbO7X8YPQyaRZIxy3/pqaRoz+yqUPjuYtPgKJLgFTpsVoX7RGj1rh08mso42IZcyNLodqy67gS9zDvowssDW0r7Ih028W+kQGkV8gwSx89uszCJiwLo6Fwa62qw4mz+q3G1WBP/5c1K/RiUPl0iNjj8n+X+DKUHwhKhAglggtVkRhFAxYPeT/v/Q/41zv8wY8qb/P7+JRAUSxFxtVhpMHudwtVlxNV4UBEFoKlGBBLFAbbPSkon+X6HD35WAIpVPM4kEIgQspU+oYLqVIAhKCLkEotSc8ZY2W0Q4n+j/JbREIZVAlFxwNHXqVJ8lkWBus+INTakEquxmAMLVjW+JrnTlIwjBIqQSiIu/qwGxUjbw/Fq6Bwn4U9xQpUMRWpBT5iIAOurjGjgyNIRkAgkVwd5mRUkri39DkiSRQAS/WnB6DQAvJN2qcCT+IRKIEHJKbVXsqDjkft1KE65wRC1bS3kuecpcxPKiXQA80P7qFlGFiHUgQshZXZKBTbZjk+38UpKhdDgtmtLPJf1pwek17p87VyUS6kQFUste4my1rY5JbOBIIdCtLP7tnNdp3NJmpILRCNC0asBqsgGgNTT+a8rfycNVfWgkZ5PM5UW7WkQVIhJIrcqN8wCIvuEVhSMRmiPfUkp65TH0Ki0AaZVHybeU0k4XGDPZlJ7hFUxrW7JT85GAbqMTlA6lQa7q48bWwwH4sXAHC06vCflnIeIWFs7qozrjB6ozfnBXIkJw+rkkDQcyV0b34cro3jiQWVWSrnRYQhMc2ZrHkW15SofRIFf1oZJU3N9+LA+0vxqNpGZZUSonzAVKh+dTogKhtvqw29yvRRUSvFYWpwEwIXYQ4HwesrL4N+5qN0bBqC4m2mTUz1RhIXdvofu1IbLxnYz95dzqo5O+DeCcPv5j4Q4+Ov1rSFchLT6BuKoP1M7/FdUZPxDxh5niWUiAyTadodphocZhxuqwA2CV7dQ4LLVHyORbysisPkWE2sCoqBQAItQG9lef4ov8DbTTRQPOrWGNKh3a2vvVWpUao0pPmEpHZ0PL3fkvkBzbcRqHXXa/Trm6k8IR1e3C6sPlgfZXs7xoF8uKUrm//Vh3Ygk1LT6BuKqPsMG3AFD922JRhQSo2dlfc6im4Vsa41r1Q6/SuF8vLUrl9VNL6x3T3RjP612CazOfUHZka+45r/MCNoHUVX2AcyFhS6hCWnQCcVcfKjXhVzyMpFI7n4Wkf0/4FQ+jieusdIhCrc6GtnzZ6zFePvE9S4t2AiAhcUV0CkaVFpCIUhsBuKn2QSbArW1GoZWcP+bl9hpApsZhZXNZJjLOK9wb4i7juU43YVAF7m2SlqSq2ET+wVI0OmeFmH+whKpiE+GxBoUjO9+lqg+XllCFtOgEcm714UoWYQMmU/3bYqo2vy+qkABjUOmY0/k2hkV246UTS6hxWMgxF/F6l7vpamxf55g+4Z3oE3726vW4qYCnjn6GjIxepeGZxMlMaX25v/4KggeObs1DlmU6DW6LLMsc23Gao9vy6DcpWenQznOp6sPFG1VIoC/CbLGzsC6sPlwi/jAT1Bqq07/HVpStXIDCJV0XN5SFKU/Q1dieo6Z8ph94+7y1H5fya+kebj8wl6yaXJIMbfiy1+NBkTwKrRX8XJzGF/kb+CJ/Az8Xp1FkrVA6LJ85ss15+6rryHi6juzg/L2tgTUbq6Hqw6U5M7KCYRFmi61A6qo+wLmQUFQhga+LoR1f9HyM/z2xmJXFv/HssS9JqzzG04k3uh+Ou1hlO/86+SPfFmwBYELsYP6n0y1N6tTrT5nVp3g75yd2lGfhqL3d5qJC4vKonvwlYRK9wgJ/nQRAWV4VVpMNm9mO3eb8+zhsDmxm56QIWZapKjZReKwcXZiGjgOcV/W6MA2Fx8rYs+IY4bEGJMk5EUKjV6PSOK+B1RoJjV6N1qAhOt73rWsaqj5cvFGFBHJz2BaZQC5VfbhE/GGmeBYSBMLVel5Jnk4PYzxv5/zEsqJU/trxBtdEKzeHLLOsKBWAxxImcV/7cQpE2zhfndnI66eW4ZAdGFQ6RkR1J1HfGoCT5kK2lx9iS/kBtldk8VTHG7i9refbGitp4/t7KD7ZcPXUeWg71FqV+3XWxhx2fHmg3jGxiZGMe3yQV+Ksj6fVh0soPwtpkQnkUtWHi6hCgkuUOgyAy17KL9YAACAASURBVKN6umdfnUuv0nB5VE9+Ld3jPjaQfXVmI6+d/BEJibvajeHB+GuIrJ0g4FJhr2F+3mq+zN/Iqyd/AAj4JBIdH871cy5n66f7ydpwyvmbEiQObINGp0aSJHRhzn+/nlednUafck2Su9KwVNuQZRmbxc7J9AJchVmPKzsy8p7eaPTnV5++4Gn14RLKM7JaXAJpqPpwEVVI8FhftheAK1v1AZxfrv934nvMspX/6XQLrTThXBndm19L97C+bB9T2gTuc4/M6lO8fmoZEhIvJd/OpNghdR4XqTbyVMcbSAnryN+PLeT1U0sZEtGFngF+O0ujV/OHh/oR3zuWLR/vw2a2U3GmhnGPDSKmY0SdY9p0jaZN12j3r8vyqlj7dhrIoNaquPzu3vQa6591W+d23NVKaj4+/atH47Qh2iOrxSWQhqoPF1GFBMBOiIb7GjykxmFhZ8VhVEiMjkphS/kBZmd/Q6G1HID0ymzmdL6N0dG9USGxs+IQNQ4LxgCdsvtOzgocsoO72o25ZPI416TYIWTWLpR8J3cF87o94Icom6/76ATadIlm7dtplJyqZNnsrVwxox9dR8bXOy47NZ+N83/HUm0jOj6ccY8NIrZTpJ+iPlt9ACwu2Nro8a5OvaFShbSoBOJp9eEiqpDAt708C7PDSk9jB+bnrWZRwVZkZIZEdAVgd+URZh5awNQ2I+lujOdgTS7by7O4qlVfhSO/WKG1gu3lBzGodDwYf43H4x6Mv5ZFBVvZWnaAImsFcVr/faE2R6uECK6fczmbP9zLka15rHs3nfyDxYy4M8V9y8rFYXOw/YtM9v9yAnDO0LpiRt8mdeptKptsp602ivs8eO5RH42kxibb3Z17vamopIzdv2dSUFyKhETr2GiGDkghtlV0w4OboEUlEE+rDxdRhTj5e2fExlQ+G8r2AXCwJpeDNbnoJA0zEya4e199nr+eeTkr3TOwXGMCMYHsqjiMA5kRUd0veuZRnyi1kcsiu7OpbD+7K49wbcxAH0bpXVqDhqtmDSS2UxSp3xwka2MOw6enXHScLEPWxhwAht3WkwHXd/F3qGgkNTM7TPDb5zVm9tWBw9nM+3QxO9P24ZAvmLEnSQwf3JeZ99xCz65JXo2xxSQQd/UBoNZSuXm+ZwPVzrbg9fXI8vc0O8HJgczGsv3uX3c3xvNy8h30MHZw/9497a5iZFRPnjv2lbsNysay/TiQUV04XUth+VZnok7SN74fV2dDGzaVwWlLcG6DrA93nmcJ/Vq7Z1+dS61VkdCvNcd35buPFZy+WbqauQu+xuFwYNDruGxQHxLj2wFwMi+fnWn72LZ7DzvT9/P4jGncdoPn1W1DWkwCObfjbnXqwsa/gd0memQFmL1VJyiyVqBCYnq7K3k0YSI66eIf6R7GDixMeYJ/56zgy/wNFFkr2Ft1gv7h3r0aay6pNqHJF6z5aMp7BJvju/MBSBriTJ6WaitbP9mP3epg1P19METqSBrcluO78jn+Wz69xoV+s1PXeoz6LlC/WbqaN+Z/hSRJTL9pAvdNu57I8PNnGlZUVfPRwqUs/HEVb8z/EsBrSaRlJBC7DVVkWyKueKh576PWOJOQ+vz/bZ78Qwvet750L/G6GP638zSGRXar91idpOGvHa9nXKv+/CP7KzaU7gu4BOLa9Oq4qfF7SGTXjnF2HA4uNrOdvP3FSJJE4sA2nMooYOP8PVSXmgHIzyrhDw/1I3FQGyRJIm9fMTaz3S9TdgPZgcPZzF3wNZIkMeeph/jjVXXPLowMD+PxB6bRs2sSz7/xAW99+DWD+/WkR5fmN6hsGQlErSFybHDthyA0LEoTxpLeTxOh9rzJ3sCIznyT8leWFG7zYWRNMySiKyokdlQcosJe4/FzkDJbNTsrDqFCYmgDiTQQ5ewtxGaxE5sUSdr3h9m/5gTI0L5XLACnDxTz82u76H11J2I6RVB8vIKcvYUkDWmncOTKeu+zJTgcDqbfNOGSyeNcE8aO5MCRbBb+sIp5ny7m7Tl/bXYMLSOBCH4jW/KxlW9GtpwGJCRdOzTRo5G03t9n4552VzVpXITa0OSxvtRaG8nlUT3ZUn6A+XmrearjDR6Nm5+3GrPDyujoFGI1da+lCGQndp8BoPh4BcXHK1BrVQy5pQf9JnUGYM9P2exenOWegeUa4+sEEsibcBWVlLHjt70Y9Drum3a9x+Pun3YD3/20ju2791BcWtbs2VkigQheYa/MwHz8BWyl6wHHBX+qQhMzFn3SbNTh/RWILnj8JWES2yuy+DJ/IylhHRtcC7K8aBcLz2xCLal4NGGSn6L0HlmWOZF29pZdbGIkY2YOOG9tR/8/JdOxf2vWz8twt0E5kVaALMvuvlgtze7fM3HIMpcN6nPRM4/6REWEM2xgCpt3ZvDbnoNcPfqyZsUhEojQbJbc9zFl/x1kO5LKiLrVGFQG5zRLh+ko9tL12ErWYCtdjyH5RXTxDa/Baal6hSXwVMcbePXkD/z92EIyq0/xYPy17r1OXMps1czPW83CM5uQkXm64430PGf2WbAoOFJGTZkZSZLoO7EzQ6f2qHMWVmynSG54cSS7FmWxd0U2NWVmCo6U0bab9xe7+nu74aY4U1gCQKeEurcxqE9SQjybyeB0QVGz4xAJRGgWS+77mI49C0joEmah7/g0kub8sli2lWE++RqW3PcwHX0WoFFJJJBvJfjC7W1HIwH/OrWUL/I3sKhgK8Mju5NkcPZdOm4qYEfFIcwOK2pJxdMdJzOt7RXKBt1Ex3efIaK1kSsf7kd87/rbe6i1Kobf0YvOw9qx4T+/c2L3GZ8kkKDgKryaMGHPNcvPG9VbSCYQJfvoe9OHt69U9POnzqz/z+2VGc7KAwljj/lo29T9/13SRGNIfgl1RH9qsh7GdOwfqKNGoQ7v5/2gQ8S0tqMZHNGFd3JXsLXsgHO9S9nZP1chMTo6hUcTJgVl5eGiD9dy0ytXuJsoeqJdjxhufGkUB3496cPIAlu71s4JBsdzTjd67InaMa73aI6QSiCLFi0K+B28Qon5+ByQ7egSZl0yeZxL2+ZW7JUZWHLfw3x8DmG9F9d7fDDcSvClnmEJzOv2AMW2SnZVHCbf4swg7XTRDI3sFpQPzC/U/09N22VQF6Zp8thQMLhfL1SSRGr6Piqqqj1+DlJeUUVqeiYqSWJwv17NjiOkEgiE5hf5jIX+a58AnlU+siUfW+k6JJURfcenPX5vfeIzWE5/jK1kLbL1jE9mZ4WaWE1EULUnEXwvLiaa4YP7sm33Hj5auJTHH5jm0bgFC3/EbLEwatgAYltFNTuOFrulrdA8tvLNgAN1qzEXPfOoj6RphSb6SsCBrWxLg8cLglC3mffcglqtZuGPq1j5a8OdgVf8uoVvl/2CWq1m5t1TvBJDyFUggn/IZue+1Spj4xeuqYzdoGQVsjnH22EJAcoft5Zddx9C5RloQ3p2TeLxGdN4Y/6XPP/GBxw4ks39024gKuL8LX3LK6pYsPBHvl32C7Is88QD0+juhVXoIBKI0GTNmAbiGtNC5/C3JOK5pG/ddsM1SBLMXfA1C39YxXc/rWPYwN50SnAusjyRk09q+n7MFgtqtZonH7ydqddd7bXPFwlEaBJJ75z546g53OixjpojzvfQBe/sIcFz/v4ibwmJ41y3Xn8Ng/r2ZN6ni9m+ew+bd6af9+cqSWLUsAHMvHuK1yoPF5FAQkxNqZnczGKqS0xISBhj9HToHYsxWu/Vz9FEjQJU2Es3INvKPH4OIttKsJVtAFRoooNz7YI3tLS1LYJv9ejSibfn/JXi0nJ+23PAvdCwbesYBvfr5ZUH5nURCSREFB4rJ/Xbg+TuKUK+YEMZSZJI6N+aYbf2IK6zd36QJF07NDFjsZWswXzyNQzJL3k0znzyVXCY0MRci6Rt45VYBEFwim0V1ez2JI0hEkgI2PtzNju+PIDskNHo1ST0jSOqnfNBWnl+FTl7iziVUUDu3kKG35FCnz96p425Pmk2ttL1WHLfQx3RH22b+vd5tp75BkvufJA06JNmeyWGYNPS17YIoaVZCWTYxLu9FUeTpK74TNHPDwR7f85m++eZIEG/SckMmtwVXdj5O7ZZqq2kfX+EPSuPse1z5w5+3kgi6vD+GJJfxHT0WWqyHsZemYE+8RkkzfntJWRbCeaTrzqTB7JzVXp44G0pKwhC44gKJIgVHitnx5cHQIIxjwyg26i6H0rrwrQMn96LuM5RrP9PBju+yqR9SgxxSc2/neXsaSVhOvZ3LLnvYTn9MZoLminaSteDwwSSBkPyy+jiH2z25wqCoDyvJJCmVALVNSYAwoyebwbkonTlEyh2fXsQ2SHTb1LyJZPHubpd0YHC7DL2rshm17dZjH9mqFfi0MU/hDpqJObjc7CVrMVW/PMFR6jQxFxb285dVB6CECoUq0DWbd2NJMHEsaOUCiGo1ZSaydlThEavZtDkrh6PGzS5GwfWnORURiE1ZWavzc5Sh/cjrPdiZGsBtrLNyJY8ACRdPJroK8QDc0FookBeGKlYK5NV67exav12pT4+6OVmFiPLMgl94y565lEffbiW+D6xyLJMXmax1+OStG3Qtp6MrsMj6Do8grb1ZJE8BKEJlFzP4ulnK1KBlJZXkJqx3/26VVRkAyOEC1UXOW8BRsWHN3DkxVrFR3AyrYCq2vdoacq3KLuHRNSoUkU/Xwgegb4oUpEEsmZTKjabHYC1m1O5eeJYJcIIbl7YUAbRSSToKb1njL87RQuBRZEEsnrD2VtXq9ZvFwmkCcJjnZMPyvKqGj3WNcb1Hi2VvysBpSsfQfA2vyeQM4XFZOzLQq/TAZCxL4szhcW09cLuWC1JfEoskiSRu68IS7XV4+cg5korefuKkSSpwS1EheARiHvGCKHP7wlk9YYdOGSZ0cOdG+Ss2bST1Rt3MP0mUQo3hrGVnoT+rTmVUUDa90cYPt2z3cXSvj+MzWIncWAbjFE6j8aIK2dBEOri91lYq2pvX40fM4LxV44AYLWYjdUkw27tgUotsWflMQ5vzm3w+MObcti7KhuVWmLYrT39EKEgCKHMaxXI8VN5VJvMmExmrFYbAFabjRqT2X1MfmExBw5nExFuZOSQ/gBEhBvJPJzNVz/8fN4m70aDHq3GGZ5Wq8Fg0BNm0JPUMd5bIQe9uM5RDL8jhW2f72f9fzIozC5j0ORu6MPPv51lrrSS9v1h9q7KBhmGT08hNqnhmW9itpAgCPXx6i2sOW8u4HD2qQaPGzNyKDqd1v16+S+beGvB1/WO6da5I688N8srcYaSPn9MAgl2fJnJ3hXZHFhzkg594oiKDwOgPK+a3H1F2Cx2VGqJEXem0Pta7zRTbElkSz628s3IltOA5OxGHD1a7OkutGheSyBJHeP5ZO7zvPbe5/z3l02As434qGH9Meidq50jI5xfajeOH+Med8ukcWg1agAqKqsBMJnNbEn93d2W/LprRvPMI3dh0Ht2z76l6TM+ifa9Ytj1bRanMgo5kXYG0s7+uSRJJA5sw7Bbe3pUeQhn2SszMB9/wdnPC8cFf6pCEzO2tkVLfwWiaxp/7RkjhD6vViAGvY7ZT8xgSP8UXp33GTUmMzl5Bbzy3Cy6JCXUOaZ3j2R690h2//pEzmmeffldZFlGp9Py1EPTmTxhjDfDDElxSVGMf2YoNeUW8vYXUV3svHUYFqsnvnecxw/MhbMsue9jyv47yHYklRH1BU0i7aXrsZWswVa6HkPyi7WNJQOXv/eMEUKfT2ZhTRo3it49knn25Xc5ejyHe5+cw3OP3sv4MSPqHbd+625emLuAyqoaOiW055XnZtE9OdEXIYYsY5SOLiPEc6LmsuS+j+nYs4CELmEW+o5PX7Tromwrw3zyNSy572E6+ixAwCYRpfaMEUKbz6bxJid24JM3Z/Pyvz9h1frt/OO1/5C+P4snH7zd/XDcxWqz8eYHC1myfC3gnKH13KP3NqlTryA0l70yw1l5IGHsMR9tm7qb2UmaaOfeJhH9qcl6GNOxf6COGoU6vJ9/A26AknvGCKHNp9N4w4wGXnzmz8y85xYAflqzGdlxce8N2SHz05rNAMy85xZefObPInkIijEfnwOyHV3CzEsmj3Np29yKrsOfQbY5xwaQC/eMGX5HrzoXnbr2jBnz5wHOSRlfZVJ0vFyBiIVg4pd1IFERzlJ5+KC+7tlX59LptAwf1Pe8YwVBCbIlH1vpOiSVEX3Hpz0ep098BlQGbCVrka1nfBhh47j3jJno+Z4xfSd0xmGX2fVtlh8iFIKZXxLIxh3OKUF/GDEIgIqqav7nX+/z/176N6XlFQDulembdqbV/SaC4Ae28s2AA3WrMRc986iPpGmFJvpKwIGtbIvP4muM5uwZo9Gp3XvGCMKl+LyVSY3JzK6MTFS1U3q37d7DnLkfUljsXKT2e+ZhZj8xgysuG4BKkkhNz6TGZMZoEFMKXUTfIf+Rzc4V/Spjt0aPVRm7QckqZHOOt8NqkubuGXMyrYC8zGIxKUO4JJ9XIDvT92G2WOianMiChUt5bPYbFBaXMqhvTwb17UlhcSmPzX6DBQuX0jU5EbPFws70fb4OSxAuoRl98t1t8gOjT35z94wBWuyeMYJnfF6BbNqRDsChoyc4dPQEOq2Gh++8mTtudjZP/Oq7lbz/xXfuGViuMVeOGOzr0AKe2GvB/yS98zmBo+Zwo8c6ao4430PX8LMGvxB7xgg+5tME4pBldwIBZzuSOU8/fN7ajjunTGTEkH7M/tf77jYom3ak45BlVAFyJSe0HJqoUYAKe+kGZFuZx89BZFsJtrINgApN9BU+jdFTYs+Yuim1x3ig7y7YFD69hbXv4FGKS8tQSRLTb5rAZ2+/UOfCwO7JiXz29gtMv2kCKkmiuLSMfQeP+jI0QaiTpGuHJmYssqMG88nXPB5nPvkqOExoYq4OmD3gL9wzxlOhvGeMUslD6c/2FZ9WIBu3/0b7NnE8/9cHGNo/pd5jdVoNj824jatGDeH51z9g0440+vXyfOaIIHiLPmk2ttL1WHLfQx3RH22bW+s93nrmGyy580HSoE+a7acoG+bPPWOCTVOqgeoa5/OgpqxRC8XkAT5OIFER4Xz93ktEhBs9HtM/pTtfvDOHH1au82FkyhNldOBSh/fHkPwipqPPUpP1MPbKDPSJzyBpzt9YS7aVYD75qjN5IDtXpYf3VSboSxh2aw9y9xayZ+Ux4jpH0e2K+p/PiD1jLm3d1t1IEkwcO0rpUAKGTxPInVMmNmlcRLixyWODgdJltEgiDXP2tJIwHfs7ltz3sJz+GM0FzRRtpevBYQJJgyH5ZXTxDyoac118vWdMYwXzhdOq9duQJKlJCSRUzzm/b2krnOXvH6pQLaN9RRf/EOqokZiPz8FWshZb8c8XHKFCE3NtbTv3wKo8zhUoe8YE84VTaXkFqRn73a9bRYltEUAkEEGolzq8H2G9FyNbC7CVbUa25AEg6eLRRF8RMA/MGxJIe8YE44XTmk2p2Gx2ANZuTuXmiWObFEOoVSJeSSDDJt7tjbcRhIAladugbT1Z6TCaRewZ03SrN2x3v161fnujE0ioEhWIILQwYs+YxjlTWEzGviz0OmeCzdiXxZnCYtq2jlU4MuU1K4GkrvjMW3EIHso5XQBAQvvguHUiCMFu9YYdOGTZ3fB1zaadrN64g+k3iU4RfunGK3jPx98s4+NvlikdhiD4Vc7pAvfFk7+tqr19NX7MCMZf6dxVdfX67fUNaTHELawgknO6gBW/OluF33fb9aIKEVoM10XT/zx+v9fe8/ipPKpNZkwmM1arDXDujlpjOtvCPr+wmAOHs4kINzJySH/Aucwg83A2X/3wM+3OuY1lNOjdu61qtRoMBj1hBj1JHUP3dqFIIEHk42+WuWeCfPzNMq+eTC1R+ZZWDR8kKM6XF05z3lzg7sFXnzEjh7o3wxszcijLf9nEWwu+rndMt84deeW5WV6JM1CJBBIkXCeRRqMGYMWvW0QVIriF8p4xvrpwSuoYzydzn+e19z7nv79sApzTmUcN649B79yPKDLCuVbmxvFj3ONumTQObe15WFFZDYDJbGZL6u/IsrOL8XXXjOaZR+7CoA/tmW0igQQJ10l0/bV/AGDZ6o2iCmmiqFGlSocgeMjXF04GvY7ZT8xgSP8UXp33GTUmMzl5Bbzy3Cy6JCXUOaZ3j2R690h2//pEzmmeffldZFlGp9Py1EPTmTxhjFfiC3QigQQB10mkUqm4Z+qfUKlUrPh1C8vXbOaeqX8isUM7pUMUFBLqe8b468Jp0rhR9O6RzLMvv8vR4znc++Qcnnv0XsaPGVHvuPVbd/PC3AVUVtXQKaE9rzw3q86O46FKzMIKAq6T6E9XX0Fih3YktG/DxLGjcDgcfLpoudLhCYJPXHjhdN9t16PRqFm+ZjMnc/O9/nnJiR345M3ZjB8zguoaE/947T+8+t7nWG22i4612my8+t7nPP3iO1RW1TB+zAi+eKfu7SpCWcBWIMPmN35HOG9Kfajxe2L7woUnkct9t10vqhAhpJ1bfbh+vieOHcWy1Rv5dNFyn9y+DTMaePGZP9OtcyLzPl3MT2s288SMaRcdJztkflqzGYCZ99xy3rnZkogKJMBdWH24iCpECGX1XTj5sgpxiYpw7iM/fFBf9+yrc+l0WoYP6nvesS1RwFYgLv6uBJSufM51qZPIRVQhQqiqq/qAsxdOvqxCADbucHaa/MOIQQBUVFXz2nufY7FY+duj99AqKpLRwweyfttuNu1M46aJV/kkjkAX8AmkJbvUSeTir5NJCBxKT9f1x0N7pS+cakxmdmVkoqqd0rtt9x7mzP2QwmLn7L3fMw8z+4kZXHHZAFSSRGp6JjUmM0aD3qtxBANxCytANXQSufirpBcEf7nUbVsXX9++3Zm+D7PFQtfkRBYsXMpjs9+gsLiUQX17MqhvTwqLS3ls9hssWLiUrsmJmC0Wdqbv83ocwUBUIAGqoerDRVQhLZO/p+/6q/JpzIWTr6qQTTvSATh09ASHjp5Ap9Xw8J03c8fNzv/nX323kve/+I4ly9eeN+bKEYO9FkOwCMkKJKfcSk65VekwmszTk8hFVCFCMFi0aFGDGyo1VH24+KoKcciyO4GAsx3Jp2/9kzunTEQlSagkiTunTOTTt/5Jt84d3cdt2pGOo3YVeksSkgnk47QSPk4rUTqMJvP0JHIRM7KEUBAIF077Dh6luLQMlSQx/aYJfPZ23Ws7uicn8tnbLzD9pgmoJIni0jL2HTzqlRiCScjdwsopt7IiqwKA+wbFkBB18RS8QHZu4zitRsNni3/yaJyrC6jokSUEqoa2dfX0tq2LL27fbtz+G+3bxPH8Xx9gaP+Ueo/VaTU8NuM2rho1hOdf/4BNO9Lo16trs2MIJiGXQD5OK8HmkN2v/+fKtgpH1DjnNo77bsWvjR5vs9lFjywh6ATKhVNURDhfv/cSEeFGj8f0T+nOF+/M4YeV65r12cEopBKIq/rQqCQAVmRVBFUVYrPZaRPbirtvmdSs99Go1dhsdncDOqFlqyk1k5tZTHWJCQkJY4yeDr1jMUYHzrTTQLlwunPKxCaNiwg3NnlsMAupBOKqPq7vFQXAsgPlQVWFaDRqHr7rZqXDEEJE4bFyUr89SO6eInebcRdJkkjo35pht/YgrnOUQhE6iQun4BUyCcRVfagkuGdgDCrJWYEsP1jOPQNjSIwOjipEELxh78/Z7PjyALJDRqNXk9A3jqh2zpYb5flV5Owt4lRGAbl7Cxl+Rwp9/pikWKziwil4hUwCObf6cCWLiT0iWXagnE/Tg6cKEYTm2vtzNts/zwQJ+k1KZtDkrujCzr+AslRbSfv+CHtWHmPb5/sBFE0i/uZ6oC80T0hM472w+nC5b1AMGpXE8oPlnCwL3nUhguCpwmPl7PjyAEgw5pEBDL+j10XJA0AXpmX49F6M+fMAkGDHV5kUHS9XIGL/amgdSqh+tq+ERAVSV/UBkBClFVWI0KLs+vYgskOm36Rkuo3q0ODx3a7oQGF2GXtXZLPr2yzGPzPUD1EqKxS/yJUS9AnkUtWHy32DYgL2WYivymjXCSLK9JalptRMzp4iNHo1gyZ7vh5h0ORuHFhzklMZhdSUmQNqdpYQ2II+gVyq+nAJxCpk0aJFin25i6uv0JWbWYwsyyT0javzttWl6MO1xPeJ5WRaAXmZxXQZEe/DKMWFTSgJ6gTSUPXh4o8q5PR1oxt1/Dte/vz2/9100e+JZNGyVBeZAIiKb/wGR63iIziZVkBV7Xv4grhwCj1BnUAaqj5cArEKEQSvk2r/24SefrJrkFT/cc0lvshDS9AmEE+rDxd/PQupqxLwpcZWPkLoCo81AFCWV9Xosa4xrvcQBE8E7TReV/Xxp571Vx8urirEIcOn6cHbqVcQLiU+JRZJksjdV4Sl2vNp6+ZKK3n7ipEkifjecT6MUAg1QVmBnNtxV6uS+MzDhKAN0h5ZgS5h7UeKfn7OONE4EsDYSk9C/9acyigg7fsjDJ/ey6Nxad8fxmaxkziwDcYonY+jFEJJUCaQczvufre/rNHjbQ45qHpkCYKnht3ag9y9hexZeYy4zlF0u6L+tSCHN+Wwd1U2KrXEsFt7+ilKIVQEXQKxOWTahGm424PnHvXRqCRsDtnduVdoPn9XAkpXPoEornMUw+9IYdvn+1n/nwwKs8sYNLkb+vDzq21zpZW07w+zd1U2yDB8egqxSZHKBC0EraBLIBqVxMPDYpUOwyscJcVY9qRhLy4ESUIdE4eu/yBUrULj7ycoo88fk5ztSb7MZO+KbA6sOUmHPnFExYcBUJ5XTe6+ImwWOyq1xIg7U+h9bcvpgyV4T9AlkFBgPZJF5WfzMafvAtlx/h9KKvSDhxFx10Nou3RXJkAh6PUZn0T7XjHs1lnKjgAAFqpJREFU+jaLUxmFnEg7A2ln/1ySJBIHtmHYrT1F5SE0mUggfla9bDHlH70LDgeS3oBu4FA08QkA2PJysKTvwrx7B+b0XUTdP4uw66YoHLEQrOKSohj/zFBqyi3k7S+iutgMQFisnvjeceKBudBsIoH4UfWyxZQveAckifDJtxF+692owiPOO8ZRVUnVN59StXQR5R+8DRDSSeR4jXM2XZJRXAX7ijFK5/P2JELLFLTrQIKN9UiWs/KQJKKf/AeR9828KHkAqMIjiLx/FtFP/AMkifKP3sV69JACEfvHO9npvJOdrnQYgiA0QcBXIMPmH1Y6BK+o/Hw+OByET74N45hrGzzeeNW12I4cpGrpIio//4CYf/7LD1H61/GaCpbkOf99/9J5oKhCQsSwiXcr+vmpKz5T9PNbElGB+IGjpBhz2i4kvYHwWz0/ucJvuwdJp8f8204cpcU+jFAZ72SnY5Md2GSHqEIEIQgFbAWS+lA3pUPwGsueNJAd6AYOrfO21aWoIiLRDRiMOXUblr3pGK4Y68Mo/ctVfWgk5zXMkrzDogoJMU2pBKprnN2Aw4yN78mldOXTEgVsAgkl9qIzAGg6JDZ6rCahE+bUbdgLzng7LEW5qo/bOvQA4JvcLN7JTueNFNEc0hMf3r5S6RB8Yt3W3UgSTBw7SulQBA+IW1h+0Zw+264226GzYt5VfagliVlJA/hL54FoJBWL8w5xrDr09+UWLm3V+m2sWr9d6TAED4kKxA/UrdsAYMs52eixttyT571HKDi3+kgOiwJgSnw3vsnN4t3jGS2uCmnURJErvb+4NFBuF5eWV5Casd/9ulWUuJ0Z6EQF4ge6voNAUmHJ2I2jqtLjcY6KciwZv4GkQtdvkA8j9J8Lqw8XUYUIazalYrPZsdnsrN2cqnQ4ggdEBeIHqphY9IOHYd69g6pvPiXy/lkejav85lNkixn90MtRRTeveWSgqKv6AOdCwpZchYD/K4FAmyK/esPZW1er1m/n5omhM2kkVIkKxE8i7noI1Gqqli6iZt3qBo+vWbeK6v8uAbWayLse9EOEvnep6sNFVCEt15nCYjL2ZaHX6dDrdGTsy+JMYehNXQ81IoH4ibZLd6LunwWyTNncF6n48N84KisuOs5RUU75gncom/sSyDJR9z+KJjkw7lE3l6v6uCW++3nVh4urCrHLMu8ez1AgQkEpqzfswCHLjB4+kNHDB+KQZVZv3KF0WEIDxC0sP3L2tJIo/+jfVC1dRPXKpegGDEHToSMAttxTWDJ2I1vMoFYTNeNRwv50s7JBe0lD1YfLXzoPZEneYRbnHWJW0oA6E40QelbV3r4aP2YEyLBm005Wr9/O9JsmKByZUB+RQPws7Lqb0fbpT+XnH2D+bSfm1K2Yzz1AUqEfejmRdz0YMpUHXPrZx4XEs5DQcvxUHtUmMyaTGavVBoDVZqPGdPanPr+wmAOHs4kINzJySH8AIsKNZB7O5qsffqZd67P74xgNerQa59eWVqvBYNATZtCT1FE0i1SCSCAK0HbpTsw//4WjrMS5oVRRIQDquNbo+g0KmQfmLp5WHy6iCmlYUbWd3bk1FFTbkIDWYRqGJhiJNaqVDu0ic95cwOHsUw0eN2bkUHQ6rfv18l828daCr+sd061zR1557uJJKVOnTm1asA1YtGhRve/v+vOWQiQQBamiY0KqPcmleFp9uIgq5NIOFJqZt6OInTnVOC5Yl6qSYHjHMGZeFkfP1nplArxAUsd4Ppn7PK+99zn//WUT4NzMatSw/hj0zhgjI5w7Jd44fox73C2TxqHVOJNhRWU1ACazmS2pvyPXLq697prRPPPIXRj05+9r4qvk4YmpU6e2qCQiEojgU+d23NVKKuYd/92jcVrRI+si3+wpZe62QhwyGDQSl3UMIzHKecV+stzKzlPVbDtZzc6cGh6/PI7b+rZSOGIng17H7CdmMKR/Cq/O+4wak5mcvAJeeW4WXZIS6hzTu0cyvXsku399Iuc0z778LrIso9Npeeqh6UyeMKbez/XlF3ld761k4lKKSCCCT7mqD4Avcg40eryrU29Lr0K+2VPKG1sLkYDp/Vtx35BYInXnT6KssDj4aHcxC38v5Y0tztuigZJEACaNG0XvHsk8+/K7HD2ew71PzuG5R+91Pjivx/qtu3lh7gIqq2rolNCeV56bRffkxveVE7xPJBDBZ2yyg3b6MGYm9W/W+2hUKmyyw925t6U5UGhm7jZn8pgzth1/7F53NRapU/H45a3p2VrP87/m89a2IgbHG+kRFxi3swCSEzvwyZuzefnfn7Bq/Xb+8dp/SN+fxZMP3u5+OO5itdl484OFLFm+FnDO0Hru0Xub1KlX8A2RQASf0UgqnukyROkwgt57O4twyM7K41LJ41wTukdyoNDMwt9Lmbfj/7d373FR1XkDxz/nzDAwXJWLiICoiEjqVt7NTNOt51FLa7OyNtNX1+3ltmZWu1tP7m6vtd0td1vbx+dZ89lW17Ky3NRVKNdI8ZJIeBdFAhW5OAIDw8AMMJfz/HFgAkFBYJgZ+b3/Gl5zfjPfP4b5zvec7/n+Klg1a0APRNlxgfoAfvvKcwwdFM/qdZ+yY9c+lj71SKvjFKfCjl37AFi86EEWPXRPT4cqtEMkkG526d7efapF6F4VFgeZRRYCtBJPjAlvf0GjJ0eHsznHxMEiC0arwyu7s0KDgwCYcOtIV/dVczqdHxNuHcnub7JdxwrepXeeExAEH5FdYsWpwPi4wFbXPK4l1F9m3IBAnAocLrG6McLOy8g8AsAdE9VBoeZaC6+//Vd+vuIvVFWrUxqmTLgFgL2Hjrg1lnKbmS+MR9hg2MMGwx6+MB6hwtZ6UoTQkqhAukn/f+31dAjCDehyrXrz3cCw1r/Q25PQx499hXCp8TW8ibWunm+PnUZubOn9JvsEb7zzf5QbqwA4fvo7li99itvH34wsSWQdPY21rh59QPdezzltKWJV8Q4yq8/ivGK/HhmJSaHJ/Cx2NsMD2+4W6+1EAhEEb9aVvciueAlvcujoKeobGkgaMpC1G7eyeUc6iqJw68hkAI6czGXJ8j/ywOzpJA6OJ6+gkENHTzF14uhui+HDyxmsLNqGU3ESIOuYGJpEvH8kABfryzlYncf+6jMcNJ/lpbi5PNpPnJ6+kkggQreJ/epvng7hhhMdpP6LXjDZrnttYZWtxWt4k72ZRwHIKygkr6AQnZ+Wnyx4gB8/oM6++nBzGn/dsNnVgdW0prsSyIeXM3jr4hYkJB6PnsYzMXcRotG3OMbssLKmdCcfGDL4w8XPAUQSuYK4BiIIXmx0jB5ZgqxiC+YGZ4fXVdc7yCqxIEsweoC+/QU9yKkorgQC6jiSdX/+NQvmzUKWJGRJYsG8Waz7868ZOijOddzezKM4lU6UYlc4bSliZdE2JCRWDH6UZXFzWiUPgBCNnpfi5rJi8KNISKws2kqupbjL738j8b6fJoLPKZ7xpKdDuGFFBGqYEBfINxct/C3byAuTIju0bm12JfV2hckDA72uA+tUbgHGKhOyJPHo/f/JcwvnofNr/VWUNDie9at+w/+u/4yNn3+BscrEqdwCRg1P7NL7v1ucilNx8nj0NGaHt99mPjt8DKctRWww7OHdklRWD326S+9/IxEViCB4ucXjI9DIEhuPV5GW135nUOpZM5+cqEIjSyweH9EDEV6fjIOH6R8Vwerf/ZwlT81vM3k00flpWfLUfNaufI24mH7szexaN1a5zczB6lwCZB3PxNzV4XXPxNyNv+zHAdMZ0Z3VjKhAeplxsxZ69P2zUtd79P19UXKkPy9MiuCP+8v5VbqBM+X1PDk6nFD/lr//qusdrM2u5JMTVSjA0kmRJHnRXehNQoOD+Oh/VhAc1PFTaz9ISWLDu2/wedrXXXrvb83f4URhYmhSm6etriZUo2d8SBJ7TTlk1+Rzd99buhTHjUIkEMFreGoYnS9MT50/sg8SEu98U87G41VszjExLjbQ1d5baLKRVWyh3q6gkSVenBTJQyPDPBx12xbMm9WpdcFB+k6vbWKwqW3CCf79rnvtoIAo9prgUkNVl2K4OfvFLq3vqmNj/tRtryUSSC/V05VAe5WPGMHdvodHhnFrTACrMys4WGRh34XaFs/LEkweqI5z98bKwxtIjU3NSmf6oq94DUEkEMHLdOaLvMahtqsGa67/ZjtfG8E9LMKfVbMGYLQ6OFxidd1o2C9Iy+gB3rmhlDeJ1qnTiS/UlV332vONa6J13VPZdaYSqHWoOzkGaa7/B4I7Kh+RQASf98XlCyDBvP43zhbA7QnXa/hhYrCnw7gmT19va8uY4ERkJDLNeZgd1g5fBzHZLRwy5yEjMTbEc5+z9KoTSMA9EWM9FkNzogtL8HlbDPlsvZTv6TAEHxDpF8Kk0GTqnA2sKd3Z4XVrSndS77QxOWw44VrPJe4042HSKt07F+x6iApE6LDiS2oJH9s/ysORfM9oq2OvscT1ONxP7BXhaZ7utGvvtOTPYmdz0HyWDwwZpATGtXsvyPaKb9l4eS8aSeb52NndGep1qbLXkmnOcz3uo/X8hGJRgQgd9v7H23j/422eDqOF7YZz2BUndsXJjsvnPR2O4AOGB8byUtxcFBReO7eRlUVbqXa0nlhsslt46+IW/uv8RygovBw3l2S95/ZW2Vl5DLviwK44+HflMY/F0ZyoQIQOKb5URmr6fgCemD/Ha6qQLYaC7x9fymdB7HAPRiP4ikf7TUEC3i7aygbDHjaVHWBCSBIJAern+kJdGZnmPOqdNjSSzMtx9/NIv9s9GnOa8XCzx0d4MOo2D0ajEglE6JD3P96G3e5wPX79Bc+PLymtryXLZCBAVjuPDpkMlNbXEuPv+dK+M8at+c7TIfQqj/SbwujgIbxbksoB0xkyTDlg+v55GYkpYSk8Hzvbo5UHgKGhiqM15/CX1U7DIzUFGBqqXF1lniISiNCupupDq1W/qFPT93tFFbLVUIBTUbir30AUBbZfPsc2QwHPDhzl0bgE35EcGMvqoU9jtNfwrfk7DA1qBonWhTE2ZKhHL5g390XlEZwoTA0bASjsrDzGl5VHeTx6mkfjEglEaFdT9THn7jsA2LYzwyuqkC2NnVf3RSeioCaQLZd8L4FkPdt72o+9Vbg22KvHk6QZ1c6rmeHq7o07K4+RZjwsEojg3ZqqD1mWWfTQPciyTGr6frbv2seih+4hfkB0t79nvsVErcOGxWHH5lRHmNsUBxaHetOcoqinr06YKwjR6rgzQh35HaLVcdxcznuFJ4nxD0JqvGE4UKPFT1KrJz9ZJlCjJUjjR2Kgd476EHqP83WXsTgbsDrrsTnVU8Q2xYHV2dB4hIKhwcRpSxHBmgAmh6YAEKwJIKdxQrB6Y6P6YdfLumafdQ162Z9AWceggOsf3dIRIoEI19S8+mhKFrOmT2bbzgzWbdrutipkaU4GZ2oq2z1uZlQC/o3XQGZGJbCpNI/f5GVec83w4L68N2pGt8QpCF21/PxH5FlL2z1uRp9R+Mta1+OtFVmsLNp6zTVJ+hhWDnHfDZ0igQhXdWX10eSJ+XPcWoUkBoaxfewcXsv9hk9KzwLq76vpkfHoZS2SBGFadZTDIwOGudYtjEtB15hMTPZ6FAWsTjvp5Rddk48ejhnGiuRJ6DXioy943qCAfnwwfAlvFv6TrRWHAHXW1u1hKehlP0AitPFu+R9FTnCtezhqMn6S+hlWW5AVrE4b+0ynXXO+5kaM59WBPyJA1rktfvFfJFxVW9UHqDcSursK0Wu0/OmmKdzWN4Zf5u7H4rBTaDWzZtR0koP6trnmltAobgn9/sJ+gcXEMyfSUQB/WcMbwybymGjzFbxMgKzjjUHzGRcylBWFn2F1NlBcX8HKIQtJ1Pdvc82IoIGMCBro+vtCXRkvFaxHQcFf1vJK/P3Mi5zk9thFAhHadLXqo4m7q5Am82KGcnNoJM+eSCe3tpJ7s/7FWymTuS/62rvSpZVdYGlOBmZ7A0MCw3hv1HRSgsPdEqPgnXxtUOa9EWMZERTPSwXrybde4rEzq1ie8CAzw6+9D3x61QleP/8RNY46EgKiWDlkIcN6qO1Y3IkutKmp+rjnh7e3mRyaqhCn08m6TdvdGktSUB+2jbuX+6ITqXXYWHxyN6/mHnBdYG/O5nTyau4Bnjq+C7O9gfuiE0kbP1ckj17Ek6P5u/reQwKi2ZC8hJnho7E46/nFuQ94s3AzNsXR6lib4uDNws0szf87NY46ZoaP5qPhL/ZY8gBRgQhtaK/6aNJTVQioo9pXj5xGSnBffpf/LZ+W5vGrpAmtjnOi8GmpOi/ol4lj+emgm90Wk+C9fGF/l6sJ0vjz+8GPMUwfw6riHWyryGJZ3Fyu3IbEqShsq8gCYEnsbJ7o3/ONIaICEVppr/po0pNVSJMwP/Xi+R3hsa7uq+b8ZQ13hMe2OFYQfFGoJhCASaHJru6r5vxlLZNCk1sc29NEAhFa6Gj10eSJ+XPQajVs37WPiyUGt8e3s6wQgLuj1AuI1fYGnj+1m2dOfIXRVgfAXZHqc/8uL3R7PILgLrtNJwGY2mcEAGaHlVfPfciygnVU2dXdKKeG3dR47CmPxCgSiNBCR6uPJj1ZhVgcdg5UliBLEtMj4vm6ooipBzfzz0v57Lh8nhmZn/N1RREzIuORJYn9xhLXzYeC4EuszgYOmb9T53GFprC/+gz3nfoDO4zZ7Ko8zgM5b7O/+gxTwm5CRuKQOa/ZzYc9R1wDEVyaT9z102pZ/+mODq3z06ofI3fPyNprLKbO6eCm4HDeOXeEfxSdRgEm9lFbHQ9WXWLB0S95PC6F4UF9yakxstdYzH9EJbglHkFwl4PVZ6l32kjWD2BN6U42lR1AQWFMsNp9mF2Tz+K8tTwUdRtJ+hhyrSUcrD7LnX1G9micIoEILs0n7m5OTb/u9Xa7w60zsppOSeXUGMmpMaKTNbwyZAzPDlT/adYUnuStgmzWF51usUYkEMHX7Gk8JZVrLSHXWoJO0rI4dqZr9tU/DLtZXZzGJ2X7W6wRCUTwCLvdQVR4HxY+2LUd17QaDXa7wzW5t7s4FYVd5Rddfw8P7st/j5jWoj33uYRRTIuI5aendrvGoOwqv4hTUZAlqdVrCoI3cqKoo+UbJeljeHPwj1u05y6KvpPbQpN59dyHrjEoGaYcnCjIV7ZruZFIIAIAWq2Gnzz+gKfDuKqj1WWUNViRJYmn40fyi8QxrrElzaUEh5M2bi6/z89m7cWTlDVYOVpdxugw9wyTE4TudrK2kAqbGRmJx6Kn8nzsLHRS66/qYfoBbExZyl+KU/nAsIcKm5mTtYX8IKjnKm5xEV3wCTvLC4kNCOaTW2eyPGl8m8mjiU7WsDxpPJ+PmU2CPlR0Ywk+ZXfVSWJ0fXlv2HMsi5vTZvJoopO0LIubw9+TnyfeP4I9VT3bjSUSiOATwrT+fDXhfm7rG9PhNWPDovly/FxCteJ+EMF3hGoD+eymlxkX0vF9Ym4JHsTHKcsI0erdGFlr4hSW4BOeS+jcJlEhWl2n1wqCJyyKvrNT64I1AZ1e21miAhEEQRA6RVQgvdS4We7bZEYQhN5BJBDBq7hzBHfTgD1fG/Mt3Jhuzn7R0yF0mUggvUxW6npPh9CmTZs2eeyL3ZcntwqCJ0mKoijtHyYIgiAILYmL6IIgCEKniAQiCIIgdIpIIIIgCEKniAQiCIIgdIpIIIIgCEKn/D9AEPESx7+WAwAAAABJRU5ErkJggg==</v>
+      </c>
+      <c r="E724" t="str">
+        <v>18-09-2026 03:18:00 pm</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="str">
+        <v>6aad08dc052542ee778a5dcb</v>
+      </c>
+      <c r="B725" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C725" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D725" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E725" t="str">
+        <v>18-09-2026 03:18:12 pm</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="str">
+        <v>6aad08dd052542ee778a5dd3</v>
+      </c>
+      <c r="B726" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C726" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D726" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E726" t="str">
+        <v>18-09-2026 03:18:13 pm</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="str">
+        <v>6aad08e4052542ee778a5edb</v>
+      </c>
+      <c r="B727" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C727" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D727" t="str">
+        <v>Started Playing game and Debited "10" and Balance "230"</v>
+      </c>
+      <c r="E727" t="str">
+        <v>18-09-2026 03:18:20 pm</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="str">
+        <v>6aad08f9052542ee778a5f2e</v>
+      </c>
+      <c r="B728" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C728" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D728" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aad08f8052542ee778a5f1e , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E728" t="str">
+        <v>18-09-2026 03:18:41 pm</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="str">
+        <v>6aad08f4052542ee778a5f08</v>
+      </c>
+      <c r="B729" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C729" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D729" t="str">
+        <v>Answerd Correctly to Qst ID : 6aad08e5052542ee778a5ee7, Reward : 10, Qst No : 2 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E729" t="str">
+        <v>18-09-2026 03:18:36 pm</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="str">
+        <v>6aad08f9052542ee778a5f30</v>
+      </c>
+      <c r="B730" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C730" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D730" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aad08f8052542ee778a5f1e , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E730" t="str">
+        <v>18-09-2026 03:18:41 pm</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="str">
+        <v>6aad0909052542ee778a5f69</v>
+      </c>
+      <c r="B731" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C731" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D731" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6aad0908052542ee778a5f59 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E731" t="str">
+        <v>18-09-2026 03:18:57 pm</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="str">
+        <v>6aad0904052542ee778a5f43</v>
+      </c>
+      <c r="B732" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C732" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D732" t="str">
+        <v>Answerd Correctly to Qst ID : 6aad08f8052542ee778a5f1e, Reward : 40, Qst No : 3 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E732" t="str">
+        <v>18-09-2026 03:18:52 pm</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="str">
+        <v>6aad0909052542ee778a5f6b</v>
+      </c>
+      <c r="B733" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C733" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D733" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6aad0908052542ee778a5f59 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E733" t="str">
+        <v>18-09-2026 03:18:57 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E659"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E733"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E733"/>
+  <dimension ref="A1:E757"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -12860,9 +12860,417 @@
         <v>18-09-2026 03:18:57 pm</v>
       </c>
     </row>
+    <row r="734">
+      <c r="A734" t="str">
+        <v>6aad090d052542ee778a5f7b</v>
+      </c>
+      <c r="B734" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C734" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D734" t="str">
+        <v>Answered incorrectly for Qst ID: 6aad0908052542ee778a5f59, Qst: How many broken boxes are there?, Submitted Answer: 11, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nOzdd2AUZf748ffM9mx6aDG00DsEQRAVsQuWEwvinYqnWM7und55eurX+vNsnHd4FtQDT1GxgYciGgRBOgiRDqETShppm+0zvz8muxAIqbs7u5vn9ddudp6dTyC7n/nMPM9nJFVVVQRBEAShiWS9AxAEQRBik0gggiAIQrMY9Q5AiE0VS1N13X/yWWW67l8QBFGBCIIgCM0kKhChRZpTCaj+KgAkQ2KTx+pd+QiCcIyoQISI85XMxVcyV+8wBEFoIZFAhIjzFn+Ot/gLvcMQBKGFxCksIaJUbwm+sp+CjyVThs4RCYLQXKICESLKWzIbVC+oXrwlc/QORxCEFhAJRIgob9HndT4WBCH2iAQiRIziOYi/YiXIVpCt+CtWoHgO6h2WIAjNJBKIEDG+oi8ABVP6WEzplwIKvqIv9Q5LEIRmEglEiBhvsXbKytTmWkxtrq31M0EQYo+YhSW0mOLcgep3gFKNqni0H6oeVH91zRYqqucg/qo8JEMyxrQLAJAMyfir1uM5+AaS+TRAqvl5Akhm7bFsBjkByWBHtvWM8G8mCEJ9TplAJkyYEMk4gmbNmqXLfoWWce64G6V6c4PbGTMu166B1Dz2Fs7EtfvxesfICf1I6DMjJHEKghA6dSYQvZJHYN/RnkTe/e08Xfc/eeZYXfd/ItnWE/vgBbh2Poy38KOan0oY0y5GMtgACcmYAoCp/c3BcebMyVqFAai+ckBF9TvxHf0e0G5TY2r3O6zdX0GSbZH7hQRBaJR6T2FF+otcz8QltIwk27D1fANjyjm4dv0R1V+N4tpDQp8ZyAl96hxjSByKIXFo8LnizMe5bRKggmzFmv0i5g63ROYXEAShycQ1kBaIdCWgd+XTGKZ2EzEk5VC9dRJK9VYcv16AtfvrmNpeW+84X8lcnDvuRvVXINt6YOs9A4O9f4SiFgShOUQCEUJOtvXGPigX184H8RZ9jnP7ZPyVK7BmvxC8OB6kenDtfgzPoXcBMLW9Fmv3fzSrU68gRKNwnFkJnB2q770jcQZJJBAhLCRDIrZe7yIn9Me992m8hTOxdn0uMNHqGFXBWzgTAEuXp7B0fCjywYaRmIzSusX79WSRQISwkoza/TsMqecFZ1/VIlsxpJ6Hr+Sb4LbxIt6/PITGC9f/xaneN1J/eyFLIMrRUjwb1uEvLQZJwpCWgXlQDnJqeqh2IcQgX6l23caUPg7QZlu5dj0Cigtr9ylIpgxMaWPxlXyDr/Q7zB1+r2e4YSEmowjxqsUJxLtzO1Uz3sa9fg2oSu0XJRnL0OEk3nwnpm6texGYs8zNwS2lVB91ISFhS7NwWr90bCkWvUMLG9Vfja98MSBjTLsI39FcnPn3onoOA+CrXIWtx1SM6RcDMr7yn1D91dpCQkEQol6LEkj1159R8d5UUBQkixXzkGEYM7MA8B0qwLN+De61K3GvX0PybfeScEX9M3HiUfHuClZ/uo2DG0pQVbXWa5IkkTWoDcOv70VG12SdIgwff/kiUFwY7ANw738Jz6H3ABVD8ijt9YplVG++DnPmbRjs/fA7NuIvX4SxploRBCG6NTuBVH/9GRXT/gmShH38ROzXT0K21545oziqcHwyHcecWVS88zpAq0oiG7/bw8oPt6IqKkaLgawBGSS3twNQccRBwcYSDuQVcXBjMSN+15f+l3bROeLQ8tacvvI7NuJ3bATZgrXz45iz7gXAUzAV177ngzOwAmNEAhEEqCzUWgEltYveirxZCcS7c7tWeUgSKX/8G7YxF9e5nWxPJOm2ezF260X5lOeoeG8qpv6DW8XprI3f7WHFB1tAgoGXZZMzvjvmBFOtbTzVXtZ9uZMN83az/AOtDUj8JBEFX+n84DM5oR+2XtNqre0wZ92PIfUCnNtvD7ZB0cYotPY+n7Hw5SGE17rZOwEYfcdAnSM5tWYlkKoP3gZFwT5+4imTx/Fs512Mb+c2HHNmUfXBO6T938vN2S2HrzinWeNCpcP/ljRqu+LdFaz8cCtIMObuwfQ467Q6tzMnmBhxYx8yuiaz6M08Vn60hQ5908joEvuns/yVa1G9hYCMOeturJ2fAPnk6z0Ge38SBy/Ete9ZPAX/RvUW4q9ciyFpeOSDjiKx8OUhhE9lYTX5SwoAyLmqe9QeSDT5ME85Wop73RokixX79ZMaPc4+8RYkswX3L6tQykqbutuYsubTbaiKysBx2adMHsfrcfZpDBjbFcWvsubT7RGIMPx8pfOQLR1JGDBHW/9RR/IIki1Yuz6HfdA8ZGs2vtLvIhdoFAp8eeQvKQhWIkLrsm72ThS/iuJXgwcT0ajJFYhnwzpQFcxDhp10zaM+cmIS5sFDca9ejmfjeqxnn9/UXQc1thI4nurUPoiSremZvCmVj7PMTcGGEowWAznjuzd6XM74HmzN3c+BvGKc5e6Yn50lGVOx5yxDMjS+mjIkjcA+5Ce8h6eHL7AYEPjyCDwWVUjrEjiAkA3aqtv8JQVRW4U0uQLxlxQCYDytU5N3ZszqrL1HUWGTx7aUa/liXCuannia6uCWUlRVJWtAxknXPOpjsZvI7J+Oqqoc2hL7FZo56/4mJY8AyZCMOev+MEQUG47/8pANkqhCWqHAAUSPc7LocU5WVFchzbhSGehFoda7VZ0C01ilE/tZhJ9rcS6un3LDvp/qEhcAyZn2Jo9NzdQqOkfNewitTyx9eQihFziAkGSJwVd2I+eq7sgGiR2LCyg/7NA7vJM0OYEY2rQFwFewv8k78x3cX+s9IkWpKMedtxZ33hqUivLw7qwl+TUwKPL5VYgCsfblIYRe4ACi5+gsUjrYSWqXQI9zslAVlbyvd+kd3kmafA3EPCAHJBlP3loUR1Wjr4MolRV48n4BScY8MKfJgbaE6+eF4PNpj5cuJGHsVWHblz1d6/dUfqjpH/jAmMB7xIKKpfHVv0pPgS+PXmM6ktJBq2B7nJPF9kUHyPt6l7gWEudOPIAIyLmqO/lLCtixuIDBV3YL/m1EgyZXIHJaOpahw1HdLhyfTG/0uKpPpqN63FhOH4GcktbU3baIa3FunY/DIbNvOpIkcXBTCZ5qb6PHuau8HNpUiiRJZPbLCGOEQjSq78tDVCGtw4nVR0A0VyHNWgeSePOduNevwTFnFsZuvbCdV/9aEOfC+VT/73MwGEi6+Y5mBdpc/uIiPJs3IJm1WU2eTRvwFxeF7TSaLdVC1qA2HMgrYt2XOxlxY9134zvRui/z8Xn8dBrSFluyueEBOks+q0zvEOJKXdUHHPvyEFVIfDvVAURAtFYhzVrua+rWk+Tb7gVVpXzKc1S++y+UqsqTtlMqK6iY9k/KpzwPqkrybfdhzO7R4qCbwrUkF1QFyxlnYTljFKgKriULwrrP4df3QjZIbJi3m/yfDza4ff6SAjbO34NskBh+fe+wxiZEn8Z8eYgqJL6dqvoIiNYqpNm9sLSeVhIV7/0Lx5xZVM+bg3nw6RhP6wiA7+ABPHlrUT1uMBhInnwfCZdfE6q4Gy0w88p67oWgqrh+XohrcS728RPDts+MrsmM+F1fln+wmUVv5lG8p5yc8T2w2GtP63VXeVn3ZT4b5+8BFUbc2Jf0Lklhi0uITqeqPgJEFRLfGjqACIjGKqRF3XgTrrgGU/9BVH3wDu5fVuFevQz38RtIMpZhZ5J08x0hrzx8BftQnU5Ulwt82rUG1efVnmvP8BcX4d25HcluxzJ0hBaS3Y43fxuO2Z/WnMbSpjxJViuSseYL3mjSnttswbUrTdX/0i4gwcoPt7Dx2z1szd3Paf0zSM7UFgNVHKrm4KYSfB4/skFi5E196XdxvPTBEhorlr88hNBo6AAiIBoPJFp8PxBTt56k/d/LKOVHtRtKlRQDYMhog3lgTlgvmJe//gK+PQ2Xc9aRo5HM5uBj54J5VL43td4xxq7dSH302RbF1/+SLnTok8aaT7dzIK+YfesKYd2x1yVJotOQtgy/vreoPFqpWP7yEFqusQcQAdF2IBGyOxLKKWktak/SVMaszmS88jYVb03Bmfut9kNJwjJsJJLFCkjIidoUY9vFlwfHJVw2HsmkVRpKVRWgorpduNesCC50tF04juS7Hqp5n5bJ6JLMJX8ehrPCw6HNJVSXajVaQrqFzH4ZMXHBXAiPWP/yEFqusQcQAdF2IBHT90SXLFZSHvgr5oE5VLz5KqrLhf/wQVIffRZj5+w6x5h69sXUs2/wua9gP2UvPgGqimQ2k3T7AyRcemXIY7Ulm+k2MjPk7yvErlj/8hBa5viOuwajTN7/Gndx3GDU5j5FQ4+smE4gAbbzL8XUsy9lLz6Bb99uSv50Jyn3/Rnr6AvrHedavpjy119AdTgwZnXSEk/XxjdAFITmiocvD6Fljm+auSV3X5PHB9rc6HkgERcJBMDYqQsZr7xF+dSXcS3Opezlp0nY9CtJt9937OJ4DdXnpXLav6j+9isArKMvJOXeR5rVqVcQmiMevjyE5lP8KvY0C4OvaPjUZX1ko4TiV4OdeyMtbhIIaK3aUx95Ckd2dypnvI3zx3kk3XbvyRsqKs4ftdutJk26E/u1N0Y4UqE1i5cvD6H5ZIPE6df10juMFqs3gUyYMCGsO581a1ZY9iMlajOaLEOGB2df1XrdbMYyZDiuFUuC2wpCpMTLl0e4xMqdR4VTJJBZs2aFPXmcSiCptIR75VIALCPOBkBxVFH51hRUj5vkex5BTk7BcsZZuFYswb1qKQmX/qZZ+3n3t/NaHKsgCEKsOmUFEoov8sYK5b5UlwvPr7/ULGIciXvtSsr/+f9QSksA8GzdSMr9f8Uy/MyarsK/oLpcSNbY6YArCK1BpCsBvSufWBRX10AAPHlrUD1ujNk9qPp4OtXzZoOqYh4wWHt9Yx5Hn36EhLFXYezaDd/ufDx5a4LVSmNMnjk2XOELgiDEjLhLIK6a01e+3fn4ducjmUwk3ng79vHXA+D46lOqPpwWnIEVGNOUBNLa6H3PD9H5V4h1el0SCLf4SiCqgnv1suBTY9dupP7pyVprO+xX34Bl6BmUvfpMsA2Ke/UyUBWQmtWcuMli+fpStBj+dr6u+199Z+N7uzXn/ztcE0yElmvKqa5/hmH/99satyA5Ep/3uEog3u1bUMpKQZKxXzWBxJvuCLYtOZ6xa3cyXnuXqv++g2P2LJSyUrzbt2Dq3T/sMer5hTBhwoQW/VFFuhLQu/JpquHjJp3wExvZic4WvVd24274eZJ4OlgQaoum/9u4SiCulUsxtG1PyoOPYR40tN5tJZOJpFvvwXrmuZRNeQ7XqqURSSABzfkjUP1VAEiGpn+rxOuRbFMqgYBqrwJAgqnpFWdTK5/dVbYm76O541d/O6NF+4plytFSrZlraTFIEoa0DMyDcpBT08O2z+Zc5Fed1QDNWrQcjRf54yqByIlJtPnXDCR745vMmfoOoM2U96ie/3UYIwsNX8lcAEztwncvk9Zg4W4HEjCuV3jWADXni7zaqd2GIMHW9NmAJ1c+rYd353aqZryNe/0a7TT08SQZy9DhJN58J6ZuPfUJ8ASu5YtBkrCdd4neoYREXCUQ+9U3NGucZLc3e2wkeYs/BySRQFpofn5lWBNIcyxcthZJgnHnn6V3KDGj+uvPqHhvKigKksWKecgwjJlZAPgOFeBZvwb32pW4168h+bZ7a26Cpy/X4lxAJBAhwlRvCb6yn4KPJVOGzhE1juLaA4Bs7aprHAFlLj+rC5zBx6lWg84RaeYvWo4kSSKBNFL1159RMe2fIEnYx0/Efv0kZHvtU7uKowrHJ9NxzJlFxTuvA+iaRJSKctx5a4OP5eQU3WIJlchMOxJazFsyG1QvqF68JXP0DqfR3AdewX3gFb3DCMrdVYVPUfEpKgt2VekdDgBlFZWsztvMqvWbKKuo1DucqOfduV2rPCSJlD/+jaRb7zkpeQDI9kSSbruXlIf+BpJExXtT8e7aoUPEGtfPC8HnA58P19KFusURSk2qQKLlIk60xBFJ3qLPaz02d7hVx2gaR3HtwVv4KQCWjg9HRRXyff6xpDE/v4pr+ul/FJi7ZDU+nx+ABT+v5ppxkbsxWyyq+uBtUBTs4ydiG3Nxg9vbzrsY385tOObMouqDd0j7v5cjEOXJtNNXxx4njL1KlzhCSVQgMUDxHMRfsRJkK8hW/BUrUDwH9Q6rQe4DrwSrpmioQgodPvIOO7EYJSxGibzDTgodPr3D4vufVgQfz1+0op4tBeVoKe51a5AsVuzXN37ygH3iLUhmC+5fVmlT/SPMX1yEZ/MGJLMFyWzBs2kD/uKiiMcRas26BtIae9To2aHTV/QFoGBKHwuoeItn4yv6EnNWHa3qo0Sw+pC0dTjewk91r0K+z69CUeGcLnZQtdNZ3++s4sZB+q03KSwuJW/Tdiw1XaPzNm2nsLiUdm3CN/00lnk2rANVwTxkWJ2nrU5FTkzCPHgo7tXL8WxcH9HbbwO4luSCqmA54yxAxfXzQlxLFmAfH9sTYmLuInprTF7a7CswtbmWQALxFn8e1QkkUH2Y2mv3WvEe+RD3gVew9ZiqW0zz87XrC5f0SDqWQPIrdU0g3/+0EkVVOWfEEAByl6zi+8UrufFq0W+tLv6SQgCMp3Vq8lhjVmfcq5fjLyoMdVgNcv2knb6ynnshqDUJZHGuSCBC8ynOHah+ByjVqIpH+6HqQfVX12yhonoO4q/KQzIkY0y7AADJkIy/aj2eg28gmU8DpJqfJ4CkHclKshnkBCSDHdkW2Tnwx6oPA5ash0Ay4C38FG/hx1iyHkK2hfa2wXvLPFR7VVw+Ba+i3eXP6wenr2ZdgApHHD62FrtJNMuM6qQt4ko0y2wpcvPRr2W0txsD/4zYjDKmmslZJlnCapRJMEl0ST353jItNb/m9NUlY0ZqSW3JKr5ftEIkkFMK3DxLbfpQtWaMFLobcPkK9qE6naguF/i82m58Xu259gx/cRHenduR7HYsQ0doIdjtePO34Zj9KYY2bQl+hq3WY3dQNZq05zYbxqzOIYs5lEQC0Zlzx90o1Zsb3M6Ycbl2DaTmsbdwJq7dj9c7Rk7oR0KfyK9OPr76CCQLU7vrtSqkYEpYqpBnFh0hv9TT4HZjshMx19zBb0x2InO3VfCP5cX1jumRbubFizo0KZ69Bw5R7XLjcrnxerXrLF6fD6fLHdzmSHEpW/P3kGi3Mer0QQAk2m1syd/DR199R/vjTmPZrBZMRu3jajIZsVotJFgtdOnYuL5I8UL7sgVfwf4mj/Ud3F/rPUKl/PUXgn316mMdOTp4gzvryNE4F8yj8r36PwvGrt1IffTZkMQZDiKB6Ei29cQ+eAGunQ/jLfyo5qcSxrSLkQw2QEIyarOETO1vDo4zZ07WKgxA9ZUDKqrfie/o9wSOzEztfoe1+ytIcstaaTTVSdVHDUvHh8NWhXRJNfOf8Z146eci/retAtCO587qbMdqlECCJLM2X+SqvsdmXV3XP4VAN5NKjwIquHwqS/c5gse3V/RO5s9nt9Xep4meeW0a+XsONLjdmFHDMJtNwcdzf1jCP6Z9XO+YHl078uJj0XsKM1zMA3Jq7uOzFsVR1ejrIEplBZ487T5B5oE5IYvHmNWZjFfepuKtKThzv9V+KElYho1EslgBCTlRi9F28eXBcQmXjQ/26VOqqgAV1e3CvWZFsFKyXTiO5Lseqnmf6BT2BKJHj5pYIsk2bD3fwJhyDq5df0T1V6O49pDQZwZyQp86xxgSh2JIPNbrS3Hm49w2CVBBtmLNfhFzh1si8wucoK7qA7SFhOGsQqxGiSfHtOP002z8fUkRTp9CQaWXFy/qQLe0uk899WtroV/bdsHn+8q9PPrDIVTAbJB4+Ky2jO+b3Kx4unTM5D9TnuKlf3/A/37QrttJksRZwwdhtVgASErUTqVddcmY4LjrLrsAk1E7f1ZZpZ3KdLndLF39K2rNF8sVF53Dn+++Gasl9KfUop2clo5l6HDca1fi+GQ6Sbc1LolWfTId1ePGMuxM5JS0kMYkWaykPPBXzANzqHjzVVSXC//hg6Q++izGztl1jjH17IupZ9/gc1/BfspefAJUFclsJun2B0i49MqQxhkOYUsg0dCjJpaSl6ndRAxJOVRvnYRSvRXHrxdg7f46prb1r5z1lczFueNuVH8Fsq0Htt4zMNgj1xTyeKeqPgLCWYUEXNYriX5tLTz6w2F2HfXw+68O8NjottqF83os2u3g6UVHqPIodE4x8eJFmfTMaNkXtNVi5smHJnP6oL78/Y0ZOF1uCg4V8eJj99KtS1adY/r1yqZfr2NfOvsKDvPoC1NRVRWz2cTDd97I+LFjWhRXrEu8+U7c69fgmDMLY7de2M6rfy2Ic+F8qv/3ORgMJN18R9jisp1/KaaefSl78Ql8+3ZT8qc7Sbnvz1hHX1jvONfyxZS//gKqw4Exq5OWeLqG/rMRDmFJIHr3qImG5NUcsq039kG5uHY+iLfoc5zbJ+OvXIE1+4XgxfEg1YNr92N4Dr0LgKnttVi7/6NZnXpD5VTVR0C4q5CA7DQz/xnfkRcWFzE/v5K/LTjC+sMu/jiqDSa59qkor6Ly2rJiPt9UDmgztB4b3bZZnXpP5bILzqJfr2wefWEqu/YW8Ps/PsNj9/1eu3Bej0XL1vL0lGlUOZx0zurAi4/dS8/sps8+ijembj1Jvu1eKt55nfIpz+HbuQ37xFuQE2sfJCiVFVR9Ml1LHqpK8m33YcxuevfmpjB26kLGK29RPvVlXItzKXv5aRI2/UrS7fcduzheQ/V5qZz2r+DN7ayjLyTl3kea1alXLyFPIHr3qNE7ebWUZEjE1utd5IT+uPc+jbdwJtauzx2bfBKgKngLZwJg6fIUlo4nH/FHUkPVR0AkqhDQWrU/d0F7emSYeWNlCd9sq+ShM9uctJ2qwjfbtOm994zI4JYhoT29EZDd6TT+89qTvPCv/zB/0Qr+9tKbrN+8nT/e8dvgxfEAr8/Ha+/M5PO5CwBthtZj9/2+WZ1645X2uZWoeO9fOObMonreHMyDT8d4WkcAfAcP4Mlbi+pxg8FA8uT7SLj8mojEJtkSSH3kKRzZ3amc8TbOH+fVfapNUXH+OA+ApEl3Yr/2xojEF0ohTSAn9qg5VZuBQI8aY7delE95jor3pmLqP7jFFYHeySuUJKO2NsGQel5w9lUtshVD6nn4Sr4JbqunhqqPgEhVIQHJNRfPR3S0BWdfHc9skBjR0caiPY7gtuGSYLPy3J//QI+unXhj+md8k/szD00+uQu0qqh8k/szAPfcch23TLj8pG0ESLjiGkz9B1H1wTu4f1mFe/Uy3MdvIMlYhp1J0s13hL3yqItUUxFZhgwPzr6q9brZjGXIcFwrlgS3jTUh/cQEe9RcdX2je9TYr7wO/H6qPninRfuO1QZrp+Ir1Y5MTOnjAG22lXP7HTi33ozqLdFeSxtbs+13+gRZo7HVR4Cl48MgmfAWfozi3BnW2BbvdQAwuqt2j5hKj8ITPx7hLz8cpsyl9Z86p4v22pK91XW/SYglJ2r7G5EzIDj76nhms4kROQNqbSvUzdStJ2n/9zLt/jub1L88TdLk+0iafB+pf3madv+dTdpTL+mSPADcK5cCYBlxNqAdvJa/+ixl/+9vKBXaKVNtZTq4Vy3VJcaWClkC0btHjZ7JK9RUfzW+8sWAjDHtInxHc6laNwJv0Sy8JV9Ttf4sfEdzMaZfDMj4yn86bvFh5AWrj3Y3NOqUVKAKQfXjLpgStricPoU1B53Ikjald/n+aiZ8uo/vdlTy464qbvhsP8v3V3N2FzuyBKsPVh9bfBhGi1euA2D0SG06aaWjmidefou/PP+vYDfewMr0JavWhT2eeCCnpGE9+3zsv5mA/TcTsJ59fshnWzWF6nLh+fWXmipoJO61Kym++0aci77Htewniu+bhHvtSizDz6yZlvzLcYsPY0fITmHp2aOmJcmret6cYPKKltlZ/vJFoLgw2Afg3v8SnkPvASqG5FHa6xXLqN58HebM2zDY++F3bMRfvghjTbUSScd33JUkM+4D/2jUOKlmUkA4e2StOuDE7VPpmWFh2tpSvthUjgrkZGprY9YdcvLAtwe5pn8K3dMt7Chxs+qAk3O7hu+o3+lysyZvC3LNlN7lazfwzJR3KS7V7jf/65Z8nnxoMmefMRhZkli9fgtOlxub1RK2mITQ8+StQfW4MWb3oOrj6VTPmw2qinnAYO31jXkcffoREsZehbFrN3y78/HkrQlWK7EiZAlEzx41sdpg7VS8Naev/I6N+B0bQbZg7fx4sPeVp2Aqrn3PB2dgBcbokUCCHXcBz+H3m/4GNZ16w3EtZEnN6asdJW52lLgxGyTuGp7O7wZpR6Yf/XqUt1aXBmdgBcaEM4GsWr8Jt8dDz26dmTZzDl988yOqqpIzoDcA6zZu44EnX+Way86ne3Ynduzax6r1mzh35NAG3lmIJq6a01e+3fn4ducjmUwk3ng79vHXA+D46lOqPpwWnIEVGNNqE4iePWpitcFa3RR8pfODz+SEfth6Tau1tsOcdT+G1Atwbr892AZFG6MQ0Q79qhfZnIml44Mtex/JpCUh6eTrAc2lqMcSCGjtSJ45v0OttR03DU5jZEc7T/54ONgGZcleB4oKcujaJdWyZOV6AHbs2seOXfswm4zcddM1/O4a7XrWR1/M463/fhGcgRUYIxJIDFEV3KuXBZ8au3Yj9U9P1lrbYb/6BixDz6Ds1WeCbVDcq5dpyw6k2LnLRsgSiL49aqKrwVpL+CvXonoLARlz1t1YOz8B8smnLwz2/iQOXohr37N4Cv6N6i3EX7kWQ9LwyAUrmbB0rr8fl142FboodfqRJfjtwFT+cEZGnbOwemaYmXF1J95cVcLMDWWUOv1sKnQxsH3op8wqqhpMIKC1I3nmkbtqre246VbzloQAACAASURBVNpxjDx9IE++/FawDcqSletRVBU5Sv5Ghfp5t2/RrudKMvarJpB40x3BtiXHM3btTsZr71L133dwzJ6FUlaKd/sWTL31WQjcHCFLIHr2qInGBmvN5Sudh2zpiLXnmxhTGmglL1uwdn0OU8YVOLffha/0u8gmkCi2eK+DDolGnjqvPcNOq78fmNkg8cCZbTivWyJP/XiEJXsdYUkgm7btorSsHFmS+O34S/nDpGsxm07+CPbM7sSM15/mzRmfM/Or7ygtK2fTtl0M7BMbq5NDJRpupdAcrpVLMbRtT8qDj2EeVH/lKJlMJN16D9Yzz6VsynO4Vi2NqQQSslop0KNGdbtwfDK90eOCPWpOH9HsWRMnJq/GCleDtZaQjKnYc5Y1nDyOY0gagX3IT8HGiwIkW2Q+vq5zg8njeIPaW/nvNZ1IsoTnFMLiFb/QoW0Gb/y/v/DA5Il1Jo8As8nIA5MnMu2Vx+mY2Y4lK8VsrFghJybR5l8zGkwexzP1HUCbKe8h22NrPUhIFxLq1aMmGhusNZc56/5mjZMMyc0eG49uGty8/89Es9zssQ1JTrTz8b+fJ9HehKTWtyf//eczfDVvYVhiikZ63v0zFOxXn7w4tDEku73ZY/US0kOtQI8aVJXyKc9R+e6/UKoqT9pOqaygYto/KZ/yfMh61CTefCcYDDjmzMK58PsGt49UgzVBCLjp2nFNSh4BiXYbN10b+Rl2gtCQkPfC0qtHTTQ3WIsXFUv1b5kiCEL0CEs3Xr161ERzg7UTTZgw4ZSvzZo1q8FtBM3wt/P1DkFopWL1In8ohe1+IIEeNUr5Ue2eHCXabUMNGW0wD8wJ2zWHaG+wNmvWLN0SQyAxNVXyWWUhjiS+DR/X+G4IghDLJDVwm7NGCGTcSF/kOj7TN2XfoUheev3OQuyJ9cSx+tsZeocgxJi4vid6oMGaIERCS7+AYz0BCa1PXCcQQYhFka4EROISmit2mq4IgiAIUUUkEEEQBKFZmnUKS0xfEwRBEGLuGohIXoJwsoLDRQBkdYiOpqBC69CkBKLnVFaROATh1N7/5GsAnnjwNp0jEVqTmKlAxDoMQahbweEivv1RuwPerROvFFWIEDExk0Bau3d/O0/X/U+eOVbX/Qun9v4nX+Pz+YOPRRUiRIqYhSUIMSxQfRiNBoxGA9/+uDR4PUQQwk1UIDGmOZWA1+UDwGRt+n+33pWPUL9A9XHlxaMB+Pr7xaIKESJGVCCtwJ7VR9i7+ojeYQghFqg+ZFnmlgmXc+vEKzEaDczN/Zn9B8X/txB+IoG0AjuXHWLn8kN6hyGEWKD6uPzCs+l0WnuyOrRl3PlnoSgK02fN1Ts8oRUQCSTOuSo9HNxYTMGGYlyVHr3DEULkxOojQFQhQiSJBBLndq88jOJXUfwqu1ce1jscIUROrD4CRBUiRJJIIHFu57KDxz0Wp7HiwamqjwBRhQiRIhJIHHOUujiyrQyj2YDRbODItqM4Sl16hyW00KmqjwBRhQiRIhJIHNu17BCqqtJ5aDs65bRFVVV2iYvpMa2h6iNAVCFCJIh1IHFs53Lt9FX3UZmoqnY9ZOeyQwy8LFvnyITmOn7dR13VR0CgCvn6+8VMnzW30etCJkyYEKpQm2TWrFm67FdoGZFAYlD5IQdelw+f24/fp93SXvEp+NxaOwtVVXGUuijeXYE5wUjHwVpvJHOCkeLd5Wz4djf2dCuSJAFgtBiQjVoxajBKGC0GTFYjKZl2HX474VQaW30E3DrxSr79cSlzc3/mlgmX15twQL/kEdh3XUlEJLToJhJIjFr81gZK91c2uF3XYe0xmOTg4+2LC1j54dZ6x6R3SuKCB3NCEqcQOo2tPgKaW4VE+svzVEkiGhOaUJtIIDEoJdPOlc+cybLpm9n+0wHthxJ0GtIWo9mAJEmYE7T/2t7ndQqO63tRl2Cl4an2oaoqPo+f/euLQCtk6HVuR0bd0g+jxRDR30mo3/Edd01GIzM++6ZR40xG7e/g2x+Xxmyn3uZ8kav+KgAkQ2KTx+qZuGKNSCAxymgxMPrOgWT2S2fp+5vwuf1UFjq54IEc0jrW/aFp2z2Ftt1Tgs/LDzlY8Po6UMFgkjlzUj/6nN+pzrGCvo7vuPvFtz82ebzP529VPbJ8JdrsM1O7iTpHEt9EAolxPc/Jom23FBa8vo6jB6r4+sllnD15IN1HZdY7bs/qIyx++1c81T5SMu1c8EAO6Z2TIhS10BQ+n5+26alMuu6yFr2P0WDA5/NjNMZ/dekt/hyQRAIJM5FA4kBqViJXPnMmP7+7kZ3LDrFw6nqObCtl5E19g6esAhSfwor/bmHzD/sAbYbW2ZMHNKtTrxAZRqOBu26+Ru8w6lVZWA1AUrsEnSMB1VuCr+yn4GPJlKFzRPFLrAOJEyarkfPuHcLwib0B2L64AFU9eTtV1V4DGD6xN+fdO0QkD6HF1s3eybrZO/UOAwBvyWxQvaB68ZbM0TucuCYSSJyx2E0AZA1sE5x9dTyDSSZrYJta2wpCS1QWVpO/pID8JQXBSkRP3qLP63wshJ5IIHFm71pt1XGX09sB4Kn2suiNPBb8Y12wG2+Xodpre38RK5SFlls3e2ewYWdzqpBZs2aFbMqs4jmIv2IlyFaQrfgrVqB4DjY8UGgWkUDiiM/t59DmUiRJotOQthzIK+Lzh5eQv/Qgu1cd5su//MyBvCI65bRFkiQObSoNLj4UhOYIVB+yQUI2SLpXIb6iLwAFU/pYTOmXAgq+oi91iyfeiZPfcaRgYzE+j5/0Lkms+zKfzbn7QIUOfdIBOLy1lO9eWkO/CzuT1jmR0r2VFGwspsvpDS9KEyJn+LhJeofQaIHqo9eYjgBsX3SAdbN3MvqOgY1+j8C6i1BUIdrsKzC1uRZQ8RbPxlv8Oease1v83sLJRAKJI/vWFgJQureS0r2VGEwyp1/Xi4GXdQVgwzd7WPvZ9uAMrMAYkUCE5ghUH5IsMfjKbsiyVoHsWFzA4Cu7kdIhdK1wFOcOVL8DlGpUpebGaKoH1R+odlRUz0H8VXlIhmSMaRcAIBmS8Vetx3PwDSTzaYBU8/MEkMzaY9kMcgKSwY5s6xmymFsDkUDihKqq7FtXFHye3imJMfcMrrW2Y9Dl2XQc1IZFb+QF26DsW1eEqqrBvliCflZ/O0PX/Td1Bfbx1UcgWfQ4J4vtiw6Q9/WuJlUhjeHccTdK9eYGtzNmXK5dA6l57C2ciWv34/WOkRP6kdBH33//WCQSSJwo2lmOs9yNJEkMGNeVYRN61TkLK71zEr95bhRrZm1n47d7cJa7KdpZTrseqTpELcSqE6uPgJyruoelCpFtPbEPXoBr58N4Cz+q+amEMe1iJIMNkJCMWpcFU/ubg+PMmZO1CgNQfeWAiup34jv6PYH+PaZ2v8Pa/RUk2RaSWFsTkUDixN61hSS2sXHuXQPJ7Ff/wimDSWbE7/rQdXh7fnrzV/atLRQJRGiSuqoP0BYShqsKkWQbtp5vYEw5B9euP6L6q1Fce0joMwM5oU+dYwyJQzEkDg0+V5z5OLdNAlSQrVizX8Tc4ZaQxdjaiFlYccJiN3H1i2c3mDyO175XGlc9fxZmsR5EaIJTVR8BOVd1RzZI7FhcQPlhR8j3b2o3EfvghcgJfVCc23D8ekGj1nv4SubiyDsfv2MTsq0H9kELRPJoIZFA4sSgy7ODHXibwpxgZNDl4gZTQuMFqo+eo7PqPEUVqEJURSXv611hiUG29cY+KBdT22tR/Q6c2yfj2vUwqJ6TN1Y9uHY9TPXWG1H9FZjaXot98CIM9v5hia01EQlEEIRGa6j6CAh3FQJaq3Zbr3exdHkKAG/hTFCVkzdUFe01wNLlKWy93m1Wm3fhZHF5DUTcxUwQwuNU1z5OFM5rISeSjNr1O0PqecHZV7XIVgyp5+Er+Sa4rRAacZdA4v0uZu/+dl5Y318QTqWx1UdAuGZknchXqn0mTOnjAG22lWvXI6C4sHafgmTKwJQ2Fl/JN/hKv8Pc4ff1vp84EGy8uEsgAdFyW05BiBeNrT4CIlGFqP5qfOWLARlj2kX4jubizL8X1XMYAF/lKmw9pmJMvxiQ8ZX/hOqv1hYSCi0Wtwkk3kyeOVbvEIRWLFB9ABiMMnn/a9zFcUPN/WjylxSQc1X3kN8vxF++CBQXBvsA3PtfwnPoPUDFkDxKe71iGdWbr8OceRsGez/8jo34yxdhrKlW6hLK1irxTiQQQRAaFKg+ALbk7mtg65MFOvWGugrx1py+8js24ndsBNmCtfPjwd5XnoKpuPY9j+fQu7XG1JdAhMYTCUQQGqB3c0O9W5wofhV7moXBVzR83aM+slFC8avIhlC1zVHwlc4/9v4J/bD1mlZreq45634MqRfg3H57sA2KNkZBTEJtOZFABEGol2yQOP26XnqHcRJ/5VpUbyEgY866G2vnJ0C2nLSdwd6fxMELce17Fk/Bv1G9hfgr12JIGh75oOOMSCBAydFy1v66haLSMiQk2qSnMGxwX9JTU/QOTYgizakEqp0uABJsdUwvbYDelU+085XOQ7Z0xNrzTYwp59S/sWzB2vU5TBlX4Nx+F77S70QCCYFWnUC25u/hjemfsWrdJpQTbiAuSxIjhg7gnluuo3f3LjpFKMS6hcvWIkkw7vyz9A4l7kjGVOw5y5AMyY0eY0gagX3IT3gPTw9fYK1Iq00gn8z5ninTPkZRFKwWM2fk9KdTpnZfjP2HjrBq3SaWr93AqvWbeXDyDUz8zUU6RyzEovmLliNJkkggYWDOur9Z4yRDcrPHCrW1ygTyyZzvefXtj5AkiRuvHsutN1xJkr329MJKRzXvzZzDzNnzefXtDwFEEhGapKyiktV5m4OPU5OTGhghCLGl1SWQrfl7mDLtYyRJ4pmH7+TS886sc7skewIP3n4Dvbt34alX3+Ef737M0IG96dWtc4QjFmJV7pLV+HzaPecX/Lyaa8adr3NEjSMWxQqN1eoSyL9nfI6iKNx49dhTJo/jjT1/FFt37mHmV/N5Y/pnvP7MnyIQZfwK95dTYPHXifvRY1HY9z+tCD6ev2hF1CeQWbNmRWUfOZHQolerSiAlR8tZ+ctGrBYzt95wZaPH3XbDb/jim4WsWLuB0rJyMTurmeK9T9nxCotLydu0HYtZuxte3qbtFBaX0q5NesRiaI5oWn0drQlNOKZVJZC1v25BUVXOyOl/0jWP+iQn2hk+pC8/r8rjlw3buPCcM8IYZfyLxIfz+H3o8SX0/U8rUVSVc0YMASB3ySq+X7ySG68WLWmaQnyRR7dWtRSzsPgoAJ2zOjR5bJesTAAOF5WENCYhPs2vOX11yZiRXHLuSAC+X7SiviGCEHNaVQVCoIOCWu9WdVJrBklSqNowCLFo74FDVLvcuFxuvF4fAF6fD6fLHdzmSHEpW/P3kGi3Mer0QQAk2m1syd/DR199R/vjTmPZrBZMRu1jaDIZsVotJFgtdOmYGcHfShCap1UlkMAHd2/B4SaP3Vczpn2Un8MWwu+Z16aRv+dAg9uNGTUMs9kUfDz3hyX8Y9rH9Y7p0bUjLz52b0jiFIRwa1UJZOjAPsiSxOr1m6h0VDf6OkhFpYPV67cgSxJDB/YJc5RCNOvSMZP/THmKl/79Af/7YQmgVaVnDR+E1aL1YUpK1P6urrpkTHDcdZddgMloAKCyqhoAl9vN0tW/otZ0QbjionP48903Y7WYI/XrCEKLtKoEkpGWwoihA1i+dgPvzZzDg7ff0Khx02bOxu3xcNbwwaSnNr5tgtBySlUR7t0rUSqPgCQhJ7bDkj0SObGNbjFZLWaefGgypw/qy9/fmIHT5abgUBEvPnYv3bpk1TmmX69s+vXKDj7fV3CYR1+YiqqqmM0mHr7zRsaPHROh30AQQqNVJRCAe265jlXrNzNz9nx6d+/C2PNH1bv9tz8u5dOvf8BgMHDPpGsjFKXgPbSJyh9exr1rKahK7RclGUv3s0m68BFMmf30CRC47IKz6Ncrm0dfmMquvQX8/o/P8Nh9v+eSMSPrHbdo2VqenjKNKoeTzlkdePGxe+mZ3SlCUQtC6LSqWVgAvbt34cHJN6CqKk+9+g5Tps2kospx0nYVlQ5effsj/u/VaaiqykO330BPsQo9IhwrplP8znjcO5cgGS1Ye1+IfdRt2EfdhrX3hUhGC+78xRS/cxWOFfreKyO702n857UnuWTMSKqdLv720pv8/d8f4PX5TtrW6/Px939/wCPP/ZMqh5NLxozkv/98WiQPIWa1ugoEtJ5WkgRTpn3MzK/m88U3Cxk+pB+ds7RmivsKjrB6/WbcHg8Gg4E/3vFbJlxxoc5Rtw6OFdOpmPcsSBL2UZNJPPceZGvt04aKq4Kqn6biWP4+FfOeAcA+Ur/W5wk2K8/9+Q/06NqJN6Z/xje5P/PQ5JNPj6qKyje5PwNaJXzLhMsjHaoghFSrTCAA1195ETkDevPG9M9YsXYDP69aX+t1WZI4a/hg7pl0rag8IsR7aBMV818ASSL16lexDfpNndvJ1mSSL3kMU4d+lH31MBXzn8fcdTimDvqdzgJtwSnAiJwBwdlXxzObTYzIGcCi5WuD2wpCLGu1CQSgV7fOvP7Mnygtq+CXDVuDCw3btUlj6MA+4oJ5hFXmvgKKH/uoyadMHsezDb4K76FNOJa/T2XuK6Tf+H4Eojy1xSvXATB6ZA6gdXR+6d8f4PF4+et9t5CanMQ5I4awaPlalqxax9XjztMzXEFosVadQALSU5NFexKdKVVFuHf+jGSykXjuPY0el3juvVSvmYk7fwlKVbFus7OcLjdr8rbUVK6DWL52A89MeZfi0jIAft2Sz5MPTebsMwbXTCXfgtPlxmY9+RasghArRAIRooJ790pQFSzdzjrpmkd9ZFsK5uwzcW9fiGfPSqwDLgtjlKe2av0m3B4PPbt1ZtrMOXzxzY+oqkrOgN4ArNu4jQeefJVrLjuf7tmd2LFrH6vWb+LckUN1iVeIvHhsDNnqZmEJ0UmpOASAoU12A1uezNimGwD+mvfQw5KV2jW0Hbv28fncBZiMBu6/9Xre+vtfeevvf+X+W6/HZDTw+dwF7Ni1r9YYIf7p3Yk6XEQFIkSHQI8xtTmNygJj9OlTpqhqrWTQo2tHnnnkrlrTc2+6dhwjTx/Iky+/FWyDsmTlehRVRRb91VqN5lQDqr8KAMmQ2OSx4U5cogIRooKcrDUP9JfsbvJYX80YQ3LTuyyHwqZtuygtK0euuUXyjNfrXtvRM7sTM15/mhuvHossSZSWlbNp2y4dIhZiia9kLr6SuXqHUae4rUBCnXlPdac7ITQsXc8ASca9axmKq6LR10EUZxme3ctBkjFn178CPFwWr/iFDm0zeOpPtzNsUN96tzWbjDwweSLnnXU6T73yDktWrmNgn+4RilSIRd7izwEJU7uJeodykrirQPS8AY24+U3zyYltsXQ/G9XrpOqnqY0eV7XoX6heF5Yeo5HtGWGM8NSSE+18/O/nG0wexxvUtyf//eczTbqxmdD6qN4SfGU/4StbhOqNvnsRxWUFEs4vcpEkwifpwkdw71qKY/n7mDr0wzb4qnq3d+Z9hWPlDJANJF34cISiPNlN145r1rhEu63ZY4XWwVsyG1RvzeM5mDvcqnNEtcVdBSLELlNmP5IveRxUVVth/t3zKM7yk7ZTnGVUzHuWsq8eAVUl+dK/YerQ+KN/QYgV3qLP63wcLeKyAhFil33kJJAkKr57Dsfy96leMxNz9iiMGV0B8JXswbN7GarXBbKB5LF/wz7iZn2DFoQwUDwH8VesBNkKgL9iBYrnILL5NJ0jO0YkkHrE48KfWGAfcTPmLsOozH0Fd/4S3Nt/xH38BpKMpecYki58OKKVx/Bx+jVsDDfxtx59fEVfAAqm9LGAird4Nr6iLzFnNf6OleH+9w17Ahn+dn64d1Gv1Xf2aNY4vRf+tPYPlqlDP9JvfB/FUYJn9wr8lUcAMCS1x5w9UrcL5vFI/K1HJ232FZjaXEsggXiLP29SAgk3UYE0oDl/3FV+7aJXouHkjqwNEdOEa5PtGbq1JwlY/a2+9xyJlEh/kbfWv3XFuQPV7wClGlXxaD9UPaj+6potVFTPQfxVeUiGZIxpFwAgGZLxV63Hc/ANJPNpBBbOSoYEkLTbIEuyGeQEJIMd2dYz+G8crv/biCWQ5lYCzaVn5fNd4V6Q4NoOkf2dBUGIDc4dd6NUb25wO2PG5cFrIMaMy/EWzsS1+/F6x8gJ/UjoE5mDHlGBhMHsIzuREAlEEISTybae2AcvwLXzYbyFH9X8VMKYdjGSwQZISMYUAEztj00QMWdO1ioMQPWVAyqq34nv6PeA1s7H1O53WLu/giTbIvK7iAQSYqVeF0tKDwYfp5usOkckCEK0kWQbtp5vYEw5B9euP6L6q1Fce0joMwM5oU+dYwyJQzEkHuverDjzcW6bBKggW7Fmv4i5wy2R+QVqiHUgITb3yG58qoJPVfimcI/e4QiCEMVM7SZiH7wQOaEPinMbjl8vaNR6D1/JXBx55+N3bEK29cA+aEHEkwdEeQVSUKFdjM5KbvrFaL3MPnKsOd7swzu5Kavuo4nWrLVePI0nzjI3B7eUUn3UhYSELc3Caf3SsaWIG2Q1lWzrjX1QLq6dD+It+hzn9sn4K1dgzX4heHE8SPXg2v0YnkPvAmBqey3W7v9oVqfeUIjqBPL+Ou0Ws0+c207nSBrnkNvB6vIjWGUDAKvKj3DI7SDTIu5/DdpMELHeILYV765g9afbOLihBPWE1vuSJJE1qA3Dr+9FRldxO+imkAyJ2Hq9i5zQH/fep/EWzsTa9bmT71CgKngLZwJg6fIUlo4PRT7Y40RtAimo8PLt9koAbs1Ji4kqZM6RXSiqykXtOqOqMLdwN18f2cWdnQfqHVrUEF/ksWvjd3tY+eFWVEXFaDGQNSCD5PbawVHFEQcFG0s4kFfEwY3FjPhdX/pf2kXniGOPZEwFwJB6XnD2VS2yFUPqefhKvgluq6eoTSDvrzuKT1GDj2OhCpl9eCcAV7XvjoqWQGYfFglEiH0bv9vDig+2gAQDL8smZ3x3zAm1D+o81V7WfbmTDfN2s/wDbYqqSCJN4yudB4ApXWuyqfrKce16BBQX1u5TkEwZmNLG4iv5Bl/pd5g7/F7PcKMzgQSqD6Os1W/fbq/UtQrZWV2Ow++l2u/DqygAeFU/1X4foN0Q75DbwYbKEpKMZs7L6AhAktHMr5XFvLNvI5kWe/CmewkGIyZJO81lkmUSDEbsBhPdE1Ii/8sJQgOKd1ew8sOtIMGYuwfT46y6ezGZE0yMuLEPGV2TWfRmHis/2kKHvmlkdBGnsxpD9VfjK18MyBjTLsJ3NBdn/r2onsMA+CpXYesxFWP6xYCMr/wnVH+1tpBQJ1GZQALVx5V9tD+8r7dW6F6FPLR5MVurjja43di2XbDUXAMZ27YLsw7t4OkdK+sd0ycxjXcGXhCSOAUh1NZ8ug1VURl4WfYpk8fxepx9GsV7ytn47R7WfLqdS/48LAJRxj5/+SJQXBjsA3DvfwnPofcAFUPyKO31imVUb74Oc+ZtGOz98Ds24i9fhDFdv1sCRF0CCVQfsgS3DElDlrQKZO62Cm4ZkkanlMhXId0TUpg77Eoe37acTw9tB7RrW+e36YRNNiJJkGLUZp/ccFqv4LhJHftirkkm5T43qgpOxcePxfsJXH68PrMXz/c+E5sh6v4rBAFnmZuCDSUYLQZyxjf+zok543uwNXc/B/KKcZa7xeysRvDWnL7yOzbid2wE2YK18+PB3leegqm49j0fnIEVGCMSyHGOrz4CyWJcryS+3lrB9PX6VSE2g5HX+p3DqLRM/rptKdV+H/uclbw98Hx629PqHDMkuS1DktsGn++qLueODT+iAhbZwDO9RnKjmOYrRLGDW0pRVZWsARknXfOoj8VuIrN/OvvXFXFoSyndRmaGMcp4oOArnR98Jif0w9ZrGgZ7/+DPzFn3Y0i9AOf224NtULQxCnot6YuqhYQnVh8Bt+akYZQl5m6rYH+5V8cI4drMHnw7/Df0tqexw1HGFav/x+wjOxscN69oL+NWf82WqlK6JaTwzfArRfIQol51iQuA5MymT0VPzdTWJjhq3kM4NX/lWlRvISBjzrqXxMELayWPAIO9P4mDF9ZUJTKqtxB/5dqIxxsQVQkkUH1c3ju51qmqrGQT43oloagwfX3D1yHCrac9la+HX8FV7bvj8Hu5Z+MiHtu2LHiB/XheReGxbcuY/GsulT4PV7XvzrwzfkPfxHQdIheEJgqsQ1Dr3apOamDQiWsZhJP4SuchWzqSMGCOtv5DrueUn2zB2vU57IPmIVuz8ZV+F7lATwxFtz2f4FTVR0A0VSGgtWp/Y8AY/tpdu0D42aEdKHV8yhRUPju0A4C/dh/GGwPGNKvNuyDowZ6urUUoP+Ro8tjAmMB7CKcmGVOx5yzDmHJOo8cYkkZgH/JTsPGiHqImgZyq+giItiokIMWkHSmMTs8Kzr46nkU2MDo9q9a2ghArMvumI0kSBzeV4Klu/IGbu8rLoU2lSJJEZj9x86+GmLPuRzI0fbqzZEjGnHV/GCJqnKhIIA1VHwHRVoUAfF+0D4CL23YGoMLn4b5Ni7hjwwJKvdq534vaaK/9ULxPnyAFoZlsqRayBrXB5/az7suGr/UFrPsyH5/HT8fBbbAlmxseIMSkqEggDVUfAdFWhVT7fSw7ehBZkjg/oxMLSw5w7oov+PLwTr4p3MMFK79iYckBLmjTCVmSWFp6MLj4UBBixfDreyEbJDbM203+zwcb3D5/SQEb5+9BNkgMv753BCIU9KL7NN7GVh8Bt+ak6b4uJGBJaQEuxU+/xHSm7F7HBwe2oAIjUzsAsKLsMDetn8/NHfvSx57G5qpSlpQWJNXazgAAEVJJREFUcElb0d5BiB0ZXZMZ8bu+LP9gM4vezKN4Tzk543tgsdf+7LmrvKz7Mp+N8/eACiNu7Et6lyR9go5S8daJWvcEUte6j/oEqhC914XAsVNSm6tK2VxVilk28Odup3Nn5wEAvL1vIy/tWsuMA1tqjakvgYhmg0I06n9pF5Bg5Ydb2PjtHrbm7ue0/hkkZ2ptNCoOVXNwUwk+jx/ZIDHypr70u7h5B0qHr2j8heRw6PC/JSF/z3jtRK1rAjm+465JlpjRyNNSpijokaWoKrnF+4PP+ySmMbX/mFrTc//QZSBjMrK4d9OiYBuU3OL9KKqKLIm5jUJs6X9JFzr0SWPNp9s5kFfMvnWFsO7Y65Ik0WlIW4Zf31tUHnWIx4NDXRPI8R13v9hc3uTxPkXVrUfW+ooiijxOZEni9k4DeLT76cG2Jcfrm5jOvOG/4cWda5m2fyNFHifrK4oYmlJ3zIGjlHj8YxNiX0aXZC758zCcFR4ObS6hutQNQEK6hcx+GSG9YN6cSkB1VgMg2ZreYFDvyicW6ZZAfIpK2wQjkxpx3aM+RlnCp6jBzr2R8n3xPrKsifyj32hGpdXfpsEsG3iy5xmMa9eF+zct5ofifadMIIIQC2zJ5qhsT+JavhgkCdt5l+gdSqugWwIxyhJ3DY/d1dgpRgsLRownydj4I65hKe2Zf8Zv+LBgWxgjE4TWy7U4FxAJJFJ0v4geq/7QpXk3iUoymps9VhCEU1MqynHnrQ0+lpPF/XXCLSrWgQiCILSU6+eF4POBz4dr6UK9w2kVRAIRBCEuaKevTn4shI84hdWAeFv4IwincvzfemAWYKz8/fuLi/Bs3oBk1vrNeTZtwF9chKFN2wZGCi0RsQQy/O38SO0qJOJ14Y8gnCge/tZdS3JBVbCccRag4vp5Ia4lC7CPnxiS9xfqJiqQeogvcqG1ONXfeqx8Blw/aaesrOdeCGpNAlmcKxJImIU9gay+s0e4dyEIQpzyFexDdTpRXS7waR24VZ9Xe649w19chHfndiS7HcvQEQBIdjve/G04Zn9acxpLWycmWa1IxprOFUaT9txmw5jVOcK/WXwQFYggCFGt/PUX8O3Z1eB21pGjkczm4GPngnlUvje13jHGrt1IffTZkMTZGokEIghC1DJmdSbjlbepeGsKztxvtR9KEpZhI5EsVkBCTtTuvW67+PLguITLxiOZtEpDqaoCVFS3C/eaFaBq7ZNsF44j+a6Hat5HaA6RQARBiGqSxUrKA3/FPDCHijdfRXW58B8+SOqjz2LsnF3nGFPPvph69g0+9xXsp+zFJ0BVkcxmkm5/gIRLr4zUrxC3xDoQQRBigu38S8l47V2MnbPx7d9LyZ/ubNR6D9fyxZT86XZ8e3ZizOpExqvviOQRIiKBCIIQM4ydupDxyltYR1+I6nJS9vLTVLz5Gqrv5Ftcqz4vFW++RtkLj6M6HFhHX0jGlHcxdu2uQ+TxSSQQQRBiimRLIPWRp0iadCcAzh/nQc1tIWpRVO01IGnSnaQ+8lSz2rwLpyYSiCAIMUlK1G5aZRkyPDj7qtbrZjOWIcNrbSuElkgggiDEJPfKpQBYRpwNgOKoovzVZyn7f39DqdBuUKetTAf3qqX6BBnnxCwsQRBijupy4fn1F5BkLMNG4l678v+3d+/BUZb3Ase/z16y2WyypNlQE1BIAlYDUdQhJIgHrZMpUHoh/HEoldY5KLXn0MucqXTqqT0OxWo7IkyrnXoOl1EPxw7tjDAex+icVC3IJUMqEwkGM4FQuQRPsjFZssm+e3vPH5tdiYTceHffZPf3+SfZ3efZ/YVh8svvfZ7399D7u6eJdnsBCJ5qZtqPHsNRuRiUhWDT++iBACpbtuwaSRKIEGLKCTY1ogc1bKVz6fvji/TX7QddJ6tiQez15iY+3byJnBWrsJWUEW5vI9jUmKhWhDEkgRhs57frTP38h19ZYernC5EKgcHLV+H2NsLtbSi7ndx1G3DVrgHAv28vfXt20P/GviFzJIEYS9ZAhBBTix5FO3Y48dBWUoZn2w5cq9eCsoCy4Fq9Fs+2HdhKyhLjtGOHQY+aEXHakgokSVJdCZhd+YjxuZ726ddzVsdU6a47klBrC9Ge7liiWPWP5H7ne4m2JVeylczBs20nff/1n/j3/4loTzeh1hbst8w3Ier0JBWIEClm5iFNU+WAqJEEGg5hnX4DBU9uJ2/9xmGTR5yy28lbvxHPb36PtXgmAdmNZSipQIQwyUSqAX2gH32gH+XMGff8dEgeAJbcPAqfewnlco15jr28gsLtu+h/67UkRpZ5JIEIMYUEjhwApXB+eZnZoZjGtXrthOYpl2vCc8Xw5BKWEFNI4EB94vQ9IcwmFcgkMNCjcbGlm/5PAygUzi84mDGvAOc0h9mhiUkk6utFa/pb4nuLe5rJEYlMN64E0vGEuV0sizefNvXzjdbV7uPY3o+4eMKLrg9tBqeUYubthVSu+RKeErdJEYrJJPDeOxAOx74/9A45K1aZHFFyXfr6P5gdghiFVCAmaX7zLA17TqFHdWwOKzMrPLhviC0K+j7xc6HZy/mmTi42d1H1QDnzl882OWJhtivPvggcqE/7BCImvwklkFRXAmZXPkZrfvMsR19uAQW3rSzlzto5ZOUM3YoY7A9x/NXTnKhr58jLHwJIEslgka5Ogh+eQGXFLmsGT54g0tWJtXC6yZEZr+h/DpodghgjWURPsa52Hw17ToGC+/5lAVUP3HpV8gDIyrFTte5W7vvnBaCg4b9b8P7dZ0LEYjIIHKwHPYpj0RIci+4GPUrg4F/MDktkOEkgKda49yP0qM5tXy1l7pIZo46fe88MKlaUEI3oNO5tTUGEYjKK77zKvreG7KU1sefGcJyrEMkkayApNNCjceGEF5vDyp21Y78sd2ftXE7Vn+N8UxcDvZohu7PMuqksHVppGCl84WP0gQH0QAAGj2XVw6HY49gjIl2dhE63olwuHHdVAbF7GkJtH+Hfv3fwMpaKPZ+djbINVrQ2e+yx04lt5qwU/2QiE0gCSaGLLd3ous7MCs+wl62uxeGyUzy/gHPHO+lo6aasuvi64jC7lYYkkaF6f/sU4bNnRh2XXb00cfJedvVSBv5Sx+Vdz484x1ZSRv7PthgSpxCfl/QEEu3rRGtvIHr5E1AKS+4XcZRWY8ktTPZHTzr93thfle7isbdgiMsvzuXc8U783sDog8co1b/I06WVhpFsM2fh2fof+F7YzkD9G7EnlcKxsBrlyAYUltxcAJxf+VpiXs7K2kQPqGhfH6CjawG0xqMwuCXcWfNV3N//18H3EcJ4SUsgoY6TXP7fZ9DOHLq6hbKy4JhzD3k1m7AXz0tWCJOPGvyqjzhqWHp8khp53GQmlcfwlCObaT9+jKzb7sT3h2fRAwEily6S/7Mt2GaVDjvHfnM59pvLE4/DF87R8+tfgK6jsrLI2/BjcpZ/I1U/gshQSUkg/qMv4nvrKYhGUHYnjrIlWD2xLagR79/RzhxCazuAduYQ7mU/x1X9YDLCmHRcBbG/BHs7/OOeG58Tfw+Rfpz3L8d+czk9v/4F4Y/b8f7kEab98KeJRfNrCRw5QO9vn0L3+7HNvCmWeErSa+u7mJwMTyD+oy/iq9sCSuG6+2Fy792IJXvondTRgI++vz6P/8hufHW/BMiIJFJcXoBSiosnvQT7Q2NeB9H6QnSc7EYpRfE8T5KjTJ74JSypRK7NdtNsPFtfoPf5ZwgcqKfnmc3knPyAvA0//GxxfJAeDnF5x3OJU/eyl9Yw7QebUM4cM0IXGcjQbbyhjpOxykMp8lc/i3vZY1clDwBLthv3sn8jv3YrKIXvrV8RuvShkaFMSs58BzNvLySsRTj+6thvxjz+ahvhYIQbFxTidGclMcLRnde8nNe8psaQ7pQzh/xNT5D34CMADLxdB9FhrntG9dhrQN6Dj5C/6QlJHiKlDE0gl+u3QjSCa/FDOG//5qjjnQtW4ar+J4hGYnMzQOWaL2GxKk7UtdP23sVRx7cdvEDzW2exWBWVa25JQYQj23Gpnh2X5P6DVFC5eQA47qhM7L4a8npWFo47KoeMFSKVDEsg0b5OtNPvoexOcu/dOOZ5uff+AGXPRms7SLSvy6hwJi1PiZuqB8pBh3f/0MTRPS1o/tBV47S+EEdfbuHdFz4AHarWlVMw29xfEuc1L697G3nd2yhVSApoDbHT8xxV9wAQ9ffR++wWep5+nKivN/baoiWxsXLSnjCBYWsgWntDrNVC2ZJhL1tdi8U5jazSxWit7xA820B2xUqjQpq05i+fHWtPsqeF5jfOcqr+HDPme3AXxy4/+Dr6uXjSSzgYwWJVVH+nnHlfMb8P1o5L9YT1SOL7zbPXmBxR+tIDAYIfvB/bsbiwGu1vDfT+7mmi3bHEHTzVzLQfPYajcjEoC8Gm99EDAVS2bLIQqWNYAon6OgCwFg6/7XDEIArL0FrfITL4Hplg/rLZFN36BRr3tnK+qYuPj/8fHP/sdaUUN90xnco1t5heecBn1YdNWQF43dvIhqIabnRM3UX9ySzY1Ige1LCVzqXvjy/SX7cfdJ2sigWx15ub+HTzJnJWrMJWUka4vY1gU2OiWhEiFYzbhaUGb1DQJ3KTQ3zOFL7JYQI8s90s++lCBnxBOj700t+tAZBT4KB4nsf0BfMrxauPVYWxVhr7uxqkCkmiwODlq3B7G+H2NpTdTu66DbhqY//e/n176duzI7EDKz5HEohIJcMSiMUda68R8baPe254cI7VXWRUOFOK05113e1JkilefViUhYeK7seChde9jbzmPcZDRfczy5F+LcVNpUfRjh1OPLSVlJH/k38fcm+Ha/VaHHctoufZXybaoGjHDsdu2lXSI1WkhmH/0xwli0BZ0M4cJhoYe9vx6EAPwfYjoCxklVYbFY4wULz6+IanklmO6dzo8PA1z0KiepRdl942O7y0E2ptIdrTDcqCq/ZbeLbtHPbGQFvJHDzbduKq/RYoC9GebkKtLSZELDKVYQnEkjsdx5x70EMD9P115AZvV+p79zn0UADH3KVYXHI9fbL5fPURt6GoBpuy8pr3GB9rnSZGmH4CDYewTr+Bgie3k7d+Y6Ln1XCU3U7e+o14fvN7rMUzCchuLJFChta6eTWbwGLFf2Q3A037Rx0/0LQPf8NLYLGSV/OokaEIg3y++oiTKiR5LLl5FD73Elm33zXmOfbyCgq378LiMn/DhcgchiYQe/E83Mt+DrpOz75H8b35K6IDvVeNiw704KvbQs++TaDruJc/jr2ofJh3FGa6VvURJ1VIcrhWr0W5xt+xWblcuFavTUJEQgzP8F5YruoHY+1J3nwS/5Hd9De+Qlbp3dg8JQCEvWcJth9GDwXAYsW94nFcVd81OgzT7fx2ndkhXLcrd14Nt1Aer0L2dzWw69LbsiNLiAyTlG68rqrvkjV7IZfrt6K1HURrfRvtygHKguPm+8ireVQqj0lqtOojbkNRjezIEiJDJe08EHvRPArW7Sbq9xJsP0rk8icAWPNuIKu0Om0XzB9+ZYXZIRhitOojTqqQiZMDtsRUl/QN4xaXh+yKlbgWr8e1eD3ZFSvTNnmki7FWH3GyFjI+Zrazl1b6wkhyJrq4ylirjzipQsZPfpGLdCAJRAwRrz4A7MrK7jFu0bVLjywhMo4kEDHElR13/9x5eJTRVwvrEemRJUSGkAQiEsJ6hC/a3awfw7rHSGzKSliPJDr3CiHS04QSSMcTV/flEVOfTVnZOCM9dpEJIZJP2nYKIYSYkHFVIMWbTycrDiGEEFOMVCBCCCEmRBKIEEKICZFdWBlMWmkIIa6HVCAZSFppCCGMoHRd180OQgghxNQjFYgQQogJkQQihBBiQiSBCCGEmBBJIEIIISZEEogQQogJ+X/VaLYRW+FpfAAAAABJRU5ErkJggg==</v>
+      </c>
+      <c r="E734" t="str">
+        <v>18-09-2026 03:19:01 pm</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="str">
+        <v>6aae55ed4047c2fb29b0f4db</v>
+      </c>
+      <c r="B735" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C735" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D735" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E735" t="str">
+        <v>19-09-2026 02:59:17 pm</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="str">
+        <v>6aae55ee4047c2fb29b0f4e2</v>
+      </c>
+      <c r="B736" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C736" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D736" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E736" t="str">
+        <v>19-09-2026 02:59:18 pm</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="str">
+        <v>6aae55f74047c2fb29b0f5ec</v>
+      </c>
+      <c r="B737" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C737" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D737" t="str">
+        <v>Started Playing game and Debited "10" and Balance "220"</v>
+      </c>
+      <c r="E737" t="str">
+        <v>19-09-2026 02:59:27 pm</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="str">
+        <v>6aae55f74047c2fb29b0f5f2</v>
+      </c>
+      <c r="B738" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C738" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D738" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E738" t="str">
+        <v>19-09-2026 02:59:27 pm</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="str">
+        <v>6aae561f4047c2fb29b0f62b</v>
+      </c>
+      <c r="B739" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C739" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D739" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E739" t="str">
+        <v>19-09-2026 03:00:07 pm</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="str">
+        <v>6aae561f4047c2fb29b0f630</v>
+      </c>
+      <c r="B740" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C740" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D740" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E740" t="str">
+        <v>19-09-2026 03:00:07 pm</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="str">
+        <v>6aae5664434caf29ae010cb5</v>
+      </c>
+      <c r="B741" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C741" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D741" t="str">
+        <v>Started Playing game and Debited "10" and Balance "210"</v>
+      </c>
+      <c r="E741" t="str">
+        <v>19-09-2026 03:01:16 pm</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="str">
+        <v>6aae56c2434caf29ae010d0e</v>
+      </c>
+      <c r="B742" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C742" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D742" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aae56c1434caf29ae010cfe , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E742" t="str">
+        <v>19-09-2026 03:02:50 pm</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="str">
+        <v>6aae5676434caf29ae010ce8</v>
+      </c>
+      <c r="B743" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C743" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D743" t="str">
+        <v>Answerd Correctly to Qst ID : 6aae5667434caf29ae010cc8, Reward : 10, Qst No : 2 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E743" t="str">
+        <v>19-09-2026 03:01:34 pm</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="str">
+        <v>6aae56c2434caf29ae010d10</v>
+      </c>
+      <c r="B744" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C744" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D744" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aae56c1434caf29ae010cfe , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E744" t="str">
+        <v>19-09-2026 03:02:50 pm</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="str">
+        <v>6aae56e2434caf29ae010d4b</v>
+      </c>
+      <c r="B745" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C745" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D745" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6aae56e2434caf29ae010d3b , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E745" t="str">
+        <v>19-09-2026 03:03:22 pm</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="str">
+        <v>6aae56cf434caf29ae010d25</v>
+      </c>
+      <c r="B746" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C746" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D746" t="str">
+        <v>Answerd Correctly to Qst ID : 6aae56c1434caf29ae010cfe, Reward : 40, Qst No : 3 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E746" t="str">
+        <v>19-09-2026 03:03:03 pm</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="str">
+        <v>6aae56e2434caf29ae010d4d</v>
+      </c>
+      <c r="B747" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C747" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D747" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6aae56e2434caf29ae010d3b , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E747" t="str">
+        <v>19-09-2026 03:03:22 pm</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="str">
+        <v>6aae57188f284258f96064db</v>
+      </c>
+      <c r="B748" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C748" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D748" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E748" t="str">
+        <v>19-09-2026 03:04:16 pm</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="str">
+        <v>6aae56e5434caf29ae010d5f</v>
+      </c>
+      <c r="B749" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C749" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D749" t="str">
+        <v>Answered incorrectly for Qst ID: 6aae56e2434caf29ae010d3b, Qst: How many broken boxes are there?, Submitted Answer: 13, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nOzdd2BUVfrw8e+dmkmZdEIIIYQeeq8iWBGw4SI2LOvadtVV1/Kqu4sru/pT17K64optRREVC+oqCNJ7KIZICYSSEFII6W36zH3/GGakhDRm5s4k5/PPTsg9cx/cME+ec859jiTLsowgCIIgtJJK6QAEQRCE0CQSiCAIgtAmGqUDOFPJMz0VvX/ys4cVvb8gCEKoEBWIIAiC0CZBV4F4BLoSULryEQRBCDWiAhEEQRDaJGgrEEHoaGbNmqXIfRcvXqzIfYXQd84EotQP8+sZitxWEBSl1L83z71FEhHaotEEouQP80M5I3g9Y2ebxjqrjgGgjk31ZUiCEDCB/iBX8t+6EPqanMJqyw+zyWwBINwQ1uqx5/vDXL9+HgDR17xwXu8jCIIgNM/ni+hrNu9k7Za2VRDnw1l1DFP2EkzZS7yViCAIguA/Pk8gy9duYfnarb5+22bVr58HTgc4Hd5KRBAEQfAfnyaQ6to6tmfvY9uuvVTX1vnyrZvkqT5Qa0CtEVWIIAhCAPg0gazcsB2Hw4nD4WTVxu2+fOsmeaqP8CEzCB8yQ1QhQodQbq/jx8osPi5dx8el6/ixMosKe+B+cRMEnz4HsmLdr1NXy9du5TfTLvbl2zfKW32o1ERccB+SSu1eC9n1NREX3IcmvrvfYxCEQMoxFfJ60Q9k1ubi4vTTGFRIjDP25Y8p0+kXnqJQhEJH4bMK5ER5Jdl7c9HrdOh1OrL35nKivNJXb39O3upj6HVo4rujjk11VyEuJw0b3/b7/QUhkD45sZ6b9/+LLbUH0Km0TI4ZwK1Jk7g1aRKTYwagU2nZVLufm/e/xqITG5QOV2jnfFaBrFiXiUuWmThmKAArN2xjxfpMZl831Ve3OMuZ1YdH5IX3iypEaHc+ObGel459g4TEbUmTuSf5MqLUhtOuqXOamV+ygoWl63nx2BIAbu40UYlwhQ7AZxXI8pPTV1Mmj2XKpLEArPDzbqwzqw8PUYUI7U2OqZCXC79DQuK59Jt5tOvVZyUPgCi1gce6XsNz6TcjIfFy4bccMBUpELHQETRbgRwtLMFksWKxWLHbHQDYHQ7MFqv3mtLySvYfyicywsD4EYMBiIwwkHMon0+W/EhSQpz3WkOYHq3GfVutVkNYmJ7wMD1pXZNbFfi5qg8PUYX4zns3L1P0/nct8l8VGyreKFqKS3ZxW9JkpseNaPb66XEjyDEV8nHpOt4oXsq8XncHIEqho2nRFNbcV9/lUH5hs9dNHj8SnU7rff39Txv417ufNjmmV/euvPD0Ay0J4zTe6mP49Y0mB08VYvr5Cxo2vi2eThdCVrm9jq21BwhT6bgn+bIWj7sn+XIWl21mc81+Kux1xGuj/Bil0BE1m0DSuibz39ee4aW3PuJ/P7kX5SRJYsKowYTp9QBERYYDcO2Uyd5x10+/BK1GDUBdvQkAi9XKpu2/IMvunSNXXTaRJ/5wG2F6XauCbq768BBViG8FuhJQuvIJFjvqDuFCZqyxd6PTVudiVBsYHdWbDTX72Fl/mMtjh/oxSqEjalEFEqbXMeeRuxgxOIMX5y3AbLFSVFLGC08/QI+0xrcK9u+TTv8+6d6vC4qO8+TzbyLLMjqdlsfunc2MqZPbFHRz1YeHklWI0h9+Ytqn/Si1VwOQpu/U6rHdwxLZUAPHbdW+DksQWrcLa/olE+jfJ50nn3+TI0eL+O2f5vL0g79lyuSxTY5bu3knz772LvUNZrqldOaFpx+gd3rbOua2tPrwEFWIEOokJADkM575aMt7CMEpVM+CafU23vTULvz31Tk8/+//snztVv7y0n/YtS+XP91zs3dx3MPucPDqO4v48vtVgHuH1tMP/rZNnXo9Wlp9eCi9FiKmfYTzlaSLAeCopazVY/NPjknSRfs0JsF3QvksmDY9BxJuCOMfT/yeXt1TmffhF/ywciOP3HXTWdfJLpkfVm4E4P47rueOWVe2OVA4pfoAUGup3zi/ZQPV7oV9U/YSIi+8X5wXIoSUEZE9USGRWXeQOqe5xesgNQ4T2+oOokJiZFQvP0cpnK9QPAvmvB4kNEZGADBm2EDv7qtT6XRaxgwbyNotO73Xng9vx13AtH1R69/gZI8ssSPL/8zVVopzKjFVWZCQMMTq6dI/DkO0XunQQk6CNopxxr5sqt3P/JIVPNb1mhaNm1+yAqvLzsToDOI0kX6OUuiIziuBrM/MAuDCscMAqGsw8dJbH2Gz2XnqwTuIMUYxccxQ1m7ZyYZtWVw37aIm32/x4sWUPNOz8W86HaiiOhF5wb3nE7K7Y6/T4f5fwefK82rZ/vkBindXeHfbeUiSRMrgBEbd0If47kaFIgxNf0yZzta6XBaWricjvGuzz4J8X7GDRSc2oJZUPJgyPUBRCh1Nmz9FzRYrO7JzUJ3c0rtl527mvvYe5ZXu3R6/5BxiziN3ccHoIagkie27cjBbrBjC2vgbqFpD1MV/amu4QgDs+TGfzIX7kV0yGr2alIHxGJPclWdtaQNFeyoozC6jeE85Y27JYMAVaQpHHDr6hafwWNdrePHYEv6ct4gcUyH3JF+O8YzprBqHifklK1h0YgMyMo93vZa+hi4KRS20d21OINt27cVqs9G7RzfeXfQtX/2wGlmWGTawLwBZew7w0JxX+M30i+mZnsrBIwVs27WXSWOHn/M93XNybT8TPdSF8rTPnh/z2fpRDkgwaHo6w2b0RBd++rSmzWQn6+vD7F6Wx5aP9gGIJNIKN3eaiAT8s/BbPi5dx+KyzYyJ6k1aWCLgXmTPrDuI1WVHLal4vOsMbup0gbJBC3511Oxu359mUOYh0TYnkA2ZuwA4eKSAg0cK0Gk13Hfrb7jlN+5dR598tYy3P/7KuwPLM6apBNJRhfq0T3leLZkL94MEk/8whF4TGv+NVxeuZczsfsR3N7L2P9lkfpJD54xY4tOC8+8VjG7qNJHhkT14o3gpm2v2s75mH9T8+n0VEhOjM3gwZbqoPDqAN/Ldn8OvZCjTMLNNCcQly94EAu52JHMfv++0ZztunTmNsSMGMeefb3vboGzI3IVLllFJYk+6R3uY9tnx+QFkl8yg6ennTB6n6nVBF8rza9izNJ8dn+cy5YmRAYiy/egbnsK8XndT6ahnR90hSm3uDJKki2ZkVC+xYN5BHDXX8WXJIQD+2H2oIlVImxLI3gNHqKyuQSVJ3DzjCn5/+0x02rPfqnd6Kgtef5b/LPiSRUt+pLK6hr0HjjCo3zkWyjuY9jDtY662UrS7Ao1ezbAZLf//ddiMXuxfeYzC7HLMNdaQmKbzp7Zs4YzTRIr2JB3YG/m7cMgu72slqpA2JZD1W3+mc2I8zzx6NyMHZzR5rU6r4aG7buSiCSN45uV32JCZ1aIEcs7dWO1Ee5n2Kc6pRJZlUgbGn5X8mqKP0JI8II5jWWWU5FTSY2zrujELQkfmqT40kvtEji9LDrW6CvHFcydtOg/EGBnBp28912zyONXgjN58/MZcoiLC23LLdsc77TOt5dM+A6d2x+WU2fF5bgAibBlThQUAY3Lrn/OJSXZPtTScfI+ObNasWYo+kSyEFk/1MTO5FzOTe+GQXd71kEBqUwVy68xpbbpZZIShRWOTnz3cpvcPFe1q2seznNWGNk3e3k5iSUwQWsxTfagliQfS3I9JfFlyiC9KDvJA2hDSw1s2O+H5heV8KhGfnUgotNz5TvvIskxJjv/Pm2+JiDh3X7OakoZWj/WM8byHIAjN81Qf1yf3Jj3cSJohipnJvXDKMm8ezQ5oLOJxbAWc77TPsayyoJn2Sc6IQ5IkivdWYDPZW5wQrfV2SvZWIkkSyf3j/Rxl6BDTWEJTzqw+PP7YfWibqpDz1WQCET/MftKOpn0MMXpSBidQmF1G1teHGTO7X4vGZX19CIfNSerQRAzG1h0o1h4tXrw4ZFt6C4HjqT5u7NLntCThqUI+K87lzaPZAduR1WgCET/M/tXepn1G3dCH4j3l7F6WR3x3I70uaHpTwKENRexZno9KLTHqhr4BijL4dYSffaHtzlV9eChRhZyzAhE/zP7T3qZ94rsbGXNLBls+2sfa/2RTnl/DsBm90Eec/vey1tvJ+voQe5bngwxjZmcQlybO6W5PhuxUtl9d9ohXFb2/P52r+vBQogoRayAKaI/TPgOuSAMJMhfmsGdpPvtXHqPLgHiMye5t27UlJor3VuCwOVGpJcbemkH/y4PngUhBCGbNVR8ega5CRAJRSHuc9hkwJY3O/WLZ8XkuhdnlFGSdgKxfvy9JEqlDExl1Q19RebRzbakEGpxWACLUrd+ernTl42/NVR8ega5CRAJRSHud9olPMzLliZGYa22U7KvAVOn+UAiP05PcPz7oKicheKyu3o0EXBkveqOdqqXVh0cgqxCRQBTUnqd9DEadaE8itMqyyp+RJEkkkDO0tPrwCGQVIhKIwsS0jyBAtaOBzLqD3tcxmvM/Ars9OLXjrlZSMe/oLy0apz2PHlmtIRJIEBDTPkJHt6IqG4fsBOCnqmyuTxyvcETB4dSOux8X7W/1eE+PLH9VISKBBBEx7SN0VMsqfz7ldZZIILg//JP04dyfNvi83kejUuGQXd7Ovb4kEoggBLH3bl6m6P3vWjTV7/cotVWzqz4Pvcq9gSSr/giltmqSdDF+v3cw00gqnugxQukwmiQSiNBiSn+YCe3Tj1VZuJCZFD0AkFlRlc3yql3cljRZ6dCEZogEIgghoC2VgN3iAEAb1vp/5oH8ZWFZpXvXyNS4YYB7PWRZ5c8igYQAkUCEZgViGkPwvfztpUhAr4kpytzfcgKTy4bZZcXuci+Q22UnZpft5BUypbYackyFRKrDmGB0H1AXqQ5jn6mQj0vXkaSLxtM51KDSoZXUAGhVagwqPeEqHd3DOgX6ryacJBKIn4lpH0EphzeXIEnKJRCAOfmfctBc0ux1l8QMQq/SeF9/W7Gdlwu/bXJMb0MyL/e43SdxCm0jEoggtEOWOhvFe8q9r8OiAr8VvHtYJxb2e4jnC77m24ptAEhIXBCdgUGlBSSMagMA1yWM8Y67IXECWsn90VTrNAMyZpedjTU53uMMrokfzdPdriNM1X62uIfi8RkigfiJmPYRlJSXeRyXU/a+zri0myJxhKl0zO1+I6OievFcwZeYXTaKrBW83ON2eho6NzpmQEQ3BkT8Gu9RSxmPHVmAjIxepeGJ1BnMTBgXqL+C34Xy8RkigQhCO3R4c/Epr0sUSyAeV8WPZEBEKo8dWcBh83Fm73+dOWnXMzVueJPjVlfv5q/5n1LvtJAWlsjLPW6nj6HpxqOhKFSPzxBnogtCO9NQaaH0QDUanRqNTk3pgSoaKpU/ArlHWBIf932IqXHDMbmsPJm3kOcLvsJ+8gn0U9llJ88XfMUjh/9LvdPC1LjhfNrvT+0yeYQykUAEoZ05srkEWZbpNrwTqcMSkWWZI1uaX8gOhAi1nhfSZ/NQynQAvqvYjks++2xnlyzzXcV2AB5Kmc4L6bPb1OZd8C+RQAShnTm8xT191XN8Mj3Hu39jP7w5OBKIh1Ht7jg9ztjXu/vqVHqVhnHGvqddKwQfsQYiCCGipqQBu8WBw+rE6XD/1u5yuHBY3VNAsizTUGmhPK8WXbiGrkMSAdCFayjPq2H30jwi4sKQJPdzFRq9GpXG/TukWiOh0avRhmmITvZ/J9y1NXsAmBQzAIA6p5n/K/gaq2znr92uJ0YTwaTo/qyu3s3amr3MTGw/i+btiUggghBC1r+9m8pjdc1e131kEmqtyvs6d30RmQub7uYalxrFJQ8P80mcTTG7bGyrO4QKiYnGDDbV7mdO/meU22sB2FWfz9zuNzIxuj8qJLbVHcTssmFoR1t22wuRQM7DqGnKPsS0fekCRe8vBFZ0cgRXzx3H5g/3kbuu0P2HEqQOTUSjUyNJErpw9z/pvhelesdlXJbmrTRsJgeyLOOwOTm2q4yTj1XQZ1JXxt/RH41e7fe/x9baXKwuO30NXZhfsoLFZZuRkRkR2ROAnfWHuf/gu8xKHE9vQzIHzMVsrc3lopiBfo9NaB2RQAQhhGj0ai68dxDJ/ePY9MFeHFYndSfMXPLQMGK7RjY6JrFnNIk9o71f15Q0sOr1LJBBrVUx7vb+9Ls4tdGx/rCuZi8AB8zFHDAXo5M03J8y1dv76qPStcwrWsbnZZtOGyMSSPARCcQH2lIJmMzubZXhhrBWj1W68hGU13tiCok9oln1ehZVhfV8N2czF9w1iJ7jmz5PJn97Kevn/4LN5CA6OYJLHhpGXLfAnXTpQmZ9zT7v170NyTyffstp23PvSLqI8ca+PJ33ibcNyvqafbiQUZ3siyUEB7ELSyFrNu9k7ZadSochhLCYlEiunjuOnuOTsVucrHlzF5v/uxeXw3XWtS6Hi83/3cvK137GZnLQc3wy1z43PqDJA2BPQwEV9jpUSNyWNJlFGY80+mxHH0MXFmU8wm1Jk1EhUWGvY09DQUBjFZonEohClq/dwvK1W5UOQwhx2jANFz0wlFE3ure85q4vopHHKpBl9/cARt3Yl4seGNqmNu/na231HpJ1sbzT5/c82vVqdNK5Y9BJGh7tejX/7fsgqfp41lXvDWCkQkuIKSwFVNfWsT17n/d1jDGwvwUKradUr6LLNb9t0XX6CPdpfimDEry7r06l1qpIGZTA0R2l3muVYNSE82X/x4lUt3zqdmhkdz7LeJQvy7f4MTKhLUQFooCVG7bjcDhxOJys2rhd6XCEZoRCl9SjO0sBSBvhPhvDZrKzdl42q/6VhaXOff5G2nD3947+XKpMkLjXN1qTPDwi1WHckXSRHyISzoeoQBSwYt2vU1fL127lN9MuVjAaoaUC3fCupYnLYXVSsq8SSZJIHZpIYXYZ6+fvxlRtBaA0t4oL7x1E6rBEJEmiZG8lDqszIFt2hfZNVCABdqK8kuy9ueh1OvQ6Hdl7czlRXql0WEIIK9pTjsPmJLZbJFlfH+LHl3ZgqrbSuV8cnfvFYaq28uNLO8j6+hCx3SJx2JwUnTwrRBDOh6hAAmzFukxcsszEMUMBWLlhGyvWZzL7OnF+iNA2BTtPAFB5tI7Ko3WotSpGXN+HQdO7A7D7h3x2fpHLvp8KThuTNiLJbzEN2fknv723EDxEBRJgy09OX02ZPJYpk8YCsELsxhLaSJZlCrLKvF/HpUZxzd/HM/jKdCRJQpIkBl+ZzjV/H09c6q+bNQqyypAb264lCK0gKhAfOVpYgslixWKxYrc7ALA7HJgtVu81peWV7D+UT2SEgfEjBgMQGWEg51A+nyz5kaSEOO+1hjA9Wo37/x6tVkNYmJ7wMD1pXZt+UEwILnUnTABEdfJPR9mywzWYa6xIksTAad0ZOatPo7uw4rpFcc0/xrNjcS57luZjrrFSdriGTr1ifBpP9ohXffp+QnATCcSH5r76LofyC5u9bvL4keh0Wu/r73/awL/e/bTJMb26d+WFpx/wSZxC4GR9cxiAC+8Z5Jf3P7rzBJEJBibdN4jk/vFNXqvWqhhzSz+6j0pi3X9+oWDnCZ8nEKFjEQnER9K6JvPf157hpbc+4n8/bQBAkiQmjBpMmN59EE5UpPu30GunTPaOu376JWg17t0wdfXu31YtViubtv/inWK46rKJPPGH2wjTi26kSmjr7qu6EyYObXA/vDfs2p5+qUL0EVque+ECbxPFlkjqE8u1z01g/+pjPo9H6FhEAvGhML2OOY/cxYjBGbw4bwFmi5WikjJeePoBeqSlNDqmf590+vdJ935dUHScJ59/E1mW0em0PHbvbGZMneyT+JR6nuHUD+D3bl6mSAwedy0K3GaFrG8O43LK3tf+qEIGX5ne/EWN0IVr2jxWEDzEIrofTL9kAgte/xs90lLIO1bMb/80t0VtS9Zu3sntD/+Ng3nH6JbSmQ9feybkk4fS9/aFWbNmtfrv4Kk+VGoJlVri0IYi73qIILQXogLxk/TULvz31Tk8/+//snztVv7y0n/YtS+XP91zs3dx3MPucPDqO4v48vtVgHuH1tMP/rZNnXqbEywPwwWyEoDAVz6e6qPP5K4A5K4t9FsVIghKCYoEkrLqfUXvX3TJ7/zyvuGGMP7xxO/p1T2VeR9+wQ8rN/LIXTeddZ3skvlh5UYA7r/jeu6YdaVf4hECw1N9SCqJIVf3QKVyVyAH1xcx5OoeRHdu/ZGxSk/9CUJjxBRWABgj3R8YY4YN9O6+OpVOp2XMsIGnXSuELk/10fvCFKI7RxDVKZxeE1OQXTLZ3x1ROjxB8JmgqEA8/FUJnEugKp/1mVkAXDjWfd50XYOJl976CJvNzlMP3kGMMYqJY4aydstONmzL4rppomlcqDqz+vAYdm3PNlUhKxz/Dfi0oyC0lKhA/MxssbIjOwfVyS29W3buZta9T/Hjmi2s3rSDm/7wF7bs3M0Fo4egkiS278o57eFDIbScWX14iCpEaI+CqgJpj7bt2ovVZqN3j268u+hbvvphNbIsM2yg+wCgrD0HeGjOK/xm+sX0TE/l4JECtu3ay6SxwxWOHGRbKY7ajci244CEpEtCEz0RSdspoHGYq60U51RiqrIgIWGI1dOlfxyGaH1A42jOuaoPj7ZWIYIQrEQC8bMNmbsAOHikgINHCtBpNdx362+45TfuXUiffLWMtz/+yrsDyzNGyQTirM/GevRZHNVrgTOPR1Whib0Yfdoc1BGD/RpHeV4t2z8/QPHuirP6NkmSRMrgBEbd0If47ka/xtFSp+68aiw5eKqQ3LWFZH93ROzIEkKeSCB+5JJlbwIBdzuSuY/fR+/0VO+f3TpzGmNHDGLOP9/2tkHZkLkLlyyjkqSAx2wrfhtL/p9BdiKpDKhjJqMKc/827bIcwVm9FkfVShzVawlL/we65Pv8EseeH/PJXLgf2SWj0atJGRiPMcn9oVxb2kDRngoKs8so3lPOmFsyGHBFml/iaKnmqg8PUYUI7UnIJpATNjNbqkootZqQgE76cMbHJpOoMygdmtfeA0eorK5BJUncPOMKfn/7THTas/+T905PZcHrz/KfBV+yaMmPVFbXsPfAEQb16xnQeG3Fb2PJexKQ0KU8gL7r40ia6NOukR01WI+9hK34LSxHngTweRLZ82M+Wz/KAQkGTU9n2Iye6MJP371mM9nJ+vowu5flseUj9/HASiaR5qoPD1GFCO1JyCWQ3XUV/N+h7WyoKsZ1xrSGSpKYFJfCkz1HMjCq6cZygbB+6890ToznmUfvZuTgjCav1Wk1PHTXjVw0YQTPvPwOGzKzAppAnPXZ7soDCUOf+WgTG38AUNJEE5b+HOrIwZhz78OS9xfUxgmoI3zzQVieV0vmwv0gweQ/DKHXhC6NXqcL1zJmdj/iuxtZ+59sMj/JoXNGLPFpgZ/Oamn14SGqEKG9CKkE8t6xvcw9mIlTljGoNUyM7UL3cPcHRr6plg1VxaypKGRDZTFzeo/md6kDFI3XGBnBp289R2REy6uiwRm9+fiNuSxZtsaPkZ3NenQuyE50KQ+cM3mcSpt4A876bGzFb2E9Opfw/l/4JI4dnx9AdskMmp5+zuRxql4XdKE8v4Y9S/PZ8XkuU54Y6ZM4WqOl1YeHqEKEtgqGfnanCpkE8t6xvTyTuxUJuLfbIB5OH4pRc3p32lqHjdfysni3YA9zct29p5RMIrfOnNamcZERhjaPbQvZVoqjeg2SyoC+6+MtHqdPfQLb8Q9wVK1Ctp84791Z5morRbsr0OjVDJvR8upr2Ixe7F95jMLscsw11oDuzjq1465aoyL7fy3boqvWuHfQH9pQ5LdOvUL7onQ/u8aSSEgkkN11Fcw9mIkEvDFgMtd1bvzDxajR8UzvMQyMiuehveuYe3AbY2M6MyAIprOCmaN2I+BCHTP5rDWPpkiaGDTRk3BULcdRswltwozziqM4pxJZlkkZGH/WmkdT9BFakgfEcSyrjJKcSnqMDdyhW6d23M1ZWdDM1WdzOWXRI0tolWDpZwchkkBeOLwDpyxzb7dB50wep/pN517srqvg3YI9vHB4Bx8PnRKAKEOXbC0GQGXo1eqxKkMvqFqObC067zhMFRYAjMmtXxOISY7kWFYZDSffIxBcTpmIWD1Drmp+3aMpKo2EyymjUgd+150gnI+gTyAnbGbWVxZhUGt4OH1oi8c9kj6UjwtzWFtZRJnN7NfdWaOm3e639w4MzwdXW87IPjnmHFuOW/Xb0nmEIXvjaP3YtlKpJUZc3ydwNxSEIBP0rUy2VJXgkmUmxnY5a82jKdEaPRPiuuCSZbZWHfdjhKFP0rsXq13mQ60e6zK7j2yVdM0veDcnIs7dvr6mpKHVYz1jPO8hCIL/BX0FUmJ1fzD0CG/53LxHz/BoVnGMYmu9r8MCYPvSBX5530DTGCcAKpzV65AdNS1eB5EdVThq1gEqNNEXNHqNZ/60JZVIckYckiRRvLcCm8ne4nUQa72dkr2VSJLU7LnggiD4TtBXID6YXEEK5LxGCJJ0SWhiL0Z2mbEee6nF46zHXgSXBU3spUjaxPOOwxCjJ2VwAg6rk6yvD7d4XNbXh3DYnHQdkoDBKM6NFwQP2VaKvfwrbMXzsBW/hb38K2T7CZ+9f9BXIMl694LqEVNNq8d6xnjeQzg3fdocHNVrsRW/hTpyMNrEG5q83n7iM2zF80HSoE+b47M4Rt3Qh+I95exelkd8dyO9Lmh6auzQhiL2LM9HpZYYdUNfn8UhCKEsUP3sgj6BjI1NRiVJbKwqptZha/E6SLXdyqbKYlSSxLjYzn6OMvSpIwYTlv4PLEeexJx7H876bPSpTyBpYk67TnZUYT32ojt5ILufSo8Y6LM44rsbGXNLBls+2sfa/2RTnl/DsBm90EecPp1lrbeT9fUh9izPBxnGzM4gLi3KZ3E0JtTPdhc6hkD2swv6BNJJZ7oeP2wAACAASURBVGBSXAprKgp5LS+LZ3qPadG41/KysLicXByfSkIQ9ccKZu4fJAlL3p+xFb+F7fgHaM744XNUrwWXBSQNYenPo0u+x+dxDLgiDSTIXJjDnqX57F95jC4D4jEmux+2qy0xUby3AofNiUotMfbWDPpf7r8+WIsXLw66J4AFoTGB7mcX9AkE4MmeI9lQWcy7BXsYGBXPbzo3/bzCl8cP8f6xvWgkFU/1Cnxri1CmS74XtXE81qNzcVStwlH54xlXqNDEXn6y/PVd5XGmAVPS6Nwvlh2f51KYXU5B1gnI+vX7kiSROjSRUTf09XvlAeKDXAh+SvSzC4kEMjAqnjm9RzMndysP7V3H7roKHkkfSrTm9JYV1XYrr+Vl8f6xvcjAM73H0D8yTpmgQ5g6YhDh/b9AtpfhqNmIbCsBQNIlo4m+wCcL5i0Rn2ZkyhMjMdfaKNlXganSfVJjeJye5P7xYsFcEE6hRD+7kEgg4O5pJSHx7MFM3i3Yw8eFOVwQl0L6yWaKeaZaNlYWYXE50Ugq/tZnDL/t2l/hqEObpE087/YkvmAw6gLankQQQo1S/exCJoEA3JnanzExSbxweAdrK4tYWX567yGVJHFxfCpP9RopKg9BEDoMpfrZhVQCARgQFc/HQ6dQbjOzpeo4x08+aNhZH8G42M5iwVwQhA5HqX52IZdAPBJ0Bq5KSlc6DEEQhCDgv352TQn6J9EFQRCEpinVzy5kKxChbYLlYbj3bl6mdAiCcJZQfd7Hn/3smiIqkA5CyecYxDMUQihQ+sS/86FUPztRgXQgwfBBfteiqUqHIAhNasu/E9lsAkAytP5oYl8lLiX62QVVAklZ9b7SIQiCILSaZct6kCQMFyl3+qkS/eyCKoEIgiCEIsv6lYCyCQQC388uKBJI0SW/UzoEQRCENnHV1mDN3ul9rTK2/vA7XwpkP7ugSCCCIAihyrJxDTgc7teb1hA+9VqFIwpcP7uAJZAhO/8UqFs1KnvEq4reXxCE9sk9ffXr62BIIB7+7mcntvEKgiC0kbO8DNu+3Ug6PZJOj23vbpzlZUqHFTABn8IKdCWgdOUjCEL7ZdmwEmQX+tETABnLxjVYNqwiYsaNPr9XMGzDP5OoQARBENrIss49fRU26VLCLrzU/WenTGm1d2IRXRAE4QyOogJksxnZYgGHHQDZYXd/7f4KZ3kZ9sO5SBER6Ie7j9qWIiKwHzpAwzefo05IxNPkUAoLQ9Jo3UM1WvfXBgOalG4tjsnzwGEwVSIigQiCIDSi5vXnceQfafa6sLEXIul03tfmVcuoe//NJsdouvcg5sm/tymuYOlnByKBCAoJ1aZ1QsegSelG/MvzqX37Ncwrl7r/UJLQjxyLpA8DJFSRkQAYLr/SOy58+gwkrbvScNXXAzKy1YJ1x1aQ3W3TDZdOw3jfIyffp+UWL14cdP9ugjqBlNvr2FF3iDJ7LQCJWiOjonoRr41SODLhfCjdtE4kEaElJH0Y0Q89hW7QMGr/8wqyxYLzeDExT/4dTbfGzyLS9s5A2zvD+7Wj6BjVL/wVZBlJpyPq7ocIv+LqNscUbD+7QZlAckyFvF70A5m1ubjOOCBFhcQ4Y1/+mDKdfuEpCkUo+EKg/zEEU+kvhA7DxVeg7Z1B9Qt/xVGQR8Wj9xL94BPeRfNzsWxZT83rzyM3NKBJSXUnnu49AxR1YARdAvnkxHpeLvwOl+wiTKVjrLE3qfoEAI5Zy9lae5BNtfvZWpfLY12v4eZOExWOWBCE9k6Tmkb8y29T8+Y/saxfSfU/nyV87y9E3f3gr4vjJ8kOO3Xv/hvT0iUAhF14KdEPPN6mTr3BLqgSyCcn1vPSsW+QkLgtaTL3JF9GlPr0M87rnGbml6xgYel6Xjzm/j9IJBFBEPxNMoQT8/gzNKT3pG7BfMyrlxH1uwfOvtAlY17tPjAt6vZ7iZg5O8CRBk7QJJAcUyEvF36HhMRz6TczPW5Eo9dFqQ081vUaMsK78ue8Rbxc+C0jInvQV0xnCULIGjXtdkXvv33pghZPqUqR7jVY/dBR3t1Xp31fp0M/dBSWrRu817ZXQfMg4RtFS3HJLm5NmnTO5HGq6XEjmJ10IU7ZxRvFSwMQoSAIAlgzNwGgH+M+AtbVUE/NK3+n+v/+gqu2xv290RPc127bpEyQARIUFUi5vY6ttQcIU+m4J/myFo+7J/lyFpdtZnPNfirsdWJ3Vjvmqi/DmpeJq64UJAlVZCf06WNRRSa0+D2CbQeLcLbtSxcE9H6nVj4teVBPtliw/fIzSCr0I8di3ZlJzRv/h6uyAgDb/j1E//Ep9KPGgaTClv0zssWCFNa6LbuhIigSyI66Q7iQGWvsfdaaR1OMagOjo3qzoWYfO+sPc3nsUD9GKSjBXrKXup/+ifXIJpBdp39TUqHveQFRlz6ONrm/MgEKHYoteweyzYomvRf1n36Iadk3IMvoBg5xf39PNlXPPk741GvRdO+BI+8Qtuwd3mqlNYLtmY/GBEUCKbVXA5Cm79Tqsd3DEtlQA8dt1b4OS1BYw9YPqV3+PLicSFoD+h4TUMenAeCsOIr1yCash9ZjPbIJ45Q/EzG26Xn0YGwFIYQWy8npK0feIRx5h5C0WiJn303EDPf54w1LPqd+4bveHVieMa1NIKHyrFRQJBDpZL8Y+YxnPtryHkL70LD1Q2qX/R0kiYjxdxE56X5UYcbTrnFZaqlf9yYNWz6gdtlcgGaTiCC0mezCun2z90tN9x7EPDrntGc7Iq67Cf3w0VS/MtfbBsW6fbO7epZav+Tcll92GpxWdyxqfavHtjZxBUUCSdK5D30/aml9H/38k2OSdMoeIyn4jr1kr7vykCRirnsFw+BrGr1OFWbEOOVptJ37U73kMWqXP4eu+yi0nQMznRUKUwyC79hzc3BVV4KkIuLaWUTeeo+3bcmpNN17Ev/qe9R//A4N3yzGVV2JPTcHbd8BAYlzdfVuJODK+JF+v1dQ7MIaEdkTFRKZdQepc5pbPK7GYWJb3UFUSIyM6uXHCIVAqlv5MricRIz73TmTx6kMQ64lYuxvweV0jw0ApacYBKioqmHFuq18suRHFi1Zzop1W6msrvHb/SyZm1AnJhH3j9eIuvP+RpOHh6TVEnXn/cS/OA91cgqWAO7GWlb5M8uqsgJyr6CoQBK0UYwz9mVT7X7ml6zgsa7Nf2gAzC9ZgdVlZ2J0BnGaSD9HKQSCq74M6+GNSFoDkZPub/G4yEkPYNqxCOuhDbjqy1u1O+t8iHYsgbf/UD7zPvyCbVl7cclntDqSJMYMH8j9d1xP355pPr2vKjKKhH8vQIqIaPEYbcZAEl57H9Py73way7lUOxrIrDvofR2jaXmsbREUFQjAH1Omo5ZULCxdzw+VO5u9/vuKHSw6sQG1pOLBlOkBiFAIBGtepvuEtx4TzlrzaIrKEI0ufRzILmz5mX6MUFDSZ9+u4PaHn2Xrz3vQ6bRcOHYYt8y4gltmXMGFY4eh02nZsnM3tz/8LJ99+5NP7x1x3U2tSh4eUkQEEdfd5NNYzmVFVTYO2YlDdvJTVbbf7xcUFQhAv/AUHut6DS8eW8Kf8xaRYyrknuTLMZ6xrbfGYWJ+yQoWndiAjMzjXa+lr6GLQlELvuaqLQFAndB4t9OmaBJ6YM1dg/Pkewjty2ffruCV+Z8gSRKzr5vKnTddTVTE6f2l6hpMvL/oWxZ9s5xX5i8E4MZrWv5sWahbVvnzKa+zuD5xvF/vFzQJBNw9rSTgn4Xf8nHpOhaXbWZMVG/SwhIB9yJ7Zt1BrC47aknF411ncFOn1u+vFoKYdHI3ndyGHXneMWJHXnuz/1A+r737KZIkMfexe7nionGNXhcVEc7Dd99E355pPPPKO/zrvU8ZPqgvfXq0/OS/UFVqq2ZXfR56lXttJqv+CKW2au8mJX8IqgQCcFOniQyP7MEbxUvZXLOf9TX74JR1MRUSE6MzeDBluqg82iGVMRkAZ0Veq8c6To5RGzv7NCZfK6p1H5GaYjz3IqxwurcWfInL5WL2dVPPmTxONfXi8ew/nM+iJcuZ9+EXvD730RbfK1TXmX6sysKFzKToAYDMiqpsllft4rakyX67Z9AlEIC+4SnM63U3lY56dtQdotTmziBJumhGRvUSC+btmL77aJBUWI9sxmWpbfE6iMtcjS1vC0gqdOlj/Rzl+fkgqwqAv05q/YOzHVFFVQ2ZP+8hTK/jzptafhjT7266hq9+WMPWnbuprK4hLqbprf7BeOJfayyrdO+8mho3DHCvhyyr/LnjJRCPOE2kaE/SwagiE9H3vADrofXUr3sT45SnWzSufu2/ke0W9L0no4qI93OUbVdUa2dpbh0Adw6LFVVIC+z8JQeXLDN62ICz1jyaYoyMYNTQDDZuy+bn3Qe4dOLoZscE4zM2+ZYTmFw2zC4rdpcTALvsxOyynbxCptRWQ46pkEh1GBOM7hMRI9Vh7DMV8nHpupPPybmndg0qHVpJDYBWpcag0hOu0tE9rPW/0AR1AhF8572blyl6/7sWTW3xtVGXPo71yCYatnyAtnN/DEOubfJ6c/YSGjIXgEpN1KWPnW+ofvVBVhUOl+x9LaqQ5p0od1ds3VJaPzWZlpLMRrI5Xlbh67ACak7+pxw0N7855JKYQehVGu/rbyu283Lht02O6W1I5uUebevgIBKIEHS0yf0xTvkztcvmUr3kMewle4mc9AAqw+lTEC5zNfVr/+1OHrKMcepf0HbOOMe7Ks9TfWhU7t8El+bWiSqkJTx7Itqyr+LkIEkK3Y0V3cM6sbDfQzxf8DXfVmwD3K2bLojOwKDSApJ3t+p1CWO8425InIBWcn/E1zrNgIzZZWdjTY73v8s18aN5utt1hKnOPtekJUQC6WBaUwl42C0OALRhrf9xaWvlEzH2dpAkan/8Bw1bPsC0YxG69PFo4rsD4KjIx5a3GdluAZUa49S/EDHmtjbdK1A81cfV/dzrOt/tr/VLFZKy6n2fvl9rFV3yO5++X1JCHABHi463emzByTGe9whVYSodc7vfyKioXjxX8CVml40iawUv97idnobGK7MBEd0YEPHr7rOjljIeO7IAGRm9SsMTqTOYmdD8hoSmiAQiNCt/eykS0GtiYE99jBhzG7q0kdStfBnroQ1Yc1djPfUCSYW+92SiLn0sqCsP+LX6UElwx9BYVJK7Avn+QC13DI0lNVpUIecyfFA/VJLE9l17qWswtXgdpLauge27clBJEsMH9fNzlIFxVfxIBkSk8tiRBRw2H2f2/teZk3Y9U+OGNzludfVu/pr/KfVOC2lhibzc43b6+GAXa8ATyJCdfwr0LYXzdHhzCZIU+AQCoO3cn7jZH+BqqMCWtxVnXSkA6qgkdOljg3rB/FSnVh+eZDGtTxTf7a/lw13+WQtpSyVQ73RvMY5Utz6h+avyiY+NZszwgWzZuZv3F33Lw3e37Knudxd9g9VmY8KoIcTFtLyrQbDrEZbEx30f4u8FX7Cs8meezFtIVn0ej6de610c97DLTv557Bs+L3P34poaN5y/dru+TZ16GxM0rUyE4GSps1G8p5yi3eVY6mzND/ATVUQ8YQOnEzHuTiLG3UnYwOkhkzzOrD487hwWi0Yl8f2BWo7V2BWM8Fc/njjKj2VHlQ7jLPffcT1qtZpF3yxn2erNzV6/dPUmPv/uJ9RqNfffPjMAEQZWhFrPC+mzeehkG6fvKraf1RcMwCXLfFexHYCHUqbzQvpsnyUPCGAFkj3i1UDdSvChvMzjuJyy93XGpe3/iV5fa6z6APeDhP6uQlrrm9LDSMDMzsHV3bpvzzQevusmXpm/kGdeeYf9h/P53U3XYIw8vTdVbV0D7y76hs+/+wlZlnnk7pvo3Y6fQjeq3dN544x9vbuvTqVXaRhn7Mvq6t3ea31JrIEITTq8ufiU1yUigbTSuaoPjzuHxQbNWkil3cKGymLv6zhtcJ3jfeM1lyFJ8Nq7n7JoyXK++mENo4b2p1tKEgAFRaVs37UPq82GWq3mT/fczKyrLlU4av9aW7MHgEkx7rNG6pxm/q/ga6yynb92u54YTQSTovuzuno3a2v2MjPx/BbNzyQSiHBODZUWSg9Uo9G551VLD1TRUGkhIi64PliC2bmqD49gqkK+L83DcfLc+R9O5HNrSvAtPN9w9WUMG9iXeR9+wdadu9m4bddp31dJEhNGDeH+22e268oDwOyysa3ukLu9kzGDTbX7mZP/GeX2WgB21eczt/uNTIzujwqJbXUHMbtsGNq4ZbcxIoH40PGrJip6/87/2+DT9zuyuQRZluk2vBOyLJOXeZwjW0oYNL31nXI7ouaqD49gqUK+KT3y6+vjh4MygQD06dGN1+c+SmV1LT/v3u990LBTQizDB/VrVwvmTdlam4vVZaevoQvzS1awuGwzMjIjIt1H7O6sP8z9B99lVuJ4ehuSOWAuZmttLhfFDPRZDCKBCOd0eIt7OqPn+GRk2b0Gcniz7xJIqData6nmqg+PYKhCSqwNbK8pJUzlrja31ZRSYm0gWe/fA4nOR1yMsUXtSdqrdTV7AThgLuaAuRidpOH+lKne3lcfla5lXtEy7w4szxiRQIKcryuB5rS28qkpacBuceCwOnE63AvkLocLh9XdZ0eWZRoqLZTn1aIL19B1iLudvi5cQ3leDbuX5hERF+Z9ulejV6PSuDf0qTUSGr0abZiG6OTGP3xCvWldS7S0+vBQugr5tvQILlnmsk7dkGX4/kQe35Ue4d5ugwIah9AyLmR3p/KTehuSeT79ltOe7bgj6SLGG/vydN4n3jYo62v24UJG5aMjD0QC6aDWv72bymN1zV7XfWQSaq3K+zp3fRGZC/c3OSYuNYpLHh7W5DXB2LTOl1pafXgoXYV8c/wwANcm9UTGnUC+OS4SSLDa01BAhb0OFRKzkybxYMo0dNLZH+d9DF1YlPEI/y5aysLSdVTY69jTUMDgCN8c9ysSSAcUnRzB1XPHsfnDfeSuK3T/oQSpQxPR6NRIkoQu3P2j0feiVO+4jMvSvJWGzeRAlmUcNifHdpV5+xT1mdSV8Xf0R6M//YGm9qapBHhqx12tSmLBrqoWvafWDz2yDptqaHDaMTkd2F3uBXK77MTkdLenkWX39NXuugqiNDouiu8KQJRGxy915bxTsIdkfYT3nK9wteaUTq4qwtUaItRaeoY33Spd8K211XtI1sXy9+43MSqq6S3XOknDo12v5pKYwfwl/xPWVe8VCUQ4Pxq9mgvvHURy/zg2fbAXh9VJ3Qkzlzw0jNiujZ+3ktgzmsSev35Q1JQ0sOr1LJBBrVUx7vb+9Ls4tdGxHcmpHXe/2lfTzNVnc7hkn/bIemTfevbXN5/EpiamoT+5BjI1MY3FJQd59mDT58v3i4zlnUGX+CROoeWMmnC+7P84keqW74gcGtmdzzIe5cvyLT6LQySQIOE87l6wVncO7CmLvSemkNgjmlWvZ1FVWM93czZzwV2D6Dk+uclx+dtLWT//F2wmB9HJEVzy0DDiukUFKGrledZwzqxEHC6ZxHANt7dg3aMpGpWEwyV7O/e2Vc/waL4feTV/PrCFz0tyAXdz24sTUjGoNEgSRGvcTybf1KWPd9ztXTPQnUwmNQ4rsgxml4PV5ce8TXFvSO7Dc33HYVD77mNk1LS2tRXvaO5IuqhN4yLVYW0e2xiRQIJE/eKPAIj+45MBv3dMSiRXzx3Hxvf2cHhzCWve3EXpgUrG3prhnbLycDlcbP04h30/FQDuHVoX3DWwTZ162yONSuK+UcHV+dWg1vBq/4mMj03mqQObMDkdFJjrmD/oYvpGNJ7ohhoTGWpM9H59xFTDPbtXIwN6lZq5fcYyO0i3+QqBI/7VBwHn8WLMa5YDEDnrtoBXIeBu1X7RA0OJ62Zk+2cHyF1fxJjZZ3e4lWXIXV8EwKgb+zLk6h6BDlVoo5nJvRhiTODe3as50FDFVdv/x0sZE7g2qWeT45aVHeWRfeupc9joER7NO4MuJiPSt0ly+9IFPn0/ITBEAgkC9Ys/AofD+1qJKsRDH+FeuE0ZlODdfXUqtVZFyqAEju4o9V4rhI7eETF8N+oq/l/OJr4pPcz9e9ayrbqUZ3uPRas6/f9vu8vFMwe3sqAwB3Dv0HoxY0KbOvUKbXPmdnfPlGmwPEMluvEqzFt9aDSg0WBes9y7HqKEozvd7dLTRrgXcG0mO2vnZbPqX1nebrxpw93fO/pzqTJBCuclUq1l3sDJPNVzJABflBzE1chxfy5kvig5CMBTPUcyb+BkkTwCRMlt7q25t6hAFOapPgyXudsym3/6QbEqxGF1UrKvEkmSSB2aSGF2Gevn78ZU7T7GqTS3igvvHUTqsEQkSaJkbyUOq7Pdb9ltr6K17sXzC+NSvLuvTqVXqbkwLoUfy456rxUCp6kP8mB5jkokEAV5qw+VisiZs0GlwrxmOeZVy4icORt1l64BjadoTzkOm5O4tCiyvj7EvpUFIEPnfu757uP7K/nxpR30v7Qbsd0iqTxaR9GectJGJAU0zmASLFMJbbGizL0R4vJEd9PBWoeNPx/YjNXl5IV+E4jThnFZQjd+LDvKT+UFQdsbS1COmMJSkLf6uGQq6i5dUXfuguGiKeByUf/lwoDHU7DzBACVR+vY91MBao2K0Tf3Y/pfRzP9r6MZfXM/1BoV+34qoPJo3WljOppQmWI4F5PTweaqYlSSxMXxqaypKGTS1q/4+vhhfjiRzyWZS1hTUcglCamoJIlNlcXehw8FwUNUIAo5q/o4KXLWbYpUIbIsU5BV5v06LjWKyfcPOe3ZjsFXptN1cAJr52V726AUZJUhy7K3L1ZHEizTCG2xobIIi8tJ/8g4XsvL4qPCHGRgbExnALZWH+fWXcu5rWsG/SJi2VdfyYbKIqYk+uYJZqF9EBWIQs6sPjyUqkLKDtdgrrEiSRKDpqdzzT/GN/pgYFy3KK75x3gGTU9HkiTMNVbKDrf+aWtBWT+Vu6ev9tVXsqAwB61KzV96jeaL4dP4Yvg0/tJrNFqVmgWFOeyrrzxtjCB4iASigHNVHx6Rs25z78hatQxncWFAYjq68wSRCQam/XkUY27p1+gWXg+1VsWYW/px5TNjMCaFd9hprFDlkmVWlh/zft0vMpalo67m92mDUEkSKkni92mDWDrqavpF/vqg4cryY42euy10XCKBKOBc1YeHElWIPkLLdS9cQHL/+BaPSeoTy7XPTUAnngcJKbtqyyizmVFJEvd2G8SyUdc0+mBgRmQcy0Zdw73d3ImlzGZmV21ZI+8odFQigQRYc9WHR6CrkMFXpns78LaGLlzD4CvFCYWhZEV5ASlhkXw+bCpzeo/29rxqjE6lZk7v0SwZMZ00g1FMYwmnEQkkwJqrPjyU3pEltF/RGj2rxsxgfGzTDTNPNTI6ieWjr8GoEc+DCL8SCSSAWlp9eCixFiK0f79PG0SURtfqcVEaHb9PEwdMCb8S23gD6NSnzluyPddThZh/+oH6Lxf65On0925edt7vIQiCACKBBMypHXcljZaGLz9p0ThJ416gNq9ZrlinXkEIpFHzDyl6/+33Nn3Cn/ArkUAC5NSOu6Zl37T+DRyO8+qRddeiqW0aJ4SulFXvKx2C0M6JBBIIDgfquAQiZt5yXm8jqTXuJKQR/7cJ7V+gKwGlK59QJD6JAkGjIXL2XUpHIXQQRZf8TukQhA5CJBBB8AGluvKGcj8uIfSJbbyCcJ6UbOkeyu3khdAnKhBB8JG2VAOytQEASR/R6rEieQhKEwlEEBRkyVkBEhiGzFA6lJBWYXKys9hMmcmBBCSEaxiZYiDOIE7L9CeRQPzg+FUTlQ5BCBHm3d+BJIkE0kb7y63My6xgW5EJ1xmNglUSjOkazv2j4+mbIFqw+INIIIKgEJepCmveZu9rVXhsMyOEU322u5rXtpTjkiFMIzG6azipRveDt8dq7WwrNLHlmIltRWYeHhfPjQNjFI64/REJxIc6/2+D0iEIIcSydymcPCbWsncZ4aNuVjii0PHZ7mpe2VyOBMweHMOdI+KI0p2+J6jO5uL9nZUs+qWaVzaVA4gk4mNiF5YgKMS8+3+Nvhaatr/cymtb3Mlj7sVJPDQu4azkARClU/HwuASevTgJCfjXlgpyK6wBj7c9EwlEEBTgrD2OrWAnkjYMSRuGrWAHztrjSocVEt7aVoFLhlsGx3BF77OPXT7T1N5R3DQ4BqdLZl5mRQAi7DhEAhEEBVh2/w9kF/q+l6DvczHILix7vlc6rKBXYXKSWWgiTCNx54izT1E8l98Nj0OvkdhaaKLS7PRjhB2LSCCCoADPlJVh0FUYBl112p8J57az2IxLhtFdwxudtjoXo17FqC7huGT4udjsxwg7FrGILgg+5Cg/gmwzIdtNyE67+w+ddmSbyf1alnHWHsdeshcpLAp9rwsBkMKisBfvoWHz+6iNnUGS3H+uCwe1e2eRpNYiacORdOFoEnoE/O8WDE40uDcddIvWtnpsWoyWjQVw/OR7COcvaBKI6CUktBfV3zyBo/RAs9eFZVyOdPKI2LCMyzFnfUXt8uebHKNJ6kvsrDd9EmdIkk7+r9zkVY3yDJGavOrcRk27vY0jfWP70gWK3r8xQZFAlO4lJJKI4CuahB4k3P0VtT/8DVPWl+4/lCT0vScjaQ0gSajC3Au/4cNv8I6LGDUb6WSl4bLUgSwj281YD64F2f3RFz5sJsbpf3O/TweVFOH+yDpaY2/12IJq+2nvIZy/oPovGegPctFLSPAHSWsg+toX0XUfS80Pc5BtJpxVx4id9SaaTr0bHaNNGUx0ymDv146KPKo/fwBkGUmjxzh1DuEjbwzUXyFoDU82oJJge5GJOpurxesgtVYn24tNqCQY3uX8EnCgKwGlK5+miEV0QfATw9AZJNyzBE2n3jjKlEzWdgAAC39JREFUDlH+7nUtWii35Kyg/J0Z2Ev3o4lPJ/6er0XyOCk+XM2YruFYHDLv76xs8bh3d1ZhdciMSw0X/bF8KKgqEKFjULpXWCA7BmgSe5Fw11fU/O/PmHf/j+ovH8ZWsAPjFX/xTll5yE47tT/+A9O2hYB7h1b0Vc+1qVNve3b/6Hi2FZlZ9Es1fRP0TG3mWZCluXV8vrsatUri/tHxAYqyYxAViCD4maSPIGbmv4i69HEAzLu+Btl19oWyy/09IOrSx4mZ+S+RPBrRN0HPw+PikYFnVpfy2pZyaq1n//estTp5ZXM5f1tTigw8Mi6B3vGiqaIvhXwFUlTrXhhLMbZ+W5+grED3DlO68lEZogHQ95jg3X11KkmjR99jApb9P3mvFRp348AYJCRe21LOol+q+WpfDaNSwr3bewtq7GwvMmF1yKhVEn8al8Csgcr9Ny06XgZASudExWLwh5BPIB9kVQHw10mdFI5EEJpm2b8SAH2/SwFwWWqp/eFvyA4r0Vf9A1V4LPq+l2DZ/xOWA6sIH3mTkuEGvRsGRjMsOYx5mRVsLTSx8WjDad9XSTChm7udu9KVxweffQfAXx9uX+fVh3QCKaq1szS3DoA7h8WKKkQIWrLNhC1/K0gqwnpPxnpoPdXf/D9cdScAsB37mZhrXySsz0XUSCpseVuQbSb3g4TCOfWJ1/P6tC5Ump38XGz2PmjYKULD8C7BcaBU0fEylq7eBMCdN17drqqQkE4gH2RV4Th5iswHWVWtrkLE8x9CoFiPbEa2W9B2zqBu3b8xbf8EZBld2mgAbEe3UbnwTsJH3YI2qS/24zlYj2wm7GS1IjQtzqDm0p6RSofRqA8++w6Hw+l93Z6qkJBdRPdUHxqVhEYlsTS3zrseIrRfzuPFOI8XKx1Gq1kPrALAfjwH07aFSGotxsufJP63nxD/208wXv4kklqLadtC7MdzThsjhC5P9aHRqNFo1Cxdvcm7HtIehGwC8VQf0/pEMa1PFA6X7F0PaalZs2aJhwlDTP3ij6hf/JHSYbSO7MKSu9r7pSapL/H3LCFiwt0gqUBSETHhbuLvWYImqa/3Okvu6sZ3awkhw1N9TLt4AtMunoDD4fSuh7QHIZlAPNWHSoI7hsZy57BYNCqJ7w/UcqwNLQ6E0OA8Xox5zXLMa5aHVBViL8rGVV/uThTj7yLhnm/QJvU76zptUj8S7vmGiPF3gaTCVV+OvShbgYgFX/BUHyqVijtmXcmdN16NRqPm+5UbOVZcqnR4PhGSCcRTfVzZ10hqtJYUo5ZpfaJwyfDhrtZVIULoqF/8ETgc4HCEVBVi2b8KdXQX4m//GOOUp5A0unNeK2l0GKc8RfzvPkcd1w3LgdXnvFYIbp7q48pLLyC1SxIpnROZdvEEXC4XHy5uH2e/hNwi+pnVh8edw2JZmlvH9wdquWNoLKltaPcsBC9P9YHG/SNrXrOcyFm3oe7cReHImqcyRJP4h6VIYc2fnuehSx1O4r3fYdr5mR8jC26j5h9SOoQ2O7P68LjzxqtZunoT36/cyB2zriS1S5KCUZ6/kKtAzqw+PEQV0r55qg/DRVMwXDQlpKqQiAl3typ5eEhhUe51EiHknFl9eLS3KiSkKpBzVR8eogppn7zVh0pF5MzZoFK510JWLSNy5mzUXboqHWLIqt0Uo+j9jROqz/qz7ff2UiAS3zlX9eHRnqqQkKpAzlV9eIgqpH3yVh+XTEXdpSvqzl3cVYjLRf2XC5UOTxBOc67qw6M9VSEhU4H8//buJjSKM4wD+P+dnc0mq6khG5MaoxWs9RIKjSQSpBdpoVV6aquWioLtQRDaWDwUeujHWYlCLZRiQdDUUIVCMYIFe6gakxAPEUSsB41J0LCbbhKz67of08PurBvzsZOJO+87O//fKZB9Jw9Lkof/vjPPWyx9mJhCysuc9JGzctc+5VJIqW8JNx98LcXPmS8JlJLs5FMqxdKHqVxSiGsSSLH0YWIKKS8vpg+TSilE5kQDTlNQS7H0YSqXFOKKBGI1fZiYQsrDQunDpFIKcfIfOZuGmqymD1M5pBBXJBCr6cPEFFIeFkofJpVSCJHV9GEqhxSifAIpnLjr1wROW2wIfk0AyJ5Gxkm97lMsfZhUSiFek3l6HwCgVW6QWocKCifu+nUdp3+/aGmdP/dcU8+Va66c1Kt8AymcuHvh9uSS15szsnheiLvk08e7OxdtCmYKif91EU/On8GqL752sEpvS4wcBQBUvf6j5ErkK5y4e6Fn6dMDzBlZbpvUq3QDSWUMrA7q2G9h32MxuiaQyhjQc6nEKbKfpHXr/fRW04eJKcR5maf3kRzvBgAEmo54OoWkUmmsrq3B/o93Lus6us+HVCoNXZd/holVSjcQXRM42ForuwxymNX0YWIKcV5i5ChgJPNfezmF6LoPB/d9KLsMKZRuIOXC6SQgO/ksRz59ABC6HzPnz1paJ/TsHpebZmS5VT59iOx7nhzv9nwK8So2EFJKfuIugNilP5Z+gdyMLKaQ0jHTh78h+/Fi8vEZz6cQr2IDIXWkUvDV1mHFR58u6zLCp2ebkM5f75ftefrwIbD2MCB8SI53Izn+GwJrD0Or2ii7RHIQ/8JIHbqOlXs/l10FLaIwfZjNwl+/O5tCRjuZQjxGqQbC42WJ1DUnfeQEmo54KoW07tgvuwRlKPEkOmcJPReJpXH53hOcHYqiayiKy/eeYCKell0W0fP0Uf/JrCahVW6Av343YKSRGO2UWCE5TZkEoto/cqfdCSdwsi+C/tEYcs9N5mkC2NoUxKG2EDbXBeQUSJ62UPoweSGFDPScll2CcpRpIF527lYUnb1hZAygUhdoawpiXW70ysOpJPpHYuh9GEP/aBwd7SHsaS7PUdikrvn2PgqZKYR7Id7CBiLZuVtRHLsehgCw980aHNhSi+qK2Z8sTj/L4NTgBLqGojh2LQwAZdFEHn3wtuwSyIJi6cPkhRRCsymxB+JVd8IJdPZmm8cP2xvwZXvdnOYBANUVGjra6/D99gYIAMd7I7gbSTheL3nTQnsfL+JeiPcwgUj0U38EGSObPN7bVF309e9vqsadcAJdQ1Gc7IvgxA53Pm396p//yC6BLLKaPkxMId7CBCJJJJZG30gMlbrAgS3W53191lKLgC5wYyTGu7Oo5KymDxNTiLcwgUgyOBZHxgDamoLzfmy1kFcCGlobg7g6PIObY3G8s3FlCaskLyucuCtEBRIjxy2tE6ICAGdkeQEbiCTjM9l5T+ttHLf7Wo0fV4eBR7lrEJVC4cTdZ49+XfoFjCRnZJU5NhBZzKNJjEVfNS9zibOnm5CnGEloFWsQaOpY3nWEP9uEBE8ELUdsIJI0rMi+9Q8mk0teOxxNzroG0Usn/Ais/0Z2FaQ4bqJL0rKmCpoABkZjmH6WsbxuKpHGwFgMmgBaGqtKWCER0eLYQCQJBX3Y2hTE05SBU4MTltf9MvgfEikD7euCqK1yz9GXRFR+2EAkOtQWgk8T6BqK4tK/00Vf33N3Gt23ovBpAofaQg5USES0MDYQiTbXBdDRHoIB4Nsrj9HZG8ZUYu7HWVOJNI5dD+O7vx/DAHC4vQ6bQhyqSERycRdWsj3NNRAQ6OwNo2soigu3J9G6Npi/vXd4MomB0RgSKQM+TeCr9jrsal4luWoqN1PX3D9bjZzHBqKA3c2r8NaaSpzsi+DGSAxXH8zM+r4mgG3rs+PcmTyISBVsIIp4IxTAiR2NmIincXMsnn/QsH6FjpbGKm6YU0m8si0quwRyMTYQxdRW+TiehIhcgZvoRERkCxsIERHZwgZCRES2sIEQEZEt3ER3QOvP92SXQET00jGBEBGRLcIwDBsnUhARkdcxgRARkS1sIEREZAsbCBER2cIGQkREtrCBEBGRLWwgRERkCxsIERHZwgZCRES2/A+i5p1aVjc1wAAAAABJRU5ErkJggg==</v>
+      </c>
+      <c r="E749" t="str">
+        <v>19-09-2026 03:03:25 pm</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="str">
+        <v>6aae57188f284258f96064dd</v>
+      </c>
+      <c r="B750" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C750" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D750" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E750" t="str">
+        <v>19-09-2026 03:04:16 pm</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="str">
+        <v>6aae57238f284258f96065eb</v>
+      </c>
+      <c r="B751" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C751" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D751" t="str">
+        <v>Started Playing game and Debited "10" and Balance "200"</v>
+      </c>
+      <c r="E751" t="str">
+        <v>19-09-2026 03:04:27 pm</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="str">
+        <v>6aae57368f284258f9606646</v>
+      </c>
+      <c r="B752" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C752" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D752" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aae57368f284258f9606636 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E752" t="str">
+        <v>19-09-2026 03:04:46 pm</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="str">
+        <v>6aae57318f284258f9606620</v>
+      </c>
+      <c r="B753" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C753" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D753" t="str">
+        <v>Answerd Correctly to Qst ID : 6aae57268f284258f9606600, Reward : 10, Qst No : 2 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E753" t="str">
+        <v>19-09-2026 03:04:41 pm</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="str">
+        <v>6aae57368f284258f9606648</v>
+      </c>
+      <c r="B754" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C754" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D754" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aae57368f284258f9606636 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E754" t="str">
+        <v>19-09-2026 03:04:46 pm</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="str">
+        <v>6aae57498f284258f9606683</v>
+      </c>
+      <c r="B755" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C755" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D755" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6aae57488f284258f9606673 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E755" t="str">
+        <v>19-09-2026 03:05:05 pm</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="str">
+        <v>6aae57448f284258f960665d</v>
+      </c>
+      <c r="B756" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C756" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D756" t="str">
+        <v>Answerd Correctly to Qst ID : 6aae57368f284258f9606636, Reward : 40, Qst No : 3 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E756" t="str">
+        <v>19-09-2026 03:05:00 pm</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="str">
+        <v>6aae57498f284258f9606685</v>
+      </c>
+      <c r="B757" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C757" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D757" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6aae57488f284258f9606673 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E757" t="str">
+        <v>19-09-2026 03:05:05 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E733"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E757"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E757"/>
+  <dimension ref="A1:E773"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13268,9 +13268,281 @@
         <v>19-09-2026 03:05:05 pm</v>
       </c>
     </row>
+    <row r="758">
+      <c r="A758" t="str">
+        <v>6aae574c8f284258f9606697</v>
+      </c>
+      <c r="B758" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C758" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D758" t="str">
+        <v>Answered incorrectly for Qst ID: 6aae57488f284258f9606673, Qst: How many broken boxes are there?, Submitted Answer: 8, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nOzdd2AUZf748ffMzrZsGiGUEFroIF0RBAsCFqzoIWI58QTLHZynnvq1nZ6c+lPPeqeelQPvjlPUExFFlN6LCEgREAgtBRJC+rbZnd8fk10DpGyS3Z3d8Lz+2iTzzHyiYT/7eaqkaZqGIAiCIDSQbHQAgiAIQnwSCUQQBEFoFMXoAAQhHmUu/sDQ5+eMnhy1Z71/84KoPasmU2aPNfT5Qu1EBSIIgiA0iqhABKEJolkJgLGVT2MqAa9LBcBsa/hbjdGVj1A/UYEIghAxBzYe5eDGo0aHIUSISCCCIETMvjV57FubZ3QYQoSILixBECLCVeYhd3th8LUtyWJwREK4iQpEEKLsoLOMg84yo8OIuOz1+fh9Gn6fRvb6fKPDESJAJBBBiLK/HdjC3w5sMTqMiNu3Jrfaa9GN1RyJBCIIUXTQWcaneXv5NG9vs65CKopcHN1djGIxoVhMHN19gooil9FhCWHWbMZASlenGvr85BHFhj5fiA9/O7AFVfMHX7/c+wKDI4qM/Wvy0DSNjoNbo2l6F9b+tXn0uzLL6NBizoQJEwx57pw5c5p8D1GBCEKUBKoPRZJRJLlZVyH71urdV12HZ9B1eDv9e6Ib6zRGJY9wPbvZVCAB0a4EjK58hPgRqD4mtusBwEe5e+KuCinJq8DrUlHdPnyqvpG3X/Wjun0AaJpGRZGLwuxSLAkK7Qe0AsCSoFCYXcK2r7NxpNmQJAkAxWpCVvTPsSZFQrGaMNsUUjIcBvx2xglHNdAQ4UpczS6BCEIsClQfJkliWqcByJLEp3l7+STvZ6Z1GkBWQrLRIYZsxdvbKDpcf+XU+Zw2mMxy8PWeFTms//euOtukdUhi9H2DwhKnEHkigQhCFFSvPgLJYnxGNz7K3cMbB7fGTRWSkuHgmunnsWbmTvYsP6J/U4IOA1uhWExIkoQlQX9b6Xlxh2C73pd0ClYankoVTdNQPT4ObymAqhOJelzUnuG390GxmqL6OwmNJxKIIETYqdVHwL2dB8ZlFaJYTVx4dz8y+qSxesYOVLePsmNORv9hEC3aJ9bYplXXFFp1TQl+XZJXweLXN4MGJrPMeZP60GtUhxrbCrFLDKILQoQFqo8bMrqflCQ62ZMYn9ENn6bxxsGtBkbYON0vyGTcM8Np0T6R4pxy5j25JqSB8gMbj/LFn9ZQdKiMlAwH1/5luEgejZCTX0BOfoGhMZzRCUTzHMVb+Bme3Dfx5L6Ft/AzNO8xo8MSmpHaqo+AezsPRJFkPsn7mezKUgMibJrUzESumX4eXYdn4HX5WPrGFtb8cwd+1X/atX7Vz5p/7mDRqz/gqVTpOjyDcc8OJ61jkgGRx78ZH81jxkfzDI3hjEwgvvKtVO64nrKNvXHunowr+3Fc2Y/h3D2Zsg29qNw5Hl/Fj0aHKTQDtVUfAfFehYC+VfvF0wYyZGJPAPasyEHTTr9O0/SfAQyZ2JOLpw1s1Dbvgl59fL1kNV8vWW1oFXLGJRBP7ttU/DgKtXgJkmxFSRuLpd1ULO2moqSNRZKtqCcWUbF1FJ68t40OV4hj9VUfAfFehQRYHWYAMvulB2dfVWcyy2T2Sz/pWqFxZnw0D1X1oao+Q6uQMyqBeHLfxpX9CGh+LJnTSByyi4Te/8WW9Sy2rGdJ6P1fEofswtJuKmg+XPsfEUlEaLT6qo+A5lCFABzcpJ/70ens1gB4Kr0se3Mri1/bjKvMo/9ssP6zgz+IM0IaK1B9KIoJRTEZWoWcMQnEV74V14HHAQl7j3ewdX4GSUk57TpJScGW9Sz2Hm8DEq7sJ/BVbIt6vEJ8C7X6CIj3KkR1+8jbWYQkSXQY2IojWwv49MGV7F2dS/aGfP73f6s4srWADoNaIUkSeTuKgosPhYYJVB9XjBrBFaNGGFqFnDEJxH1wOmg+LJlTMbeqfxWmudWNWNr9FjRVbysIDRBq9REQ71VIzvZCVI+PFh0T2fy/vXzz4vdUFrtp2yuNtr3SqCx2882L37P5f3tp0TER1eMjp+qsECF0gepDlmVun3AVd0y8BkUxMX/RKg7nRr+qOyNGsDTPUdTipUiyHWv7h0JuZ+3wMJ78GagnFqN5jyGZW0cwSqG5CFQfAGZJ5s2DoU3IMEv657lP8/Zyb+eBdLLHz+ykQ5v02YtFB8soOliGySxz9g096HdlZwC2fXWATZ/sYed3h05q0+nsNkaEG7cC1cc1l15Ih3b6f7srRo1g3rcrmDlnPn+6b3JU4zkjEohaugrwY0odWWO3VW0kJRUl5SLUEwtRS1ZjTr8uckEKzUb1HXf/lVP31h01UTV/XO2RpWkahzb/0gef1iGJkVMHnDQ9t/9VWbTvn86yN7cGt0E5tLkATdOC+2IJdTu1+gi4Y+I1fL1kNfMXreL2CVcFE0s0nBEJRHPrO4PK9m4Nbivbu8GJhWjunHCHJTRDquanjTWBqZ36N+k+iiyjan4UKfZ7mQv2leAscSNJEn2v6Mw5E3rUOAsrrWMS1z4znO/n7GH71wdwlrgp2FdC625iQ9JQ1FR9AGS2bWVYFXJGJBAIfMKpYXJ6varaiE9JQggUSebhLmcbHUZUHdx0jMR0Oxfd04+MPi3rvNZklhl6Sy86D2nD8n/8yKFNx0QCCUFt1UeAUVVI7H+8CQPJqp9H4HfubXBbv3Offg9Lu7DGJAjNhdVh5vrnz683eVTXpkcLxj07AotYDxKSQPVx1Zjza0wOgSrE7/czc878qMV1RiQQJXkEIOMrXo6mloTcTlNPoJYsB2SUlPMjFp8gxLP+V2UFd+BtCEuCQv+rxAmF9amv+ggwYkbWGZFAJEsblBaj0PxO3IdfDLmd+/AL4HehtBiDZG4VwQgFQRBqVl/1EWBEFXJGJBAAa6cnQVL0TRMLPq73eu+xj/DkvgOSorcVBEGIslCrj4BoVyFnyCA6mBz9sWU9g2v/Izj33IOvfCvWDg8jKScP4GnqCdyHX9CTBxq2rGcxOfoaE3SUvH/zAkOfP2X2WEOf3xSZiz8wOoSoMfrv5ExU28yr2kR7RtYZk0AALBn3oG9P8jie3Lfw5M9ASR2JbOsCgN+1H7V4GfhdICnYsp7DknGXoTELgnBmClQfAGZFYdYnX4XUzqzob+tfL1nNHROvIbNt5Lrfz6gEAmDJuBtT8nDcB6ejnliMWvTNKVfIKC0uxdrpyWZfeZyqMZWA16UCNGpb7nj+RJszOrorfo0UzxViPAtUHwCffb2kwe0De2RFsgppUgKZMKH+PaUaYs6cOSHdN3BdY5kc/Ujo8wmatwC1ZBWaRz9FTbJkoKScLwbMG+DAxqNIQLcLMo0ORRCaDVX10SotlUk3XNmk+ygmE6rqQ1Eic858oxNIuJNHQ5/d1CQCIJlbie1JmmjfmjwkSSQQQQgnRTFxz22/MjqMejW5Cyscb+QNuaeRiUs4mavMQ27VjqquMg+2JIvBEQmCEE1nzDReIfyy1+fj92n4fRrZ6/ONDkcQhCg74wbRhfDZtya32us8eo/pGJHnGFV1RqK6FoTmRFQgQqNUFLk4ursYxWJCsZg4uvsEFUWusD/H6LE2QRBqZ0gF4ncdAEC2dQ77vUtXi509o2H/mjw0TaPj4NZomt6FtX9tHv2ujMzeRtGuBkTyEKKpMX9voc5ajSRDKhD3kZdwH3nJiEcLYbJvrd591XV4Bl2H6zsV71uTZ2RIghB3jOwmDcezo16B+F0H8B7T96Kytn8wbFVI8ojisNznTFeSV4HXpaK6ffhU/SwUv+pHdesLmjRNo6LIRWF2KZYEhfYD9DUzlgSFwuwStn2djSPNFjxlTrGakBX9c4pJkVCsJsw2hZQMhwG/nSDEnqa+kRuZhKKeQNxHXgLNG3xt7/ZGtEMQ6rHi7W3BY0fr0vmcNsGT5zqf04Y9K3JY/++6j3BN65DE6PsGhSVOQRCMFdUEEqw+JP0QGe+xj8NahQhNl5Lh4Jrp57Fm5k72LD+if1OCDgNboVhMSJIUPPuh58Udgu16X9IpWGl4KlU0TUP1+Di8pSB4qGOPi9oz/PY+KNbIrIoVBCG6oppAAtWHuc2tAHiP/ltUITFIsZq48O5+ZPRJY/WMHahuH2XHnIz+wyBatE+ssU2rrim06poS/Lokr4LFr28GTT/G9LxJfeg1qkONbcPNX16AO3s9/rKjIEnIia2xZg1DTkyPyvMF4UwRtQTyS/Vhwpp5P0gmvMc+xnvsv1gz70e2d41WKEKIul+QSasuKSx+fTMnjpQz78k1nD+lH12HZ9TZ7sDGo6x450c8lSopGQ5G/2EQaR2TIh6vN28HZd/9Fff+1aD5T/6hJGPtej5JYx7CnNEn4rEIwpkgarOwgtVH65uQ7V2RbZ0xt74RNB/unFejFYbQQKmZiVwz/Ty6Ds/A6/Kx9I0trPnnDvyq/7Rr/aqfNf/cwaJXf8BTqdJ1eAbjnh0eleRRsW4mhe9eh3vfSiTFiq3nGBzDJ+MYPhlbzzFIihX33hUUvjuOinWzIh6PIJwJolKBnFZ9VLG2f1BUIXHAbFO4eNpA0joms/Gj3exZkcPQW3ufdp2mwZ4VOQAMmdiTAdd0iUp8FetmUrrgLyBJOIZPIfGiqci25JOu8btKKV/+BhVrZ1C6YDoAjmGTohKfIDRXUalATq0+gg8XVUhcsTr0yQ+Z/dKDs6+qM5llMvuln3RtpHnzdlC68DmQJFKvf5nkyx49LXkAyLZkki97jNTrXgJJonThs3jzd0YlRkForiJegdRWfQSIKiR+HNykn7Hc6ezWAHgqvaz55058Xj8jJp+FLclCp8GtOfj9UQ7+cJReoyM/aF626CXw+3AMn4K9/7X1Xm8fMA5v3g4q1s6gbNFLpN06I+IxCuFV18rrSK7OFnujnS7iFUht1UcwAFGFxAXV7SNvZxGSJNFhYCuObC3g0wdXsnd1Ltkb8vnf/63iyNYCOgxqhSRJ5O0oCi4+jBR/eQHufauQzHYSL5oacrvEi6YhmW24967EX14YwQiFcBN7o8WWiFYg9VUfAaIKiX052wtRPT7SOiWx+X972bnoEGjQtlcaAPm7ivjmxe/pM6YjLTomUnSwjJzthXQ6u03EYnJnrwfNj7XLiBq7rWoj21OwZJ2He89SPAfWY+vbtFPfmoO8p4z9N5fx9L4GXV9fNVDTzyud+mafCXZbg54FInnUJqIVSH3VRzAIUYXEvEObjgFQdLCMnd8dwqTInHtzL67807lc+adzOffmXpgUmZ3fHaLoYNlJbSLFX6rvvWVKb/gGjkq6PsDvKxX7d50plq7ZxLK1m4wOo1mJWAUSavURIKqQ2KVpGoc2FwS/TuuQxMipA06antv/qiza909n2Ztbg9ugHNpcgKZpwX2xwi5wX01reNtgmwjFFqcaWgk0VTQrn4XL1iJJEleMGhG1ZzZ3EatAQq0+goGIKiRmFewrwVniRpIk+l2ZxbXP1Ly2I61jEtc+M5x+V2YhSRLOEjcF+0oiFpecrC9o9B3PbnBbtaqNKbltWGMSYlNxaRkbt+5kw5YdFJfWv8+bEJqIVCDVd9yVJAvuI6+F1E6S9DO1xR5ZseXgpmMkptu56J5+ZPRpWee1JrPM0Ft60XlIG5b/40cObTpG626ROaPF2vlckGTc+9fgd5WGPA7idxbjyV4Lkowla1hEYhNiy6KVG1FVfVLH4lUb+dUVowyOqHmISAKpvuOuJ78R0yQ1r9gjK4ZYHWauf/784CaKoWjTowXjnh3BriWHIxaXnNgKa9fzce9dQfnyN0i+7LGQ2pUv+zua14W1+0hkR90JUWgevl2+Lvh64bJ1IoGESfgTiOZFtmRgbX9f0+4jmfUkJEVnQZpQu/5XNe6UQUuC0ui2oUoa8xDu/aupWDsDc9s+2AeMq/N659bPqVg/C2QTSWMejGhsQmw4VljE1h17sFr0Ho6tO/ZwrLCI1ulpBkcW/8KfQCQz1o6Ph/22glATc0Yfki97nNIF0yn+/EG8eTtIvGgasj3lpOv8zmLKl/1dTx6aRvLYJzC3PX07FqPkX32BsQEMbniTeNn1+Nvl6/FrGhcMHQjAopUb+HbFem69fqzBkcU/Q85EF4RwcgybpG9P8s0zVKydQeX3s7FkDUdp2RkA9fgBPNlr0LwukE0kj30Cx9DbjA06jsXbrscLq7qvLhs5DLSqBLJsnUggYSASiBD0/s0LjA6h0RxDb8PS6RzKFr2Ee+9K3HuW4K5+gSRj7T6SpDEPxlTlcaq2X66M6vMaWvlUrJup7z3m9yGZ7Vi7jMDUshMAvuMHce9fjXvvCtz7V5N82eMR3bDy4JE8Kl1uXC43Xq8KgFdVcbp++T9/tLCIXXsPkOiwM/zs/gAkOuz8tPcA//n8G9pU68ay26yYFf0t0WxWsNmsJNisdGpf9/EFZzKRQIRmw9y2D2m3zsBfcRxP9jp8ZfreXaakNliyhokB8yaKxV2Pp7/yHnsPHKn3upHDz8FiMQdfz/9uJa+9998623Tr3J7nH5sWljibK5FABKbMbl6lvOxoKbYnCbNTdz2ubePKwK7H5rZ9KP78QUoXPoul8xDMbcPfndWpfQb/fPUpXnzrQ778Tq/cJElixJD+2KxWAJISEwAYd9nIYLsbrhyNWdGPVS4rrwTA5XazeuOPaFULTK++5AIe/t1t2KyWsMfdnDQ5gYg9YgSh+YvVXY9tVgtP3j+Fs/v35oU3Z+F0ucnJK+D5x6bRpVNmjW369MiiT49fZgceysnnkefeQNM0LBYzD959K9eNHRmReJubRq9EN3JrY7GtshBpc+bMEX9nVeJh1+MrR49g1ut/pkunTLIP5/KbB6azcNm6etstW7OJSff9mZ+zD9Mxsy0zX31KJI8GaFIFIv6BCYJx/CeK8GzbjK+oECQJU4uWWPoPQk4N7/qGeNn1OKtDO/75ypM89/d/snDZOp548R9s2bmHB+66OTg4HuBVVV55dzafzl8M6DO0Hvv9bxq1U++ZTIyBCEINAl2zsfghybtvD+Wz3sG95fuap9EOHkLibXdj7tI9LM9r6q7H7j1Lo7brcYLdxjMP/5ZunTvw5sxP+GrRKu6fctNp12l+ja8WrQJg6u03cPuEq6ISX3MjEogQF8RYm65y3ieUfvAG+P1IVhuWgeegZOh9/WpeDp4t3+PetB73lu9JnjyNhKvHN/2hcbjrcXKiA4Chg/oGZ19VZ7GYGTqoL8vWbgpeKzScSCBCTJszZ45hySPWqo/KeZ9Q+t7f9Gm0103EceMkZEfiSdf4K8qp+GgmFV/MofTd1wGanETicdfjFes3A3DhsEEAlFVU8uJbH+LxeHn097eTmpzEBUMHsmztJlZu2Mz1V1wc1fgAMhd/EPVnVpczenKT7yESiBDzYu2N3AjefXv0ykOSSHngCewjL63xOtmRSNLkaShdelDy6jOUfvAG5rMGNKk7K952PXa63Hy/9Sfkqim9azdtY/qr71NYVAzAjz/t5cn7p3D+uQOQJYmNW37C6XJjt1mjFmNzIRKIIMSB8g/fAb8fx3UTa00e1dkvvhR1324qvphD+Yfv0uLPf230s+Nt1+MNW3bg9njo3qUj783+gs++WoKmaQzq2xOAzdt384cnX+ZXV46ia1YHft5/iA1bdnDRsEZsCBYGjakEyn36bueJpoZvNhvOyieiR9oKgtB0/hNFuDd/j2S14bgx9FXdjom3I1msuH/YgL+4qEkxJI15CGQTFWtn4Nw6t97rjdz1eOX6LQD8vP8Qn85fjFkxce8dN/L2C4/y9guPcu8dN2JWTHw6fzE/7z90Upt48c2xg3xTcNDoMEQCEYRY59m2GTQ/loHnnDbmURc5MQnLgMGg+fFsb9obZGDXYzRNX2H+zbP4naefNul3FlO64C8Uf/6Qvuvx5dHd9divaSclg26d2zPztT/z6/FXIEsSsiTx6/FXMPO1P9Otc/vgdSvXb8HfmEkCBpl7dB9f5Ef3+OGaiC4sQYhxvuPHAFDadWhwWyWzI+6Na/EVHGtyHPGw6/GO3fspKi5BliRuvu5yfjtpPBbz6W9z3bM6MOv1p/nHrE+Z/fk3FBWXsGP3fvr1it4Z7Y1V5HWxsig3+DrNbNzaFZFABCHmBabANmEarRSeabSxvuvxinU/0LZVS576452c07/u51vMCn+YMpGLR5zNUy+9y8r1m+Migcw/mo1atf7nq2MH+HVmL8NiEQlEEGKcKb0VAGpOw48HVnMPn3SPcIjlXY+TEx38961nSXTYQ27Tv3d3/vW36Xy+YGkEIwufuUf3//I6f59IIIIg1M7SdxBIMp6tm/BXlIc8DuIvK8Wz9Qd9Gm2/QWGPKxZ3Pf71+Csa1S7RYW9022jKc1ewseQoNlnfTXhDyVHy3BVkWI1ZDCkG0QUhxskt0rAOHoLmdlHx0cyQ25V/NBPN48Z69lDklBaRC1CImi+O7sevaVzSqiNj0jvi1zTmVatIok0kEEGIA4m33Q0mExVfzMG59Nt6r3cuXUjll5+CyUTSbXdFIUIhGuZWzbwa16Yr49p2rfqecQlEdGEJQhwwd+lO8uRplL77OiWvPoO6bzeOibcjJyaddJ2/rJTyj2bqyUPTSJ78e5SsbgZFHTnNbW+0fZUlVPi8VPpUvH59gNyr+aj06Uf1aprefbWt7DhJioWLW+pTkJMUCz+WFfLuoe1kWB3BuRIJJgWzpHdzmWWZBJOCw2Sma0JKWOMWCUQQ4oS+p5VE6Qd/p+KLOVQu+ALLgLNR2ulvJmruETxbN6F53GAykTzl9yRc9Stjgw6z5rw32v07V7Cr/ES9141t1Qlr1RjI2FadmJP3M0//vL7ONr0SW/Buv9FhibM6kUAEIY4kXP0rzGf1p/zDd3H/sAH3xjWnT6M95zySbrurUZVH3lOxP421Oe6N1jUhhfnnXMPju9fycd4eQJ+8PSq9A3ZZQZIgRdH36rqpXY9gu0nte2OpSiYlqhtNA6dfZUnh4eCk7xszevBsz/Owm8L/di8SiCDEGXOX7rT481/xl5zQD5Q6rp/2Z2qZjqXfIDFgHqfsJoVX+lzA8BYZPLp7NZU+lUPOMt7pN4qejpr/nw5MbsXA5F+maO+vLOGubUvQAKtsYnqPYdwawWm+IoEIQhVDP30PBumHdg1qIqe0wHb+qLA8PuNp47fFEHTjM7oxIDmdu7ctYXfFCa7e+CUv9h7BuDZ1/30uKDjI/TtXUKZ66JKQwrv9RtE7MbynU55KzMISBEGIMd0dqcwbcjXj2nSlwudl6vZlPLZ7TXCAvTqv389ju9cw5cdFlKkexrXpyoJzr4148gBRgTQ7zXWAMZqi/Wk8HsYdhOhLNJl5s+9Ieie24P/t+55P8n7mqe5DT7vOj8YneT8D8GjXc5jWeUDUYhQVSDNi5NTG5jatUhBiRYpZHzy/MC0zOPuqOqts4sK0zJOujZaIVSBD3tkbqVuHZOPdzW/ue6iiXQ2I5CEIkfNtgX5myaWtOgJQqnp4fPca3H4fz/caQZrZxiXpHfmm4CDfFR6K6t5YogtLEGJI/tUXGB2CEEMqfSprTuQiSxKjWnZg6fEjPPDTSo65KwHYWHKMV3pfwOj0DsiSxOqiXCp9KgkRmLJbk4g/JdqVgNGVjyAIQrisLMrB5ffRJzGNV7M38+GRn9CAYaltAVhXnM+vtyzktva96eVowc7yIlYW5XBZq05RiU9UIILQBP7yAtzZ6/GXHQVJQk5sjTVrGHJieoPv1fbLlRGIUIhn3xXq3Vc7y4vYWV6ERTbxcJezubtjXwDeObSdF/dvYtaRn05qIxKIEFU5+QUAZLYN37kRzZk3bwdl3/0V9/7VoJ0ytVKSsXY9n6QxD2HO6GNMgELc82saiwp/OQOmV2IL3jhr5EnTc3/bqR8jW2Yybcey4DYoiwoP49c05DAdIlYXMQtLAGDGR/OY8dE8o8OICxXrZlL47nW4961EUqzYeo7BMXwyjuGTsfUcg6RYce9dQeG746hYN8vocIU4taW0gAKPE1mSuLtjPxYMqXltR+/ENBYMuZa7O/ZDliQKPE62lBZEJUZRgQjk5Bfw9ZLVANwx8ZoGVyGhzvoyeoA4HF1EFetmUrrgLyBJOIZPIfGiqci25JOu8btKKV/+BhVrZ1C6YDpQdZ64IDTAt4WHyLQl8lqfCxneIqPOay2yiSe7n8sVrTtx744VfFd4iMEprSMeY0xVIMcrfXy7t5z//FjM7B+L+XZvOUVOn9FhNXszPpqHqvpQVZ+oQurgzdtB6cLnQJJIvf5lki979LTkASDbkkm+7DFSr3sJJInShc/izd9pQMRCPEtRrCweel29yaO6c1LasPDca0lWorMeJCYqkF2Fbt5cf5wNOZX4tZN/JkswtH0CU89tSc/06C6SORMEqg9F0Rcofb1kdYOrkMA6kFArkcZUAppTn7Yo2RMa3DZclU/ZopfA78MxfAr2/tfWe719wDi8eTuoWDuDskUvkXbrjLDEIZwZftupX6PaJSmWRrdtKMMrkI+2FTPpf4dZd6QSi0niws4Obumfyi39U7mwswOLSWLt4UomfX6Ej7YXGx1usxOoPq4YNYIrRo2I2SrEtXYFrnXGzVLylxfg3rcKyWwn8aKpIbdLvGgaktmGe+9K/OWFEYxQEKLP0Arko23FvLymEAm4tX8qd5ydRpLl5JxW5vHzwaYiZv9YzMur9X+AE/umGhBt8xOoPmRZ5vYJVyHLMl8vWc38Rau4fcJVdGjXxugQg1wrFgES9osvM+T57uz1oPmxdhlRY7dVbWR7Cpas83DvWYrnwHpsfa+MYJSCEF2GJZBdhW5eXasnj+mj2nB596Qar0uyyNx3Xjo90608teQor609zuAMOz1aiu6spgpUH9dcemEwWVwxagTzvl3BzDnz+dN9kw2OUOcvLcG9dVPwtZwc3mM5Q4shDwBTelaD24DOdvYAACAASURBVCrpXXDvWYqv6h6CUF3m4g+MDqHRDOvCemvDcfwa3NI/tdbkUd3Y7knc1D8Vn1/jzfXHoxBh83Zq9RFwx8RrUBQT8xet4nDuUQMj/IVr1VJQVVBVXKuXGhNEYE69ptV9XU2CbSI/L18QosmQCuR4pY/1RyqxKRJ3nB36nvWTB6fx2c4S1h2ppMjpI81++s6UQmhqqj5AX0gYa1WI3n31y+uEseOiHoOcrM+E8R3PbnBbtaqNKbltWGMS4lvOaOP/bTWVIRXIplwnfg3ObZ9w2phHXZKtMkPaJeDX4IdcZwQjbN5qqz4CYqkK8RUW4Nm5DcliRbJY8ezYhq8wOoukqrN2PhckGff+NfhdpSG38zuL8WSvBUnGkjUsghEKQvQZkkCOVagAdEwxN7htp1S9TX7VPYSGC1QfV405v8aB8kAV4vf7mTlnvgER/sK1cpE+eH3uCKznDgfNj2vl4qjHISe2wtr1fDSvk/Llb4TcrnzZ39G8LqzdLkR2tIxghIIQfcaMgQS6ghvTnXzKLYSGqa/6CIiVKsS1XO++sl00BtuFY/TvVevSiqakMQ+BbKJi7QycW+fWe71z6+dUrJ8FsomkMQ9GIUJBiC5DxkDaOPTHHizxNrjtoWLvSfcQGqa2sY9TRXosRM05hOZ0orlcoOr/TzXVq3+tf4WvsADvvj1IDgfWwfpRnpLDgXfvbirmfowpvRWBjxKSzYakVFW0iln/2m5HyewYtpjNGX1IvuxxShdMp/jzB/Hm7SDxomnI9pNnhfmdxZQv+7uePDSN5LFPYG7bO2xxhEvpamOnwyePEOu64p0h78KDM+zIEmzMqaTM4w95HKTU7WNjbiWyBIPb2SMcZfMTavURcMfEayK6LqTk9edQD+yv9zrbsAuRLJbga+fiBZR9UHc3ktK5C6mP/CUscVbnGDZJ357km2eoWDuDyu9nY8kajtKyMwDq8QN4stegeV0gm0ge+wSOobeFPQ5BiAWGJJCWCSaGtk9g7eFKPthUxH3nhXZ2wnubTuBWNUZ0TBAzsBoh1OojIJJViJLZkZYvvUPp26/iXPS1/k1JwnrOMCSrDZCQExMBsF/6S7JLuPI6JLNeafjLywENze3C/f264HRZ+5grSL7n/qr7hJ9j6G1YOp1D2aKXcO9diXvPEtzVL5BkrN1HkjTmwZisPE4V7UrA6MpHCB/D+oGmntuSDTlOZv9YTM90K2PrWQvy9Z4yPt5WjEmWmHquGIxsqOo77poVhVmffBVSO7Oi/4k0Zo+s+khWGyl/eBRLv0GU/uNlNJcLX34uqY/8BaVjzQv2zN17Y+7+y5uymnOY4uf/BJqGZLGQdOcfSLj8mrDFWBtz2z6k3ToDf8VxPNnr8JXp40SmpDZYsoaJAXPhjGBYAumZbuW+81ry8upCnlpylF2FbiYPTiPZenJ3Vqnbx3ubTvDxtmI04P7z0ukuVqE3WKD6APjs6yUNbh/YIysS60Lsoy7H3L03xc//CfVQNsf/eDcpv384OGheG9faFZS8/hxaRQVKZgc98XTuGvb46iI7WortSYQzlqEj0RP7piIh8eraQmb/WMxnO0sYkpkQnN57qMTLxpxK3KqGSZZ44Lx0JvSN/jYW8U5VfbRKS2XSDU17o1NMJlTVF9y5N5yUDp1o+dLblLzxV1wrFlH816dJ2PEjSXf+/pfB8Sqa6qXsvb9T+fXnANguHEPKtIcatVOvIAiNZ/hUphv7pjAow8ab64+z7kglqw5WnPRzWYIRHfXt3EXl0TiKYuKe235ldBj1kuwJpD70FBVZXSmb9Q7OJQtImjzt9Av9Gs4lCwBImnQ3jvG3RjlSQRAgBhIIQI+WVl6/oh1FTh8/5DqDCw1bOxQGt7OLAfMzjJSoj4dZBw4Jzr466ecWC9aBQ3CtWxm8VogOzXMUtXQVmicfkJAsbVBSLkAyR/70OyH2xEQCCUizmxjTNdHoMASDudfrg/3WoecD4K8op+ztV9E8bpKnPoScnIL13BG41q3EvWE1CZfXf7iT0DS+8q24Dz6NWrwM8J/yUxmlxSisnZ7E5OhvQHSCUWIqgQiC5nLh+fEHfSrsOcNwb1pPyd/+H/4ifQdmz67tpNz7KNYh54Ek49n6A5rLhWQL35TdvKeiOxAf6zy5b+M68DhoPiTZjil1JLKtCwB+1358xctQTyxCLV6GLesZLBn3GByxEC0igQgxxbP1ezSPGyWrG+X/nUnlgrmgaVj6DtB/vn0rJ55+iISx41A6d0HN3otn6/fBakUIL0/u27iyHwEkLJnTsLZ/CEk5eSKLppbgPvwinty3cO1/BEAkkTOESCDNUOCM8njkquq+UrP3ombvRTKbSbz1ThzX3QhAxecfU/7v94IzsAJtwpFAMp7e1+R7NCe+8q165YGEvcc7mFvV/HclKSnYsp7FlNgf5557cGU/gSl5BCZHdM7lFoxj+JnoQvjMmTMnvp+t+XFvXBP8UunchZavvIfj+ptAkkGScVx/Ey1feQ+lc5fgde6Na0A7tV9eaCr3wemg+bBkTq01eVRnbnUjlna/BU3V2wrNXsQrkCHv7I30I4RqjEwiTeXd8xP+4iI9UYybQOKv7wpuW1Kd0rkrLV95n/J/vUvF3Dn4i4vw7vkJc8+zDIi6edI8R1GLlyLJdqztHwq5nbXDw3jyZ6CeWIzmPSZmZzVzogIRYoZr/WpMrdqQ9syrJN0xtcbkESCZzSTdMZWWL7yJKSMT14bVUYy0+VNLVwF+TKkjTxvzqIukpKKkXAT4UUvE/5PmLmIVyMa7u0Xq1kIzJScmkf73WUgOR8htzL37kv7qB1QunBfByM48mjsXANne8H/Hsr0bnFiI5s4Jd1hCjBGD6ELMcFx/U6PaSQ5Ho9sKtWnCqW+BNpI49q25E11YgiCcRrK2A8DvbPgYpt+pz2aTLO3CGpMQe0QCEQThNEryCEDGV7wcTS0JuZ2mnkAtWQ7IKClibU5zJ7qwhKjLv/oCo0MQ6iFZ2qC0GIV6YhHuwy9iy3o2pHbuwy+A34XS4lIkc/jOjhFik6hABEGokbXTkyApeHLfwlvwcb3Xe499hCf3HZAUva3Q7IkKRIiatl+uNDoEoQFMjv7Ysp7Btf8RnHvuwVe+FWuHh5GUk4+k1dQTuA+/oCcPNH1VuqOvMUELUSUSiCAItdL3tJJwZT+OJ/ctPPkzUE7ZTFEtXgZ+F0gKtqznsGTcZWjMQvSIBCIIQp0sGXdjSh6O++B01BOLUYu+OeUKGaXFpVXbuYvK40wiEoggCPUyOfqR0OcTNG8BaskqNE8eAJIlAyXlfDFgfoYSCUQQhJBJ5laY068zOgwhRohZWIIgCEKjiAQiCIIgNIpIIIIgCEKjiDEQoHR1av0XRVDyiGJDny8IgtAYIoEIwhnO6A9QZ6q8p7oa+vxwHOEsEkg1jakENF85AJIpscFtxT9cQRDimUggTaQenw+AufVEgyMRhIYRXaexoTGVgOauAECyhn74WkA4Kx8xiN5E3sJP8RZ+ZnQYgiCcQVw/fYtr17dGhyEqkKbQvMdRi5cHX0vmlgZHJAjCmcC5bR5IEvYBxi7qFBVIE3iPzwXNC5oX7/EvjA5HEIQzgL/yBO7sNbj3r8ZfecLQWEQCaQJvwac1vhYEQYgU146vwaeCT8W1Y4GhsYgE0kh+Ty6+0vUg20C24Stdh9+Ta3RYgiA0c85tX9b42ggigTSSWvAZ4MecNhZz2uWAH7Xgf0aHJQhCM+YrzcdzaBOS2YZktuE59D2+0nzD4hEJpJG8hXqXlTl9POb08Sd9TxAEIRJc274EzY+152isPUaB5se1fb5h8YhZWKfwO39G81WAvxLN79G/qXnQfJVVV2honlx85VuRTMkoLUYDIJmS8ZVvwZP7JpKlHSBVfT8BJIv+WraAnIBkciDbu0f5NxMEId4Fuqzs/a4GTcO142uc277EMXyKIfGIBFID58+/w1+5s97rlJZX6WMgVa+9x2bjyn68zjZyQh8Ses0KS5yhmjBhQlSfFzBnzhxDnivEn/yrLzD0+W2/XGno89XC/WieSjRvJZrPq3/T50XzVH1w1TR8pfl483Yg2ZKwdrsQAMmWhDd3OxVrPsCU3Bakqg+ulgQwmfXXJjOSOQHJkoCS3iWscYsEcgrZ3h3HgMW49j2I99h/qr4robS4FMlkByQkJQUAc5vbgu0sGVP0CgPQ1BJAQ/M5UU98C2j69a1vwdb1JSTZHrXfx6jkEXi2SCKCEJriuQ+jHt1d73W23pciKdbga+fmzyhd+FydbZQ2PWkx4Y2wxHnSfcN+x2ZAku3Yu7+JknIBrv0PoPkq8bsOkNBrFnJCrxrbmBIHY0ocHPza79yLc/ckQAPZhi3reSxtb4/OL1CDaL+RG5m4hPgV7UrA6MonQEnvQvqdn1H61Z+p3Fw1lipJWLuPRDLbQZKQbUkAJAy+MdjOMeRWpKpKw+8qA01D8zpx/7wMNP2Da8Kg8SRf+Wf9PuGOO+x3bEbMrSdiShpE5a5J+Ct3UfHjaGxdX8fcanyd7dTj83H+/Ds0XymyvRv2nrMwOc6KUtTNk+iGE5o7yWwnZdwLWDoPo+SrJ9E8lfhOHKbFhDdQWtc8ZmrO7E9KZv/g1+rxbIo/ngaahqRYSR77JAnnRG6fPjELqx6yvSeO/oswtxqP5qvAuWcKrv0PguY5/WLNg2v/g1TuuhXNV4q51XgcA5aJ5NFERnfDCUI02QdeR/pdn6O07o5asJfC964Pab2H66dvKXz3OrxHd6G0zKLlXf+LaPIAUYGERDIlYu/xPnLCWbgPPo332GxsnZ8JTLT6hebHe2w2ANZOT2Ftf3/0g23GRDeccKZQWnUjfcpnlHz5OM5tX1L86X14Dn1P8uVPBLusAjSfl9JvnqFyw78BfYZWytXPNmqn3oYSFUgDSIp+focp9eLg7KuTyDb9Z9WujWdlxyopO1ZZ/4WCYCBffi6+/Oa3C4RkdZA6/jWSxjwEgHPL/0Dzn36h5td/BiSNeYjU8a9FJXmASCANohbp+86Y064A9NlWzj134dx1G5r3uP6zFmOrrv3GmCDDaPPcfWye2/RTywQhksrnfEj5nA+NDiNiZLs+69PaZURw9lV1kmLF2mXESddGLbaoPi2Oab5K1JIVgIzS4hLUE4so3zwUb8EcvMfnUb5lBOqJRShplwIyasnyaosP40/ZsUr2rsxh78ocUYUIMcuXn4tz6UKcSxc2yyoEwLVrEQDWXmMA8LtKKf7sAU58PDW4G6+1p76g2bV7cVRjM3wM5P2bjd1NcsrssSFd5ytZBn4XJkdf3IdfxJP3AaBhSh6u/7x0DZU7b8CSMRmTow++iu34SpahVFUr8Wbz3H34fVrw9YV39TM4IkE4XfmcD0FVg69T7n3E4IjCS/NU4jmwDiQZW/eRuPeuoHju/+EvOwaA5/APpI57AVuPiymRZDzZa9E8lfpCwigwPIHEC29V95WvYju+iu0gW7F1fBxL5jQAPDlv4Dr0LJ68909qE48JJFB9yCZ9lsDelTkMGteVpNbR+aMMh+MnStj0408UFBUjIZGelsI5A3qTlhrdEl+InED1gaK/jTmXLiRxwm2Y2rYzOLLwce9fg+Z1YW7bm7Llf6dy439A07B0OhcAz8ENFP37DhKG3IK5TU+8+T/h3r8GW1W1Emkxk0BCrQTCpWGVjx+1aGHwKzmhD/Ye7500PdeSeS+m1NE499wZ3AZFb+Mn3noKA9VHj5HtAdiz7EjcVCG79h7gzZmfsGHzDvxVC6kCZEli6OC+TL39Bnp27WRQhEK4BKoP+yVXAuD87qtmV4W4q7qkvPk/4c3/CUmxkDTqARzDJwNQseYDypa8EpyBFWgTrQQSX+9sBvGVbULzHgNkLJnTSBywtMa1HSbHWSQOWFpVlcho3mP4yjZFPd6mCFQfkiwx4JouDBrXFdkk8fOKHEryK4wOr04fffEtk+57mnU/bMdiMXPhsEHcct3l3HLd5Vw4bBAWi5m1m7Yx6b6n+eiL74wOV2iCYPUhyySOv5XECbeBouBcvABf7hGjwwsPzY9rz5Lgl0qbnrS863McI+4ESQZJxjHiTlre9TlKm57B61x7ltQ8WysCYqYCiWVq0QJka3ts3f+BklLP1geyFVvnZzC3vBrnnntQi77BlDQkOoGGQfXqI6WtPhWw2wWZ7Fl2hK3z9sdsFfLRF9/y8jv/QZIkbr1+LHfcdA1JjpO73MoqKvlg9hfMnruQl9/RP7FNvPYSI8IVmqh69WFqp1fK9osv06uQT//dLKoQb85W/OWFeqI47w6SRv8RSbGcdp25TS/S75pL2eKXqVg7A395Id6crZjbD4p4jKICCYGkpOIYtKb+5FGNKWkojoHLgxsvxoNTq4+AWK9Cdu09wKvv/RdJkpj+4N38YcrE05IHQJIjgfvuvImn/3gXkiTx2vv/Zc/+Q7Xed86cOWIrkxh0avUR0NyqENeuxZhS2tFy0r9IvuzRGpNHgKRYSL7sUVpO/hhTWkdcu5fUem04xXUCidZCN0vmvUim5Aa3k0zJWDLvjUBEkRGoPrpfmBmsPgCSWifQ7YJMNL/G1nn7DYywZm/N+hS/388t113O5RefV+/1Y0cN56Zxl+Lz+Xhz5idRiFAIp2D1MXpssPoAMLVth/3iy8Dvp/zTf9dxh/gg21No9buvsWQNC7mNpcNgWt09D9nW8PerxojrBCIWuoVPbdVHQKxWIcdPlLD+h+3YrBbuuOmakNtNvularBYL6zZto6i4pMZrJkyYILYziTG1VR8BzakKcYy4E6lqB96GkGxJ+jhJFMRtAhEL3cKrtuojIFarkE0//oRf0zh30Fk1dlvVJjnRwZCBvfFrGj9sq/8MBiE21FZ9BDS3KiTWxe0geiQWupWujv/9qxqjvuojYNC4ruxdmcPPK3IYcE2XGhNNtB0r1Ffidsxs2+C2nTIzWMVW8guOhzssIQLqqz4CEifcpq9OX7yAxPG31phohPCIywTSHBa6xZKaZl7VJFCFxNSMrMCOyFqdV9VIq2okSaduqyzEoppmXtUkUIXEy4ysvKe6Gh1Co8VlAgn3QrfkEcXhDC+uhFp9BMRaFdImPQ2Agzn5DW57qKpN4B5C7Aq1+ggQVUh0xF0COfUNT5almHpDizehVh8BsVaFDO7XC1mS2LhlB2UVlSGPg5SWVbBxy0/IksTgfjUfUyzEjlCrj4B4qEIyno7/CUBxl0DidaFbLAokYwCTIrP1y9AGx02KPvciFroOW7ZIYejgvqzdtI0PZn/BfXfeFFK792bPxe3xMGLIANJSozPlUWicYPUBSIqZik//E1I7SdEPXmqOe2TFirhKIHUtdBNVSMNVn4jw06LaF9TVxu/Tau06jOYCvKm338CGLTuZPXchPbt2Yuyo4XVe//WS1Xw87ztMJhNTJ9V9vr1gvOo77lYumNvwG6hqs9sjK1bEVQKprbsl1rpV4oHfp+FoYWXA1fWPe9RFViT8Pi04ocEIPbt24r4pN/HyO//mqZffZde+A0y+6VqSE0/+IFFaVsF7s+fy8bzv0DSN+++8ie5dOhoUtRASVcWUlo5j/C1Nuo1kUvQkpMTVW17Mi5v/mqEsdBNVSOhkk8TZN/SI2P0DC/CiVYlMvPYSJAlefe+/zP58IZ99tZQhA/vQMbMNAIdyjrJxy07cHg8mk4kH7rqZCVeHvmOp0VO8z9iJHopC4q1TjI5CqEXcJJD6BntFFSLceM0lDOrbkzdnfsK6TdtYtWHLST+XJYkRQwYwddJ4UXkIQhjERQKJ54VuQnT16NKR16f/kaLiUn7Ytiu40LB1egsG9+vV5AHzxlQCmq8cAMmU2OC2Rlc+glCXuEggcb3QTTBEWmoyYy441+gwAFCPzwfA3HqiwZEIQnjF/F5YjVnoFoub/glnLm/hp3gLPzM6DEEIu5ivQOJ9oVusELvKGkPzHkctXh58LZlbGhxRbMu/OvQzdwTjxXQCaQ4L3Yw2Z84cw5KHOIwJvMfnguatev0FlrZ3GByRIIRPTCeQSC50q0usvuHGalxC7bwFn570WiSQmrX9cqXRIQiNELMJxKiFbkZ29UyYMKHWN+tYjSvaccQTvycXX+l6kG0A+ErX4ffkIlvElhpC8xCzCSTSC93qE+03zFDfHGM1rkiK1244teAzwI85bSyg4S2ci1rwPyyZ08IWnyAYKWYTiCBUFwsVUEN5C/XuK3P6eAIJxFv4qUggQrMhEoggNJDf+TOarwL8lWh+j/5NzYPmCxytrKF5cvGVb0UyJaO0GA2AZErGV74FT+6bSJZ2BE7DkkwJIFn017IF5AQkkwPZ3j3Kv5kgNIxIIILQCM6ff4e/cme91yktrwqOgSgtr8J7bDau7MfrbCMn9CGh16ywxCkIkSQSSBgdcetna7e3irn+zZls745jwGJc+x7EeyxwNoWE0uJSJJMdkJCUFADMbW4LtrNkTNErDEBTSwANzedEPfEtgTN5za1vwdb1JSTZHr1fSBAaKWYSyPs3LzA6hCZ7L38RAE93utHgSHSa5yhq6So0Tz4gIVnaoKRcgGRubXRocU+S7di7v4mScgGu/Q+g+Srxuw6Q0GsWckLNJxyaEgdjShwc/Nrv3Itz9yRAA9mGLet5LG1vj84vIAhhEDMJJN4dcR9n/vHvAbiz7RhDqxBf+VbcB59GLV4G+E/5qYzSYhTWTk9icvQ3ILrmxdx6IqakQVTumoS/chcVP47G1vV1zK3qPqhKPT4f58+/Q/OVItu7Ye85C5PjrChFLQjhYXgCmTJ7rNEhhMV7+YtQNV/wtVFViCf3bVwHHgfNhyTbMaWORLbpa2n8rv34ipehnliEWrwMW9YzWDLuMSTO5kS298TRfxGufffhLfgU554p+MrWYct6Ljg4HqR5cGU/hifvfQDMrcZj6/pao3bqFQSjGZ5AmoNA9aFIJgDmH//ekCrEk/s2ruxHAAlL5jSs7R8K9sUHaGoJ7sMv4sl9C9d+/YhPkUSaTjIlYu/xPnLCWbgPPo332GxsnZ8JTLT6hebHe2w2ANZOT2Ftf3/0gxWEMIl4Ahnyzt5IP6JOG+/uFvFnBKqPcelDAZhbuD7qVYivfKteeSBh7/EO5lY1L7yTlBRsWc9iSuyPc889uLKfwJQ8ApNDbDoZDpKin99hSr04OPvqJLINU+rFqMe/Cl4rCPFKVCBNFKg+ZElmcttRyMjMP/49845vZHLbUXS0topKHO6D00HzYcmcVmvyqM7c6kZ85Vvx5L6F++B0Evp8EoUoazfkikmGPn/j1+GZNqsW6ZNBzGlXAHrF59r/EPhd2Lq+imRuibnFWNTjX6EWfYOl7W/C8lxBMELUEkg0KoHqolX5VK8+AsniqpbnMLdwPR/kL4lKFaJ5jqIWL0WS7VjbPxRyO2uHh/Hkz0A9sRjNe0zMzmoizVeJWrICfaLCJagnFuHcO61qFhyoZRuwd3sDJe1SQEYtWY7mq9QXEgpCHBIVSBOcWn0E3Nl2TFSrELV0FeDHlDrytDGPukhKKkrKRagnFqKWrMacfl3kggxRYyqBSqcLgAR7DV1G9Qhn5eMrWQZ+FyZHX32cKe8DQMOUPFz/eekaKnfegCVjMiZHH3wV2/GVLEOpqlYEId7E/ImEsSxQfVzTcshJSaK9tSVXtTwHv+bng/wlEY9Dc+cCINsbXuUF2mjunLDGFE1L12xi2dpNRoeBt6r7ylexXZ9lJVuwdZ6Oo998HP3mY+s8HWQLnrz38VVsP6mNIMQjkUAaqbbqI+DOtmNQJBPzjm/kkLugyc+bM2dOHRsKBqb6aI24c1UbKbTt7mPRwmVrWbhsncFR+FGLFga/khP64Oi/BEvmvej/zGQsmffi6L8EOaFP8Dq9zalrdQQhPsR0Askp9ZJT6jU6jBrVVn0ERLMKkaz6+RJ+Z8PHffzOffo94vSMiuLSMjZu3cmGLTsoLi0zLA5f2SY07zH0RDGNxAFLa1wYaHKcReKApVU78spo3mP4yoyvngShMWI6gczYfIIZm08YHcZp6qs+AsJZhUyYMKHWMzGU5BGAjK94edUeS6HR1BOoJcsBGSXl/CbFZ5RFKzeiqj5U1cfiVRsNi0MtWoBsbU9C3y/09R+ytfaLZSu2zs/g6L8A2ZaFWvRN9AIVhDCK2UH0nFIvX+/RP1HeMagFmclmgyP6RU0zr2oSqEIiPSNLsrRBaTEK9cQi3IdfxJb1bEjt3IdfAL9L3wTQHJ3pxuH27fJfuq4WLlvHr66oPaFHkqSk4hi0BsmUHHIbU9JQHAOX482fGbnAhKhqLtPRQxWzFciMzSdQ/RqqX4upKiTU6iMg3GMhtbF2ehIkBU/uW3gLPq73eu+xj/DkvgOSoreNQ8cKi9i6Yw9WiwWrxcLWHXs4VlhkSCyWzHsblDwCJFNy1TiJIMSfmKxAAtWHIusDu1/vKYuZKiTU6iMgWlWIydEfW9YzuPY/gnPPPfjKt2Lt8PBpq5019QTuwy/oyQNNX5Xu6BuRmCLt2+Xr8WsaFwwdCMCilRv4dsV6br2+eeyvJsSveJ6O3hAxmUAC1cc1vfRPdPN2lTJj8wn+dJGxC92q77hrlkzMCHFw3BylPbL0Pa0kXNmP48l9C0/+DJRTNlNUi5eB3wWSgi3rOSwZd0UklmhYWNV9ddnIYaBVJZBl60QCEeLS0jWbkCS4YtQIo0MJWcwlkED1IUtw+8AWyJJegczfXcrtA1vQIcW4KqT6jrufFKxpcHtV80V8jyxLxt2YkofjPjgd9cTiGgZoZZQWl1Zt5x6blcfBI3lUuty4XG68XhUAr6ridLmD1xwtLGLX3gMkOuwMP1vflj7RYeenvQf4z+ff0CY9LXit3WbFrOh/6mazgs1mJcFmpVP7jAbHVrpa7F8lRMbCZWuRJEkkkKaoXn0ES5bcUgAADKFJREFUksUVPZKYt6uUmVuMq0JUzUdrczJ3hDDuURdFMqFqvuDOvZFgcvQjoc8naN4C1JJVaJ48ACRLBkrK+XExYD79lffYe+BIvdeNHH4OFos5+Hr+dyt57b3/1tmmW+f2PP/YtLDEKQjhEJiOHnidmpxkcEShiakEcmr1EXDHoBaGVyGKZGJqu/jqGpHMrWJie5KG6tQ+g3+++hQvvvUhX363EgBJkhgxpD82qz49NilR3z9q3GUjg+1uuHI0ZkVPzGXllQC43G5Wb/wRTdMXTF59yQU8/LvbsFlPOaejHskjipv0OwlCXQLT0QEWr9po2GzChoqpBFJT9QGQmWyOiSpEiB6b1cKT90/h7P69eeHNWThdbnLyCnj+sWl06ZRZY5s+PbLo0yMr+PWhnHweee4NNE3DYjHz4N23ct3YkVH6DQQhdLEyHb2hYmYab23VR8Adg1qgyBLzd5dyuCQ2V6cL4Xfl6BHMev3PdOmUSfbhXH7zwPSQti1ZtmYTk+77Mz9nH6ZjZltmvvqUSB5CTIql6egNFTMJJFB9XNUzucYuqkAV4tdg5pbYWRciRF5Wh3b885UnuWzkMCqdLp548R+88NaHeFX1tGu9qsoLb33IQ8/8jfIKJ5eNHMa//vY03bM6GBC5INSv+nT0C4YOxK9pfLtivdFhhSQmurDqqz4CYmEsRDBGgt3GMw//lm6dO/DmzE/4atEq7p9y02nXaX6NrxatAmDq7Tdw+4SrQrr/mXByphCb4nk6ekwkkNrGPk4VzbGQ2vadaqjADrrhul+47hOvkhMdAAwd1Dc4+6o6i8XM0EF9WbZ2U/BaQTBCLE9HDxfDE0io1UdApKuQOXPmGPYmXft27bEbV7StWL8ZgAuHDQKgrKKSF9/6EI/Hy6O/v53U5CQuGDqQZWs3sXLDZq6/4uIG3b+5npwpGKO5T0c3PIGEWn0ERKMKicQbZjjuGUtv5EZwutx8v/Un5KopvWs3bWP6q+9TWKRPsf3xp708ef8Uzj93ALIksXHLTzhdbuy2OnbGFYQIicXp6OFmaAKpvuOuWZaYFeLguDkG98gSIm/Dlh24PR66d+nIe7O/4LOvlqBpGoP69gRg8/bd/OHJl/nVlaPomtWBn/cfYsOWHVw0bLDBkQtnquY+Hd3QBBKoPgA+2xn6ORYBgZ16xbqQM8PK9VsA+Hn/IX7efwiLWeGeX/+KW36lDzb+57MFvP2vz/h0/uKT2ogEEn2iu/VkV44eQZ8eWTzy3BvsP5jDbx6YzmO//40+cF6HZWs28fSr71Fe4aRjZluef2xaTM0oNCyBqH6NVgkKk0IY96iLIkuofi24c6/QPPk1LZhAQO//nf7QPSf9Y/r1+CsYdnY/nvzr28F+55Xrt+DXNOQ4PrI33hg50WPChAkxm0QC09Gf+/s/WbhsHU+8+A+27NzDA3fdHBwcD/CqKq+8Ozv4YeiykcN47Pe/adROvZFkWAJRZIl7hqTVf6EgADt276eouARZkrj5usv57aTxWMyn//l2z+rArNef5h+zPmX2599QVFzCjt376dera9hjOl7pY1Ouk4JKFQlIT1A4J9NOmj1y+5zFk8a8kZf79EXCiaaGd0vHwwzFSE9HjzbDB9EFIRQr1v1A21YteeqPd3JO/951XmsxK/xhykQuHnE2T730LivXbw5rAtlV6ObN9cfZkFNJVQ9skCzB0PYJTD23JT3TxeB9Q31z7CBIML5t814X01ymo8fMSnRBqEtyooP/vvVsvcmjuv69u/Ovv00nyZEQtjg+2lbMpP8dZt2RSiwmiQs7O7ilfyq39E/lws4OLCaJtYcrmfT5ET7aLjZgbKi5R/fxRf4+o8OIuJqmo//pr2/zf8/+neJSfWJR4KC0lRs2GxNkCEQF8v/bu7uYNs8rgOP/97XBYJvwZUKBYNYyAlSwNiSQ0KjRRtdtQWqSSVXaSY0qddNQlGlJejGprZSulaZNlSjtRSY1US96g9ZU1ZIuC02TJVM+oAmjRZDSkChkOHwEMA4fwY7B9rsLBycpFBwPfwDnd2XE++CDBT4+z3ue5xGLwo7nq0MaZzYlhjz2u/7WPkJtox0FeOlHKbyyNo2k+Ac/g41P+viwxUF92wi15+0AvFgiZ4gEwzF1h7OOvsDjtLjYmu9fKEupHV0qECGCcNnupq7Jnzzerspkd6VlRvIASIpX2VNp4a2qTBTgvaZhrgy7Z1wnZjo6cB2P5sOj+fjn4H+jHU7YTLej5z+ay8H6I+zeV4vdMcKakkLWlBRid4ywe18tB+uPkP9oLu7JSS62fhPtsGcVsQpEVtyKxeyvF4fxaf7K4xcF8x/2s7kgict2N/VtI+y/MMz71dkRiHJxOzzQde/xzWvsyCmKYjThs5Ta0WUKS8SU8uqXox3CDMNOLxd6nCToFV5ZG3zn4K/L0vi0Y5Qve5w4XF7pzppDv3uC5tEBElT/a3RxdIB+9wRZhti9gRyKpdaOHvYEIruMisWupc+FT4OKVcZZp62+zwqDSnm2kXO2Cb7qc/HTfHMYo1zcjgx04dM0nl1pRdPg6OB1PhvoosZaGu3QFlQstqP/P6QCETGh+dhHUX3+uaZYByf8O6laQ9i4My8ljnM2uDkx8+wScc/hu51X2zLz0fAnkMM3l14CiaV29IUgCUSI+UzPGmhzXjWr6SGxNfEQOdeco0x4p3B6PUz5fABMaV6cXn9C1TT/9FX7+DBJ+nh+kr4KgCR9PG3jdg7YLpFlMDE9c2PU6YlT/NNccaqKUafHpIsj35gc+V8uBNPt6GZTYtBjptvR/95wOoyRhUYSiBDzyDT5/026QzhK2TYy9cDPWI72dpzh8u35N0rdnJGH4e49kM0ZeRzqv8pbV+c+ma/InMqB0mcWJM5IiIV29IW0fP+qhQhSWVYiqgLNvU7GJ31B3wcZc3tp7nOiKlCWHfwnzqUk35jM0XVbeKOziY/7rwD+aqzKkkuiqkdRIFnvX9/wq+zVgXEvryom/m4yGfW40TRw+Tycst8IVHUvZK3mT4WVJOrkbSxa5JUXYh7pRh3rVxlpuuHkwxYHeyotQY072HILt0djo9W4rDuwEnV63n38aZ5KzeK1zvM4vR5srnE+KK2i0DT7ZqpPrsjgyRUZga+7nKP8tv0UGmBQdby9egMvLdE238VEEogQQdhVkc7FXhf1bSMUWgxsnmctyLEr43zcPoJOVdhVkR6hKGPb81k/5IkVFmraT9E5cYvnmv/BO8Ub2ZY5943hhqFu9nacYdwzyWPGZA6UVlFsju2NWGOxHT0cZCW6EEEotBjYU5mOBrx5aoC6Jjtjbt+M68bcXmob7fzx9AAasLfSQkF67G1BES0FphQ+K3+ObZn5THin2HXp37ze2Ri4wX6/KZ+P1zsb+U3bScY9k2zLzKehYmvMJ4/lRCoQIYL0YkkKCgp1TXbq20b4tGOU8hxjoL3XNjpFc68Tt0dDpyq8Wmlhe8ni6A6KJLMujv0lP6bYnMqfr/2HT/qv8mbB+hnX+dD4pP8qAK/lr+N3P3gi0qE+tGi3o0eaJBAhHsILJcmsyUpg/4Vhvuxxcq574oHvqwpstPq3c5fKY27Jcf7XZ1NaTqD76n4GVcemtBw+H+oOXCtiiyQQIR7S6nQD71dn43B5+arPFVhouNKkpyxbDpQK1hdDNgB+lmEFYMwzyRudjbh9Xv5StJG0uASetVj5fKibE3bbkt0bazGTBCJEiNISdbI9SYicXg+Nt/pQFYWq9FxOD/fw6rdnGXQ7AWgeHeTd4qd5xpKLqiicd/Th9HowSstuTJGb6EKIiDvr6OWOz0uRKZW661+zo/U4g24nG1IeYUPKIwy6nexoPU7d9a8pMqVyx+flrKM32mGL75B0LoSIuBN2//RVx20HHbcdxKs6/vDYWmqsJQB8YLvEO10tfNTz7QNjfp6RF5V4xeykAhFCRJRP0zhpvxH4usicyrHyLezMK0VVFFRFYWdeKcfKt1BkvrfQ8KT9Bj4thA3JRNhIAhFCRFTr2BBDky5URaHGWkpD+exrO4rNaTSUb6XG6k8sQ5MuWseGohCx+D4yhSXEfeTkzPD7wm4jJ8HMe49v4qnUrDmvjVd17CuooHplHr//5gwn7DbKkldGKFIxH6lAhBARlaw38K/1v5w3edxvXXImxyu2skIv60FiiVQgQiAnZ0bSzrzQDolK0seHPFaEh1QgQgghQiIJRAghREhkCksIERbbt28P+3McOnQoYs8lZpIKRAixoKbf1Jfbcy9HiqbJyhwhhBAPTyoQIYQQIZEEIoQQIiSSQIQQQoTkfxJvgryLwznJAAAAAElFTkSuQmCC</v>
+      </c>
+      <c r="E758" t="str">
+        <v>19-09-2026 03:05:08 pm</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="str">
+        <v>6aae64fb04b0f40ffa8ac72b</v>
+      </c>
+      <c r="B759" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C759" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D759" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E759" t="str">
+        <v>19-09-2026 04:03:31 pm</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="str">
+        <v>6aae64fc04b0f40ffa8ac732</v>
+      </c>
+      <c r="B760" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C760" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D760" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E760" t="str">
+        <v>19-09-2026 04:03:32 pm</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="str">
+        <v>6aaea544de76c5357cd43dbb</v>
+      </c>
+      <c r="B761" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C761" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D761" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E761" t="str">
+        <v>19-09-2026 08:37:48 pm</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="str">
+        <v>6aaea545de76c5357cd43dc1</v>
+      </c>
+      <c r="B762" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C762" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D762" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E762" t="str">
+        <v>19-09-2026 08:37:49 pm</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="str">
+        <v>6aaea5fe8f11059b93e61a81</v>
+      </c>
+      <c r="B763" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C763" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D763" t="str">
+        <v>Started Playing game and Debited "10" and Balance "190"</v>
+      </c>
+      <c r="E763" t="str">
+        <v>19-09-2026 08:40:54 pm</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="str">
+        <v>6aaea5fe8f11059b93e61a87</v>
+      </c>
+      <c r="B764" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C764" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D764" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E764" t="str">
+        <v>19-09-2026 08:40:54 pm</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="str">
+        <v>6aaea69a8f11059b93e61aee</v>
+      </c>
+      <c r="B765" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C765" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D765" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aaea69a8f11059b93e61ade , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E765" t="str">
+        <v>19-09-2026 08:43:30 pm</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="str">
+        <v>6aaea60d8f11059b93e61ac8</v>
+      </c>
+      <c r="B766" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C766" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D766" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaea6008f11059b93e61aa5, Reward : 10, Qst No : 2 ,Question : How many boxes are unbroken in total?</v>
+      </c>
+      <c r="E766" t="str">
+        <v>19-09-2026 08:41:09 pm</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="str">
+        <v>6aaea69a8f11059b93e61af0</v>
+      </c>
+      <c r="B767" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C767" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D767" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aaea69a8f11059b93e61ade , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E767" t="str">
+        <v>19-09-2026 08:43:30 pm</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="str">
+        <v>6aaea6a88f11059b93e61b02</v>
+      </c>
+      <c r="B768" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C768" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D768" t="str">
+        <v>Answered incorrectly for Qst ID: 6aaea69a8f11059b93e61ade, Qst: How many boxes are unbroken in total?, Submitted Answer: 10, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nO3de3wU9dn38c/sIZtkQwIBCwEhREQl5SwgykkURaggzU2h8Eio1mp5pLev8mhfRfvoS2+PvdE+rYitrRzSu1ARECsBEWwgEM7UkBBExISgEKIEciTZZHfn+WOZbQI5bJbdnZ3N9f7HaOY3c0XIXPud+c1vFFVVVYQQQoh2MuldgBBCCGOSBiKEEMIvFr0LEEIv56aN0+W4PT7apctxhQg0SSCiQ9Kreeh9bCECSRKI6NBCnQakeYhIIglECCGEXySBhLFZs2bpcty1a9fqclwhhLFIAglTejUPvY8thDAOSSBhLtRpQJpH21znzgJg7tFT50qE0JckECHaqXptBtVrM/QuQwjdSQMRoh1c585Sm7WV2qyt3iQiREclDUSIdqhemwFOJzidkkJEhycNJAKVlpZSWlqqdxkRR0sfWCxgsUgKER2eNJAItGHDBjZs2KB3GRFHSx8xEycTM3GypBDR4UkDiTClpaVkZ2eTnZ0tKSSAvOnDZCJu5oPEzUr3pJBPt+A6+43e5QmhC2kgEWbDhg24XC5cLpekkADypo+7p2DueT3mHj09KcTtpnrd/+hdnhC6kAYSptauXdvuZ0C09GE2mzGbzZJCAuTK9KGRFCI6OmkgEURLH+PHj2f8+PGSQgLkyvShkRQiOjppIBFCSx8mk4kZM2aQlpaG2Wxm586dlJSU6F2eYbWUPjSSQkRH1iGWMjHiooRazb7uQ0sfEydOJCkpCYDx48eTlZXFxo0bWbBggd+1dGTe9HHPD5qkD42WQmq3ZVK97n9I+M9f61ClEPqI+Aai96KEoVjL6sr0oUlLSyM7O5udO3cyY8YMb2MRvmkrfWjiZqV7nk7/dAtxMx9sttFEIiN+MBOBFfENRBPJixI2lz4AunfvLinkGrSVPjQdMYV0hA9mom0dpoFEqpbSh0ZSiH98TR+ajppC/DmR19bWAhATE9PusbJadHiRm+gGp6WPCRMmNNsctBTidrvZuHGjDhUaU0szr1oiM7J8d+DAAQ4ePKh3GSIAJIEYWFvpQyMppH286QNQLFZq1v3Np3GKxQpAbdZW4maly/tCWpCTk4OiKIwfP17vUsQ1kgbSCu0hvO7du+tcSfNauvdxJbkX0j7eFXeBS1v8SG2X18jqCPdC2quqqor8/Hzv1506ddK5InEtpIG0QnsILxxPuL6mD42kEB85nZgTu2Gf+b+uaTeK2eJpQhb5FWts7969uFwuAPbt28c999yjc0XiWsjf7hZoJ2jwnHzDLYX4mj40kkJ8ZLEQ9+AjelcRsXJycrxf7969WxqIwUkDaYF2gta+DqcTbuPmZrFY+PDDD30aZ7n8aTg7Ozssm6KIbGVlZRw/fpyoqCgAjh8/TllZGV27dvV5HzJ9N7xIA2lG40UJIfxOuI2b27Zt29o9XlsjK5yaooh8e/bsQVVVbr31VsBzOWvPnj1MmzZN58qEv6SBNKPx5SGArKyssDnhulwuEhMTeeCBB65pPxaLBZfL5W2SIvyUPNdPl+MmPf9VUPa7e/duAMaOHYuqquzdu5ecnBxpIAYmDeQKV96cNplMYXXz2Ww2M3v2bF1rEMGnV/PQjt2eJnL27Fnq6upwOBw4L89eczqd1NXVebcpKyujqKiI2NhYhg4dCkBsbCyFhYVs2rSpyWWs6Oho7+VWi8WCzWYjOjqanj17tnuNOBFc0kCuIIsSdiznpo3Tu4RWBSsNtMTfxrVs2TJOnz7d5najRo3CarV6v96xYwcZGa2/FrhPnz4sWrTIr7pEcEkDaUQWJew4eny0S7fm0eOjXbocN1h69uzJSy+9xPLly8nKygJAURSGDRuGzWYDwG63A3D33Xd7x02ePNmbNGpqagBwOBx89tlnqKoKwMSJE3n44Ye9+xHhRRpII7IoYccSaSdyPdlsNhYsWEBqaip/+ctfcDgclJaWsmjRInr37t3smH79+tGv378TT0lJCW+88QaqqmK1WnnooYeYNGlSqH4E4QdZC+syXxYllBc0CdG6CRMm8Oqrr9K7d2/OnDnDM8880+TZj5YcOHCAxYsXU1xcTFJSEi+//LI0DwOQBHJZWw/m6ZVCZPVRYTS9evXixRdf5J133iEnJ4ff//73HD9+nPnz53svWWmcTierVq1i61bP2mNjxozh0Ucf9WulXhF6kkBo36KEoUohes4ykRkuxuSu/o7a/E3U7HmXmr3Lqc3fhLv6vC61xMTE8MQTTzB37lwAduzY4b2v0ZiqquzYsQOAuXPn8sQTT0jzMBBJIITvooRyIhe+aCgpoGrbf+MozAHV3fSbiglbv7F0mvQU1qTUkNem3TwfPHiwd/ZVY1arlcGDB3Pw4EHvtsI4Ij6BrF27ttUTsT+LEsq9EBEuavat5Pw7P8Tx1S4Ui43omydhv+On2O/4KdE3T0Kx2HCczOb8OzOo2bcq5PUdOnQIgBEjRnjqranhzTff5PXXX6eqqqrJ9w4fPhzy+sS16fAJRBYlFEZVs28llVv+CxQF+x2PEDfhcUzR8U22cddVUr1zKTV7l1O55QUA7KPnh6Q+h8NBQUEBiqIwfPhwcnNzefvtt7l48SIAJ06cYMGCBQwfPhxFUTh69CgOh0Om7BpIh24gsiihMKqGkgIqt74MikLntNeJGdz80jam6HjiJz+NtUcq5R88SeXWl4jqOxJrj+BfzsrLy6O+vp7k5GTWrVvHJ598gqqqDBgwAIDPP/+cV155hXvvvZc+ffpQXFxMXl4eI0eODHptIjAivoG0tvSBLEoojKpq+xJwu7Df8UiLzaOxmCEzaCgpoGbvcqq2LyHxweVBr1G7JFVcXExxcTFWq5XZs2d717766KOPeO+997wzsLQx0kCMI+IbSEtkUUJhVO7q73B8tRvFGkPchMd9Hhc3YSGXDq3GcXIX7urzmOK6Ba1GVVWb3NPo06cPv/jFL0hOTvb+t+nTpzNkyBDefPNN7zIohw8fRlVVFEUJWm0icDpsA5FFCYVROYr2g+rGdsOYq+55tMYUk0BUyu04TmRRf2o/0QN/ELQaT548SUVFBYqicP/99/PjH/+42VlYycnJvPLKK/z9739n06ZNVFRUcPLkSfr37x+02kTgRPwsLCEijbvSM/vP3C2l3WMt3W4AwFUZ3BmEhw4dolu3bjz77LPMmzev2eahsVqtzJs3jxdeeIHu3bt7Z26J8CcNRAij0S7vNPNgXpu8Y4J7ichut7NkyRK+//3v+zzm5ptv5rXXXpPnQQykw17CEsKoTPGe6eausqJ2j3VeHmOO7xHQmq40ffp0v8bFxsb6PVaEniQQIQzG1ncUKCYchXtw11X6PM5dW0590V5QTESljA5ihaKj6DAJRBYlFJHCFHcdtn5jcZzMpnrnUuInP+3TuOodb6I21GHrfycme9e2BwjRhohvIGvXrtWtechaViJYOk16CkdhDjV7l2PtkUrMkNaX4ak98gE1+1eByUynSU8GrA75YNaxRXwDATmRi8hjTUolfvIzVG55gfIPnqShpIC4CQsxxSQ02c5dW071jjc9zUNViZ/yG6w9Blzz8eWDmYAO0kCEiET20fNBUaj8+EVq9i7n0qHVRKXcgaVrXwCcZaeoL9qD2lAHJjPxU36D/bb0gB1fTuRCGogQBma/LZ2o5BFUbV+C4+QuHCf+iaPxBooJW/876TTpyYAkDyEakwYihMFZe6SS+OBy3DVl1Bftw1VVCoC5U3eiUkbLDXMRNNJAhIgQJnvXoC5PIsSV5DkQIYQQfpEGIoQQwi9yCUuIyypzOuty3Pgx5bocV4hrJQ0kTMkc+9DSq3lox5YmIoxIGkgY0vPp3lmzZnXYJgKhTwNtNa6S5/qFqBIh2k8aSBgL9YlclqUIH0nPf6Vb80h6/itdjiuMRxqI8ImczEKvI//swhhkFpZok56XUeQSjhDhSxKI8FmoPxFL8xAivEkDEcJPan0pzsrdqPXnAAUlqjuWhHEo1u/pXZoQISENJEKUl5dTUFDAxYsXURSFzp07M3DgQBISEtoeLNrFVX0ER/HzOMt3AO4rvmvC0uUubMnPYrYP1qE6IUJHGojBFRUVsXr1avLy8lBVtcn3FEVhyJAhzJkzh5SUFJ0qjCz1Z/9I3alnQHWhmGIwd74TU/QNALjrCnGV78B5cTvO8h1Ep7xIVNLPda5YiOCRBmJgmzdvJiMjA7fbjc1mY9CgQfTo0QOAc+fOkZ+fT25uLvn5+aSnpzNlypSQ1+i6+DUA5i69Q37sQKs/+0fqin4NKET1Wojt+qdQLE0TnuqswPH1b6k/u4y6wl8DSBMREUsaiEFt3ryZlStXoigK06ZNIy0tDbvd3mSbmpoa1q9fT2ZmJitWrAAIeROpzn4LgIQHXg3pcQPNVX3EkzxQiLnpT1iva/6ZGcWSQHTKS5jjBlN74ufUFf0Gc/wYzPZBoS1YiBCQabwGVFRUREZGBoqisHDhQubNm3dV8wCw2+2kp6ezcOFCFEUhIyODU6dOhaxO18WvuXTkAy4d+cCbRIzKUfwCqC6iej3eYvNozHrdbKJ6LgDV6RkrRASSBmJAq1evxu12c//99zNu3Lg2tx83bhxTp07F5XKxZs2aEFToUZ39Fric4HJ6k4gRqfWlOMuzUEwx2K5/yudxtt6/AlM0zoufojZ8G8QKhdCHNBCDKS8vJy8vD5vNRlpams/jZs6cSVRUFLm5uVRUVASxQg8tfWC2gNli6BTirNwNuDF3vvOqex6tUSydsSRMANw4K3KCVp8QepEGYjAFBQWoqsqgQYOavWzVErvdzsCBA1FVlWPHjgWxQg8tfcQO+SGxQ35o6BSiOs4CYIq5sd1jtTGq40xAaxIiHEgDMZgLFy4AkJSU1O6xPXv2BOD8+fMBrelK3vRhMmMf+3Pixj/uSSG5G3CWnQrqsYNDufxPtdWtmnd5jKK0vpkQBiQNpAPRnhNRgnwy86aPoWlYuvbF3KW3J4W4XdTs/mNQjx0Mis3TeN21J9s91l3rWf5FieoZ0JqECAfSQAyma9euAJw9e7bdY0tKSprsIxiuTB8aI6cQS/wYwISrfCeq0/f7R6rzIs6KnYAJS8LYoNUnhF6kgRhMamoqiqJw9OhRampqfB5XXV3N0aNHURSF1NTUoNV3ZfrQGDmFKFHdsXS5C9Vdi+Pr3/o8zvH1a+Cuw9JlEor1uiBWKIQ+pIEYTOfOnRkyZAgOh4P169f7PG7dunXU19czdOjQoK2P1VL60Bg5hdiSnwXFQv3ZZTR8916b2zd8+3fqz/4JFItnrBARSBqIAc2ZMwez2UxmZia7du1qc/vs7Gy2bNmC2Wxm7ty5QaurpfShMXIKMdsHE53yIqBefsL8aVTn1a+/VZ0XqSv6NbVfLgBUz1Pp9oEhr1eIUJClTAwoJSWF9PR0VqxYwdKlSyksLGTmzJlXTeutrq5m3bp1bNmyBVVVSU9PJzk5OSg1tZU+NHHjH/c8nZ67AfvYnzfbaMKVZ00rhbqiZ6g/u4z6c8uxXLGYorN8B7jrQLEQnfIyUUmP6lqzEMEkDcSgtDWtMjIyyMzMZNu2bc0uplhfX4/ZbGb+/Pncd999QavHmz6G/6jVpqClkEv/ep+a3X803BpZUUmPYY6/A0fxCzgvforzwsdXbGHC0uXey8u5R1bymDWr7SVcgmHt2rW6HFe0TRqIgU2ZMoUBAwawZs0acnNzOXz4cJPvK4rCsGHDmDt3btCSB/iePjRGTiEAZvsgYlPfR234DmfFbtR6z+w2JSoJS8LYiLxhrlfz0I4tTSQ8SQMxuL59+7J48WIqKio4duyY90HDxMREUlNTQ/JCKV/Th8boKUSjWK/D2u2HepcRUqE+kevZuETbpIFEiISEBG6//faQH9ebPgDMVqp3/8m3gWYrAJeOfEDc+Mcj4n0hQnQ00kDENfGuuAtcOri6/Tu4vEaWUVOIEB2ZNBDhP5cTU6fvETf2sWvbj9niaUJm+esohJHIb6zwn9lCp7sW6V2FCHOlpaUAdO/eXedKRKBJAxGikcqcznqXEHE2bNgAwIIFC3SuRASaNJAwdi0zUBrPlpGZLG2LH1OuW/OIH3P1E+2RorS0lOzsbADS0tIkhUQYaSBhaO3atfLQlg4i+USulw0bNuByubxfSwqJLNJAwlQgT+QduSkI/Wjpw2w2A5412SSFRBZpIMJnJc/107sEYSBa+pg4cSIAWVlZkkIijKzGK9qU9PxXHfLYwn9a+jCZTMyYMYO0tDTMZjM7d+70vthMGJ8kEOETOZGL9micPpKSkgAYP348WVlZbNy4UVJIhJAEIoQIqCvTh0ZSSORpMYEEYhaQP1NJ5YavEMbWXPoAz4OEkkIiS7MJRO+lm4UQxtRS+tBICoksrd4D8ScN1NbWAhATE9PufUnzEMLYWkofGkkhkSXg90AOHDjAwYMHA71bIYSO1q5d2+aHwLbSh0ZSSOQIeAPJyckhJycn0LsVQoQ5LX1MmDCh2fSh0VKI2+1m48aNIaxQBFpAG0hVVRX5+fnk5eVRVVUVyF0LIcKYr+lDIykkMgS0gezduxeXy4XL5WLfvn2B3LUQQkezZs1q9R6lr+lDIykkMgT0QcLGl652797NPffcE8jdCyHCUOMVdy0WCx9++KFP4ywWz+lH1sgyroA1kLKyMo4fP05UVBQAx48fp6ysjK5duwbqEEKIMNR4xd1t27a1e7zL5ZI1sgwqYA1kz549qKrKrbfeCnguZ+3Zs4dp06YF6hBCiDDjcrlITEzkgQceuKb9WCwWXC6Xd+VeYQwBayC7d+8GYOzYsaiqyt69e8nJyZEGIkQEM5vNzJ49W+8yhE7abCBnz56lrq4Oh8OB0+kEwOl0UldX592mrKyMoqIiYmNjGTp0KACxsbEUFhayadOmJpexoqOjvdc+LRYLNpuN6OhoevbsGdAfTAghRHD5lECWLVvG6dOn29xu1KhRWK1W79c7duwgIyOj1TF9+vRh0aJFvpQhhBAijLTZQHr27MlLL73E8uXLycrKAkBRFIYNG4bNZgPAbrcDcPfdd3vHTZ482Zs0ampqAHA4HHz22WeoqgrAxIkTefjhh737EUIIYRw+JRCbzcaCBQtITU3lL3/5Cw6Hg9LSUhYtWkTv3r2bHdOvXz/69fv3G+xKSkp44403UFUVq9XKQw89xKRJkwLzUwghhAi5dt1EnzBhAjfeeCNvvPEGX3/9Nc888wyPPfYYY8aMaXXcgQMHWLZsGZcuXSIpKYlFixaRnJx8TYULIUJPFjwVjbX7SfRevXrx4osvMmbMGOrq6vj973/Pu+++673B3pjT6eTdd99lyZIlXLp0iTFjxvDqq69K8xDCYPR8T4+8Iyh8+TWNNyYmhieeeILk5GRWr17Njh07SE9Pv2o7VVXZsWMHAHPnzvVpjRwhWjNy6nxdjntw8ypdjhtO5EQurnRNa2FpN88HDx7snX3VmNVqZfDgwU22FcJfejUPvY8tRLi6pgcJDx06BMCIESMAz2yr5cuXU19fz6OPPkqnTp0YMWIEBw8e5PDhw7I2lggIf9LApVrPc0uxMdHtHivNQ4jm+d1AHA4HBQUFKIrC8OHDyc3N5e233+bixYsAnDhxggULFjB8+HAUReHo0aM4HA6Zsit0kbXnMIoCU+9qfcKHEMJ3fjeQvLw86uvrSU5OZt26dXzyySeoqsqAAQMA+Pzzz3nllVe499576dOnD8XFxeTl5TFy5MiAFS+Er7bu2IuiKNJAhAggvxvI4cOHASguLqa4uBir1crs2bO9a1999NFHvPfee2zdurXJGGkgItTKK6s4eOSY9+vO8Z10rkiIyODXTXRVVb0NBDzLkbz88stMnz4dRVFQFIXp06fz8ssv06dPH+92hw8f9j6FLkSobN91EKfThdPp4tPdB/UuR4iI4VcDOXnyJBUVFSiKwrRp03jllVeafbYjOTmZV155hWnTpqEoChUVFZw8efKaixaiPT7Z+e+3Y27dIW/KFCJQ/LqEdejQIbp168bjjz/O97///Va3tVqtzJs3j1GjRrF06VIOHTpE//79/SpWiPb69vwFjhScwHb5RWdHCk7w7fkLfK9bos6VCWF8fiUQu93OkiVL2mwejd1888289tpr8jyICKlPdu7HraqMu20o424biltV+SR7v95lCRER/Gog06dPJzY2tt3jYmNjmT59uj+HFMIvWy9fvpp852gmTxgNwCdyGUuIgAjYGwmFCKXib0q4VOegrs5BQ4NnHbYGp5PaOod3m9LzFzh+8hRx9hjuuNWzIkKcPYbPT57ibx98TPdGl7Fiom1YL79+wGq1EB1tIzbaRvL1SSH8qYQwFmkgwrBeeOPPnDz1TZvb3XnHCKKirN6vN23bxf/785pWx9zY93pefXphQOoUIlK12kBk6WYRrpKvT2LF757jt8sy+GjbLsDzorMxIwcTfXm1g05xnsusMybf6R33ox/cjdViBqCq+hIAdQ4HOQfzvFPMp90zjl/973SibVGh+nGEMKRmG8jatWt1ax6y4qfwVbQtimd/+Qi3Dh7Aa2+torbOwZmS73j16YXckNyr2TGpN6WQelOK999PnznHr19eiqqqREVZefKxB/nhlDtD9BMIYWwtJhA5kQuj+MHdY0i9KYVfv7yUwuIzPLToBZ7+xUNMvnN0q+N27DnM87/7M9U1tfTp1YNXn15I/5Tm37AphLjaNS3nLkS4SOndkxVvPMvkO0dzqbaO3/z2bV5blkFDMy86a3A6eW1ZBk+9+Aeqa2qZfOdo/vqH56V5CNFOchM9jMhlw2sTGxPNi79awI19e/PWyvfJ3L6bXz4y56rtVLdK5vbdADz+kx/xk1n3h7pUISKCJJAwoeeEhUibLBEf53lY9bZhA72zrxqLirJy27CBTbYVQrSfJJAwE+o0EGnNAyB7/2cAjB89DICqmkv8dlkG9fUNLP7FT+gc34lxtw1lx97D7DrwGWlTJ+pZrhCGJQ1ERJTaOgeHjnyO6fKU3r2H83nhd3/h/IVyAPI+P8mzv3yEsaOGYFIUDuZ+Tm2dg5hoedGZEO0lDURElAO5BTjq6+l/Qx/+vPpD1mf+E1VVGTbwZgA+O/oFTzz7Ov/xg7vol9KbLwtPcyC3gAmjh+tcufBVr0/f1eW4Z+7+qS7HDWfSQERE2bU/F4AvC0/zZeFpoqwWfj7vP/hf/zEFgL+t38If/7qedZs+bTJGGogx6NU8tGNLE2lKGoiIGG5V9TYQ8CxH8sJTP28yPXfezKmMvnUQz/73H73LoOzan4tbVTEpSshrFv4J9Ylcz8YVzqSBGFh5eTkFBQVcvHgRRVHo3LkzAwcOJCEhQe/SdFHwRSEXyiswKQpzf3gfC+bPJMp69V/x/im9WfX753l71TpWf/AxF8orKPiikEG39NOhaiGMSxqIARUVFbF69Wry8vKuekWwoigMGTKEOXPmkJKS0sIeIlP2vn/R47quPPd/fsaIwQNa3TbKauGJR37MxDG38tySd9i1/zNpIEK0kzQQg9m8eTMZGRm43W5sNhuDBg2iR48eAJw7d478/Hxyc3PJz88nPT2dKVOm6Fxx6MTH2Vmz7CXi7DE+jxk8oD9//cMLfLAlK4iVCRGZpIEYyObNm1m5cqX3XfRpaWlXveGxpqaG9evXk5mZyYoVKwA6TBOZN3OqX+Pi7DF+jxXGUVxbBUByTCedK4kc8iS6QRQVFZGRkYGiKCxcuJB58+Y1+3pgu91Oeno6CxcuRFEUMjIyOHXqVOgLFiLM/OFULn84ldv2hsJn0kAMYvXq1bjdbu6//37GjRvX5vbjxo1j6tSpuFwu1qxp/eVJQkS64toq1pWcZF3JSW8SEddOLmEZQHl5OXl5edhsNtLS0nweN3PmTLZt20Zubi4VFRURMztr5NT5epcgDOYPp3Jxqm7v168PaPtDmGibJBADKCgoQFVVBg0a1Oxlq5bY7XYGDhyIqqocO3YsiBWGxsHNqzrkscW10dKHRTFhUUySQgJIEogBXLhwAYCkpKR2j+3Zsyf/+te/OH/+fKDL0oWcyEV7aenjxz1vAuDvZ09ICgkQSSARTntORJGnrEUHpKUPs6KwMHkI/9l3KBbFxPslX1J0qVLv8gxPGogBdO3aFYCzZ8+2e2xJSUmTfQjRkWjp40dJ/UmJjSc5phMzk27EpaosLT6id3mG1+EvYRlhZc/U1FQUReHo0aPU1NT4fB+kurqao0ePoigKqamp/pYqhCFdmT40/9l3KOtKTvJ+yZcsTB5CSmy8jlUaW4dOIHqv7NnY2rVrW3yZVOfOnRkyZAgOh4P169f7fIx169ZRX1/P0KFDI2YGlhC+ujJ9aCSFBE6HTyBgjJU958yZQ35+PpmZmaSkpLT5LEh2djZbtmzBbDYzd+5cf0sVwpBaSh8aSSGB0aETiJGkpKSQnp6OqqosXbqUVatWUVNTc9V21dXVrFy5krfeegtVVUlPTyc5OVmHioXQT0vpQyMpJDAkgYQJ7d3krb0TXVvTKiMjg8zMTLZt29bsYor19fWYzWbmz5/PfffdF/zihQgjbaUPjaSQaycNxGCmTJnCgAEDWLNmDbm5uRw+fLjJ9xVFYdiwYcydO1eSh+iQGj/30VpT0FLI38+eYGnxEXkuxA/SQPyk58qeffv2ZfHixVRUVHDs2DHvg4aJiYmkpqbKDXPRYfmaPjSSQq6NNBA/aat66vmpJSEhgdtvv1234wsRbnxNHxpJIddGGogftE854PkEI+8XEEJ/jX8vrYqJt4rzfBpnVTxzidaVnJTf53aSBuIHWdkzMEqe0+cVsknPf6XLcUVwNf69/OuZ4+0e71Td8vvcTtJA2qnxyp4gn1r8pVfz0I4tTSSyOFU33W2xPJ48+Jr2YzGZcKpu7++3aJ00kHaSlT0DK9Qncj0blwgei2LiVzfcqhVnF3cAAA6wSURBVHcZHY40kHa4coaHSVECPoNDex5EhF6w/t83franuWO09uyPEOFMclo7BHNlTz1PInIC07dxy4cGYVSSQHwUipU95USuv2D/GVy5f2kewsgkgfhIVvYUQoimJIH4QFb2DA/u6u9wFO3HXVUKioIp7nvYUkZjiuumd2kixPR8FYP4N2kgPmjr6VZ5mjW4GkoKqNr23zgKc+DyPH8vxYSt31g6TXoKa5K8NCvSnbn7p4Z4CVxHIQ2kDbKyp75q9q2kcuvL4HahWGOw3TAGc1fPIpGusmIchTk4TmbjKMwhfvIz2EfP17liEWxyIg8f0kDaICt76qdm30oqt/wXKAr2Ox4hbsLjmKKb/hm46yqp3rmUmr3LqdzyAkDImkh5eTkFBQVcvHgRRVHo3LkzAwcOlMUs0W9ygExECS1pIK2QlT3101BS4EkeikLntNeJGfxAs9uZouOJn/w01h6plH/wJJVbXyKq70isPYJ3OauoqIjVq1eTl5eHqqpNvqcoCkOGDGHOnDmkpKQErYZwpveUaGkioSMNpBWysqd+qrYvAbcL+x2PtNg8GosZMoOGkgJq9i6navsSEh9cHpS6Nm/eTEZGBm63G5vN1uwLvXJzc8nPzyc9Pd37ErCOKNQncpkSHXrSQFogK3vqx139HY6vdqNYY4ib8LjP4+ImLOTSodU4Tu7CXX0+4LOzNm/ezMqVK1EUhWnTppGWlobdbm+yTU1NDevXryczM5MVK1YAdOgmIiKbNJAWyMqe+nEU7QfVje2GMVfd82iNKSaBqJTbcZzIov7UfqIH/iBgNRUVFZGRkYGiKCxcuJBx45r/c7Xb7aSnp5OSksLSpUvJyMhgwIAB9O3bN2C1CBEupIE0Q1b21Je7sgQAc7f230OwdLsBx4ksXJf3ESirV6/G7XYzbdq0FptHY+PGjaOwsJDMzEzWrFnD4sWLA1qPEOFAGkgzZGVPnSmK559X3KD2iXeMErByysvLycvLw2azkZaW5vO4mTNnsm3bNnJzc6moqJDZWT4oLS0FoHv37jpXInwhH41F2DHFJwHgKitq91jn5THm+B4Bq6egoABVVRk0aNBV9zxaY7fbGThwIKqqcuzYsYDVE8k2bNjAhg0b9C5D+EgaiAg7tr6jQDHhKNyDu67S53Hu2nLqi/aCYiIqZXTA6rlw4QIASUlJ7R7bs2dPAM6fPx+weiJVaWkp2dnZZGdne5OICG/SQETYMcVdh63fWNSGWqp3LvV5XPWON1Eb6rDdOB6TvWsQK/Sd9pyIogTuklqk2rBhAy6XC5fLJSnEIKSBiLDUadJTYDJTs3c5tUc2trl97ZEPqNm/CkxmOk16MqC1dO3qaUZnz55t99iSkpIm+xDN09KH2WzGbDZLCjEIuYmOrOwZjqxJqcRPfobKLS9Q/sGTNJQUEDdhIaaYpjei3bXlVO9409M8VJX4Kb/B2mNAQGtJTU1FURSOHj1KTU2Nz/dBqqurOXr0KIqikJoqCz22RksfEydOBCArK4sNGzawYMECnSvzkAUcm9ehE4iefzjh/hcjHNhHzyd+6nOgmKjZu5xvX7+DC3/7GZUfv0Tlxy9x4W8/49vXx1CzbyUoJuKnPof9tvSA19G5c2eGDBmCw+Fg/fr1Po9bt24d9fX1DB06VGZgtUJLHyaTiRkzZpCWlobZbGbnzp3eBKcnPT9ghvuH2w6fQOREHt7st6UTlTyCqu1LcJzchePEP3E03kAxYet/J50mPRnw5NHYnDlzyM/PJzMzk5SUlDafBcnOzmbLli2YzWbmzp0btLoiQeP0oU1UGD9+PFlZWWzcuDFsUog/54pqVwMAcWZru8eGe/MAaSDCAKw9Ukl8cDnumjLqi/bhqvJcGzd36k5UyuiQ3DBPSUkhPT2dFStWsHTpUgoLC5k5c+ZVl7Oqq6tZt24dW7ZsQVVV0tPTSU5ODnp9RnVl+tCkpaWRnZ3Nzp07mTFjhl8z4MLBx98WgwIze9yodylBIQ1EGIbJ3jWgy5O0l7amVUZGBpmZmWzbtq3ZxRTr6+sxm83Mnz+f++67T7d6jaC59AGeBwnDMYW018bSr1CQBiKEwNNEBgwYwJo1a8jNzeXw4cNNvq8oCsOGDWPu3LmSPNrQUvrQGD2FXGioY9eFs96vE63ROlcUeNJAhGinvn37snjxYioqKjh27Jj3QcPExERSU1PlhrmPWkofGqOnkE2lRd4FWTO/PcW8XrfoXFHgSQMRwk8JCQncfvvtepdhSG2lD42RU8jG0sJ/f33uq4hsIB16Gq8QQh9a+pgwYUKrTUFLIW63m40b236gNFyUOGo4WFFKtMlMtMnMgYpSShw1epcVcJJAhK5KnuundwkixHxNHxojppAPSwtxqyr3fK8Pqgqbvi3iH6WFPNZnkN6lBZRuDWTkn07qctyDj/k2G2LI4UVBrqR5R259Q5fjhlrS81/p1jySnv9Kl+MKj7bufVzJiPdCNp7z/B2b0b0fKp4GsvGcNJCA0Kt5aMduq4no1Ty0Y3ekJiIiT2vvQtfSB4DFYuHDDz/0aZ8Wi+dUlZ2dTVpamm7vC/nqUgU1rgYuuZw0uD03yBtUF5dcTsDzOpoSRw35VWV0skQxsev1AHSyRJFXdZ53Th8lyWb3vvIm1mzBqpgBsJpMxJot2M1W+sUaYyKGrpewfE0DgdLexhXqE7mejUt4zJo1S+8SIpqWPgC2bdvW7vHaSr16ppBfHsvmePXFNrebcl0yNpPZ+/Xaki95/sv9rY65Ja4L7wy6OyB1hoLcAxECz6dmvZpHa5/YI4nL5SIxMZEHHnjgmvZjsVhwuVyYzeYAVea7frEJbBoxnWe+2Mt7JScAz7sv7+rWmxiTBUWBBIsNgDk9b/KOm3/9AKIuN5MKpwNVhVq3k3+e/xrtHZqzk27ipZtvJ8ZsnNOycSoVIsg6yok82LRGfOX/T7PZzOzZs/UoKaBizBbeSB3HHV2SWPxFDpdcTk7XVvGnQXdxs71Ls2OGxl/H0PjrvP9eeKmCR/P/iQrYTGZeuGk0Dxpwmq9M4xVCCD/MTLqRzSMf4GZ7F76sKWfawY/YWNr2fb0t3xUz9eA/+Lz6AjfEJpA5crohmwcYsIGcqWzgTGWD3mW06BtHGd84yvQuQwgRAv3tnfnHyGnM6N6PGlcDjx/dwdNf7PHeYG+swe3m6S/28Ejedqqc9czo3o8tox5gQFyiDpUHhuEayPLPLrL8s7ZvYOnlz+e28+dz2/UuQwgRInFmK28NvJPF/UYA8H7Jl7i9dzb+zY3K+yVfArC43wjeGninX8u8hxNDNZAzlQ1sPlHF5hNVYZlCvnGUsansEJvKDkkKEaKDSbB6bp6PT+zlnX3VmM1kZnxirybbGp2hbqIv/+wiTrfq/fr/TviezhU19edz23GqLu/Xzycb/4ahEP7qaFOiP/nuNAD3XtcHgEpnPc98sQeH28Wrt4wh0RrNPd368PF3xWw7fzoi1sYyTALR0ofFpGAxKWGXQrT0YVHMWBSzpBDRYek5m02vY19yOdlz8SwmReGurr3JKvuGCfvWs+HcV2R+e4q7939AVtk33N2tNyZFIefCWe/Dh0ZmmASipY/pt8QD8I/jlWGVQrT0MaPbbQBsPL9fUojosDralOhdF85Q53aRGpfI74o+I+Obz1GB0Z09LxvbV36OeblbSb9+ALfYu3Cs+gK7Lpxh8nXGfmeMIRKIlj5MCvxkaBceHtYFi0lh0xeVfF2hfwrR0odJMfHTHnfxsx6TsChm/lF2kNOO7/QuTwgRZNvOey5fHau+wKpvPsdqMvObG0fx/vCpvD98Kr+5cRRWk5lV33zOseoLTcYYmSEaiJY+7r85nt4JVnrFW5l6UyfcKqzM1X9GlpY+pncdSR/bdVxv68r9XUfgVt28e+6fepcnhAgit6qy/fzX3n+/Ja4Lm0dOZ0HyIEyKgklRWJA8iM0jp3NL3L8fNNx+/mvc6tWztYwk7BvIlelDEy4p5Mr0oZEUIkTHkFv5Hd/V12JSFB7rM4gtI5t/tmNAXCJbRj7AY308jeW7+lpyK419bgj7BnJl+tCESwq5Mn1oJIUI0TF8cv40vaLjeG/YFJ7tP8q75lVzokxmnu0/ig9u/QHJMfGGv4wV1g2kpfSh0TuFtJQ+NJJChIh8CRYbn972Q+7o4vuLrkYkdGfrqAeItxj7eZCwbiAtpQ+N3imkpfShkRQiRORbkDyITpaodo/rZIliQbKxXzAVtg2krfSh0SuFtJU+NJJChBCRKmwbSFvpQ6NXCmkrfWgkhQghIlVYPkjoa/rQPDysC5tPVLHpi0p+MrRLqw0nEHxNH5qf9ZjEprJD/KPsID/tcVerDUcIEZ56ffqu3iWEnbBMIL6mD02oU4iv6UMjKUQI4zpz90875LF9EXYJREsfAFaTwiofG4LV5HlL/eYTVTw8rAu94oOTQrT0AWBVzCz3sSFYFc/Uvk1lh/hZj0lcb+salPqEEIEX7idyvYRdA2m84u76YxXtHu90q0FdI6vxirvvf7en3eOdqkvWyBJCRISwaiBOt8p1sRbm+3DfozUWk4LTrWK5nEoCxam6+J41nod9uO/RGotixqm6sCgtP3AkhBDhLqwaiMWk8POR4ft6R4ti5vGeU/QuQwghwkJY3kQXQggR/qSBCCGE8Is0ECGEEH6RBiKEEMIvut5EH/mnk3oevk1DDi/SuwQhhAhbuiSQg4/dqMdhfT72kVvfCEEl4XdsIYRoD0VVDf5ORSGEELqQeyBCCCH8Ig1ECCGEX6SBCCGE8Is0ECGEEH6RBiKEEMIv0kCEEEL4RRqIEEIIv0gDEUII4RdpIEIIIfwiDUQIIYRfpIEIIYTwizQQIYQQfpEGIoQQwi/SQIQQQvhFGogQQgi/SAMRQgjhF2kgQggh/CINRAghhF+kgQghhPCLNBAhhBB+kQYihBDCL9JAhBBC+EUaiBBCCL9IAxFCCOEXaSBCCCH8Ig1ECCGEX6SBCCGE8Is0ECGEEH75/95UxoTBjg+VAAAAAElFTkSuQmCC</v>
+      </c>
+      <c r="E768" t="str">
+        <v>19-09-2026 08:43:44 pm</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="str">
+        <v>6aaeb60f537f17f2a778338d</v>
+      </c>
+      <c r="B769" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C769" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D769" t="str">
+        <v>Started Playing game and Debited "10" and Balance "180"</v>
+      </c>
+      <c r="E769" t="str">
+        <v>19-09-2026 09:49:27 pm</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="str">
+        <v>6aaeb610537f17f2a7783393</v>
+      </c>
+      <c r="B770" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C770" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D770" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E770" t="str">
+        <v>19-09-2026 09:49:28 pm</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="str">
+        <v>6aaeb628537f17f2a77833d1</v>
+      </c>
+      <c r="B771" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C771" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D771" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaeb612537f17f2a77833b0, Reward : 10, Qst No : 2 ,Question : How many colour names match their text colour out of 4?</v>
+      </c>
+      <c r="E771" t="str">
+        <v>19-09-2026 09:49:52 pm</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="str">
+        <v>6aaeb62d537f17f2a77833f3</v>
+      </c>
+      <c r="B772" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C772" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D772" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aaeb62c537f17f2a77833e5 , Question : How many colour names match their text colour out of 6?, Type : Colours &amp; Name Match </v>
+      </c>
+      <c r="E772" t="str">
+        <v>19-09-2026 09:49:57 pm</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="str">
+        <v>6aaeb62d537f17f2a77833f6</v>
+      </c>
+      <c r="B773" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C773" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D773" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aaeb62c537f17f2a77833e5 , Question : How many colour names match their text colour out of 6?, Type : Colours &amp; Name Match </v>
+      </c>
+      <c r="E773" t="str">
+        <v>19-09-2026 09:49:57 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E757"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E773"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E773"/>
+  <dimension ref="A1:E815"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13540,9 +13540,723 @@
         <v>19-09-2026 09:49:57 pm</v>
       </c>
     </row>
+    <row r="774">
+      <c r="A774" t="str">
+        <v>6aaeb638537f17f2a7783409</v>
+      </c>
+      <c r="B774" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C774" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D774" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaeb62c537f17f2a77833e5, Reward : 40, Qst No : 3 ,Question : How many colour names match their text colour out of 6?</v>
+      </c>
+      <c r="E774" t="str">
+        <v>19-09-2026 09:50:08 pm</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="str">
+        <v>6aaf6b4b0e31dc3ae90555bb</v>
+      </c>
+      <c r="B775" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C775" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D775" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E775" t="str">
+        <v>20-09-2026 10:42:43 am</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="str">
+        <v>6aaf6b4b0e31dc3ae90555c2</v>
+      </c>
+      <c r="B776" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C776" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D776" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E776" t="str">
+        <v>20-09-2026 10:42:43 am</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="str">
+        <v>6aaf6b560e31dc3ae90556d1</v>
+      </c>
+      <c r="B777" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C777" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D777" t="str">
+        <v>Started Playing game and Debited "10" and Balance "170"</v>
+      </c>
+      <c r="E777" t="str">
+        <v>20-09-2026 10:42:54 am</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="str">
+        <v>6aaf6b560e31dc3ae90556d7</v>
+      </c>
+      <c r="B778" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C778" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D778" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E778" t="str">
+        <v>20-09-2026 10:42:54 am</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="str">
+        <v>6aaf6c9e0e31dc3ae905574a</v>
+      </c>
+      <c r="B779" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C779" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D779" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aaf6c9d0e31dc3ae905573b , Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?, Type :  </v>
+      </c>
+      <c r="E779" t="str">
+        <v>20-09-2026 10:48:22 am</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="str">
+        <v>6aaf6b670e31dc3ae9055727</v>
+      </c>
+      <c r="B780" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C780" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D780" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaf6b580e31dc3ae9055709, Reward : 10, Qst No : 2 ,Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?</v>
+      </c>
+      <c r="E780" t="str">
+        <v>20-09-2026 10:43:11 am</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="str">
+        <v>6aaf6cb30e31dc3ae9055761</v>
+      </c>
+      <c r="B781" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C781" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D781" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E781" t="str">
+        <v>20-09-2026 10:48:43 am</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="str">
+        <v>6aaf6c9e0e31dc3ae905574c</v>
+      </c>
+      <c r="B782" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C782" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D782" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aaf6c9d0e31dc3ae905573b , Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?, Type :  </v>
+      </c>
+      <c r="E782" t="str">
+        <v>20-09-2026 10:48:22 am</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="str">
+        <v>6aaf6cb30e31dc3ae9055763</v>
+      </c>
+      <c r="B783" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C783" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D783" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E783" t="str">
+        <v>20-09-2026 10:48:43 am</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="str">
+        <v>6aaf9375e23970ad97e3383d</v>
+      </c>
+      <c r="B784" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C784" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D784" t="str">
+        <v>Started Playing game and Debited "10" and Balance "160"</v>
+      </c>
+      <c r="E784" t="str">
+        <v>20-09-2026 01:34:05 pm</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="str">
+        <v>6aaf9376e23970ad97e33843</v>
+      </c>
+      <c r="B785" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C785" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D785" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E785" t="str">
+        <v>20-09-2026 01:34:06 pm</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="str">
+        <v>6aaf938be23970ad97e33881</v>
+      </c>
+      <c r="B786" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C786" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D786" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaf9378e23970ad97e33860, Reward : 10, Qst No : 2 ,Question : How many words are scrambled?</v>
+      </c>
+      <c r="E786" t="str">
+        <v>20-09-2026 01:34:27 pm</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="str">
+        <v>6aafa5fc1093682c88de79a7</v>
+      </c>
+      <c r="B787" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C787" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D787" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E787" t="str">
+        <v>20-09-2026 02:53:08 pm</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="str">
+        <v>6aafa5fd1093682c88de79ae</v>
+      </c>
+      <c r="B788" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C788" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D788" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E788" t="str">
+        <v>20-09-2026 02:53:09 pm</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="str">
+        <v>6aafa6051093682c88de7abf</v>
+      </c>
+      <c r="B789" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C789" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D789" t="str">
+        <v>Started Playing game and Debited "10" and Balance "150"</v>
+      </c>
+      <c r="E789" t="str">
+        <v>20-09-2026 02:53:17 pm</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="str">
+        <v>6aafa640da1d0531eddb8889</v>
+      </c>
+      <c r="B790" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C790" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D790" t="str">
+        <v>Answerd Correctly to Qst ID : 6aafa633da1d0531eddb886b, Reward : 10, Qst No : 2 ,Question : How many letters are colored with the WRONG color?</v>
+      </c>
+      <c r="E790" t="str">
+        <v>20-09-2026 02:54:16 pm</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="str">
+        <v>6aafdeb7e883a286342eacf6</v>
+      </c>
+      <c r="B791" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C791" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D791" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aafdeb6e883a286342eacee , Question : How many letters are colored with the WRONG color?, Type :  </v>
+      </c>
+      <c r="E791" t="str">
+        <v>20-09-2026 06:55:11 pm</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="str">
+        <v>6aafdebbe883a286342ead0b</v>
+      </c>
+      <c r="B792" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C792" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D792" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E792" t="str">
+        <v>20-09-2026 06:55:15 pm</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="str">
+        <v>6aafdebbe883a286342ead11</v>
+      </c>
+      <c r="B793" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C793" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D793" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E793" t="str">
+        <v>20-09-2026 06:55:15 pm</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="str">
+        <v>6aafdec4e883a286342eae23</v>
+      </c>
+      <c r="B794" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C794" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D794" t="str">
+        <v>Started Playing game and Debited "10" and Balance "140"</v>
+      </c>
+      <c r="E794" t="str">
+        <v>20-09-2026 06:55:24 pm</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="str">
+        <v>6aafded4e883a286342eae72</v>
+      </c>
+      <c r="B795" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C795" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D795" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aafded4e883a286342eae63 , Question : How many letters are colored with the WRONG color?, Type :  </v>
+      </c>
+      <c r="E795" t="str">
+        <v>20-09-2026 06:55:40 pm</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="str">
+        <v>6aafded0e883a286342eae4f</v>
+      </c>
+      <c r="B796" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C796" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D796" t="str">
+        <v>Answerd Correctly to Qst ID : 6aafdec6e883a286342eae2e, Reward : 10, Qst No : 2 ,Question : How many letters are colored with the WRONG color?</v>
+      </c>
+      <c r="E796" t="str">
+        <v>20-09-2026 06:55:36 pm</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="str">
+        <v>6aafded5e883a286342eae74</v>
+      </c>
+      <c r="B797" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C797" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D797" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aafded4e883a286342eae63 , Question : How many letters are colored with the WRONG color?, Type :  </v>
+      </c>
+      <c r="E797" t="str">
+        <v>20-09-2026 06:55:41 pm</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="str">
+        <v>6aafdeece883a286342eae99</v>
+      </c>
+      <c r="B798" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C798" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D798" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E798" t="str">
+        <v>20-09-2026 06:56:04 pm</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="str">
+        <v>6aafdeece883a286342eaea0</v>
+      </c>
+      <c r="B799" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C799" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D799" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E799" t="str">
+        <v>20-09-2026 06:56:04 pm</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="str">
+        <v>6aafdef4e883a286342eafb3</v>
+      </c>
+      <c r="B800" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C800" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D800" t="str">
+        <v>Started Playing game and Debited "10" and Balance "130"</v>
+      </c>
+      <c r="E800" t="str">
+        <v>20-09-2026 06:56:12 pm</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="str">
+        <v>6aafdf0be883a286342eb001</v>
+      </c>
+      <c r="B801" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C801" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D801" t="str">
+        <v>Answered incorrectly for Qst ID: 6aafdef5e883a286342eafe5, Qst: How many times do the letters R, F, X, B, N appear in the paragraph?, Submitted Answer: 29, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nOydd3wc5bX+v7NVvVuSJduSe7fB2BjTTU8oCYQQICSBhIS0m07yIzftQhJuchNSIL0SWkLoBEy3wbjg3nuVbMnqXSttmfn9sdZKq20zO++sRqt5Ph+DZua857zzanbOnOfMo5X6+r0KCaCE/hP2Q1KIGB3TXfw4cY+qnqKSjLnGw0kN0rjKSsxNfb+tYW4VMd6UmBtRd6j3pdpN5EFVUVVOTYnyUzI+1YVTdwEJ+dSG/083pLAfpNiGWnzF3JHwQOKjqqcoJWOu8XBSg5JYZSnuj7ZEw4XegFQ715E8VENs8tAxhZSE0gtRySNBFDHWKfxdxTYbwfUSmjzCnRiTPAT5SuhTQLCEEJs8dExBQKjEIxImEEBI9aF+pM5LVMNwkckjqerDiBEGVR+iEL/6EB1AnYH4aWjONsl6EDgwsUPhrgVkEZH3XzHVh9jkkVT1IQRSzM2hR+ImECXOlm4k6U4kdSUKIqkrURMZs9SVAaME5AOdxsk7EEldiYKhtz8TUFeiMLLUlTo/MROIoJZHdBcp5R6ix0gP6sr49UoNdaUNIi+fJAqWBGb61yuxh9Rzn6Oi+hhR6kpjpNRNST91FcdBfAorpdSVTl+jnLrSjnSirox4SklskFbUlXBfg9WHyDmF98tTeBeNg3SvPnRFjkFdDSBqAjH0BmRE4zwNqCtRMzMjdRXuNOEObcONhBHUlW6konFufuoqJW9dqUY6Nc61IXYFYkT1MaLUlcZIKbwriGyci4LI5GF4chzr1cdYp64EWOodbsbGuUjqKpaviASihP4T9sOIIt2rD12Rxzp1pW0G6qOmuHEusiVu/upD8HNxku4s6kqdz3juwxKIofyrEdSVaqRT49x4WJoPrWYjuF5GFKOCc4il+QgzN2IKAkIlN7lICiuljXOdl+gob5yLpK5MmYhibhgRQJ2BRV2pc5ju1JWl+YgTQ2X1AUMSSPgFI/jySdKdRV2p82nGxrlI6iq5GRlx0SXpXfeSpgt1JRgWdZXMKNVQ48cGYlse5mqcpxN1Zfx6WZoPrX70r1diD6nnPkdF9WFpPgSFUq/5iIZBCiul1JVOX6OcutKOdKKujHhKSWyQVtSVcF+D1YfIOVmaDz3ezKf5iAaboTcgIxrnaUBdiZqZGamrcKcJd2gbbiSMoK50IxWNc/NTV5bmQ53PkUjRwQrEiOpjRKkrjZFSeFcQ2TgXBUvzoRXp1Dg30LXJGueihpuxcZ4KzUc02IQ2QAQg3asPXZHHOnWlbQbqo6a4cS6yJW7+6sPSfGjzZl7NRzSo+3PuCSCq+hBzHadT49x4WJoPrWYjuF5GFKOCc4il+QgzN2IKAkKJm9zpBJKKxrnOS3SUN85FUlemTEQxN4wIoM7Aoq7UOUx36srSfMSJoaP6ALAJv3ySdGdRV+p8mrFxLpK6Sm5GRlx0SXrXvaTpQl0JhkVdJTNKNZL1o4vCMlfjPJ2oK+PXy9J8aPWjf70Se0g99zkqqg9L8yEolD7NRzQknUBEUldiqg9zUlfakU7UlYAZj3XqSrivwepD5JwszYceb6ND8xENQprogEVdGfzwaEbqKtxpwh3ahhsJI6gr3UhF49z81JWl+VDn0xwpOskEYi7qSmOkFN4VRDbORcHSfGhFOjXODXRtssa5qOFmbJyPlOYjGsRVIEkg3asPXZHHOnWlbQbqo6a4cS6yJW7+6sPSfGjzNro0H9GgOYGIqj5Evv+THo1z42FpPrSajeB6GVGMCs4hluYjzNyIKQgIZex6aUogIhvnooabsXEukroyZSKKuWFEAHUGFnWlzmG6U1eW5iNODMHVB+ilsKzGuXgYlDwszYcB3nUvabpQV4JhUVfJjFINkWeoOoGYq3GeTtSV8etlaT60+tG/Xok9pJ77HBXVh6X5EBRKvOYjIoIkqUsgIqkrMdWHOakr7Ugn6krAjMc6dSXc12D1IXJOluZDj7fRq/mIhuQoLIu6SmaUapiRugp3mnCHtuFGwgjqSjdS0Tg3P3VlaT7U+TRHig6HJAVnlTCBmIu60hgphXcFkY1zUbA0H1qRTo1zA12brHEuargZG+dm0nxEQ8p0IOlefeiKPNapK20zUB81xY1zkS1x81cfluZDm7fRr/kI+ZIGvcVNIKKqD5Hv/6RH49x4WJoPrWYjuF5GFKOCc4il+QgzN2IKAkIZv15DkwfESSAiG+eihpuxcS6SujJlIoq5YUQAdQYWdaXOYbpTV5bmI04Mg6mrAainsKzGuXgYlDwszYcB3nUvabpQV4JhUVfJjFINo6irAURNIOZqnKcTdWX8elmaD61+9K9XYg+p5z5HRfVhaT4EhUqN5iMaIhKISOpKTPVhTupKO9KJuhIw47FOXQn3NVh9iJyTpfnQ4y29NB/RkJjCsqirZEaphhmpq3CnCXdoG24kjKCudCMVjXPzU1eW5kOdT3Ok6HDEqj5gWAIxF3WlMVIK7woiG+eiYGk+tCKdGucGujZZ41zUcDM2zs2u+YgGQ3Qg6V596Io81qkrbTNQHzXFjXORLXHzVx+W5kObt/TUfERDKIGIqj5Evv+THo1z42FpPrSajeB6GVGMCs4hluYjzNyIKQgIlXrNRzTYQGzjXNRwMzbORVJXpkxEMTeMCKDOwKKu1DlMd+rK0nzEiTEC1NUAolNYVuNcPAxKHpbmwwDvupc0XagrwbCoq2RGqUYqqasB2MzVOE8n6sr49bI0H1r96F+vxB5Sz32OiurD0nwICjVymo9oUNlET/pjo3a4dtMUUlfakU7UlYAZj3XqSrivwepD5JwszYceb+mv+YiG8ARiUVfJjFINM1JX4U4T7tA23EgYQV3pRioa5+anrizNhzqf5kjR4dBSfcDQBDKi1JXGSCm8K4hsnIuCpfnQinRqnBvo2mSNc1HDzdg4H42aj2jQrQNJ9+pDV+SxTl1pm4H6qClunItsiZu/+rA0H9q8jR3NRzQEE0iSj48i3/9Jj8a58bA0H1rNRnC9DCxGRfmyNB9h5kZMQUAoc2g+oiFOBaLzEh3ljXOR1JUpE1HMDSMCqDOwqCsVDgU3zgHTUVeW5iNODJNQVwOwWY1zoVOI8GnGxrlI6iq5GRlx0SXpXfeSpgt1JRgWdZXMKNUYaepqADEqkNSV/elBXRm/XpbmQ6sf/euV2EPquc9RUX1Ymg9Bocyl+YiGKAkk6Y+N2uHaTVNIXWlHOlFXAmY81qkr4b6Moa4szYceb2NT8xENmt/CSnfqStTMzEhdhTtNuEPbcCNhBHWlG6lonJufurI0H+p8mummPwC91QdEJJDUfQRHlLoSFsrA12wGXFqaD41Ip8a5ga5N1jgXNdyMjfN00XxEg6YKJN2rD12Rxzp1pW0G6qOmuHEusiVu/urD0nxo8za2NR/RMCSBxL9SRb7/kx6Nc+NhaT60mo3gehlYjIryZWk+wsyNmIKAUObVfETD6QSi8xId5Y1zkdSVKRNRzA0jAqgzsKgrFQ4FN84B01FXluYjTgwTU1cQnJMqCsuirtT5NGPjXCR1ldyMkjyPFFNXIh2Yn7oSDIu6SmaUapiRuhqALZVlf3pQV8avl6X50OpH/3ol9pB67nNUVB+W5kNQKPNrPsJ8nf5/wgpETPVhTupKO9KJuhIw47FOXQn3ZQx1ZWk+9HizNB/DMXROcRNIulNXomZmRuoq3GnCHdqGGwkjqCvdSEXj3PzUlaX5UOfTlDd9wdTVAHT/OXc1GFHqSlgoA1+zGXBpaT40Ip0a5wa6NlnjXNRwMzbO01nzAcPmJMVJIOlefeiKPNapK20zUB81xY1zkS1x81cfluZDmzdL8xHhJ8pG1AQi8v2f9GicGw9L86HVbATXy4hiVHAOsTQfYeZGTEFAqNGl+YgG7RTWKG+ci6SuTJmIYm4YEUCdgUVdqXOY7tSVpfmIE2OUUVcDiEggFnWlzqcZG+ciqavkZpTkeaSYuhLpwPzUlWBY1FUyo1TDjNRVuNPwTQOa6OlEXRlfY1iaD61+9K9XYg+p5z5HRfVhaT4EhRqdmo9oCEsgYqoPc1JX2pFO1JWAGY916kq4r8HqQ+ScLM2HHm+W5mM4YlFXAztCCSTdqStRMzMjdRXuNOEObcONhBHUlW6konFufurK0nyo82nKm77BjfPTUQADKKwRpa6EhTLiNZthLi3Nh0akU+PcQNcma5yLGm7GxvlY03xEgw3Sv/rQFXmsU1faZqA+aoob5yJb4uavPizNhzZvluYjwk/MjfAdNpHv/6RH49x4WJoPrWYjuF5GFKOCc4il+QgzN2IKAkKNfs1HNMSnsEZ541wkdWXKRBRzw4gA6gws6kqdw9FNXen0NcqpK+1IJ+oqfEfsBDLmqKvYPs3YOBdJXSU3oyTPI8XUlUgH5qeuBMOIxnkaUFdjVfMRbcY6m+jpRF0ZX2NYmg+tfvSvV2IPqec+R0X1YWk+BIVKH81HNERPIKOcutKOdKKuBMx4rFNXwn0NVh8i52RpPvR4szQfw6GFuhpAZAJJA+pK1MzMSF2FO024Q9twI2EEdaUbqWicm5+6sjQf6nya8qafQs1HNOiisEaUuhIWyojXbIa5tDQfGpFOjXMDXVuajyRNLM3HcKjRfERDeAJJg+pDV+SxTl1pm4H6qClunItsiZu/+rA0H9q8WZqPCD8xN6LuCEMSFUg6Nc6Nh6X50Go2gutlRDEqOIdYmo8wcyOmICBUemo+omEwgYzyxrlI6sqUiSjmhhEB1BlY1JU6h6ObutLpa5RTV9qRTtRV4hkHE8iYo65i+zRj41wkdZXcjJI8jxRTVyIdmJ+6EgxL85HMKNUwI3UV7jThjqjQQGGlE3VlfI1haT60+tG/Xok9pJ77HBXVh6X5EBQqvTUf0WAb7dSVdqQTdSVgxmOduhLua7D6EDknS/Ohx5ul+RgOvdTVAFRWIOalrkTNzIzUVbjThDu0DTcSRlBXupGKxrn5qStL86HOpylv+iOs+YgG1RTWiFJXwkIZ8ZrNMJeW5kMj0qlxbqBrS/ORpIml+RiOZDUf0aAigZi3+tAVeaxTV9pmoD5qihvnIlvi5q8+LM2HNm+W5iPCT8yNqDsS+kqQQNKpcW48LM2HVrMRXC8jilHBOcTSfISZGzEFAaHGjuZjKAZmlLACMWPjXCR1ZcpEFHPDiADqDCzqSp3D0U1d6fQ1yqkr7Ugn6iq5GcdJIOlCXcX2acbGuUjqKrkZJXkeKaauRDowP3UlGJbmI5lRqmFG6ircacIdqofHSCDpRF0ZX2NYmg+tfvSvV2IPqec+R0X1YWk+BIUae5qPaH5iViBmpK60I52oKwEzHuvUlXBfg9WHyDlZmg893izNx3AYQV0NIEoCMS91Zfhrrcn4sjQfIs0EIRWNc/NTV5bmQ51PU970Taj5iGYdtQIZUepKWCgjXrMZ5tLSfGhEOjXODXRtaT6SNLE0H8MhUvMRDcMSiHmrD12Rxzp1pW0G6qOmuHEusiVu/urD0nxo82ZpPiL8xNyIukO9ryEYkkDSqXFuPCzNh1azEVwvI4pRwTnE0nyEmRsxBQGhxrbmI9oBx9BtMzbO1Y5o3PoYkt3JuAUfjupA9nmo3/RX8qqWkVOxKK6vjsOr6O8+RenCm1ECPuo3/JGCaZeSNW6W5vknQrTqY8crBymsyGPigtKY47Y8t4/xs8cxfmaxhgCw960jZOZlUL24IqqBreZ5ZGc2jL9M1fzVwRjqSuprwVbzb+RJN6BkxFirJO/wz+z3EIj6kBDcd8mkDIoyE/8hh6ZemVW1fVxZnUGeO4G9yairv+5ax7Lxk5lTXK5q+Hv1xzne0cpNs85Mbk6W5kMYjGycD3Vx+ooe/dRVb9N+Dv/n6/h7W6P6bNm3gpo3f4jNnpHQV+v+FZza+OegC9lPzZs/pKd+56BbgzUfm57ew9FNJ+OOXfvYDk7sbIjuKw62v3yQA2tqYo6yHXkce+2L8Z2kmLqKBamvAeeun4CnXrUDtWFeOdrHiij//rnXw9929tLUK6vy09Ab4O87e+nojx15ZDQfiYc9sHklWxpPqPa56sQh/rRrrf7gceakejIJDluajySHD4MjXair0jNvpf69P9K89z+Un/XxiONNO/9FTuVZZJXNSW6OA3Myiebj47+5Gne2C0h/6iqxB/Hc5x+vKozYV9Pp5+6V7ZxR6mJaoT1559FgQs3HKzd8nsKMzKTnoz6SFkP9sDQfOv0MOeAAc1JXWpE1biY5lYto3vF0MIEMCdnfWU/nsTVMfv9PgrORA3Qee5fexr0oyGQWT6dg6nIkmyOG90h0122l+8RGsDnIqz6frJIZAPh7W+lp2E1OxRnY3bkh+0B/F91128ipXITdlZ2gcR5Ee10XNdtOIdklpi6dQFbBYPXU0dBNflk27mwn3S29dDb2UlCRy8E1NeSNy6J6UQWSTaL9ZBdHt9Rhd9iYft6kuEFj/Zakjr1IzRvB34OUUUagfDm4CkH2Y2tej5I7FSVz/BBHMramtSi5U0L7pa6j2BrfBbkfuehMlOKzBv17GpC6jyMXLcJ2aiW2nmPIuVORS89HsbnC/Z5aia37MErudJSMsiizVbA1rsfWsRvFloFcvhwlqzJ0fraOvSh2N5Lsx9a0FrnkHOT8xNRkR3+A763uIMdp455zcrDbBj9FLR6Zjae89PoUqvLsnFnmwjbs06cAWxu8HO0MMCHHzuLyoI0EtPUrnOzyU5Xv5N0TfRRm2Dh7fPB4Q0+ArY0+uvplclw2zip3UZql/nvgOr197Gqp58xxE3jl6F5cdjtXVM3CaXfQ5OlizcmjNHl6yHI4ObdyMpPzikP3hxNd7ThsNnKcbup6Omns7WJOcTlv1Rykrqed6QWlLKuoxmELn0+3r5+3aw/T2NvNsopqZheF/54UFNbVHeVAWxOZdicXT5pGWXYeAHtbTyHLCnNLBq+nnU112CSJecP2ZTvdTCkoiX3yluYj3lEhUH/HVIGR1nyUnnELR17+Jv1tNbgLJoX8NO96Gpsjg5K5H8Tf18GeRz+Et/0EORMWE/B0UFv3I3KrzmHObU/Hn6qigKJw5KVv0LzzSXImno3i66fm9e8z4cK7qTjvSyBJHHjy40y4+FuMX/rZ0NimbY9zcs2vOfNLWxKcaHBH7fYGdr12iNIpRbTVdfHOn7dww72XMH528APz/L1vs/Qj81h84xwOrz/Bpqf24Mpy0nysndySbD711w+w85VDvPXbDRRXFeBw29n01G4URaJoYr7qNXVs+Q62Y/9EKVqMYndia9mC3ebCd/kKlIxy7Dt+hJI3E//ZvwyNkZo34Fx9G97LXobM8TgO/An7rp8Eb9TOXOy7f4Zc8T78S34Okg2pYTWOXT9ByZ+O1H0cxVWAs2MfSuEZ9F/8FCBBwINrzR3Y2nYgF5+JdPBvKDnVYXOV5H4c6z6HrWkdSvFi8Lbg3PlDfIvuxz/xegCcex5ACfRha9mEJPcTqPow3kU/ibsGAVnm/nVddHkVfnFJPjmuwRvm6hP9PLCxi7JsOyWZdh7f08u0Qgc/OD+PDPvgB/Y3W7o51RtgQo6DR1p6mFno5IcX5uG0SWxr9PKHbT1U5NjZ1+Ij12Xj0WuKeOFIH3/Z0cO0Agd5bokDrX5+v62bn1yUz6xiZ/i5D5/06R0H25r55CuPc/HE6ayqPYjDZmPp+Go2NtTwzXdeYEp+EWVZeRxsa+RH773Kry7+EFdUBxPqna8/zj1nX8Ftsxfz2rG9PLJ3I8WZ2bR6eshyuDjQ1sT5Eybz5ytuDYXt9vZz0wt/I9PpxCZJ/GTD63zlrIv43MILAGj19PDZN/7FgbZGFpZO4GR3O/dteJUfn3ct102bx+vH9vP43k2svfVr2CQJvyxzxyuP4bTbWXfrV5GQ8AYCfHzFo/z3OVfGTiCW5mN4FDHWww440knzUTLvgxx7/fs07XqWCed/OXS0aceTFM/5IDZnNifX/hRv+wkWfPYdXDnBxmvjtsc58p+v09u0L06jPBijafvjNO98kpk3P0b+5AuD+3Y+xZEXv0xu1TJyJyyhYPplNO96OjyB7Pw3JXM/iM3hVnV+LcfbufmBKyidUoS/388z31vJm7/byEd/9T6iXW+djT2cee1MPvKzK+nr7KenzcPKP25i0QdnccEngy8N7HrtMK//ej0Q+eQetUndshXbkUfxn/sH5IorQQGp9yTOV5cj1TyPMuMu5Kobse/+Gfh7wZEFgL3mGeSCuSj5s5Fat2LfeT/+hd8hMO2TQb+t23G+8xHsR5cQmBy8+Uj9zchZl+E77xGQ7Nhrn8ex8SvYWjYhFy/BcfAvSK3b6L/kBZS8GUiBPpxrPhE2X/u+h7A3v4f34mdDVYVj34M4tn4bufhs5NOViL1pLd6lvyEw7jwkuT/h7+LP23vZ2eTjO8vymJg3SF21eGQe2NjFVZMz+PTCHGwSnOoJ8PW3Onh8t4dPLsgaXEsJ/nRlES47HGr38/W3OlhxpJ/rpgerys5+mbPHu7jvgny6vTIev8LfdvTw0TlZ3Dw76MfjV/jsq628fKQvLIGouTUEZJl1t36d7v4+CtxZ3LvuFa6fNp97z70aAJ8c4JaX/s5j+zeFEshwnOhq5/KqWXzr7EuRkHh832b+Z+0KDrQ1MqMw+Flq7evlE3OX8rmF5wPwu+2reWjraq6ePI9JeYX8YP0KarrbefH6zzIxtwAZhR+sXcG3332RM8smcOmkGTy09R32tpxibsl4djbX0R8I0Ont40BbEzMLS9nUcByP38clk2aoOPNBWJoPkQGC0PCd6PFhBs2H3ZVD8axrad71dOhId91WPM0HKV0UvFGNX3Inc29/MZQ8ZH8/jozgE3lYAz4GmnY+TV7VuaHkATBu/o248yfSfuA1AEoWfITeU7vxNO0HoLdhL70NeyhZcJNqzceMi6oonVIEgMPtYMmNc2g83Erbyc6Yc1t49QxcmQ7ySrM5tO4Esl9m6c3zQ8fnXj6V/PKciHExfw0Fs/Fd9h/kiitOGykg+1Bcudi87QAEJn0QlAC2uleDY+Q+bCdeRq4Ovg1nr3kOJaOYwLQ7BuMVLUQpvQBb3eth4QIzPgNS8AYdGLcMAMlzCgDbiZeQK9+Hkhe8aSj2DAIzPx823l7zLIGJ14VRUv4ZdwXHN6wajJ9VSaDiKnDmorjjUCDAm8f7eP6Qh1vnZLGs0hV2bM2JfvwyfHRudoiyKs+2s7zKzfq68MR029wsXKdzz7QCB0srXLxd2xdm8/4pGWQ7Jcqy7WQ7JX59WSEfmD7Yg+j2KhRl2OnyJmjgR/mg3zBjAYXuTCbmFWKTJB57/8f56lmXhI53evsoy8qjra83rs/PzF+GdHpj6fgqAE71doXMijKy+NT8ZaHtT81bhtNm45Vje+kL+Hmr5gAfn7OEibkFANgkibuXXIqsyLxydA9zSsopz87j3ZNHAFhz8gjLKquZlFfI+rpjAKysOcSisokUZQwm6ETnrxuW5iMq1FFYJm2cR0PZmbfQtONf9NTvIGv8App2PElW6ezQq7uOrCK6Tmzk5Jpf0tu4D0/zQWx29+ngiaP3tR0n4Gll889nh+0PeHvoazsKQMGUi3HmltO862kmLv82zTv/Tea4mWSPXxjn/MKPFE8Ip5kKKoMccUd9F0UT8iJGSxLklmeH3HQ29pCZ78aV5QyzKazMjRgbc0b2DCSbC/vW72Nr34vUsRdF8SMpfmQlEDRyFyOXL8dW+yyBSddjr3sNRfERmHhdMGZ3DZK3HfeL4a92KoE+GNo3AZTMIa+LOk+fo+wDwNZbg7/yyqHWyLlTBzdlH1JvHbaa58ioeyX8RGQfUs/xwZHZE1Wd/8E2Pw9u7mJZhYtb52RF/O7qewIoCty5IvzBoz+gICsSAXlwxITcwcpFAipzbOxu8oWNK88ZtLHbJLJdEv/a28uBVj9HOvz0+hTsksICtyvMVxhifPon5hSFfrZJEoUZ2fxr32Y2N9Syv62RFk8PbrudCbmRLw8MwGmzU5g5eNPOdQY/N/5AILRvUm4hLtvgebjsDipzCqjpaqOxpwtvIMDU/JKwuea63JRl5VLX3YGExCWTZrD65BHuWngea08e4Yrq2ZS4s1hfd4xPzD2blbUHuHX24uiTtDQfuqD1vYvECcSEmo+YIxTInXA2mcVTadr1DBPHzaRl93NMuODrIZO69b+n5s17GTf/Q4xf+hlyJyxB9vWz40+XqEogTncuORVnUDmEIhuA3RW8OUs2B+PmfSgY+6Jv0bL7WcqXfkZV43wAciD8KdPf7wfAneOOPkCScDgGP7gOpw1/f2CYkYIsK8P2xIatbRf2lTdC4TzkyvchL/gOSsEcnK9cGDYyUH0TzvV3IfU1Yzv+HMr4S4NNdgBXDkrOVPyLfzZ8KijDXlqQJBvKac8R16vNjRQYRjcpQ87P5gB7JnLVjQSqBrVAA7NUXIM3UEXFq9wd/TI/WttBebadb5wdPelmOiWynBL3XRC9pzT0BjHs10l/AHJdEkPP1DWk897aF+Arb3SQ45K4eJKbW+ZkMaPIyX1rOkKXqZbbj8s+eG14/D5ue+lhPH4v109fyCfmLuXM0kp+suENtsZ5bVeSpFD1EQt+JbI66gv4yHO5yXNnnN72R0ze4/eR6Qg+7FwyaQZPHdhKU28X25vq+P6576MkM5sfrF3BwfZmjne2cXnV7OFhBCKdqCtxmo9o0N1EHznqKoZPSWLcGbdwamNQNCj7+iiZf2PIrHHLoxTPvo6p1z0Y2te6N6h7CATCKYWg2/DJZpRMxdN8iKzSuUinn7QUOcDx179D/uSLyCiaDEDJwo9Qt+43NGz5B77eForn3RA519g7aDwc/lR7cncTNptEYWWuquUbN7UIb6+PluPtFFcVAAp+XyDUZFcD6fjTSA433gv/GbxBA/g6kfqbYcjNXCm7CD4LzqYAACAASURBVMVVhO34k9gaV+Nf9ofQMTl3Go66N5GzKweTigL2vQ8iuQoIqHgDCkAumIvUsmkgIgC2th1DZ4ucMwWp+xhywbxBK383rh334Z90I0pWBWoQkBXuX9eJx6/w4wvzyXRIUdd8Yq6DHp+C2y4xaUhvZMURD619CtMLBz9eh9v9FGe6Qp/FPc0+JuTFfhX4vTofrX0BfnFpMeNOv3UlK3CyO0B5rLewVN4rNjXUcLijmSeuvp0zSyeEhh3uaKFP9iflc8DwSHszfQE/Gfbgudf1dFLf08m0gnEUuDMpysxmc0MtH5g2SK0eamuita+X6UVBWvmc8VU4bXYe2rqaPHcGM4tKGZeZQ5e3n4e2vMOsorIQBaZmrpbmI8nhKhC/B2Jq6ir2iHELbsLX00Tt2z+hcOb7cGQOXmyOjFw8zQfwe9oA6D65meNv3hv06AtPINE0H2WL7qCv5TDHX/1v/J42At4ejr/xPzRueRRH9iCfnlk8jdzKxZxYeX+Q0soJNq6767dx7OVv4mk5HPfsDq0/wbb/HMDXH+DEzkbWP7GTWcsnk5EXowIZhslLKiickMdrv1pPx6lu+nt9rPrDZnrbBs8x4Zo788Hvwda+BwgK9xwbvhykhAKeQT82B/Kk67Hv/TWKq4hA2WB/KFD1IZBsODd+BXpPgOzFfvgRHHt/gWJ3RoSMNafA9DuxtWzCvv+3SIE+bO27cez+v7CBgamfwNa4Gsf+h8DfjdTfimvLPdhOvBhOjyXAP/f1sqPJx4WT3Bxu9/POiX5WD/tX3xPgnAoXJVk2frahi2MdAQKywrqTXv64vQffsOLvd9t6ONzux+NXeHRPL4fa/HxgegwOH8hxBj/Ou5u9APT4FH63rZuGngB9gcEP+zMHPPxjV6+mT3+uK1gJbGqoRUGhP+DjoW2r2dxQQ7/fn2B0bEhAr9/HN995jmZPN6d6OvnWO89TkpnDldXBiuG22Yt5+sA2nj64nf6AjyPtzXxr9QtUZOdxedVMIEh7XTBhKk8d2MY54ycjIVGcmc3MolJWHN0TslM7J+1noctB4gijVPMRDbErEBNrPqJRV0N/dGaPo3DaZbTuX0H15feFmVZf9SMOPnMXm38xH8megTu/gqlX/4JDz3+R7lM7KJp9TdzIeZPPZ8p1v6b2zXtp2PIPAFw5ZUy97iFyK8N52ZKFN3H05W9SvOCm0D5v63Eatz1K0dwPkFk8NfJcTmP+FVPZ8vw+3vrdRiSbxLzLp7D8rhi8bxQXDqed63+wnJd/+i5/vfN5ACadUc6kM8pjDYlAYPqnkJrfw7HyOnDmAhKBOV8h4C7C1rY73Lb6RuwH/kBg2u2hRjgAWRPwnfdXHFu+jXvFBacnl41/7t3I1TcnOo1B/2UXwaL7ce76X9j9fyg2N4GZn8Oxd/D14UDVjUi+Dhz7fo1jzwNBn9lV+Jb9WXXfA6CuO3j3f+lQHy8diqxKAT5/Zg5XT83gh+fn84tN3Xzh9eADicMm8f4pGXxsbrgA78pqN19/qwOfrJDrsvHtZXksGBeZQAdw3gQ3l1Rl8H/vdfHg5m5kReGaaVncNi+LZ/Z78AbAZYeN9f009sp8fH7sZDQcZ4yr5M755/KrLSv5zda3UZC4dspc7j33/fxg3Qoaejspy4rss8XG4F1mYWkligLnPvELAOYUl/PIVR8j2xns23xu4fn0B/z8YM0K7nnnBQCWlFfx8Ps+Rs7pnooEXDpxJq8c3ct5ldWhGOdWTGFfawOXRksgluYj3lHDZiB193oEslCp0nxETyBq/ShyAG/nSeyuHBxZRdFtEvRDFEWmv70GyWbHlVsRorOGomnb49Su+l8WfnEjNodbFXUVPk+F9pNdZOS7ycyL8/pvghPvaupBURTySgepq4RrNcRA6mtGCXggewLDL0wtinPJUw/+vqCwz+aKOK5GcS4F+sFzMvi3rxw5UQcqsg+ppwYc2SiZZRFzThQjyv8Soq1PodsrU5ZtD71tNRQSwSqitV+mPMuG067uBcgur0KXV6YsyxYSLw49mx6fwj3vtPPry6I1v+Ofd6/PS5Oni4rsgrAeicrhYUbDTRt6O+n3B5iUVxjNnL6An5Nd7RRmZEW8TRU9bJzJGNU4NyCBGFZ96HiHN9nqI3YCMar6iHJYVPJIzleMCDr/XIns68XvaWffE7dQMPMqJl58z2nHEZHUz0nzgdgGqqKqnJqi3VhHOHUXkL7f3mDmEFlLS6H/hP2QnJ8h+PP2bsZl2fnAjOF/ciRxjLgWGnofGtskSZgkGBjlsBmTB4yi13ZVJA8guQQyctWH8ckD9CeQ/U/eTvvB13DnT2Dup17FkVmoK3nEtY7rJhXJQ+UAI5JHlN2ikod+X4MIzxv6biDDR3d65Rh/5Td+HFHJIwlzjYeTGqQvgYz15JHQzeDByARiRPVhMHWVnK8YEQT8sURPyyE8TQfIrT4vJFLU9A7v8DlpPhDbIIkhCcxSUX2kInmc9mBo8gj7IXlfCV2lovoQmzxim1jUVYSvmBtRd6jzo8lFrAQyxqkrEJNAIFG+EJBALOoqSV8JYowS6krjTvUWo5y6UhkutvVYrz40JA/Q+KdMRFJXujDWk4dBowTkA53GyTsQSV2JgqHvwSTpXCR1JQojS10Z6wfEVh+DThPu0DY8SQwmEINv9Cp2a3ckEGb5no+hSJ66SmKIUdSVrpDCLiDVEO7aZNSVKIxQrhEcKnb1IQrppPmIZhBMIEZRV0KQGupKFERWH4kDqDMQv06poq50h1E/2qTUlUike/WhK7JB1JUoiKSuBMwgtEcVhSWSuhLW7BbkBwyqPkaEukoSRlBXupH6t65EQSj9odq5jreuVEN84zzJKaQklF6M5u/5UAtbKu8KIhvnoiAyeRieHMd69THWqSsBlnqHj3jj3IgRo7r6EB1AncHAnoQVyMg1zi3qSscM1EdNceNcZEvc/NWH4E+71TgXj7H+1pXOUcK+UCqE1Pc9k0ZqGueCqKsUvuQQ22wE18uIYlRwDhHZ8jBX4zydqCvj1ysdvudDra+4CURU41wkdWXKRBRzw4gA6gws6kqdw3SnrsRUH+akrrQjnagrI55SEhsM3xMzgYwcdRXbpxkb5yKpq+RmlOR5pJi6EunA/NSVYFjUVTKjVMOM1FW404Q7tA0XCHEUljDqyvgaQzR15Q0EkDX4PN7Zxh92rKXXP/iVprFG1zS08aeX1vCdv7zADx9dwT/f2kRXb/Q/MZ7Il3qD4Wb61yuxB2O4z3VNtTxTs9cI15GQwOPv5+GtL1LTcSpZFwAcb6/j71tfoF/2JbCMDdnbSs/x3+LvPRj1eF/jS3jq/qV6TrHQ37IST/2/Lc1Hmms+og2JmkBEUVfaMfqoq0NtTVzz9O/wBoZ/EU/sGR9qa+L/NrxBd3/sRKAoCr9/fjXX/fdv+cdr62lo76K2sY1fPPUml33jV7y+aW/UGGlFXQnwtfLUMf5xZFv4aMU4zUevt48H1z/BkdYoXw2rAYdaanlw/RN4vPEfFuLNSfY10nX4x/i79kQeBDz1/6bnxF8TeEmMvqaXE/iJ583SfAyHWTUf0RDxhVIiqSvDX2tNxpfg6mN3Sz1HOlqGR9HkI5r1o29s4KHnVnH7Vcv40vUX43IGf1Xdnn6++7cX+frvnuYv37yNJTOrtE3YCOpKN1LRODc/dSWq95FqzUfOlP8HeIVEjTIFtbtHFGNB8xENur8TPRZGSvPR7evnzWMHaPJ0U5VfyPKJM3DYgoXWupNHmVFUys7mOmo721lcNpGWvh4WlU0g0zH4BUdt/R72NNezuGwiboeTYx2trK87So/fy9SCEi6YMBWbZKOhp5MDbU0ArD95lOlFpVTmBL8+d19rA5sbaun2eSnNzObiSTModA//zobop9nt6ec3z7zNtcvm842bLgs7lpPp5qefuZ4bf/An7n/sNZ6599OhY/0+P6u2HaCupZPxxXksP2NGKPEAeH1+3t52kJrGNkqL8li+cDo5meFfkdvY3sm63Udp7ughJ8vNsjmTmVga/FIgWVHYsPcYc6vHU9fSyYa9RynMy2bpzCrGFeRG/X3E+zXuam9ke+spPLKP8Rk5XFReTc7p30NLXy9Huts4o6Cc1+oP0+ztZWZeCUtLJoTG13u6aezrZnpeMa/VHabT188ZhWUsKIz/9bXtvn7ebjhGU38P1dkFXFRahSPKF4IBHGuro8vbw/yy6aF9B5uP4/F7WVB+ep8U3Idkoyhz8Jv89jQdYUvdPrKdGVw8+SwKM/PDfB9oPs72U/vp9fVRml3I+VWLyHPH/r56v+xnzfHtHGuvozAjjwurz6IgM/q6x0SCm4cie+hvXknAU4vNXUpmyRVIA1/cBXjb1mDPnoW/eyf+3mNkll6D4m9D8fdgd4/H76lF9hyNGtaRMw+bK/gFbrK3if7WNQT663FkT8ddvBxJCl6rSsCDr2MjzsKl+Dq24evcii2jAnfRRdid+RG+NZ3wqK4+RAdQZxBvSFgCGe2aj80Ntdz16hO47A5mFZfxm621TMwr4olrbifb6eJTrzzOuZWTeavmAAB3L7mUn296ix9dcA03zVwU8vPwrvd4ev823r7lyzx/aCfffPs5ziitJNeVyS82rWJWURmPX/sJdjTV8fLh4Fe7PrB5FZ+afw6V0/L57rsv8e8DW1lUNhG3zcGWxlpc61/jPzfcRVl24q8KXbfnCN19/dx48aKox50OGx++aBH/+8SrHK1vYfL4Yo7Ut/C5XzyOp9/HnOrx7Ktt4FdPvcXD93yCcQW51Da1c9fPH6PH08+cqvEcqmvmgX+9we++ejOzJgVvuC+u3cH3H36JqRUllOTnsr+2gfsfe5UHv/Rhzp8/Db8/wGd+/jhXnT2Hd3ccZkpFCYdONgLwyLdvZ3pladg8Y/3uFODuza/yRv0RFhWPx6ZIbGmtI9/l5rnlt5LvdLOh+STf276SGfkl9Pq9VGbm8su973FJeTU/XXQFNknitfpDPHJkO9kOF1l2J4XuDH6+Zw23VC/g/807P2rgra2n+MKml8l2OJmSXcjfD2+n2J3JH5deR2lG5NfCbqrbwwNrHuHNT/6RTEcw2X7rtV9xqruFlZ/8ExmnE97XXnmA6+dcwgdmXQzAP7a9yLG2k0wtmsih1hoeeu8J/nbDfUzKD671vSv/wMsH3mVh+QwcNjs7Gw7idjzKv276CcVZBRGf2lZPB59/8X5OdTUxr3Q6tZ2neGDtP3jgfXezqGJ2yE5P49zftYu2HXeiyH04c2bj695H18H/oWjBwzjzzwjOY9vHcRedT1/zGwDYnIV4297F17WLkrNX4G1+g56aPw6GtOcS8NYje1spWfwcLlcRnobnad/7TeyuEuwZE+k68gCOrCkUn/EoNncpAU8tzVtuJrP8g/S3vI09swp/914kZz6l57yB3VUS/0RUnL8ZG+dm13xEg74KxESaD1lR+NpbzzCzuIy/XHkrGQ4np7o7ueqp3/LXnev44pkXArCruZ5XP/wFchwuCjOyWFt3lOcO7QwlEAWFZw9s54YZC7FJEr/Z+g53LjiXu5dcenp8HTe9+He2nKrl8upZ9Pq8fH3Vszx53R1k2B1sazzJE/s289vLbuKK6lkAnOxu5/J//4YXDu/m0wuWheYca50On2gGYHpFaQwLmFMdvBEdOdXM5PHF3PvwS2S53Tz5/U+Tl51Bt6efG7//R37z3Dv84Par+e8/PU+my8U/v/Mp8rIz8Pr8fOU3T/GtPz7Hs/fdhd8f4MePvcrNy8/i7puvABR8Pj833/c3/rlyC+fPnxaKvfPISf5z/+coysumrbOX677ze/799ha+fetVqn5XqxuOs+LkQf5+3vUsKa4A4FBXKx9Y+QRv1h/hhonBG2JvwEd5Rg4/WXQ5dkliY0sdn1z7LBeXVXPNhOD3Yp/ydHPb5AX8v3nB71tfcfIgd295jeXl1WHVCgp4ZT9f2/wKiwrLeeCsK3Ha7LR7Pdyx7nl+vOsdfrk4cv4XVC3ip6v/xua6PZw/6UzqOhs52dWAXXKw/dR+lk6cz+HWE9R3NXHx5MHvrO8PeHn+o78m151FQ3crNz7xNV7Yt4ovLr2ZLXX7eGHfKn75/rs5v2oREnCys5HrH/8qrx1azy0LI+fx47f/Qnd/L0/f8gDFWQX45QD/89bvuee1X/Pix36Fyx75FcED6Dn+EL11/4y4P/i7d2Nzjw8uj+KnbddnsbnHUXTGP7E5clACPbRu+xhtuz7DuGXvIp3+GmJv507GLVuFZM/G7izC2/ZuyGfWxDvImnhHaNvXtYuWTTeQPekuXAVLCPTV0b77q2SW30D+7J8iSXYCfSdo2ngtHfvuoXDhX0LzDPTVUnbBRiR7Fv6ewzSuuwhP/dPkVN0V81zDYWk+1B1IwtdphJroo13zsbO5jtquNr54xoVkOJwAlOfk8bf338YHps0P2V08cTrTCkooz8nD7XBw48wz2Fh/nPruDgA21ddwsruD66cvBMBus/Hm8f2sqj1Iv9/P3JIKdt/xbZZWVEed4KziUl64/tNcXj3z9Dko+AIyua4M2vt6Ep+IAn3eIJ+c6XZGNwCyM4If5h5PP03t3Ww+WMsnrlpKXnYGEKS6fvnFD3PbFWdT29TO1kO13PG+ZaHjLqeDO963jCP1zRxvaMVut/HYd+7grmsvDMXo6O2jtDCHjm5P2Aw+cP5CivKyQYHC3CymTyilsa07yiyjY3FJBU9fdHMoeQQUBZsk4bbZae0Pj/Xl2Uuxn/6QLimuYFHxeF6pPxQ67rTZ+MLMpaHt91VOZ1JWPq/WDdgMzmRd80ma+nv5/MyzcZ6mrApcmdxcPZ+3G4/jV+SIuZblFDFrXDXv1e4E4L2TO5lZUs2c0slsOhmsPlcf20JV/nimFA4mrKumnUuuOyvkY1pxFQ3dwV7Z7NLJPHbj/ZxXdWaw2a0o+JUAOe4s2vu6IubQ7e3lnaObuWXBVcHqBHDY7HzyrA/S3NvGrobDQOwPu+Qqxp41CXtm+D/JlhGy8XfuJNB7jJwp38B2mrKS7NnkTLmbQN9JfB0bQrYZJZfgyJqOPaMC7BkR8QYQ6D9J27bbcRddQP707wDgaVqBovjIm/5dJCn4O7BnTCBn4p30Nb+G4h+8jrIm3I5kD66hI3sqdtd4Av1q325LJ+rKHJqPaHBAemg+ajvbAKjOLwrbf2bphLDG+aS8wrDjV1bN4ntOFy8c3sVdC8/jmYM7OKtsQsjPfedfwzdWPsunXnmcTIeLiyZO5dqpC7jydHUxfMYZdidOm4N7177C3tZT7GtpxC/L+JUAAZXnUpIf5LXbunsoLRhKeQ2eR1N78IM2Lj+Xk83tKIrCpNLwcx+gptbtCnLSP3zkZe5//JXQcVkO+jve0Mrk8mLyszN57M0N7Dh8gv01jbR19+Jy2Jk6YVyY39KC3LBfUE6mG69f7dlBlt1JQJG5d8fb7O9oZn9nMxISPkVGGeLYabczISuc867KLmBHW0Noe1xGNrnO8KfvSTn5nOjtZPhVVNsTfEi4c93zYR8OnyzjlwPUe7qYmBXJsV9YdRavHloLwHsndrGkcl6wIqoLvt30bs1WLpqyOGxMRW549ZjhcOI//aZepsONzWbjp6v/zoHm4xxsOY6iKHgDPmQik1h9ZxMBReZ37z3Jnzc9E9o/sFa1HfWcNYTGGo6silvIKPtAxP627bcT6K8HwN9XC4Aja3qYjSN7RvC45wSu0x8dR1biFzcUfzdtWz+B3V1C4byHQAo+q8q9tdhcJdicBeFxcmagKAEC/XWhffaMwV6WBEjOXBRZX7PejNRVuNOEO7QNNxJSshSWCTUfOc4gP+2Vw29ksiIz9LvTXPbwZqnb4eSaqfN54fBO7pi3lBVHd3PP0itCxxeXTWTVzV9id0s9rx7dx4oju/nC0X9x3/lXc8us8JsGBCmuj/znYeYVl3Nl9WzuWXolc4rLWP6vB0OJLOZZnz6wdHY1AGt2HeH688+Iarpm52HcTifzplRQ3xq8MfqG3cQVRUFCIvd0o/xbt1zBzAmRDebKcfl0efq57f6/g6Jw7bkL+MSV5zB/SiX3/eNlahpbw+zttviXaaLf6obmE3xm/QssLqrk/ZXT+e/5FzIzv4SzX/5jWLJXZAVZUUIVCECv30eGffCyDciRN9xev498Z/iTsQJkn+5X/HLxVWQ5Iimf0oyciH0AF04+iz9seoq6zkY2ntjFDZd/CZvNxiPbX+JkZxM7Tx3kS+fcGjbGHqMpD7Cr4RCfef4+5pVN4fKp5/D18z7GzJJqrnrkCxDlLcGc0431u86+kcUV8yKOl+cURezTCpvj9A09MOy1YTlYEQ5UAsENd9w7lSL7aNv5aQLeNsYtfRHJPvjyiOTMj4wBKP5gdS45sgd/xn76/1phaT60BUiu+gCwpYvmY0pBMQA7Gk+G7f/86//my289HXfsh2YsZF9LA0/s24IvIHP11LlA8Eb0/TUvsb3pJHOKx/PVxct55cNfYEZRKWtOHAHAfvrJauBz/9yhnWTY7Tx29Sf45PxzWDiuAo/fR4unh/4IrcgQDDnp6RNKOWf2ZB569m2aO7ojDPbXNvDk21u57tz55GS6mVRaiMNuY+fRujCXP33idT72479TVV6E3WajpbOHOdXloX+yLPP06q30+3ys33OUE41t/OLzN/K56y7gnDmTyc5wcayhhX7fsOpCp+bj2dq9jMvI5k/nXsdHpyxgTsE4Gvt66Av46QsMxvIrMns7msK2d7Q3MK+gLLSvqb+Xes8g7dHt93Kwq4X5hZH9oyk5hSGbufnjQv/qe7t48cR+Yt3yZxRXUZZTzD+2vYjH52Xh+JksLJ+OXbLx0PonKMjMY17Z9BijI/GfA++Q7crkD9d9j1sWXMXc0ql09/fS6emiLxD5hF2WU0Kmw01jTxuzSyeH/mW53Dy953W6vCqo0QRwZAfn721fH7bf2/4eAM6cmap9dez7Ft72zRQv+gd2d8WQIxKO7GnI/k583eHiTm/7BmzOfGzuMvTBoq50zEB91NNGUYSEo1PzMSmviPMqp/CzjW+xo/EkPjnAi4d28ebx/VxZHbu8hyDNNa2ghAc2vsWVk2eFqpksh5MNp2q4b+0r1Ha1ISsKm+trONHZxvxxwQ9GUWbwyezVo3up7+kgz5WBx+9jT0uQGmjs6eKrK5/FJwfo83tVn9//3HEtkiRxy31/5dl3t3P8VCuH6pp4+NX1fOJ//8GkskK+dlOwse92Orl22QIefnU97+09ij8Q4L29R3n6na1cdtYscrMyeP85c/nzS2t4Y/M+fP4AR+qb+e7fXmTLgRqK83PJywo+sW8+WAOAx+vjwWdWsefYKfq8sdTQ0fHo6xt48NlVMY4q5DrddHj7ONIVrGzqerv4f1teB6Bf9p+2CuK+Hauo6e2g2+/lp7vW0NTXyy3Vg0/hsqLw3W1v0djXS7vXww+2B+NeP2l2xMU0v7CMeQVl/HjXara01uNXZLa01nPvzrdp7OuJ+SovwEXVZ/H8vrdZWD6dDIcLl93FmRWzeePwe1xUfRY2DU+kuc4serye4Ku/QEN3K9958yECiky/f/haS9gkiRvnXcG/d73Gf/a/gzfgpa6zkR+8+XvW1myjPDfJt5KGxLBnVJBRcjldR/4Pb+tqFNmLt309nQd/jKvoQhzZM4eax0T30V/hqXuS3GnfQpFlvJ07Q/8C/fVkjLsce8YE2nd/BX/3AQj00Vv/b3rrniB7wh2hV3lVhKLz0P/SXfMnfaeeBMaq5iOaTyE6kJHSfAzHry69kW+ueo7rn/szCgqZDhffPPtS3j9lTsKxH5pxBj/Z8AY3zAinjH59yY18feWzLP/nr4EgBXb9tDP45Pzg21TzSsYzvXAc33j7OT42ZwlfW3wJG+qPc8PzfyHX5UZC4r8WXUhxRha7mmM0AKOcf2VJPv/67qf45dNvcd8jL+P1BW+s+dmZfOjCM/nC9ReR6Rpssn/7tqsIyDJ3/fwJArKMw27ntsuX8LErgg3m733sahw2O3f/4Rn8gSDts3hmFT/61HXYJImzZ1fx0cuW8NMnXudXT61EVuAD583nm7dczgNPvkVbV2+ocR8LA6exeschTjS38V/XXxzV7q7pZ7GztYHrVj5BrtOFw2bnKzPPIc/hZk97U5jt4uJKrn3rMQKKQnlmDr9e8j6m5g5SNi6bg8k5BVz6+t9QgOrsAv6w9FrGubMi1lUCHlzyfr63/U1uX/ssCmCTJK4YP5UfLFge99wurD6LJ3e9xpKJA8lL4uzKeayv3cFF1WfFHTscHz/zWrad2s+tT91DjisLu83GXUtuJD8jl31NkRoKgC+e8xECSoAfrvoT33/ztwDMK53GQ9fcgzvWG1gabh4SkD/3QTr3fYvWbR9FUQJIkoOM0mvIm/lj1X48jS8DCp37vxdxLKfq8+RN/w4li/5J254v07j+4mBsezY5VZ8lZ+rXNE3fc+o57JnV5Ewa0EKlU/UhOoA6A63TkLp6POrJIyHVh/F/rqS1r5e2vl4m5BRE9Dxi4S871/HI7o289ZH/CnuaHJhTi6eH9j4P5dl5ZIeatsGjsqLQ3u8hz5UREi02e3rw+H1MyM0P9WAS9T5iHfT5A9S3duKw2ygtyMVuj/0nzLp6+2ju6KGyOD9MRDiAnj4vDW2dFOVmU5CTOSR08KduTz+tnT1UlOTjGL52uv9cSbhVY18vfjlAxTAxnMLg67hrr7oTRVFo9/VRmZWHQxo894ePbOPBfe+x6f130dLfi8fvpyIrJ/j7SyA87/D20er1UJqRQ7Yj2ttu4ZDCftD3aR8Y3erpoM/Xz/j8cWF9uihRQ+jze6nvaqLAnUNRlIZ/nKFxDYeay74OZF8jNlc5NkduNHONYaPvlfsbkf0d2LMmIdncEcd1qseAYQAAHGZJREFU9T4szUdSoiCtOUd9BWIizUciFLozo6q+o6HX76O5t5uHd23gtjmLY1IRxZnZFGcMVQkPnrlNkigaJkIryQxXFCeXPIJwOuxMKh18eyzekNysDHIzY79amZ3hYsr4kmF+Bn/KyXRHqNPFIHLWpRmRVUK0c8t3ZZDvin1OAMXuLHCHe4i3Tmp8DkCK+CF5DHVRlJkPkdrFuMEyHC4mF1bqn8iQGMMj2Zz52KIpvgU/JdvcpdgyomuddDfODcBY13xEMxiSQEaP5kMk7ljxKJtO1TCtoITb5p4ddkyJuSEICX1GGoifhkqPuqsPkQMTOFQMcC0gi6gfmdgyiYdLfaYqDJN8phWAdKKuzKv5iOopSGGlqnEePWOI/LBr/WOJ+1oaqO1q49zKKUOoqUTJQxdpp9JNku/Hac4HKgbolgSpu4CGbnZ4+zjh6WJWXknYa7xD0dLfS2NfL7PzSxiaPNTNSR0i84bABJLk46OY5BG9+kjWb1LJI8ZhUa/tmpG6gniXUqoa50kkkFi/q4QJxCjNhwEJRORf2hWVQJKnrpKoPoxIHgnMRCUPDbOJH0dw9RHe8hj55JHQQkNGGPHqI8phUckjOV8xIhil+dCRQFKaPOIY2Uaj5sNoiKw+EgdQZ5BW1JVwX+ZOHiIhsvoQBZHVh67IY5260jYD9VHjGMX/RkKDG+cjSV2pc5pwh7bhRkJ/PjAA2qmrpGMIPjGh9Idq5zqoK9UQS13pmEJKQumFpfmIf1jzV9qKpK5EwTDqygg/Y736MDCDpXvjXNTwEaeujBgxqqsP0QHUGYiYRuwEIuTTaFFXOmagPqoR1Yfu5CHSKsFoQ6sPwZ/2JN1Z1JU6n2ZsnIukrpKbkREXXRDRE4jB1JVIGEJdRUYRY23EVI1qnOtCKqgrY3yJbHmIbJzrRzpRV8avl6X5UOdHNYVlxreuRCJ+9SE6gDoDi7pS4VBw4xwwHXUlpvowJ3WlHelEXRnxlJLYQOQ6RSYQg2+eZmyci6SukptRkueRYupKpAPzU1eCYVFXyYxSDTNSV+FOE+7QNtxIqAwmMTyBCKOujK8xUkNdaYNI6mrENB+6Qqae+xwV1ceIUlcaI6XwTiWycS4K1vd8aIPmt7ASI52oK0vzodGD3jDqR1uaDxFeNGPkGucWdaVjBuqjaqg+YGgCsTQfiXZoG24kLM2HUAilP1Q7jx9V5Ps/6dE4Nx6W5kOrmRS/ArE0Hzr9jPXqY6xTVwIs9Q43Y+NcJHVlykQUc8OIAOoMxE8j6PH097GKcGhRVzpmoD6qpfkQCinOlmDnYoaNOeoqtk8zNs5FUlfJzciIiy62mc3SfEREEWNtaT7UWCUVytJ8JEI6UVfGr5el+dDqZ/CnqBSWpfkQGUCdgUVdqXOY7tSVmOrDnNSVdqQTdWXEU0piA6OoqwGIfwvL0nwYMsrSfOhyEgFDb0AWdZXMKNUwI3UV7jThDm3DjUSS1NUAIhKIpflQB0vzYWk+oo4cUepKY6QU3qlENs5FwdJ8aEWkR50VSDpRV5bmQ6MHvWHUj7Y0HyK8aMbINc4t6krHDNRH1Vl9wLAEYmk+khxuJCzNh1AIpT9UO48fVeT7P+nRODceluZDq1n0AaEEYmk+dPoZ69XHWKeuBFjqHW7GxrlI6sqUiSjmhhEB1BmkgroaQJIUlkVd6ZiB+qiW5kMopDhbgp2LGTbmqKvYPs3YOBdJXSU3IyMuOm1mNjDpTd/SfGg0szQf8SCy5WGuxnk6UVfGr5el+dDqJ/4Am6X5EBlAnYFFXalzOLqpK52+Rjl1pR3pRF0Z8ZSS2CCV1NUA9L2FZWk+DBllaT50OYmAoTcgIxrnaUBdGf5aazK+LM2HSDNAcwKxNB/qDiThS6NPS/OhEUZUHyNKXWmMlMI7lcjGuShYmg+tUOdRQwJJJ+rK0nxo9KA3jPrRluZDhBfNGLnGuUVd6ZiB+qgGVB9IAv6UiRmpq3CnCXdoG24kLM2HUBjarzCCulKNdGqcGw9L86HVTP0kVCYQS/OhLUCaVx9jnboSYKl3uBkb5yKpK1MmopgbRgRQZzBS1NWAmYoEYlFXOmagPqql+RAKKc6WYOdiho056iq2TzM2zkVSV8nNyIiLLknvQ4wN+E507bA0H1rNLM1HPIhseZircZ5O1JXx62VpPrT60T6JBAkknaoP0QHUGVjUlTqHo5u60ulrlFNX2pFO1JURTymJDUaauhqA+grE0nwYMsrSfOhyEgFDb0BGNM7TgLoSNTMzUlfhThPu0DbcSBhBXUVBnARiaT7UHUjCl0afluZDI4yoPkaUutIYKYV3KpGNc1GwNB9akXy2iZFA0om6sjQfGj3oDaN+tKX5EOFFM0aucW5RVzpmoD6qwY3zodDURDcjdRXuNOEObcONhKX5EApD+xVGUFeqkU6Nc+NhaT60mumbRJQEYmk+tAVI8+pjrFNXAiz1Djdj41wkdWXKRBRzw4gA6gzMRF0NYFgCsagrHTNQH9XSfAiFFGdLsHMxw8YcdRXbpxkb5yKpq+RmZMRFl6T3BMYp14FYmg+tZpbmIx5EtjzM1ThPJ+rK+PWyNB9a/ehfL4mwBJJO1YfoAOoMLOpKncPRTV3p9DXKqSvtSCfqyoinlMQGZqSuBg5Fr0AszYchoyzNhy4nETD0BmRE4zwNqCtRMzMjdRXuNOEObcONhBHUlUqcTiCW5kPdgSR8afRpaT40wojqY0SpK42RUninEtk4FwVL86EV4qoPAFt6UVeW5kOjB71h1I+2NB8ivGjGyDXOLepKxwzUR01x43z4oZhNdDNSV+FOE+7QNtxIWJoPoTC0X2EEdaUa6dQ4Nx6W5kOrmfhJhCcQS/OheWRaVR9jnboSYKl3uBkb5yKpK1MmopgbRgRQZ2B26moAgwlkrFNX2magPqql+RAKKc6WYOdiho056iq2TzM2zkVSV8nNyIiLLknvSUzFUB2IpfnQamZpPuJBZMvDXI3zdKKujF8vS/Oh1Y/+9YrlIZhARnX1ITqAOgOLulLnMN2pKzHVhzmpK+1IJ+rKiKeUxAajhboagM3SfBgzytJ86HISAUNvQBZ1lcwo1TAjdRXuNOEObcONhBHUlQ4YQmFZmg+tfizNhyoYUX2MKHWlMVIK71QiG+eiYGk+tMLY6gOGJBDz3fItzYdaM0vzkXqke/WhK/JYp660zUB91BQ3ztX4sYE5qatwpwl3aBtuJCzNh1AIpT9UO48fVeT7P+nRODceluZDq1lq1ksohWVpPrQinRrnBro2WeNc1HAzNs5FUlemTEQxN4wIoM5gNFJXA7CNSepK2wzUR7U0H0IhxdkS7FzMsDFHXcX2acbGuUjqKrkZGXHRJeld95IGHQirQCzNh1YzS/MRDyJbHuZqnKcTdWX8elmaD61+9K9XYg+DFin/QqlEsDQf6szMQ11Zmg+NgUxJXWlHOlFXRjylJDYYzdTVAIQkEEvzYYB3S/NhDCzqKplRqmFG6ircacId2oYbCSOoK90Ij6Y7gViaD61+LM2HKhhRfYwodaUxUgrvCiIb56JgaT60IvXVB5iIwrI0H+rMLM1H6pHu1YeuyGOdutI2A/VRU9w4V+cn0kpXArE0H0LNBMHSfET1leTjo8j3f9KjcW48LM2HVrORW6+kE4il+dCKdGqcG+jaZI1zUcPN2DgXSV2ZMhHF3DAigDqDdKGuBgaOOIVlaT7UGVuaD2HOxQwbc9RVbJ9mbJyLpK6Sm5ERF12S3nUvaWwHSSUQS/Oh1czSfMSDyJaHuRrn6URdGb9eluZDqx/965XYQ/wLaEQrEEvzoc7MPNSVpfnQGMiU1JV2pBN1ZcRTSmKDtKKuhkBzArE0HwZ4tzQfxsCirpIZpRpmpK7CnSbcoW24kTCCutKNxBeQpgRiaT60+rE0H6pgRPUxotSVxkgpvCuIbJyLgqX50IqRbZwPxYhQWJbmQ52ZpflIPdK9+tAVeaxTV9pmoD5qihvn6vyos1KdQCzNh1AzQbA0H1F9Jfn4KPL9n/RonBsPS/Oh1WwE1yvK84SqBGJpPrQinRrnBro2WeNc1HAzNs5FUlemTEQxN4wIoM4gnamrAaSUwrI0H+qMLc2HMOdiho056iq2TzM2zkVSV8nNyIiLLknvupdUG8GVMIFYmg+tZpbmIx5EtjzM1ThPJ+rK+PWyNB9a/ehfr8QetF9AKatALM2HOjPzUFeW5kNjIFNSV9qRTtSVEU8piQ3SirpK4CtuArE0HwZ4tzQfxsCirpIZpRpmpK7CnSbcoW24kTCCutIN9Y3zoYiZQCzNh1Y/luZDFYyoPkaUutIYKYV3BZGNc1GwNB9aYb7G+VAYTmFZmg91ZpbmI/VI9+pDV+SxTl1pm4H6qClunGtriWu3ippALM2HUDNBsDQfUX0l+fgo8v2f9GicGw9L86HVbATXS2UxGpFALM2HVqRT49xA1yZrnIsabsbGuUjqypSJKOaGEQHUGYw16moAhlFYluZDnbGl+RDmXMywMUddxfZpxsa5SOoquRkZcdEl6V33kuonuMISiKX50GpmaT7iQWTLw1yN83SiroxfL0vzodWP/vVK7EHMBWRIBWJpPtSZmYe6sjQfGgOZkrrSjnSirox4SklskFbUVRK+QgnE0nwY4N3SfBgDi7pKZpRqmJG6CneacIe24UbCCOpKN/Q1zofCBpbmw9J8GOTaiOpjRKkrjZFSeFcQ2TgXBUvzoRWjo3E+FEIpLEvzoc7M0nykHulefeiKPNapK20zUB81xY1z/S1xrVZgszQfQs0EwdJ8RPWV5OOjyPd/0qNxbjwszYdWsxFcLx3FqLAKxNJ8qDMzT+PcQNcma5yLGm7GxrlI6sqUiSjmhhEB1BlY1NUghCQQS/OhztjSfAhzLmbYmKOuYvs0Y+NcJHWV3IyMuOiS9K57ScVSVwMw+G9hWZoPbbA0H1FdjGjjPJ2oK+PXy9J8aPWjf70SezCO+9SdQCzNhzoz81BXluZDYyBTUlfakU7UlRFPKYkN0oq6EuRLVwKxNB/JGifvwPzUlWBY1FUyo1QjFdSVoigR/9Q7TbhD23AjMSxYrPPUO6dYaxg9nhRxTFEUXY3zoXAkOU4oLM2HpfmIOnJEqSuNkVJ4pxLZOBeFWMlDlmUCgUDYDUySJCRJwmazYbNFPsManhwFVB+KoiDLMoqiYLfbI85flmVkWQ6dZ+T6JFd9KIoSWk+bJIViD+wHIuYz8DsYWHcFBUmJNS9tSDqBWJoPdWaW5iP1SPfqQ1fkFFNXgUCAn//278iKHIrodjrIzMpk8cK5LD5jXlgSMZy6Sgh11JWiKKzftJ1Vazey/PyzOffsM8OOy7LMnx99ipa2Dr5y18fIzsqK6UvDVJBlmV17D/Lia6uQJIk7br6eyvGlKIrC3//1HPUNzVx92YUsWjAHCCaW/n4vD/75Ubw+P3fediPvrNvIgcPHuf6ay5g7c5quVdXfRLc0HzphaT6i+kry8VHk+z/p0Tg3HvGeYodWHjOmVDN9yiSKigpp7+jkjXfWc/DI8TDbgSf3gaf7gf2KEknDxNtmiK+w/VL8ONH2D59fIBAgEAggK0EbJdrDbGjOIMunq5WQTymsghl+DrGor4Ex2/ccCD4IKgpbd+4NnpYkMXvaFFBg74EjDLiQZZkjx2vp9/kYX1ZCcVE+8uk5K4qi+3pKqgKxNB/qzMzTODfQtcka56KGm7FxLpK6SnUikpC4+ooLcbtcBAIBXl+1lm2793HwyHFmTK0O3rQDAU7Un6KtrYu8/Bwqx5eS4XYjyzLHautwOV1MrCxHlmUam1vo6fVQXjqOrMwM+vr7qT/VRFZWBqUlxSiyTF1DE61t7RTk5lJZUYbT5USRFVrbOmjr6KBsXAl1pxqRFZnpk6uQJButre2cbGgkM8PNxIryYOUgSaHEcaKugY6uLspLi4lxnx8GBb/fz+GjNfR6+qiaUEF+Xi6BQIBjtXXYbBJTqiaGaKhTjU14+ryMLyshKysz3JMSnPuJk6coLMyjq7uHPQcOc9lF55DhdjN31jRWrd3AsdqT9PT2kp2VhaIo7D98FAmJubOnC35LTtKeQCzNhzpjS/MhzLmYYWOOuortMxWN8+FQUFBO34RlWcblcgJSaLunp5dnXnqd+obm4AQVyM7O5IZrLmd86ThWrdlIc2s7X/70bTgcdl55813qGpq48NzFLDtrIYeP1vDia29zzlnzKcrPZ8Vbq9lz4Mjp4Arjigu55UNXk5nhZsee/azbuJ2JE8Zzou4ULqeTz91eyY69B1i1ZgOyHPywZLrdfPi6K5lQUUYgEOClN95h975DIAWnOK64KMFiBvniZ19+k1MNTSiA0+Hkg1ctZ+rkSby5+j2aW1v55C03UF5agt/v56kXX6On18N/3XlbhDdZltm55wAKCmfMncWpxmb2HTzK7n2HOGvhXHJzsplYWcHxE3XsPXCERQvm4PP5OHS0FptNYu6MaeG/O1W/uVgIjhaoA7E0H9qQQs2HYF8iWx7mapynE3Vl/HppSh4KbNiyi9XrN/PyG++wadtuJEli8qQJKIrCyjXvUd/QzOwZU7j95g+y/IIl9Pb28Z/XVuHz+ZkxpSpEx3j6+jjV2Awo1NTWEQgEOHS0BoBpk6vYue8ge/YfZlr1RD778Q9zyQVLaWpp4521m8Iop8bmFq5cfh5XLD+Pjq6u/9/euXw3cZ5h/PfN6H6zDL7gu7As33G4FGgOJA2FkxCaNO1J0gWn3TSLbvrfdN1FN130nC56Tnt6oU1DCDUmIYZggyLbso3v2MZgS5YtaTRdyAgbS+jikSxgno2PRu/3fN98ozOv3uedx+K/1wZwOR38+vLP+cVH7xGLx/j759dQFIXg5BRD/lEq3S4+u/wxv/zkQ9bC4Ww7BELgdjr47WeXef/HZ4nGYvzzi/+RSCTo62oDFfyBIIlEgrmFRVZDYTzNjTgctp17qKrEFYUh/yhCCHo6vBzpSiaEwSF/Uo4Sgt5OHwD3A2Nb654mGo3haW7YxakF8koguucjt7Dyka6K0zgHyk660qb6KE/pKn+Uj3SVnFMgBPTfusPAt3fxj04gG2ROHT9Cb5ePhKLgH5lAlmXev/AWdbXVnDx6hMb6WlYerzG/uITP2wKqytj4FNOz8yRUFZfTwcz8AtFojMmpWVxOO3U1VUzPzANQV1PN8soTDlRWIBtkJmfmUutBQG+nj+N93fR0tDE9k+Ssq6lmLRQGVaXqYCVLyyuE1yNMzz4E4HhfN7XVB2moq6WrvTX7uQs4+8MTOB0O+ro7qD7gZjUUYnUtTE+nD0mSuDcaRFEU/KNJqamvp30XTyKRIDj+gLVwmKb6WmxWC00NddhsZuYXlpidT66v3duC0WDgwcw8T1bX8I+MA9DTuZNTi+oDkUcPRPd8FBpcOEH5S1caQ5euChmVM/ZDuto+++WPf4LJaMRiNmO3WzEZjQBEYzGUhILDbsNkNKYayS6nA1hgPRKhqf4QbreLiakZjEYZSQhOn+jjyhf93B66z3pkg5OdySe6QuF1AAYGv0OSk9+RjUZD6lHWp7BZralzCa1HABgdn2R8aia1VxaLmcjGBpHNDQCsFkuqirFad/Yo0kIFq8Wcemm1WRErT9jc3KTS7cLraSIQnGRm7iGB0QlMZhPtrZ6dFNub58Ds/CK/+/0fUYFoNIaKyuBdP/WHarFaLHg9zdwfCTLsH2VscgqjyUCnz5M6d62SB+yDD0T3fOiej7Qj91W6ynOmEn6N17JxrhUKacQK4FBNFWaTaddxq8WC1WxhfX2D5UePcVckm8xJmQqqKiuRJAnf4WZuDt5lOBCkvq6G9lYP/77az8DgEAhBR1srkiThdNoBuHT+LXzeFuJxhcXlFWoOVu6Y2WoxI4QEqDiddgRwtLeTc2dOoaoqcwtLVLpdOOw23E4nAEtLj5I+DFSWlh5lPW8VldmFRbwtFuJxhcePVwGoqHAiSRJHunwExib4auAWT0IhjvV2YTTuvC2rqkootM74xBRGo4Hm+roUdyKRYHJqjnuBMc6/nWym93Z6uT8S5Ma3d4nFY/R0tO3ady0gyDGB6J6P3MLKp1+hez6yv1lQ4B7YStE4Ly/pCraSTYaE8/SoLMscO9JJ/607/Pmv/6K3q52p2QWWV57Q3FhHbU0VqqrS7j3M14NDSU2/qQGH3UZN1UEeLi5jt9torKtFCEFfl4/h78e42v8N8YTC+OQ09wJButu9fPjeO1uGOpCElFpjd7uXq9e/4bt7I7hdLjaim1wfGMTtdvGbX31Kd2cbX90c5Os7wxhMMtFonEBwIsmVZne3z/GPz69z8mgvs/MPCYXXaW1pxGFPJrm21hbsdiuTM3PJHkZX2y4uVJUh/wgqgm6fl59ePJdK4oqi8Ic//YXZuUXuB8Y43teD19OMzWohEtlASDslMWnLTMjTv/ldzZ0Xjnyb6LrnY4/QPR9puQqsPrRZ06vUOC8+8r3pyHJSbpJecMMSQiSfpvrBG4TXN7h24xYPpufo6/bx6QfvpmIa62txOOxIkoSnuQFZlmn1NCFJEp3ew8hy0ll9uKWJC2+dJrKxyd+ufIl/ZAJfq4eL584k3e+yhBASQnq2HrvNxs8uncdqMfGfaze4PjBIddUBPvngXWRZ5oC7go8unsNoMnL95m1Gxid588TRLZ7dt1GDLCNJEmaTiRNvdHNt4BaB4CSN9bVcuvAjgJSbvLvdixCCygoXTQ11afdn+PsxJCmZYLbvoyzLHOvtRkiCO8MBhBAYjUZ6OrxIsoTDbqPV05zkgS33v4wkpEx5/cV4LoeIx6uhF95qtKo+Su75yCuBlKr6SBOV26E8UN7VR9qRuR/MPSKPjLDvjfM0b2spXe1v7yMDT4YXiqIQWt/AYbMiy3L+XNsOJhIJVkNhLCYTlm19iEyjBMmb+loojCxLKff4diRUlchGJO17u9mfzbEZjRGPxbDbn41TFIV4PM6VL/u5PeTn7OnjvHPmVPZzyzBbAYfywLPMsZ3nhRKW7vnILVj3fGhGrs2w1066ysz5MiUPAFk2UOF0FMb1HCRJwu1y5jVKCLHVvE8/TBIix+SxE2aTEbPJmHqtqiq3h/wEH0wzEpzAYDBs/fuRfFFwisl/jjQkBTbRdc9HftA9H2kp9rVx/ipJV8XfL/13PvLlySK/CkFciTM9O09NVRVvv3liV+IquAYv4qV6njqjhFX0x3Z16apArixz6NJVjihP6SrH6TJHv8TVxx7PPEeK9NJVYZNlCss72xQ4XW4foGJIV0+Rtomuez4KDS6coPylK42hS1eFjMoZ5Zg8dpJmPZDf8GJi7/mgCCht8siEov6kre750D0faUfuq3SV50wlvCto2TjXClomj6Inx2JVH3mhVNWHlgMLp96VQHTPR25h5dOvKG/pSku86tXHnmYuknSlFbSUrjRYQe6zFqP6KJZ0VVBUltFZSDJXILrnY4/QPR9puQr8+qilAv9qNM6Lj9I0zjWSrkp4rTKH7eN+FaMYzSGH7EggWt2HSu75yAv7WH287tKVBpF7Hb7vjfNijHipqw+tJ8gtQJeuciPMRp1KILrnI7dg3fOhGbk2w1476SozZzk2zrWUrgpbUTE+dAWy73lLy0e6eoocmui65yM/lNDzoXEO0bLlUV6N81dJuir+fumej3x59r5f2RlKr33mQv1/QdL2/NS3qCAAAAAASUVORK5CYII=</v>
+      </c>
+      <c r="E801" t="str">
+        <v>20-09-2026 06:56:35 pm</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="str">
+        <v>6aafdfea3dcec73fb026122a</v>
+      </c>
+      <c r="B802" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C802" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D802" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E802" t="str">
+        <v>20-09-2026 07:00:18 pm</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="str">
+        <v>6aafdfeb3dcec73fb0261231</v>
+      </c>
+      <c r="B803" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C803" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D803" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E803" t="str">
+        <v>20-09-2026 07:00:19 pm</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="str">
+        <v>6aafdff23dcec73fb0261345</v>
+      </c>
+      <c r="B804" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C804" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D804" t="str">
+        <v>Started Playing game and Debited "10" and Balance "120"</v>
+      </c>
+      <c r="E804" t="str">
+        <v>20-09-2026 07:00:26 pm</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="str">
+        <v>6aafe00f3dcec73fb0261375</v>
+      </c>
+      <c r="B805" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C805" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D805" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E805" t="str">
+        <v>20-09-2026 07:00:55 pm</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="str">
+        <v>6aafe0103dcec73fb026137c</v>
+      </c>
+      <c r="B806" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C806" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D806" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E806" t="str">
+        <v>20-09-2026 07:00:56 pm</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="str">
+        <v>6aafe1273c641e64d214e41c</v>
+      </c>
+      <c r="B807" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C807" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D807" t="str">
+        <v>Started Playing game and Debited "10" and Balance "110"</v>
+      </c>
+      <c r="E807" t="str">
+        <v>20-09-2026 07:05:35 pm</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="str">
+        <v>6aafe1443c641e64d214e449</v>
+      </c>
+      <c r="B808" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C808" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D808" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E808" t="str">
+        <v>20-09-2026 07:06:04 pm</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="str">
+        <v>6aafe1453c641e64d214e44f</v>
+      </c>
+      <c r="B809" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C809" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D809" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E809" t="str">
+        <v>20-09-2026 07:06:05 pm</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="str">
+        <v>6aafe1653c641e64d214e565</v>
+      </c>
+      <c r="B810" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C810" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D810" t="str">
+        <v>Started Playing game and Debited "10" and Balance "100"</v>
+      </c>
+      <c r="E810" t="str">
+        <v>20-09-2026 07:06:37 pm</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="str">
+        <v>6aafe1813c641e64d214e594</v>
+      </c>
+      <c r="B811" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C811" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D811" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E811" t="str">
+        <v>20-09-2026 07:07:05 pm</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="str">
+        <v>6aafe1823c641e64d214e59b</v>
+      </c>
+      <c r="B812" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C812" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D812" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E812" t="str">
+        <v>20-09-2026 07:07:06 pm</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="str">
+        <v>6aafe1e3379be29ae466726a</v>
+      </c>
+      <c r="B813" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C813" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D813" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E813" t="str">
+        <v>20-09-2026 07:08:43 pm</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="str">
+        <v>6aafe1e3379be29ae4667270</v>
+      </c>
+      <c r="B814" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C814" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D814" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E814" t="str">
+        <v>20-09-2026 07:08:43 pm</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="str">
+        <v>6aafe1eb379be29ae4667387</v>
+      </c>
+      <c r="B815" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C815" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D815" t="str">
+        <v>Started Playing game and Debited "10" and Balance "90"</v>
+      </c>
+      <c r="E815" t="str">
+        <v>20-09-2026 07:08:51 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E773"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E815"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E815"/>
+  <dimension ref="A1:E886"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14254,9 +14254,1216 @@
         <v>20-09-2026 07:08:51 pm</v>
       </c>
     </row>
+    <row r="816">
+      <c r="A816" t="str">
+        <v>6aafe209379be29ae46673b1</v>
+      </c>
+      <c r="B816" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C816" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D816" t="str">
+        <v>Answered incorrectly for Qst ID: 6aafe1ee379be29ae4667392, Qst: How many times do the letters Z, M appear in the paragraph?, Submitted Answer: 2, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nOydd3wc5bX+v7OrLeq9WrLcbVwwBowN2PSEDgkJCZDcFNJzSe7N/d2Um14gCcmFcBPSSAKE0EMgQAwGY4yNe8NVbrJlFVu9a1fa/vtjpZVWmtXO7L6zGq3m+XwMmtnznnN2djRnznPm0UoDLneAKAiE/hP2Q0wYszqiu/HjjPuq4hQDsZirfDmmRSqPciDiZnyf1ii3ATHeAhE3ZHco96XYzdgXFUVVmFpA5qdYfCoLp+wEEvJbG/6/uCGF/SBFNlTjK+KOqC9Ef1VxilIs5ipfjmlRDEdZGvdHU7TlQi9Aip3HUTwUQ2zxiCOFhISKF6KKR5QoYqwT+FlFNpvA4yW0eIQ70aZ4CPIV1aeAYFEhtnjEkYKAUNFXRC0ggJDuQ/nKOE9RFctFFo+Yug8tVmjUfYjC+N2H6ADKDMSnobraxOpB4MLoDoW7FlBFRF5/xXQfYotHTN2HEEgRN0e+Mm4BCYyzFTdidCeSuhIFkdSVqESmLHWlwSoB9SBO49gdiKSuREHTy58OqCtRmFjqSpmfiAVE0MhD3kVCuQf5GMlBXWl/vBJDXamDyNMnhoYliln8xyu6h8Rzn5Oi+5hQ6kplpMSlFD91NY6D8SmshFJXcfqa5NSVeiQTdaXFXUp0g6SiroT7Gu4+ROYUPi9P4FV0HCR79xFX5AjU1RBkC4imFyAtBudJQF2JykyP1FW406g71C3XElpQV3EjEYNz/VNXCXnqSjGSaXCuDpE7EC26jwmlrlRGSuBVQeTgXBREFg/Ni+NU7z6mOnUlwDLe5XocnIukriL5GlNAAqH/hP0woUj27iOuyFOdulKXgfKoCR6cixyJ67/7EHxfHKM7g7pS5nM892EFRFP+VQvqSjGSaXCuPQzNh1qzCTxeWjSjgmuIofkIM9ciBQGhYktuLIWV0MF5nKfoJB+ci6SudFmIIm5oEUCZgUFdKXOY7NSVofkYJ4bC7gNGFJDwE0bw6ROjO4O6UuZTj4NzkdRVbBlpcdLF6D3uQ5os1JVgGNRVLKsUQ4kfE4gdeehrcJ5M1JX2x8vQfKj1E//xiu4h8dznpOg+DM2HoFDKNR9yGKawEkpdxelrklNX6pFM1JUWdynRDZKKuhLua7j7EJmTofmIx5v+NB9yMGl6AdJicJ4E1JWozPRIXYU7jbpD3XItoQV1FTcSMTjXP3VlaD6U+ZyIEh3sQLToPiaUulIZKYFXBZGDc1EwNB9qkUyDcw1d62xwLmq5HgfnidB8yMEkdAAiAMnefcQVeapTV+oyUB41wYNzkSNx/XcfhuZDnTf9aj7koOzPuUeBqO5DzHmcTINz7WFoPtSaTeDx0qIZFVxDDM1HmLkWKQgIJS65wQKSiMF5nKfoJB+ci6SudFmIIm5oEUCZgUFdKXOY7NSVofkYJ0Yc3QeASfjpE6M7g7pS5lOPg3OR1FVsGWlx0sXoPe5DmizUlWAY1FUsqxQjVj9xUVj6GpwnE3Wl/fEyNB9q/cR/vKJ7SDz3OSm6D0PzIShUfJoPOcRcQERSV2K6D31SV+qRTNSVgIynOnUl3Ndw9yEyJ0PzEY+3yaH5kIOQITpgUFca3zzqkboKdxp1h7rlWkIL6ipuJGJwrn/qytB8KPOpjxIdYwHRF3WlMlICrwoiB+eiYGg+1CKZBucautbZ4FzUcj0OzidK8yEHcR1IDEj27iOuyFOdulKXgfKoCR6cixyJ67/7MDQf6rxNLs2HHFQXEFHdh8jnf5JjcK49DM2HWrMJPF5aNKOCa4ih+Qgz1yIFAaG0PV6qCojIwbmo5XocnIukrnRZiCJuaBFAmYFBXSlzmOzUlaH5GCeG4O4D4qWwjMG5eGhUPAzNhwbe4z6kyUJdCYZBXcWySjFEvkPFBURfg/Nkoq60P16G5kOtn/iPV3QPiec+J0X3YWg+BIUSr/kYE0GSlBUQkdSVmO5Dn9SVeiQTdSUg46lOXQn3Ndx9iMzJ0HzE423yaj7kEBuFZVBXsaxSDD1SV+FOo+5Qt1xLaEFdxY1EDM71T10Zmg9lPvVRosMhScGsohYQfVFXKiMl8KogcnAuCobmQy2SaXCuoWudDc5FLdfj4FxPmg85JEwHkuzdR1yRpzp1pS4D5VETPDgXORLXf/dhaD7UeZv8mo+QL2nY27gFRFT3IfL5n+QYnGsPQ/Oh1mwCj5cWzajgGmJoPsLMtUhBQCjtj9fI4gHjFBCRg3NRy/U4OBdJXemyEEXc0CKAMgODulLmMNmpK0PzMU4MjamrISinsIzBuXhoVDwMzYcG3uM+pMlCXQmGQV3FskoxtKKuhiBbQPQ1OE8m6kr742VoPtT6if94RfeQeO5zUnQfhuZDUKjEaD7kMKaAiKSuxHQf+qSu1COZqCsBGU916kq4r+HuQ2ROhuYjHm/JpfmQQ3QKy6CuYlmlGHqkrsKdRt2hbrmW0IK6ihuJGJzrn7oyNB/KfOqjRIcjUvcBowqIvqgrlZESeFUQOTgXBUPzoRbJNDjX0LXOBueilutxcK53zYccNNGBJHv3EVfkqU5dqctAedQED85FjsT1330Ymg913pJT8yGHUAER1X2IfP4nOQbn2sPQfKg1m8DjpUUzKriGGJqPMHMtUhAQKvGaDzmYQOzgXNRyPQ7ORVJXuixEETe0CKDMwKCulDlMdurK0HyME2MCqKshyFNYxuBcPDQqHobmQwPvcR/SZKGuBMOgrmJZpRiJpK6GYNLX4DyZqCvtj5eh+VDrJ/7jFd1D4rnPSdF9GJoPQaEmTvMhB4VD9Jh/bZQuV2+aQOpKPZKJuhKQ8VSnroT7Gu4+ROZkaD7i8Zb8mg85hBcQg7qKZZVi6JG6CncadYe65VpCC+oqbiRicK5/6srQfCjzqY8SHQ413QeMLCATSl2pjJTAq4LIwbkoGJoPtUimwbmGrnU2OBe1XI+D88mo+ZBD3DqQZO8+4oo81akrdRkoj5rgwbnIkbj+uw9D86HO29TRfMghWEBivH0U+fxPcgzOtYeh+VBrNoHHS8NmVJQvQ/MRZq5FCgJC6UPzIYdxOpA4T9FJPjgXSV3pshBF3NAigDIDg7pS4FDw4BzQHXVlaD7GiaET6moIJmNwLjSFMT71ODgXSV3FlpEWJ12M3uM+pMlCXQmGQV3FskoxJpq6GkKEDiRxbX9yUFfaHy9D86HWT/zHK7qHxHOfk6L7MDQfgkLpS/MhB5kCEvOvjdLl6k0TSF2pRzJRVwIynurUlXBf2lBXhuYjHm9TU/MhB9VPYSU7dSUqMz1SV+FOo+5Qt1xLaEFdxY1EDM71T10Zmg9lPvV00R9CvN0HjCkgifsVnFDqSlgoDR+zGXJpaD5UIpkG5xq61tngXNRyPQ7Ok0XzIQdVHUiydx9xRZ7q1JW6DJRHTfDgXORIXP/dh6H5UOdtams+5DCigIx/pop8/ic5Bufaw9B8qDWbwOOlYTMqypeh+Qgz1yIFAaH0q/mQw2ABifMUneSDc5HUlS4LUcQNLQIoMzCoKwUOBQ/OAd1RV4bmY5wYOqauIJiTIgrLoK6U+dTj4FwkdRVbRjG+jwRTVyId6J+6EgyDuopllWLokboagimRbX9yUFfaHy9D86HWT/zHK7qHxHOfk6L7MDQfgkLpX/MR5mvw/1E7EDHdhz6pK/VIJupKQMZTnboS7ksb6srQfMTjzdB8jMbInMYtIMlOXYnKTI/UVbjTqDvULdcSWlBXcSMRg3P9U1eG5kOZT11e9AVTV0OI+8+5K8GEUlfCQmn4mM2QS0PzoRLJNDjX0LXOBueilutxcJ7Mmg8YlZM0TgFJ9u4jrshTnbpSl4HyqAkenIscieu/+zA0H+q8GZqPMX5kNmQLiMjnf5JjcK49DM2HWrMJPF5aNKOCa4ih+Qgz1yIFAaEml+ZDDuoprEk+OBdJXemyEEXc0CKAMgODulLmMNmpK0PzMU6MSUZdDWFMATGoK2U+9Tg4F0ldxZZRjO8jwdSVSAf6p64Ew6CuYlmlGHqkrsKdhm9qMERPJupK+x7D0Hyo9RP/8YruIfHc56ToPgzNh6BQk1PzIYewAiKm+9AndaUeyURdCch4qlNXwn0Ndx8iczI0H/F4MzQfoxGJuhraESogyU5dicpMj9RVuNOoO9Qt1xJaUFdxIxGDc/1TV4bmQ5lPXV70NR6cD0YBNKCwJpS6EhZKi8dsRrk0NB8qkUyDcw1d62xwLmq5HgfnU03zIQcTJH/3EVfkqU5dqctAedQED85FjsT1330Ymg913gzNxxg/ETfCd5hEPv+THINz7WFoPtSaTeDx0qIZFVxDDM1HmLkWKQgINfk1H3IYn8Ka5INzkdSVLgtRxA0tAigzMKgrZQ4nN3UVp69JTl2pRzJRV+E7IheQKUddRfapx8G5SOoqtoxifB8Jpq5EOtA/dSUYWgzOk4C6mqqaD7mM4xyiJxN1pX2PYWg+1PqJ/3hF95B47nNSdB+G5kNQqOTRfMhBvoBMcupKPZKJuhKQ8VSnroT7Gu4+ROZkaD7i8WZoPkZDDXU1hLEFJAmoK1GZ6ZG6CncadYe65VpCC+oqbiRicK5/6srQfCjzqcuLfgI1H3KIi8KaUOpKWCgtHrMZ5dLQfKhEMg3ONXRtaD5iNDE0H6OhRPMhh/ACkgTdR1yRpzp1pS4D5VETPDgXORLXf/dhaD7UeTM0H2P8RNyQ3RGGGDqQZBqcaw9D86HWbAKPlxbNqOAaYmg+wsy1SEFAqOTUfMhhuIBM8sG5SOpKl4Uo4oYWAZQZGNSVMoeTm7qK09ckp67UI5moq+gZBwvIlKOuIvvU4+BcJHUVW0Yxvo8EU1ciHeifuhIMQ/MRyyrF0CN1Fe406g5ZqKCwkom60r7HMDQfav3Ef7yie0g89zkpug9D8yEoVHJrPuRgmuzUlXokE3UlIOOpTl0J9zXcfYjMydB8xOPN0HyMRrzU1RAUdiD6pa5EZaZH6ircadQd6pZrCS2oq7iRiMG5/qkrQ/OhzKcuL/oTrPmQg2IKa0KpK2GhtHjMZpRLQ/OhEsk0ONfQtaH5iNHE0HyMRqyaDzkoKCD67T7iijzVqSt1GSiPmuDBuciRuP67D0Pzoc6bofkY4yfihuyOqL6iFJBkGpxrD0PzodZsAo+XFs2o4BpiaD7CzLVIQUCoqaP5GImhjKJ2IHocnIukrnRZiCJuaBFAmYFBXSlzOLmpqzh9TXLqSj2SibqKLeNxCkiyUFeRfepxcC6SuootoxjfR4KpK5EO9E9dCYah+YhllWLokboKdxp1h+LlEQpIMlFX2vcYhuZDrZ/4j1d0D4nnPidF92FoPgSFmnqaDzk/ETsQPVJX6pFM1JWAjKc6dSXc13D3ITInQ/MRjzdD8zEaWlBXQ5ApIPqlrjR/rDUWX4bmQ6SZICRicK5/6srQfCjzqcuLvg41H3LWsh3IhFJXwkJp8ZjNKJeG5kMlkmlwrqFrQ/MRo4mh+RgNkZoPOYwqIPrtPuKKPNWpK3UZKI+a4MG5yJG4/rsPQ/Ohzpuh+RjjJ+KG7A7lvkZgRAFJpsG59jA0H2rNJvB4adGMCq4hhuYjzFyLFASEmtqaD7kXwjoQPQ7OY13hPf4m7h2PgtsZhy91eGr9LvYer1dkW322lT+v2YLL4x3eGSXB5+vf4WB3jbqkdEZd/bP6AN9+91V+uuNNfAG/4sBKc3L3e9n9jyN0N/apW6gYGpZEnVFXQxZuvye075mGDRzprRNOXdXvbqPxYEeMvgzNx2hoOTgf6WKwgCQLdTUIt5OB176He/Nv8FS9Jtx9pO7jkVfeZVvVKUU+jtY18+Df1+P2+gadjokyZs2jNWvZ3XlcPidFUcWsipW6evP0Ub656RXqervoc7swS2Ma4DgQdOB2etj61/10NHQryimWGHoenItyLgF93gG+uv9hDvfUhvb/6dQa9nWfFB68ZnMjDbtaY/BmaD7Gdxp1h7rlo5CSXNTVYPdxbB2SKYWUc27Au+9ZLEs/HE924RHGoa6e+f7dZNjtwmIphUjqKoaGJYrZ8E9H2psoTM3kbzd8HEnFiRw95LBFapaNOx58P9llmcbgPE7qqtPTw57OE3y68jpxOekAhuYjTj8jXkgBfVJX6jEcw3PwJcwzLiHlnBvo3/8CvsYDmErPHXe10+XmrT3HaO/u48L506koyuNoXRMrF84EYF91PTkZaVQW54XW1LV00tbVx/nzKgA429ZDcV6ArPThInKivoXtR0+TYjKxfEElc6YVRkz9YM1ZHAMuLpw3nRRz5D8ScNrRxJ7OE9hMVi4rXEKmJQ0AfyDAns7jLMiqYG9nNZ2uXq4qWkaWJQ1/IMDOjiOcdjaTZrazKn8hebYsAI721mOSJOZmlIdiHO4+jcWcwrxR+3IsGWRZ0jnaU8cFufPY03mc6r4zlKXmszxvAWlmm+xncqD1LCe720gxSWw7e5rKrDymZWQH33frWQ62NeL1+7i4bCZzc4LHaMDnZU9LPcVpmczOLgj5qmpvos/t4qLSSpmjE2DA4SHLG6THOs/0MNDnpnR+QSibgV43rac6KV1QQIrNTEdtN5ghLcvOye0NeAZ8VJ5fQm55Fs6uAU5uawBgxoWlZBakEQD6uwfoqOuhdEEBJ3c00NfeT8GMHMrPLWbktaC/x0XtnkacXf1kFWdQeUEZFps59Lqc5sPX14tj7048LU1YyqaRufwSJIsVAGfVAcwZmdimzwx71/3HDmFOTQ/t93Z10LdrK97eHmzTZ5BxwUokU/Cc8vc7cR47TNqCxfRs3QiSRPalVyBZbaEs+n3uEF16rLeOLEsas9PLQvFqnc3s6DiKWTJxSf4iSu15Yfl0uvvY0n6Ybk8fM9NLWZl3TnjHqQDdZx20nejB6/KRmm2ldHEe1vSU4GsNDlx9Xtl1+bOzaD/ZQ1qBnYzC8Bu61uPdpOfbSc+3ya4dC4O6Gg/m73znuz8U5UwkdRVryfF31uLe+CDWS79EysxVeA69TKC/i5S5V0VcU9vczkd/9Be2V9Xg8/l5ZM1mDp46w2//uZEv33o5AJ/5xd/ocQywasmc0LrH127n4Zfe4ZPXrgTgzp/8hRSzmYsWzADg50+/wbf/8go9jgGqz7bw0Atvk55q47w55RxvaGHd7iN87sZVWC0pPL9hN//58N9ZNqeCxTPLxuQI8GTtW3S7+3iybj0Obz/rWvbyXP0GVuafQ541C4/fy0e3/4RTjkYeq1nLlvZDXJg7D5vZwj3v/YZ/ntnCgM/Nu20Hebz2TWaklzAjvYSn697mzzWv89GKKwBw+zzcteNnbGs7zEcG9/X73Ny14z4WZVXi8nu5Z99vqHe28HTDBprdnfzjzLu80bSLm8suJsWUMib3/939NjuaaulyDXCss4XC1HRm5xTwjY2v8PNd6+h1D3CwrZFf792E2+/l4rKZpJhM/GznOn773iY+MOdc0ixWDrU1cseax5memcuFJdMZfaY4u1w88x9rKVtYSO60LHY+e5j9a46z5Pq5IZvG423883sbOOeqmdgzbbz76Hsc31TLruer6G7qo3bvWfa9cpy0HDtrf7GNnuY+Tm6t58CaE8xbXYktw0rde0289vPNnDnYQu2+JjxOL7v/XkXrqU5mX1KBJEk0V3fw/H+9SWdDLy6nh6p1pzi0tpo5l07HmmaRaTok+vbuoPbbX8F5cC8+p4Ou116ia/1aMpdfgjkjk5Yn/0THy8+Td9OHQu/H193FyXs+Qers+dhnzaVv91ZqvvFlBk5X4+/toePVv9O3fTNZq67EZLXhqj1Fzde/iOv0SdpeeJLe7e+Sc+0tmNMzQqk0D3Twq+oX6fL00TjQiT/g58Lc+fy19k16PA6eqF1Hr6efjW0HeK7+Hc7LnU3JYBHZ0X6ML733EMf7Gujz9vOPhk1sbDvAlYXnYTNbxp7YEtRub8FiMzPt/OCNwv5nT/LeU9V4+330d7mo2dTEqU2NTF9eiCU1hapX66jecJbGgx00Huyg/WQP1RsaqdvVwtyry3nvmRM0H+yk8uLiUJjeRidv/3wf5csKSNNRAdGs+4jjGV6lzWtKsmk+vAdfQrJlYZ51BUgmUhbdjHf3EwSu/DqSPVt29X1PriXdZuWZ73+GjFQbzR09fPiHj8SYfRCbDpzgiTd38LPPf4BbLwl2P395bSsPPP8WN6xcEmb7wsa93PfUG9z7mVu45ZIlcu5CqHE08+jy/6YyvRiHz8WX9/wfDx1/kYfP/0rIptbRzAsX/xBJgmJbLl8/8Ahd7j6eWvltim25+AI+7j3yJD88/AT/uPj7rC5cwjP1G6hztjA9rYj93cE5ztmBds4OtFNmz2dX51EALs5fxIm+MwD0+Jy8tPKHWM0Wqnpq+eyeB3indR/Xl6xg9Kf4y8tv5f6db/FOfTUv3vIZAP54YCuv11Tx+LUfC3UTzxzdww+3vc75RRVcXjGX+y69iZte+iM/3raW+y+7lf+36SWWF0/nc+deEuMnI48zh1q5+XuXMePCMjwuH3/93Ku884c9fOhnV1EyPx9H5wBPfOFfHNtUy4W3LwTA5/Fjz7Jx60+uxGSSaDzazovfXs/Rt2tYeM0s9r9yjJIFBdzyg+BNyECPi6e+spaT2xpYetNgQRtRPHx9vZy5/3ukLbmA8m/+GMliwdvZzulv3cOZB3/CjF/8npxrbqJ2/ev0Vx8jdc784OeweT2SOYWsVVfi6+2h/hc/JGv1lZR99X+QTCY8ba3U/PcXaH7s95Td843Qe/YPOFnw9Gv4HH1Yi0rCjkd5WiE/W3w3d+y4j2/O/yjLcuaEcm1xdfPUiu9QZMvG6XPx8Z0/4x8N77I0eza93n5+UPUYlxWey3cWfAyzZKLN3c0X9zzEb0++zP8suDP8wMtcqTpP93FyYyMrPr+AacsKgh1Rp4u1399D3a5W5r+/nPM/NjdsTf3uVnY9eozln56PJdVM5cUl7P3bCfo7XaTmBotF7Y4WMgrtFMzJUnhWJFP3ITpAEOp6ynGgC82H34f30KukLLwRKcVKALAs+SABrwvvoZdlV/c6B9h66BR3XbOcjNTgiVacl8UdVy2PK6vXd1QxqzQ/VDwA7rrmQv7wX3eRZreG9r20eR8/+usaRcUD4KaylVSmB++q0sw27pp+FXs6j9Pp7g3ZXF64lGmp+ZTZ83F4B9jRUcUd06+k2JYLBDBLJr4y+wO4/B7eaT3AkuxZZFvS2dkeLBI7O46yunAxudZM9naeAGBL62EuzJ0XRlHdPu0KrIN3lAuzKrGbrLS4uhQfo9dOHeKq6fPCqKg7FpzPzKx8Xj55CIBcexo/W30z62qP8em1T9LrdnH/5bdgkiREaj5Ss+3MuDDY+VlsZvIrsymem0fJ/HwA0nPsZBWm42h3hq1bedcSTKbgb1bpgnymLS6iekuQ8jKZTbSc7OTYxloG+tzYs2x85q+3svSmubKaj7492/E5HBR9+ktIluBxTcnNp+D2j+OsOoCnuZH0xUuxlk6j5503Qqu7336DrFVXYbKn0rvjXfxOB0X/9oUQZWUpKCT3fTfSu/3dsKg5V92AOTsHa1n5iCwiYMSLl+YvosgWvBlLM9tYmj2b5oHg576l7TC93n4+P/OmEGVVYM3m5rKVvNt2YLwIIWSVpXHVt8+j7Lz8YNgA+LwBLOkpuPs8YzJtq+5hzxPHOefG6VQsLwQJyi8oxGyVqN/VBgRnl3U7WqhcWRzbxdXQfMhiLNcgB10Pzofhq9mCv68F6ncx8PznQr4kswXvvr9jueDfYNQH1tjRg8/vp7wwN2z/7LJhzj0WzcfZ9i6mF+eH7Uu1Wrl40aywfQ88/xYpKWZqGtsU+Z0xWDyGMqpIC84LGvrbmD84ryhPHZ6zNLs68QcCzEwLv8PMs2WRbUmncaADs2Ti4oKF7Og8wocrLmNXxzE+WL6KQAD2dB7nxpIVbG2v4rMzw4ephbbwji4jJRWv34/ST/FMXzdXVITfSUpIzM4t4GzfcCG6rHwO189cyGs1h7lv1U0UpmZGjhGj5iO7KD1s25xiwmJPCXNitprD/JlMEtllGWHrcsoyaDjQAsCKOxfTeaaXdb/ajslsomxRIXMuqWDh1TMxW0xjflM9LY1IKSnYSsvD9tsqZgDgbmnCUlxK9jU30Pmvlyi6+x68jQ04jx2m+NNfBsDVGCxeJ7/88TAffo+bgMuFv3+4AFpL5anSaChLDZ932M0WvHgBiTP9wfP4k7vuD39vfi8Dfje9XieZKcGZXaQrldlqwpRi4sDfT9Fd76CrwUHAHyDgCzD6ye++5n62/eEw0y4o5Jwbpod8pthMlJ9fQN3OZua9fxptx7sZ6HIzfWXx2ICyMDQfSl6IXkAmgeZjCJ4DL2HKKiFl5moCjHjPqTn4jq7FV7cTc+WKsDW5GcGTud/tCdvv8486UwGfL3xfn3MgYmbpdhsej29MtoFAIHjiDKb+v1+8jZqmdh5+6R2uPn8+i2aURvQJjNFODPiCeWekpIZ8WszDH2tWSmrQLuAh/NmoAAM+D6nmYDe0On8J9x55kmZXJyf6znBh7nwgwJ9r1nKsp4FOTw+rC8I7JPmhqPLHtLKt9uHHmEe+J4+HVMswV97i7GVbYw3pFitPH93DLbOXYDEp/zNuAV/4C97+scNXs3Wsv5G/33KuA4HAmJsLT7+XFGtwSJ5ZlM7tv7gmOEPZfoaTW+vZ+MfdtJ7s5Kp7LhyKMpxDehYBn4+Az4tkGu5S/a7geWYafMIv56obaH3qLzj378F5eD/W0nLSFi0N+kjLQLJYqLz3VwwTDMMxhobxQGhoHm4hg1EvmiSzvB2QnmLHLJl4cOmXSJE5P+xD72ucgF11DjY+sJ+cigzKlxWw5LaZ5EzP4I3v7w77HAZ6PWx++BBZpWmcf9ecMT6nX1zC6W0H6DnjoG5HCwVzsxUOz5OJuhKn+ZBD3BTWhA8RfNEAACAASURBVGs+hlw6u/Cd2kjKuR/GcvnXsI74Z7/uR2BNw7Pv+THrCrLTyUq3s/dEuADw4KmzQb+DF4hUm5XeUQWjpqk9Yj4zSvI53tCMe1AoGIDgE1uf/xnbDg9rRVYunMWnr7uYOdOK+M6jr4TsI+FYb33Y4dvffRKr2cI0e76sfaEtl1Szlf2d1WH7j/bU4/K7mZURLFgr8s/BF/DzxOl1lKXmMS01nwtzF9Du6uap+vUsypxBnjUyd6zqIx00npVdwK7murCX+r0eDnc0MTe3aNA0wLc3v0qONZVnbvwUJztbeXjfJsVhLHYzrr7wm4POhh7lSY4nbgxAy4nO0LbfH6DpeAdFcweHyc8covrdOrKKM1h263w+fP81zLuskvoDTbL+rBWVEAjgrAqnepyH9iFZLFjLpgNgKSwifemF9GzZQPe768m55vpgtZPAVl5JwOMh4POROnd+6J+r9mRwVpIy9p4x0vXBNHh5UNOBV6YV4wv48QS8zM+sCP2rcTbzVsteUkyRi88Q6nY2YzKbuOxrS5hzdRl5MzPxuf0M9Hjwe4I3UD63j22/P4wkwcVfXCTb0RXOzSaj0M6Z99poPNDBjEuKFL8POeiRugp3GnWHuuUKMH4B0TV1Nequ8tDLBPxeLAtvHGtqScMy/zp81evx97aEvSRJEp+69mKee3s3b+6qwuXx8tbeozz3zp4wuwXTS3jnwAneq66nxzHAU+t3sft4+MVvJG5bfR5djn5++tQb9DgG6Orr5yd/e538zHSWzakIs00xm/jJ3TdRc7aN37/ybgSPQbzWuJM1jTtw+d1sb6/i6dr1fKDsUqwmmadbAJMkcdu01bx4ZgtvNu3B7fdy0nGWnx59hvK0Qi7ODw6E08w2zs+dy6uN27ggdx4A0+z5TEvN5+2W91hdGHk+E+tp8rFzLuRg21ke3PM2vW4Xbf19/M+7r+LwuPnIvGUAPFm1i61na/jp6puZl1vEf11wFX8+sI09zaMU/xGSKJiZg7Orn4Nrq3E5PdTva2L/v+TFmJEw3vvb+Mgeus72BgWMj++nr9XB0huDtFxvi4N3H3uP5uoOAoHgI8XNJzoomjNEAYX/yqYtWop95hwaf/cA/dXHCHg89G7bRPtLz5Jz9Q2Y04dpttz33UjXhrW4GxvIuer6kKuMCy7COq2Csw/9jP4Txwj4/PTt2U7jHx7E3+9Q9b5zrZkA7Og8Qq2zOaq9BFyUO5/KtGJ+fvQZjvbU4wv42dlxlAeOPU+ftz+o/4lypbKmpuBz++iuD+Y70O1m12PH8Hv9+NzBArLz0WN0n3Gw5EOzcLT301nXG/rndnpDCVVeXMzxt87g8/goP1/mEXrZdxF5UwQmq+ZDDpEprEmi+Rja9B5+BXPZMsgul11hPvc2PAdfxHfoJUwXfyHstS/cshqA//7Di3i8Popzs7hu+UL+te1gyOaLt6zmcG0jH7v3MQCWzi7nS7es5vkNe2XjzZlWyP/dczs/euI1nh8sRvOnF/Pb/7wDu3XkxT74XhZWlvKpa1fy6OtbufqC+SyeIc9Pf3DaKv506jXurXoSs2Tiw+WX8e+zb5U/TEO5z7oJX8DHfUef4gdVf0VC4sK8eXxrwZ3YRlAlqwqWsL39yCB9FcSFuQt4uX8LlxeMr6OJ5XO/omIu9666kQd3b+CPB7YCwa7kT++7kzk5hZzoauV/d2/gkwtXsKwo+Ll+fOGFrD19hG9sepmXP/A5MizylMRQNrNXVjB39Rk2/XEP7/x+N+l5di795FLe/NUORe8l2rsqX1LM019Zi9/nJyM/leu/eSn5M3IAWPWZZbz1q+288PV1BALBJqHivFKu+MIFyP1mSiYTFT98gLO/upea/7w7uM9qJffaWym++0thtlkXr6bxd1ZSF56LpXCY15csVmb8+EEafnUfp4Z8mM1kX30DJZ/7j7Exx3lvaSk2Lis4lydr17O3s5o/XfBfUY4GpJjMPLj0S9x75Cnu3vNLIEh1XleynK/N+VCU1UHMvXoabSd6ePv+fVhSzYDEwhunY8uw0FnbRyAQ4Oz+YPe/7Q9VY9av+NwCyi8IFovKlUVUvVpH5cpCWZoyHAZ1pTYDqc/ZL5CFSpTmQ35SGm/p6ut30dLVR0VhDs+9s4f7n36DA3/5bphNe4+DAbeHaQU5inz6AwHqWjpJs1oozMkc9aq6jIesfQE/Dc5Wcq2ZZFnSFMvHB/xumvo7yLFmkm1JV7JEcU4x/30TwOv3U9/Xic1soTR9vEcso59Ava1OHvvsK9zy/cupvGB4nuRx+ehrc5BdkoFpHJHm6JMp0rs6ua2B1+/fwmf+eismk4n+PhdZRemyvl1OD86OftKybNizhwre+L/gvu4uvD1dWItKkWzhRVLptcLX1YW3t1vWR/QMhg16PE7sJkvoiTs5Izlfne4+ur19lNjzFM0+Ruc10OvB5/aTnmcb8/CL7AKZ3f1dLl779i6u+H/nkj872uO7huZD2QvDBvIdyCTRfMToICIyUm1kpNrG5Xzzs6JceEdBkqRh9XocuY5capZMoUd51fztEbvJyoz0Eg0+3tiLB0CKycSMLPkZjlqfvS1B2mP4Qh2ExWYmd5rS5/9lXUeELdOKLdMa+fU0C/Y0S5jmIxrM2TmYs8fepCi/NEiYc3Ix5+RGN5VfHkLW4F86UGAahlxrBrnWjOiGEXzZMy0ye5XB7/YT8Ac4/Got2WXpuigeIjERmg85A2WP8Y6CLjQfozYTWPMUIxBxQ3aH1hkojxpfPVBtLErNseZnm6l7r5Hc8iwKZyrrEGVjCP5o5DQfGjkXs0yxT7HvRd5blBgRXq7d3szep6sxpZhYdc+imBPR4+B8ojQfcqvGUlhazD40pq5i8xUhwmD30d7joLmzh4WV4z9WO64vZRvq/KhyE0MBSSB1pdyDshOo4XArbqebskVF2NLkHyqIGkdhDXE5PHQ39VIwI2dcSmxs0xH7RUT5tSJ6jPgLSGTqKlafqgvIONSVq89D24kessrSyCxOVRd50lJXsjuU+VHlIlIB0WpwLvOyHosHqHtkcVw/ETdkdyj3pdhFIrqPRBSPCFZCzimZ1QGx55MU+k/YD7H5iX2ncgsVFWFCi8c4L8d1Dz7Vuw8VxQNU6kAmjrqK7HNKFg+NViWauhLpQFTxEAlNuXODuopllWLosXiEO426Q93yGDFcQDS+0CvYrd6RQCTmK2rVIXbqKoYlWlFXcYUUdgIphnDXOqOuRGGCao3gUJG7D1FIJs2HnMGg1DR60Ji6DyEwBufqXMRIXYlNIqqZ0M5RxGqdUlcikezdR1yRJ/VTV4nIeGwMCYUUlkjqStiwW5Af0Kj7mBDqKkZoQV3FDWUnULJTV6K6D5EM/IR2HxpTVyKRmD+WKIi6ijFVUyKvCiIH56IgsnhoXhynevcx1akrAZbxLp/wwbkWKyZ19yE6gDKDoT1RO5CJG5wb1FUcGSiPmuDBuciRuP67D8G/7cbgXDym+lNXca4S9oVSISR+7hkzEjM4F0RdJfAhh8hmE3i8tGhGBdcQkSMPfQ3Ok4m60v54JcP3fCj1NW4BETU4F0ld6bIQRdzQIoAyA4O6UuYw2akrMd2HPqkr9Ugm6kqLu5ToBqP3RCwgE0ddRfapx8G5SOoqtoxifB8Jpq5EOtA/dSUYBnUVyyrF0CN1Fe406g51ywVCHIUljLoS+5u9vvEUa+qPhUdIAHV1qq+RJ2rfwusf+417chiPuvIF/GO+iTAmX4oNRpvFd7y8fj/uwePQ7/Xwp4PbqO3uUJZUggfn7sDw51XV38kTrSq+O0SL7iMO7uFIx2meOv7GuDa7mo/w8qnI30Gzr+0Ef69+O2oshSnFjO7Nb9O9eTgPpaH8bpf8CkPzoXql3BLZAiKKulIP8dTVq/XHePb0oZgzGg/jdR9He2v5XfXL+FBWQCIFaOhv41O7fkG3uy9aBhH2xIv4WpWGvm5ue/XPtA9+F7fD4+KB3es50dWqZTbjr46g+VjX1cB/1WwLbe/ra+c3jYejepVC/wn7YUIhEbz4//7gS/IvDmJz436ePv5mRC+7mqt4tOpVYTkp3Tv65c51a+hct0ZVvNqffY/Ot9eOjTHVqSt1GYwbdcxf4zU0H7E4jbpD3fIRqHE0Ut13Rm1GsQVTbxYVp7paOdYx/C2QufY03vrwPeSnjvyz+PrQfGztbabH54lsIINk13zcMfd93DxzlVJzsRjhs/w/vq06VNfGdWScd4HYnCJgKmg+5BDTn3NXgonSfDT197Gh8RQev5/3T5sT7nLoL+26nGxrrafR2cfszFxWF8/AYgpvxk70tLO1tR6rZOL90+bQNuDELEnMGfzeCqXpeQN+drYepN7ZwvysitDXxQKcHWinqb+TZbnDefb73BzqrmFB5nS8fi8neoPF473uauZnTqc8tWDo3YTFOdnVxo6mWvq9HhbkFbGydCamESe1PxBgy5kaqjtbSbdYuHL6XApTh7/g6mDrWXLsaVhMJtbXHcOPxNXT51KankV9bxcb6o9jN1u4pnI+efbw74c42HqW3c31mCWJS8pmMicn+G1wHf0OqtqDX4W6t6WOxflllKRnUdfXSbrFSmqKhdruDvp9bioyc3mz9hhdLicrSipZmFdCj3uAN04fxeX3cmnZzDHfGdLQ28W7Z04y4POyKL+Ei0oqw17v87h4p/4EzY5eitIyubxiNlkWu+xnV93fQ6unnz6fhx29LSxOzwu95g34eae7kQZ3H5W2TFZnlZAijThfJNjT10aVswurSeLSzBLKbRkyUWDA5+ZgezVzsyvIsWUO5tnPkc4a5o3Y1+txcqTrNEvz52IzWwgQYFfLEU51ncWWYuXS0nMpSh3+ro+jnbVkWtLo8zjZ33aCi0rk/4R5l7uPd87spd/rYnXZUlmbEW+LXreD5v4OStOGzvsAe1qOcqKrgRSTiQuKFjAre9q4fgJ+P307t+BqqMNeOZOM85bjOPQeaQuWYEpNY6D2JH63m7S55wwf865OBk6fIH3xMiSLBU9X8BsILXnD54CnrYWenVvwOZ2kzppL5rLlIEng99O7fzcArrrTOI4eIn3B4uE3xZgfdQM9az7kYP72d777w6GNya752NBUw50b/87Jng4a+/v447Gd9Pu8pKZYuK0y+N3fa89Uc/fml9jX0USXZ4C/ndzH62dOcE3ZbNJTgl8K9Idju/jqjjV0ugY40t3G747uZEtrPQ3OHq4pm61ocH6i7wwbWw9woOsUG1sP0Obq4fHTb3Da0cxVRecB8Hz9Rn5b/TIfq7w6tLre2cLndj/ApQWLaXV18dfaN+jxOqlztpJtSeOcrOljgj5zdA9fXPc8vR43TY4efr9/C7sa67hlzhIkSaLV2csnXv8bzxzdTb/Pw4b64/xu3xZmZeczJzd4sf+PDS+wvfE0D+19hxZHH+tqj/L00d3k2FL52oYXae7v45/VB3jxxAFun7cMmzmFAAG+v/k1frz9Dfp9Xo51NPN/ezciSRLLS6azv62R3+7fRLdrgJruDjKtdioyc7j1n39iWVE5s3IKeOTgFp44sou/Vu3kSEczu5vrePTQDnLsqXxz08uc7G5nQ/0JnqjayappsyhOC15gnzu2ly++9RxnHd20OHt55OBWDrc38r7KBZglE/U9nXzglT9zqK0Rp9fNmprDPHZoB1eUzx1TAAGebqtmY08T3V4Xx/u7WZFZRIPbwfbeFjb3NLOpu5FGj5OnWqvZ72jnhtzpmCQJb8DP10/v4LdNh3EH/Bzoa+d3TVXkpdhYmCb/ZU6fefs+LGYL5xUEbyZeq9vGd7b/gSxrBucVBL9P/dXazfzyvaf5xPzr6HE7+MqmX/Hc8XX0+1xsaz7EX478i9K0fObmVADwvZ2PsL3pML8//CJbGg9gMZnJsKSxq+UIdy+8CYD97Se4e/19HOmsocPVy2NH1uDwDuD1+7h9zlUjMhx+bPfZE2/x8IEX+Pj86wgQ4Jtbf8fjR9bgD/g51HGK3x18EVuKlaWDeY+Gv99Jzbf+nY7XX0YymelY9yqOA3tpeuIRsi+7GktuPo1/+jXdG98i7/03h9b17tnB6R/8Pwpu/QgmeypnHvopjv17yL3yWgC6NrzBqW99hYGz9fi6Omn9x5M4DrxHzurg+6j7+ffxdLTh7WjH095KzqqrDM1HVDfqScb4OhAdaT4GvB6+tftNrimbzQPLr8MsSWxpruPTm19kRVEFgUCA5v4+vr77DW6YNpefXvA+zJLEWWcPH934d7733tv88eKbOdbdxkNV2/jGklV8Zm6w/X3q1AF+tG8Di3OKomQx9p0X2XP57flfxSyZ2Nx2iP/e/0euLbmQVQWLox6n5XkL+Orc2/jGgUf4v6VfJs8m/61qD7/3Ll89/3K+sPRSAHY0nubzbz5LVXsTiwtK+e6WNbQ6Hay57UuUpWfhC/j5zuZ/8fVNL7OseBrFaUG/2xpreP6mT3NOfinNzm6ufv63/HznW/zz1s9SkZXLkY4WPvDPR3in/gQ3z17MP47v54UT+/jT++9kVdksAF49eYivb3qZFaWVrCit5LsrruXz657lkffdSUl6Jm39I2c5wSNwuK2Rn1x6A7fPW4bH7+MD//wzP9n+Br+7+iNcVTGXXo+LG178Iy9VH2BJQRknOlv5yfY3+NJ5q/j3pcHvsz/e2cqdax7jb1W7uHvxSp45vpfCtHRevPmzmCRweb3c+sqfefXUQf7z/CvHHMN7ShfR7h3g5EAPT8wNvr6ttxlvwM9FGYV8pWwxEvBC+ynuq3+PEwPdLEjN4YmWE7zb3chj865gcVqwa3my5QQ/b9jH+RkFzLKHf2YpJjMXlyxhZ/NhPrXgRgB2NVdhM1vY03qETy64HiTYfPYAq0rPxWwy88u9T1Pf18xT7/8x0zIK8QcC/PK9J7lv9+MszZ9DWUbwJmBXSxUPrvoPFuXNwh/w83rt8DzHHwjw412PsTBvJr9a9VUsZgtHO2v5zPqfUp4x8ryOrPmo7m5gQ8MennzfD5ifG+z2fnPg77xYvYGPz78urOMdQuvfn2Sgppq5v3sSW+k0Ai4XJ//nHhnvY1KICHdzI/UP3kf+LR+m7LNfAUnCdaae6q99lqZnH6P0k19k7m8eZ/91Kym685PkX//B8R3Ggamk+ZBDqA+f7JqPbW0NdLj6+dL85ZgHP9RLi6ezvLA8ZLPu7CncPi/fXLI6ZFOWlsWn5yxjY1MNPR4XaxqOk22x88k5y0Lr7pp1LtMGL7JqNR//PvtmzIN0x6qCxSzInM6bzXtUvLPRGBs0RZJ4vaaKrWdP4fb5WFE6g/2f/BaLC0rpdbvYVH+STy26iLLB7xs3Sya+sfwa3D4vb5w+GvKzIK+Yc/JLgQDFaVmUZGRxecUcKrKCd9Ln5BVhN6fQ7OgB4OWTB7motDJUPABunr2Y8qwc1tcqf3rJJEncOvtcACySmUUFpUzLyOaqiuBdbYbFxuycfJodvQCsqTmMzWzmC0suDfmYl1vI1ZULWF8XjJtiMlHX08nfj++lY8CBzZzC6x/8omzxiIbbC2aFfpFWZQa/YKzJ7QQJ1nTWclXOtFDxALircA52k5nNPU2y/laXnsfB9lM4vQP4A352txzh1pmXs7+tGo/PQ7/PzZ6Wo1xetgyXz8PGxn18ZM7VTBssFCZJ4p4ltxMgwLqG3SG/s7LKuLhkMVnWNHJGUWjHu+uo723m3+Zfj2Xwu80X5FZyxbTzx+QXcWAqmQF45sRbHO+qAwm+svR2/nnTL2SLB0D3u+vJWX0NttIgzSXZbBR99NMRIihD16a3Cfh9lPzb5xn6rnTbtApyrng/PduGnigzBufqXKijroaQAsmh+WhwdANQmRH+VaazM/Oo6esE4IyzmxxrKnm28G8om52Vhz8QoNHZS72zm/L0rDCOWwJmjPKrZHBuM1kptueF7atIK+Sss1Wo5uO+1bfw7Xdf5VOvP0WGxcblFXO4dfYSrpg+lyZnD76An9k5BWFr8uxp5KWmcaavK7SvPCOccrFIZgpSw78D3p5iwT+YSn1PJ+0DDi56+n/DbBweN3W9nYrfVVFaBlazeTiuyUSePT3sHdtTLKGt+t5OXD4fq577VZiffq+XTEvwu9DvXrSSQ62N/GjbG/x4+xucVziNa6bP56Pzzyc1Rfm3FaZIJootw+eLfXBW5h18rLrO7aTe5eSyA6+E5+L3UueSe3IOLi5ZAsDu1mMU2LIY8Ln5xILreeHkeg521tDn6cckSawoWUT7QDcen4cZWeHfjJlusVOUmkuTsy20rywjQocswZm+oF1FZnHYSzOySqnubhg2HAczs8r40pLbeLzqX6w5vYWStDwuK1/Gh2ddyczsMrmwuFuayb1qWthee+XMyEEUXLXcjQ0EAgGqPn5z2H6/xx08RQKBUGGJwb1iTDXNh1yw2CgsHWo+bKbgW3H5fdjNw29rpH4i22rH5fOOWdvvDe5LS7GQbbHh8LrH2Di86p7OAfAzVrvh8rvJsAQvjhIS3hG6AwLg9A6oihEALp02k3fu+AoHWxt58/QR1p4+wppTh3ngig+yYnCwPOCVed8eN2kpttB28CIe/pmM971zmVY7C/NL+fel4U/pBAh2DUphHfq8RoQe7xch3WKjNCOLh664bcxrpsGVObZUHr32TpqdvayvPc4btUd5YM8GdjTV8vurP6I4NyTk764Hd2WaLKzKKuaOojljTLJN1gj521lWOI9dTYfJT81maf5cCu3ZzM+tZHfLEdoHullRsgi72UqmNTivccmck/0+N6nmEZ+fKfKv81CBdvnD/fhH6YuiXYDuPucmPj7vWra3HGZD/R7Wnt7Gq6c28/z191GSljfG3pyRhd8dfk4HfGMfbR+9z9/viJiTOT2NlMwsZt77UIQsDc2HugCxdR8ApmTRfCwanE/sbT8btv9QR3Po51kZeTh9HqpGaRD2tJ0h02KlJDWDpXml1PV10+DsDr3e7nJyrHv4Tk/pY7sev5dTfY2hbbffS1VPHTPSg3eBqSYLDu8A/sCwMKG2vyXMhyn0lS1ji1EA6Bhw8oMtr3G8s5VzC8v47+VXs/ZDX6Y8I5utZ05RmJZBptXG7ua6sLVV7Y04vR7mjOpMFGEw11nZedR0t7Mgv5hFBaUsKihlQX4JL1bvD+k8TNJQ/uJuL2ZlF9Ds6KUwNZNF+aWhfzsba9neVAvA44d38NyxvRSnZnLnggt4/NqP8alFK9h69nTEeBIS/ihpSqO2ZtozqHM5WJiaG/o3257NC62nOON2RPACl5Wdx/bmw+xpOcqFRcGnj5YXncOulqNsaTzA5WVBCjXTkka+PZv9bSfC1p/ubaRroJdZWWWKftnn51YiIbG/NdxPVUeN7DuTw4H2au7b/Thmk5nLys7jBys+wyNXfYt+r4uDbdVhtkPe7DNm4Dh0IGxv/7FwbY1kT8Xn6A1LwdUQfr6OhK1iJt7uLsypaaTNXRD613/0EL27tg53HyZTsBtR/A4Tj8mk+ZAzkhESTk7Nx6LcIlYUlnPfvo0c6Wql3+fhN1XbqeoeLhaXl1RSkZ7N/+xdx4medtw+H6/UH+XZ04e4a9a5WExmbiqfT3l6Fv++fQ2bmmvZ2lLHl7f9i4EhfcBggg8c3sITJ/dFzfjHVU/S0N9Gr7ef/z32PD1eJx+cFrxjn5tVgS/g54naN+n19nOwu4a/ng4XdeVZg1z2praDNA6MVm8H77Tfbajmvu1v0ujoxhfws73xNC39DhYXliEhcdeCC3n22F5ePnkQt9fLia5W/ufdfzE9K5erps+L+ZjftWA5p3va+dG2tXQMOHF43Ny/6y2ePbqXvNTgnXP+4BNPb9cdp6G3K/LxUpHEzbMXkW6x8v82vURtTwcev4+Xqg/w4N4NIWcdLkeo4/AF/DQ6etjVXMeSgpKIfvNSrJx1O9jd10afjB5E7hfrjsI57HO08evGQ/T5PPT43Nxbt4dXO+vIt9gjxlpdeh4NfS2813ac5cULQILlxedwsK2aDlcvq0rPDUW9ffZV/Kt2C6+efheXz01tbxM/3vkXitJyuLJcmc6hKDWXayqW88ihl9nfdgKXz80LJzewvWn4Yh7twpGeYufVms384dCL9PvcuHxu1jfswSyZQkP10Sj8wJ04Du+j5fknCLgGcJ44QtNf/xhmkzprHq6GOro2vIHP4aBn+2Y63nglYk7Zl15JSn4hdff/gIHaUwR8PrreXc/ZR35NwDvcyaTk5NF3cB/9J4Nzsb4D71H/fz/H09Is41U5pqrmQ86nEB3IRGk+RuM3K2/kv3et5Zb1TwGwMLuQG8rn0eHuB8BmTuHRVR/kW7vf4Ma3ngQgzWzh03OW8dWFK4Eg//6XSz/Avfs3cs/2NRTa0/jY7HPp9rjCqLFX648xJyuPT8yO/Cx9ZkoqF+XN46PbfoIv4KfYlstDS7/M9LRgt3RB7lw+MO1S/lLzOn88+S+yLel8ff5H+O6hx0I+ZmaUsiCzgl8ce54bSi7iews/HnbITJLEw9d8hG9ufJnLn/01ANaUFO5YcD53zA8OSP/j/Cvw+H3BJ682/hMJiRVlM3j40ttJTbHEfPhXlFbyv5d9gJ/uXMdzx/YCUJiayS8uu5Xzi4KPl87KyefcgjJ+sn0t781azLcuunqsI5UJ5NvTeeR9d/DdLf/iuhd/D4DdnMJnF1/CpxZdBMA9S1fT2NvD3W8+HezwgPOLyvn5qlsi+r0yu4zn2k7yueqNPDDzYnkjKfyH9+WU853yZTzcdJhHm4IPJJRZ03hwxkpm2+WfmpOAkrQ85uZW0ORoY35O8OK7NH8uFlMKiwtmkW3LCMX4xDk3MOB388u9T3PvrscBOK9gHg9f/nUyLKmyMcJzDeK7yz/Fvbse4/Nv30+AANMzi7ll1ioOtJ1UdJ2ZnV3Od5Z/j2LV0QAAHqNJREFUil/vf57Hj7wGQK49ix+u+BzTR8xWRvrKXH4xld/6MQ2/vp+mx36PyW4n79pbaXv5uZBN3jXX07trM3W//BH4/ViLSin91Jepf+g+2TzM6enMvu8h6h+4l2NfuAsAk8VK/s0fovjjnx32e/V1tLzwFL07t7DkxfUM1J6i/bWXKLjpNixFxbK+E4nJpvmQ9dDr6FdOHgnpPsT/uZLRaBtw0ud1U5meHdGmdcBJj2eA8rQsbCMKQ3N/H93uAeZlF4TldOlrf+KOGefylXNWAFDV3cqfju3iVxddHzWfbo+DLncf09IKQ09kjYTb66HJ1UmJPU+Gxw4QIEC3x0mG2U6KyRzxOLX3O+hy9VOWkU2qeeyguN/r4ayjm1xbWkgLMexLwdGPYOIPBKjv7cJsMlGSnjnmPQYI0DXQT4bVisVkHusgjvuJZmcvDo+LiowcLOaU4dWD/3N6PTQ6esi22cm3p0f0MwSv30+f30NOSvgMJ7xujP018wb8NLgd2KUUiiz2iE8lya5WePvo8rk562wnx5JOrj0rlkf6Aehy9dHjdlCeURSiGBVfOCTw+X20DHTh9Xkpywg/pyONrgNuF+7mJiyFRQycPkn11z7L3N8+QeqseaFF/n4n3vY2LGXlSCaTopy8HW34+vqwlJRiso7o+AYX+xwOTGYTJvs4hVYFprLmQ85AeQeiI81HNOTbUsm3jX/CFNrTKJQRlNX0dvKJzS/y5OoPcdHgI8AvnD5M24CTS4umh+x+e3Q7H54ur/YdjWxLOlmWCBevAFjNllBXIgcJiZxI60cgPzU9+CdCInwoqSkWZmcPzzxUFY9xYJIkpmfJi+YgmH9upF/gOJvRoLAwU/a1AMH3PCs7X/Z1OaSYTOSYxiseEdZJJmbY5POQ9RXV59gXbGYrMzNLZWzVIceWMfiYb2TNx3gpmU3mkDJd8VKrDVuFDM01IrgpNQ1r+XRVOaXkFZCSVxBxhTk9XdyQeoprPuQMRhSQyaP50BIriiq4rXIhn9j8IjMycuj3emkdcPC1hRdzfv7wL++9y64m1xrnXU3UNz3WQPxxUuhxHLOYcxL+Zoa7D+GulVQRpS4EWMbafcRsqsBQ+wdnFUY2NB+qDWKNOkhhJWpwLl8xRP6yi/pjiTV9XZzsbceExJKcEgrCupW4SDuFbmJ8Pk51PYidulLuQdkJFN8nF5D7X9wYWzcEFpAYbx/FFI/Yug91L8vv9Q8MMFB/mtTKGUi2sQ8aqD/C8gVEZPHQ5LHdCaGu5A1i6T5ASQHRSvOhQQER+Zd2AxE3ZHco86PKRQzdhxbFI4qZqOKhIpvx4wjuPsJHHhNfPKJaqKgIE959yLwsqnjE5itCBK00H3EUkIQWj3GMTJNR86E1RBUPZQGUGSQVdSXcl76Lh0iI7D5EQVTxiDvyVKeu1GWgPOo4RuN/I6FONR+yvibZ93wIR/z1QAMknroSBaH0h2LncVBXiiGWuoojhYSEiheG5mP8l1V/pa1I6koUNKOutPAz1bsPDStYsg/ORS2fcOpKixWTuvsQHUCZgYg0IhcQIb+NBnUVRwbKo2rRfcRdPERaRVmtafch+Lc9RncGdaXMpx4H5yKpq9gy0uKkC0K+gGhMXYmEJtTV2ChirLVIVavBeVxIBHWljS+RIw+Rg/P4kUzUlfbHy9B8KPOjmMLS41NXIjF+9yE6gDIDg7pS4FDw4BzQHXUlpvvQJ3WlHslEXWlxlxLdQORxGltANL546nFwLpK6ii2jGN9HgqkrkQ70T10JhkFdxbJKMfRIXYU7jbpD3XItoTCYxOgCIoy60r7HSAx1pQ4iqasJ03zEFTLx3Oek6D4mlLpSGSmBVyqRg3NRML7nQx1UP4UVHclEXRmaD5Ue4g2jfLWh+RDhRTUmbnBuUFdxZKA8qoruA0YWEEPzEW2HuuVawtB8CIVQ+kOx8/Gjinz+JzkG59rD0HyoNZPG70AMzUecfqZ69zHVqSsBlvEu1+PgXCR1pctCFHFDiwDKDMSnEfQ49H2jAmBQV3FkoDyqofkQCmmcLcHOxSybctRVZJ96HJyLpK5iy0iLky6ymcnQfIyJIsba0HwosYoplKH5iIZkoq60P16G5kOtn+GfZCksQ/MhMoAyA4O6UuYw2akrMd2HPqkr9Ugm6kqLu5ToBlpRV0MQ/xSWofnQZJWh+YjLyRhoegEyqKtYVimGHqmrcKdRd6hbriVipK6GMKaAGJoPZTA0H4bmQ3blhFJXKiMl8EolcnAuCobmQy3GeoyzA0km6srQfKj0EG8Y5asNzYcIL6oxcYNzg7qKIwPlUePsPmBUATE0HzEu1xKG5kMohNIfip2PH1Xk8z/JMTjXHobmQ62Z/IJQATE0H3H6merdx1SnrgRYxrtcj4NzkdSVLgtRxA0tAigzSAR1NYQYKSyDuoojA+VRDc2HUEjjbAl2LmbZlKOuIvvU4+BcJHUVW0ZanHTqzEyg04u+oflQaWZoPsaDyJGHvgbnyURdaX+8DM2HWj/jLzAZmg+RAZQZGNSVMoeTm7qK09ckp67UI5moKy3uUqIbJJK6GkJ8T2EZmg9NVhmaj7icjIGmFyAtBudJQF1p/lhrLL4MzYdIM0B1ATE0H8peiMGXSp+G5kMltOg+JpS6UhkpgVcqkYNzUTA0H2qhzKOKApJM1JWh+VDpId4wylcbmg8RXlRj4gbnBnUVRwbKo2rQfSAJ+FMmeqSuwp1G3aFuuZYwNB9Coem8QgvqSjGSaXCuPQzNh1oz5UkoLCCG5kNdgCTvPqY6dSXAMt7lehyci6SudFmIIm5oEUCZwURRV0NmCgqIQV3FkYHyqIbmQyikcbYEOxezbMpRV5F96nFwLpK6ii0jLU66GL2PMNbgO9HVw9B8qDUzNB/jQeTIQ1+D82SirrQ/XobmQ60f9UlEKSDJ1H2IDqDMwKCulDmc3NRVnL4mOXWlHslEXWlxlxLdYKKpqyEo70AMzYcmqwzNR1xOxkDTC5AWg/MkoK5EZaZH6ircadQd6pZrCS2oKxmMU0AMzYeyF2LwpdKnoflQCS26jwmlrlRGSuCVSuTgXBQMzYdaxF5tIhSQZKKuDM2HSg/xhlG+2tB8iPCiGhM3ODeoqzgyUB5V48H5SKgaouuRugp3GnWHuuVawtB8CIWm8wotqCvFSKbBufYwNB9qzeJLQqaAGJoPdQGSvPuY6tSVAMt4l+txcC6SutJlIYq4oUUAZQZ6oq6GMKqAGNRVHBkoj2poPoRCGmdLsHMxy6YcdRXZpx4H5yKpq9gy0uKki9F7FOOE60AMzYdaM0PzMR5Ejjz0NThPJupK++NlaD7U+on/eEmEFZBk6j5EB1BmYFBXyhxObuoqTl+TnLpSj2SirrS4S4luoEfqaugl+Q7E0HxossrQfMTlZAw0vQBpMThPAupKVGZ6pK7CnUbdoW65ltCCulKIwQJiaD6UvRCDL5U+Dc2HSmjRfUwodaUyUgKvVCIH56JgaD7UQlz3AWBKLurK0Hyo9BBvGOWrDc2HCC+qMXGDc4O6iiMD5VETPDgf/VLEIboeqatwp1F3qFuuJQzNh1BoOq/QgrpSjGQanGsPQ/Oh1kx8EuEFxNB8qF6ZVN3HVKeuBFjGu1yPg3OR1JUuC1HEDS0CKDPQO3U1hOECMtWpK3UZKI9qaD6EQhpnS7BzMcumHHUV2aceB+ciqavYMtLipIvRewypaKoDMTQfas0Mzcd4EDny0NfgPJmoK+2Pl6H5UOsn/uMVyUOwgEzq7kN0AGUGBnWlzGGyU1diug99UlfqkUzUlRZ3KdENJgt1NQSTofnQZpWh+YjLyRhoegEyqKtYVimGHqmrcKdRd6hbriW0oK7igCYUlqH5UOvH0Hwoghbdx4RSVyojJfBKJXJwLgqG5kMttO0+YEQB0d8l39B8KDUzNB+JR7J3H3FFnurUlboMlEdN8OBciR8T6JO6CncadYe65VrC0HwIhVD6Q7Hz8aOKfP4nOQbn2sPQfKg1S8zxEkphGZoPtUimwbmGrnU2OBe1XI+Dc5HUlS4LUcQNLQIoM5iM1NUQTFOSulKXgfKohuZDKKRxtgQ7F7NsylFXkX3qcXAukrqKLSMtTroYvcd9SIMOhHUghuZDrZmh+RgPIkce+hqcJxN1pf3xMjQfav3Ef7yiexi2SPgXSkWDoflQZqYf6srQfKgMpEvqSj2SibrS4i4lusFkpq6GIKSAGJoPDbwbmg9tYFBXsaxSDD1SV+FOo+5Qt1xLaEFdxY3waHEXEEPzodaPoflQBC26jwmlrlRGSuBVQeTgXBQMzYdaJL77AB1RWIbmQ5mZoflIPJK9+4gr8lSnrtRloDxqggfnyvyMtYqrgBiaD6FmgmBoPmR9xXj7KPL5n+QYnGsPQ/Oh1mzijlfMBcTQfKhFMg3ONXSts8G5qOV6HJyLpK50WYgibmgRQJlBslBXQwsnnMIyNB/KjA3NhzDnYpZNOeoqsk89Ds5FUlexZaTFSRej97gPaWQHMRUQQ/Oh1szQfIwHkSMPfQ3Ok4m60v54GZoPtX7iP17RPYx/Ak1oB2JoPpSZ6Ye6MjQfKgPpkrpSj2SirrS4S4lukFTU1QioLiCG5kMD74bmQxsY1FUsqxRDj9RVuNOoO9Qt1xJaUFdxI/oJpKqAGJoPtX4MzYciaNF9TCh1pTJSAq8KIgfnomBoPtRiYgfnIzEhFJah+VBmZmg+Eo9k7z7iijzVqSt1GSiPmuDBuTI/yqwUFxBD8yHUTBAMzYesrxhvH0U+/5Mcg3PtYWg+1JpN4PGSuZ9QVEAMzYdaJNPgXEPXOhuci1qux8G5SOpKl4Uo4oYWAZQZJDN1NYSEUliG5kOZsaH5EOZczLIpR11F9qnHwblI6iq2jLQ46WL0HvchVUdwRS0ghuZDrZmh+RgPIkce+hqcJxN1pf3xMjQfav3Ef7yie1B/AiWsAzE0H8rM9ENdGZoPlYF0SV2pRzJRV1rcpUQ3SCrqKoqvcQuIofnQwLuh+dAGBnUVyyrF0CN1Fe406g51y7WEFtRV3FA+OB+JiAXE0Hyo9WNoPhRBi+5jQqkrlZESeFUQOTgXBUPzoRb6G5yPhOYUlqH5UGZmaD4Sj2TvPuKKPNWpK3UZKI+a4MG5upG4eivZAmJoPoSaCYKh+ZD1FePto8jnf5JjcK49DM2HWrMJPF4Km9ExBcTQfKhFMg3ONXSts8G5qOV6HJyLpK50WYgibmgRQJnBVKOuhqAZhWVoPpQZG5oPYc7FLJty1FVkn3ocnIukrmLLSIuTLkbvcR/S+AmusAJiaD7Umhmaj/EgcuShr8F5MlFX2h8vQ/Oh1k/8xyu6BzEnkCYdiKH5UGamH+rK0HyoDKRL6ko9kom60uIuJbpBUlFXMfgKFRBD86GBd0PzoQ0M6iqWVYqhR+oq3GnUHeqWawktqKu4Ed/gfCRMYGg+DM2HRq616D4mlLpSGSmBVwWRg3NRMDQfajE5BucjIZTCMjQfyswMzUfikezdR1yRpzp1pS4D5VETPDiPfySu1gpMhuZDqJkgGJoPWV8x3j6KfP4nOQbn2sPQfKg1m8DjFUczKqwDMTQfysz0MzjX0LXOBueilutxcC6SutJlIYq4oUUAZQYGdTUMIQXE0HwoMzY0H8Kci1k25airyD71ODgXSV3FlpEWJ12M3uM+pGKpqyFo/LewDM2HOhiaD1kXEzo4TybqSvvjZWg+1PqJ/3hF96Ad9xl3ATE0H8rM9ENdGZoPlYF0SV2pRzJRV1rcpUQ3SCrqSpCvuAqIofmI1Th2B/qnrgTDoK5iWaUYiaCuAoHAmH/KnUbdoW65lhgVLNL7jDenSMdQPp405rVAIBDX4HwkUmJcJxSG5sPQfMiunFDqSmWkBF6pRA7ORSFS8fD7/fh8vrALmCRJSJKEyWTCZBp7D6t5cRTQfQQCAfx+P4FAALPZPOb9+/1+/H5/6H2OPT6xdR+BQCB0PE2SFIo9tB8Yk8/QZzB03AMEkAKR8lKHmAuIoflQZmZoPhKPZO8+4oqcYOrK5/PxwO8exx/whyLaLCmkpqVy4dJFXHje4rAiojl1FRXKqKtAIMD23ft5Z+surlx1EZdctCzsdb/fz5+ffIH2zm7+8wv/RnpaWkRfKlLB7/dz6MgJXn3zHSRJ4tN3fJBppUUEAgEef+6fNDa3ceM1l3H+uQuBYGFxudz85s9P4vZ4+ezHP8ymbbs4frKWD950DYvmz4nrqMY/RDc0H3HC0HzI+orx9lHk8z/JMTjXHuPdxY7sPObNmsHcWdPJy8ulq7uHtzZt58Sp2jDboTv3obv7of2BwFgaZrxtRvgK2y+NH0du/+j8fD4fPp8PfyBoE5C7mQ3lDH7/YLcS8imFdTCj30Mk6mtozf6q48EbwUCA9w4eCb4tSeKcObMgAEeOn2LIhd/v51RtPS6Ph9LiAvLzsvEP5hwIBOI+n2LqQAzNhzIz/QzONXSts8G5qOV6HJyLpK4SXYgkJG58/2XYrFZ8Ph/r3tnKvsNHOXGqlnmzZwQv2j4fDY1NdHb2kpWdwbTSIuw2G36/n9P1Z7FarFRMK8Hv99PS1o7D2U9JUSFpqXYGXC4am1pJS7NTVJBPwO/nbHMrHZ1d5GRmMq2sGIvVQsAfoKOzm87ubooLCzjb1II/4GfuzEokyURHRxdnmltItduoKCsJdg6SFCocDWeb6e7tpaQonwjX+VEI4PV6OVlTh7N/gMryMrKzMvH5fJyuP4vJJDGrsiJEQzW1tNI/4Ka0uIC0tNRwT4Fg7g1nmsjNzaK3z0HV8ZNcc/lK7DYbixbM4Z2tOzldfwaH00l6WhqBQIBjJ2uQkFh0zlzBT8lJ6guIoflQZmxoPoQ5F7NsylFXkX0mYnA+GgECBAYvwn6/H6vVAv+/vTN7aus8w/jvO0f7wmKzmB0jwGzGjonjpI7TkKSxs6dJ3Gk8aSeTtNN2pp3+Mb3uRW960ekynay148Q2JjZeghfAsgABZjfCG5LASEenF8IyBMlI4ggU5zw3jI7e9/m+8x04r77nPQ9CxF4HAkH+/dkxJqd90QmqYLdbeef1n1FSVMiJzvP4bt3hz7/9AINB5svjp5mYnuG5nzzJM227GBy6wSdHT/J020625Obyxdcd9Hm8S4OrFG7N5/13X8NqMXOl7zpnzl+moryEsYkpTEYjf/iwjCvXPJzoPEckEv1jsZrNHH7zIOWlxSiKwmdfnaLXPQAiOsXCrVvWWMyoXvyfz48zNT2DChgNRt4+1I5reyXHO7rw3brFR++/w7aiAsLhMP/85CiB4Dx/+s0Hq9gikQhX+zyoqOxubmDqpg93/xC97gHadjXjdNipKCtlZGyCax4ve1qbCIVCDAyNIkmC5vraldcuqSuXCNFsDX0guucjNWyg50NjLi1bHtnVOH+cpKvMr1dKxUOFc9/10HH2Ip9/dYoLl3oRQrC9shxVVfmms4vJaR+N9TV8+Mu3aT+wl2BwgU+PniAUClNfUxWTY+YXFpi66QNUboxOoCgKA0M3AKjdXsVVdz991wepra7g978+zAsH9jEze5tT315YITnd9M1ysH0/L7fv5+7cHN90dJHjdPDRkZ/zi7cOEgqH+OLrDhRFwTsySo97gPy8HD4+8i4fvPcGc4HAWisEQpDndPDHj4/wygvPshgK8b8T3xKJRGhtrAUV3B4vkUiEyekZ7vkDVFeW43DYVq6hqhJWFHrcAwghaN7hYmdjtCB097ijcpQQtDTUAXDNM7g07zEWF0NUV5at4tQCKRUQ3fORXFj2SFeZaZwDWSddabP7yE7pKnVkj3QVHVMgBJy5eJmu767iHhhGNsg8tWcnLY11RBQFd/8wsizzyksHKCkuZO/unZSXFnP7zhxTMz7qXFWgqgwOjTI2MUVEVclxOhifmmZxMcTI6AQ5TjslRQWMjU8BUFJUyOztu2zJz0U2yIyMT8bmg4CWhjr2tDbRvKOWsfEoZ0lRIXP+AKgqBVvz8c3eJhCcZ2ziJgB7WpsoLtxKWUkxjfU1a5+7gGefbsPpcNDatIPCLXnc8/u5NxeguaEOSZLoG/CiKArugajU1Npcv4onEongHbrBXCBARWkxNquFirISbDYzU9M+Jqai86t3VWE0GLgxPsXde3O4+4cAaG5YyanF7gORQg9E93ykG5w+QfZLVxpDl67SyUoamyFdLR/9yLuvYTIasZjN2O1WTEYjAIuhEEpEwWG3YTIaY43kHKcDmCY4P09F6Tby8nIYHh3HaJSRhGBfWyvHTpzhUs81gvML7G2IPtHlDwQB6Oq+giRHPyMbjYbYo6wPYLNaY+fiD84DMDA0wtDoeGytLBYz8wsLzN9fAMBqscR2MVbryh5FXKhgtZhjL602K+L2Xe7fv09+Xg6u6go83hHGJ2/iGRjGZDZRX1O9kmJ58xyYmJrhL3/9OyqwuBhCRaX7qpvSbcVYLRZc1ZVc6/fS6x5gcGQUo8lAQ1117Ny1Kh6wCT4Q3fOhez7iZm6qdJXiSBv4MV7LxrlWSKcRK4BtRQWYTaZVx60WC1azhWBwgdlbd8jLjTaZozIVFOTnI0kSddsrOdd9lV6Pl9KSIuprqvnq5Bm6untACHbU1iBJEk6nHYBXXzxAnauKcFhhZvY2RVvzV4xstZgRQgJUnE47Atjd0kD7/qdQVZXJaR/5eTk47DbynE4AfL5bUR8GKj7frTXPW0VlYnoGV5WFcFjhzp17AOTmOpEkiZ2NdXgGhznddZG7fj9PtDRiNK68Lauqit8fZGh4FKPRQGVpSYw7EokwMjpJn2eQF5+LNtNbGlxc6/dy9rurhMIhmnfUrlp3LSBIsoDono/kwrKnX6F7PtZ+M63AdbBtROM8u6QrWCo2CQrOg6OyLPPEzgbOXLzMvz49SktjPaMT08zevktleQnFRQWoqkq9azvnu3uimn5FGQ67jaKCrdycmcVut1FeUowQgtbGOnqvD3LyzAXCEYWhkTH6PF6a6l28cfD5JUMdSEKKzbGp3sXJzgtc6esnLyeHhcX7dHZ1k5eXw+9+dZimhlpOn+vm/OVeDCaZxcUwHu9wlCvO6i4f48uvO9m7u4WJqZv4A0Fqqspx2KNFrramCrvdysj4ZLSH0Vi7igtVpcfdj4qgqc7Fm4faY0VcURT+9o//MjE5wzXPIHtam3FVV2KzWpifX0BIKyUxaclMyIOfqV3NlReOVJvouudjndA9H3G50tx9aDOnx6lxnnmketOR5ajcJD3ihiWEiD5N9eQuAsEFOs5e5MbYJK1NdRx+/eVYTHlpMQ6HHUmSqK4sQ5ZlaqorkCSJBtd2ZDnqrN5eVcFLB/Yxv3Cfz46dwt0/TF1NNYfa90fd77KEEBJCejgfu83G26++iNVi4njHWTq7uiks2MJ7r7+MLMtsycvlrUPtGE1GOs9don9ohGfadi/xrL6NGmQZSZIwm0y07Wqio+siHu8I5aXFvPrSTwFibvKmehdCCPJzc6goK4m7Pr3XB5GkaIFZvo6yLPNESxNCElzu9SCEwGg00rzDhSRLOOw2aqorozyw5P6XkYSUqK4/Gt+rIeLOPf8jbzVa7T423PORUgHZqN1HnKjkDqWA7N59xM1M/mDyESlUhE1vnMd5W0vpanN7Hwl4ErxQFAV/cAGHzYosy6lzLTsYiUS45w9gMZmwLOtDJMoSRG/qc/4AsizF3OPLEVFV5hfm4763mv3hGPcXQ4RDIez2h3mKohAOhzl26gyXetw8u28Pz+9/au1zSzBaGodSwMPKsZznkRKW7vlILlj3fGhGrk3aj066Ssz5QyoeALJsINfpSI/re5AkibwcZ0pZQoil5n38NEmIJIvHSphNRswmY+y1qqpc6nHjvTFGv3cYg8Gw9O9HUkXaJSb1MeKQpNlE1z0fqUH3fMSl2NTG+eMkXWV+vfTv+UiVZw35VQjCSpixiSmKCgp47pm2VYUr7T14Bi/V96kTSlgZf2xXl67S5FpjDF26ShLZKV0lOVzi6B/w7mOdZ54kRXzpKr3BEoWlXG3SHC65X6BMSFcPELeJrns+0g1OnyD7pSuNoUtX6WQljWwsHitJ1zyQWnomsf56kAFsbPFIhIx+pa3u+dA9H3EzN1W6SnGkDbwraNk41wpaFo+MF8dM7T5SwkbtPrRMTJ96VQHRPR/JhWVPvyK7pSst8bjvPtY1coakK62gpXSlwQySHzUTu49MSVdpRa2RvQZJ4h2I7vlYJ3TPR1yuND8+aqnAPx6N88xjYxrnGklXG3itEodt4nplYjOaRA1ZUUC0ug9tuOcjJWzi7uPHLl1pELne9E1vnGci4we9+9B6gOQCdOkqOcK1qGMFRPd8JBesez40I9cm7UcnXSXmzMbGuZbSVXozysQvXZrs617S7JGuHiCJJrru+UgNG+j50LiGaNnyyK7G+eMkXWV+vXTPR6o861+vtRk2XvtMhvr/NfoBxg71CuwAAAAASUVORK5CYII=</v>
+      </c>
+      <c r="E816" t="str">
+        <v>20-09-2026 07:09:21 pm</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="str">
+        <v>6aaff4d83b204ec1da549483</v>
+      </c>
+      <c r="B817" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C817" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D817" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E817" t="str">
+        <v>20-09-2026 08:29:36 pm</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="str">
+        <v>6aaff4d93b204ec1da549489</v>
+      </c>
+      <c r="B818" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C818" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D818" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E818" t="str">
+        <v>20-09-2026 08:29:37 pm</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="str">
+        <v>6aaff4e03b204ec1da5495a1</v>
+      </c>
+      <c r="B819" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C819" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D819" t="str">
+        <v>Started Playing game and Debited "10" and Balance "80"</v>
+      </c>
+      <c r="E819" t="str">
+        <v>20-09-2026 08:29:44 pm</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="str">
+        <v>6aaff4fa3b204ec1da5495d4</v>
+      </c>
+      <c r="B820" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C820" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D820" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E820" t="str">
+        <v>20-09-2026 08:30:10 pm</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="str">
+        <v>6aaff4e03b204ec1da5495a7</v>
+      </c>
+      <c r="B821" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C821" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D821" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E821" t="str">
+        <v>20-09-2026 08:29:44 pm</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="str">
+        <v>6aaff4fa3b204ec1da5495d7</v>
+      </c>
+      <c r="B822" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C822" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D822" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E822" t="str">
+        <v>20-09-2026 08:30:10 pm</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="str">
+        <v>6aaff5693b204ec1da5496f2</v>
+      </c>
+      <c r="B823" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C823" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D823" t="str">
+        <v>Started Playing game and Debited "10" and Balance "70"</v>
+      </c>
+      <c r="E823" t="str">
+        <v>20-09-2026 08:32:01 pm</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="str">
+        <v>6aaff5866cd0b6ebbbbe8473</v>
+      </c>
+      <c r="B824" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C824" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D824" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E824" t="str">
+        <v>20-09-2026 08:32:30 pm</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="str">
+        <v>6aaff5806cd0b6ebbbbe845c</v>
+      </c>
+      <c r="B825" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C825" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D825" t="str">
+        <v>Answered incorrectly for Qst ID: 6aaff56a3b204ec1da549704, Qst: How many times do the letters B, J appear in the paragraph?, Submitted Answer: 2, image : iVBORw0KGgoAAAANSUhEUgAAAZAAAAD6CAYAAACPpxFEAAAABmJLR0QA/wD/AP+gvaeTAAAgAElEQVR4nO19aXQc13XmV91o7DsJkAAIghsobuIqidoXW5FlWd5i2bEVK7bjZJzxJLEdZ3ISJ+N4Fic5x+M4Y8f2mbGdSSYeO3G8jWVbsnaJ4r7vIAguIHYCXEDsS3fNjwYaaHRV13tV91W/rr7fOZRY1fd993WhWbfvd+sjjfGJSRMOMBP/SfqNK6SstqVLnyftq8JbNN2ES77sapHkVTZtD739tBbQmjRspu2B5QlxLmGa1BeFsgpuzbT4nRtOsXRiHyCSP7XJ//MMI+k3hn2gDJftCccXnF8V3qLhJlzyZVeLXFxlI+1vQ07LSW9AwuQeiocwaIuHhy34ksorqIqHQxaaaB9/VvZhGbxepMUjmURN8SDicuQkSOYI2uLhYQsEqZxXOBYQACTdh/hKjx9RieWUxcNV96FihaLugwrpuw/qBGIB9NuQrjZuGQgXOhOSUxNUEcr7L033QVs8XHUfJDBsD+e/kraAmGmOPMMlHaV0RQVK6YpqIzkrXSlYRVAPPAa7J6CUrqig9PangXRFhcxKV2I8tgWEaORhTeGr9mCdIxjSlfrr5Y90JQfKj4+LhsUhzPv1cmbwX/vMiu4jo9KVZCb/tuRdukpDkF7C8lW68siV5dKVPIIkXan4luIcECjpipxrrvug3FPyvNzHu2gaBL378JTZRrqahWUBUXoDUjE4D4B0RbUzHaWrZFLHE3LLVUKFdOUZfgzO9ZeufHnqShhBGpzLwb4DUdF9ZFS6kszk412BcnBOBcriobw45nr3kevSFUGk1+U6Ds4ppSs7rpQCYib+k/SbjCLo3YenzLkuXcntQDyrz4NzypG4/t0H8fdil3QsXYlxpqNPKiBK9VcV0pUwgjQ4Vw/2fMiGZfB6qWhGiWsIez6SwlVsgSCVu82lSli+Ds49fkSzfHBOKV1pWYhsD1QkEAtg6UqMMOjSFXs+0uQQ7D6AeQUk+QND/PFxScfSlRinjoNzSunK3Y5UfOhcsnu+pEGRrojB0pWbVcIQ4QkBtCMPvQbnQZKu1F8v9nzI8ni/Xs4M/mufWdF9sOeDKJW458MKcxKWr9KVR64sl67kESTpSsW3FOeAQElX5Fxz3Qflntjz4YVNP8+HFUJKb0AqBucBkK6odqajdJVM6nhCbrlKqJCuPMOPwbn+0hV7PsQ4M1Gi4x2Iiu4jo9KVZCYf7wqUg3MqsOdDFkEanCuk1mxwTrVcx8G5H54PK4RIByAECHr34SlzrktXcjsQz+rz4JxyJK5/98GeDzk2fT0fVhD769wdQNV90HyOgzQ4Vw/2fMiGZfB6qWhGiWsIez6SwlVsgSAV3eZmCogfg3OPH9EsH5xTSldaFiLbAxUJxAJYuhIjDLp0xZ6PNDk8dB8AECL/+LikY+lKjFPHwTmldOVuRyo+dC7ZPV/SoEhXxGDpys0qYbjl8SRh6TU4D5J0pf56sedDlsf79XJm8F/7zIrugz0fRKm8eT6s4LqAUEpXNN2HntKVPIIkXRHsONelK3Kuue6Dck/s+fDClh2eDyuQDNEBsHSl+MujjtJVMqnjCbnlKqFCuvIMPwbn+ktX7PkQ49SjRLssIHpJV5KZfLwrUA7OqcCeD1kEaXCukFqzwTnVch0H55nyfFiBrgNxgaB3H54y57p0JbcD8aw+D84pR+L6dx/s+ZBjyy7PhxWkCwhV90H5/E8wBufqwZ4P2bAMXi8VzShxDWHPR1K4ii0QpFJ7vaQKCOXgnGq5joNzSulKy0Jke6AigVgAS1dihEGXrtjzkSYHcfcBeJWweHBOD0XFgz0fCtg9X9KgSFfEYOnKzSphUL5D4QKi1+A8SNKV+uvFng9ZHu/Xy5nBf+0zK7oP9nwQpaL3fKRkMAyxAkIpXdF0H3pKV/IIknRFsONcl67Iuea6D8o9sefDC1v2ej6s4E7CYunKzSph6ChdJZM6npBbrhIqpCvP8GNwrr90xZ4PMU49SnQyDCO+K8cCopd0JZnJx7sC5eCcCuz5kEWQBucKqTUbnFMt13FwrpPnwwq++UCC3n14ypzr0pXcDsSz+jw4pxyJ6999sOdDji37PR8JLmOOLW0Boeo+KJ//CcbgXD3Y8yEblsHrpaIZJa4h7PlIClexBYJU6q/X/OIBpCkglINzquU6Ds4ppSstC5HtgYoEYgEsXYkRBl26Ys9HmhyKpatZiEtYPDinh6LiwZ4PBeyeL2lQpCtisHTlZpUwVElXs7AsIHoNzoMkXam/Xuz5kOXxfr2cGfzXPrOi+2DPB1EqfzwfVkgpIJTSFU33oad0JY8gSVcEO8516Yqca677oNwTez68sAXL82EFZwmLpSs3q4Sho3SVTOp4Qm65SqiQrjzDj8G5/tIVez7EOPUo0cmw6z6ABQVEL+lKMpOPdwXKwTkV2PMhiyANzhVSazY4p1qu4+Bcd8+HFZT4QILefXjKnOvSldwOxLP6PDinHInr332w50OOLZieDyskCghV90H5/E8wBufqwZ4P2bAMXi8VzShxDWHPR1K4ii0QpPLf82GFEEA7OKdaruPgnFK60rIQ2R6oSCAWwNKVGGHQpSv2fKTJkQHpahbWEhYPzumhqHiw50MBu+dLGhTpihgsXblZJQw/patZhPQanAdJulJ/vdjzIcvj/Xo5M/ivfWZF98GeD6JUmfN8WEFwiO76j43ocvlQH6UreQRJuiLYca5LV+Rcc90H5Z7Y8+GFLfieDyskFxCWrtysEoaO0lUyqeMJueUqoUK68gw/Buf6S1fs+RDj1KNEJ0Om+wDmF5CMSleSmXy8K1AOzqnAng9ZBGlwrpBas8E51XIdB+fZ6PmwgmcfSNC7D0+Zc126ktuBeFafB+eUI3H9uw/2fMix5Y7nwwrxAuLy6yPl8z/BGJyrB3s+ZMMyeL0UNqNUXOz5SApXsQWCVHp4PqyQpgPx+BHN8sE5pXSlZSGyPVCRQCyApSsBQuLBOQDtpCv2fKTJoYl0NYsQD85Jt5DCqePgnFK6crcjFR86l+yeL2lQpCtisHTlZpUwMi1dzcKmA/Gv7Q+GdKX+erHnQ5bH+/VyZvBf+8yK7oM9H0Sp9PJ8WMGigLj+YyO6XD7UR+lKHkGSrgh2nOvSFTmXGumKPR9e2HLT82EF6aewgi5dUe1MR+kqmdTxhNxylVAhXXmGH4Nz/aUr9nyIcep005+F1+4DSCkg/v0RzKh0RZZK4WM2s5Ts+ZBEkAbnCqk1G5xTLddxcB4Uz4cVpDqQoHcfnjLnunQltwPxrD4PzilH4vp3H+z5kGPLbc+HFeYVkPSfVMrnf4IxOFcP9nzIhmXweilsRqm42PORFK5iCwSp9PV8WGGmgHj8iGb54JxSutKyENkeqEggFsDSlQAh8eAcgHbSFXs+0uTQWLoC4nsSkrBYuhLj1HFwTilduduRy/fhs3RFSaC/dEUMlq7crBKGjtLVLEJ+tv3BkK7UXy/2fMjyeL9ezgz+a59Z0X2w54Molf6ejySumf87diA03Yee0pU8giRdEew416Urci410hV7PrywsedjIebvKW0BCbp0RbUzHaWrZFLHE3LLVUKFdOUZfgzO9Zeu2PMhxqnlTZ9YupqF57/OXQQZla7IUil8zGaWkj0fkgjS4FwhtWaDc6rlOg7Og+z5ABbsyUhTQILefXjKnOvSldwOxLP6PDinHInr332w50OOjT0fKTwWB5YFhPL5n2AMztWDPR+yYRm8XiqaUeIawp6PpHAVWyBIlV2eDyvIS1hZPjinlK60LES2ByoSiAWwdCVGGHTpij0faXJkmXQ1i5QCwtKVGKeOg3NK6crdjly+D5+lK0oC/aUrYrB05WaVMHSUrpJJkw8VDNGDJF2p7zHY8yHL4/16OTP4r31mRffBng+iVNnp+bBCUgGh6T70lK7kESTpimDHuS5dkXPNdR+Ue2LPhxc29nwshJ10NXsiUUCCLl1R7UxH6SqZ1PGE3HKVUCFdeYYfg3P9pSv2fIhxannTVzw4n8kCQIGElVHpiiyVisdsFlCy50MSQRqcK6TWbHBOtVzHwXmueT6sEAKC3314ypzr0pXcDsSz+jw4pxyJ6999sOdDjo09Hyk8tgfJJ0KUz/8EY3CuHuz5kA3L4PVS0YwS1xD2fCSFq9gCQars93xYIb2EleWDc0rpSstCZHugIoFYAEtXYoTZLV155Mpy6UoeQZKukk/YF5Cck67sOXUcnFNKV+525PJ9+CxdURLoL10RQ8XgPADSVa56Pqx27HGIHiTpSn2PwZ4PWR7v18uZwX/tMyu6D/Z8EKUKjufDCtYFJMulK3kESboi2HGuS1fkXHPdB+We2PPhhY09HwshI13NIrWABEC6otqZjtJVMqnjCbnlKqFCuvIMPwbn+ktX7PkQ49Typu+j58MKniSsjEpXZKlUPGazgJI9H5II0uBcITV7PlyGsOdjIUQ8H1ZILiAB6D48Zc516UpuB+JZfR6cU47E9e8+2PMhx8aejxQe2wPLE0lw0YEEaXCuHuz5kA3L4PVS0YwS1xD2fCSFq9gCQapgej6sMFdAsnxwTildaVmIbA9UJBALYOlKjDC7pSuPXFkuXckjSNKV847jBSTnpCt7Th0H55TSlbsduXwfPktXlAT6S1fEYM+Hm1XC0FG6SiZ1PGEJCQkrSNKV+h6DPR+yPN6vlzOD/9pnVnQf7PkgShVsz4cVQtkuXckjSNIVwY5zXboi55rrPij3xJ4PL2zs+VgIr9LVLAQ7EH2lK6qd6ShdJZM6npBbrhIqpCvP8GNwrr90xZ4PMU4tb/oZ9nxYQVjCyqh0RZZKxWM2CyjZ8yGJIA3OFVKz58NlCHs+FsKt58MKAgVE3+7DU+Zcl67kdiCe1efBOeVIXP/ugz0fcmzs+UjhsT2wPOHI5VBAgjQ4Vw/2fMiGZfB6qWhGiWsIez6SwlVsgSBV7ng+5mN2R44diI6Dc0rpSstCZHugIoFYAEtXYoTZLV155Mpy6UoeQZKu3O04TQEJinRlz6nj4JxSunK3I5fvw2fpipJAf+mKGOz5cLNKGDpKV8mkjieEl9sUkCBJV+p7DPZ8yPJ4v17ODP5rn1nRfbDngyhV7nk+rHhsOxAdpSt5BEm6IthxrktX5Fxz3Qflntjz4YWNPR8LoUK6moVFAdFXulL+WKsbLvZ8UIYRwY/Buf7SFXs+xDi1vOlr6PmwirbsQDIqXZGlUvGYzQJK9nxIIkiDc4XU7PlwGcKej4Wg9HxYYUEB0bf78JQ516UruR2IZ/V5cE45Ete/+2DPhxwbez5SeGwPLE+Ic83DvAISpMG5erDnQzYsg9dLRTNKXEPY85EUrmILBKly2/Nh9ULe/GMdB+cyK14814+ewXHb1zcsLcOOxgrpPdjhRNcQWvtH8NTWpa45jt3oxf7+Tnx09Tbkh8LJr13vxYFrXdhUWYN7a5YL8X3r/GHcX7sc6ytq4iccLuC+/ivoGLmF96/YmDhntWQyOo38cJ7FK8CBzpNo6b+MZ7Y9CWPex21g9AaebXkDdeWL8bY19yatOdHXiiNdLfjw1iewu/0YxqYn8Pia+3BrYgQ/PvMyHltzD+rLarC34wSujlzDu9Y9IvT+U0BetxSWRM2kK/Z8pMmR1dIV3beUmQ4kGNLVz0704Vu7r+CnJ3rjv44n/zrVM+Q9Cea6jwNXbuKfDnS45wFwoL8LXz61G5OxaNJr+wc68JE3f4I3ei9jS1WdEBcAfPnUbhy/3iu8g9d62/GdtiNpo84O9uOdr3wvNdkM+oav4yt7vosrN3qSzr988QC+uvd7+OvXvoPpBe/v+8eex7MtryMvlIfnW/fgR6dfBgAMjg/hq3u/h47B+Ht4/dIhfP/4c0LvRQT6S1fEYOnKzSph6ChdJZM6npBbvgB5wZKuTKxdUoLvPL0lhYBsSO2DdLV/oBP/bs+z2F5dh2/e8w4UhiPp9zTv9y8+9lFUFRSmviAIqyUnb/ThysigbcDOxtsBAMd6z6Gpqj4Rtqf9OO5v2o4324/g1NU2bF16W2LNkZ4W/NqanQCAP3ngIykFxmlPQhG5PjhnzwdRKvZ82L2QB+gpXclDfnB+uncIp7uHMBGNYWlZAe5fXY2iyJyMZJrA4Y5BtF4dxqKSfDzcvAhne4dQX1GImtJ8S87RqSh2XbiOq0MTqC8vxP2rq1GQl/qwm92e4sXjZ7i7pgFfvesJFMyTjQ4OdGFlaRVGolN4o/cyisIR3FXTgMaSOVmuc/QmIuFqlIbj+4uZJnb1tePi8HXUF5fjrXWrcGigC83l1VhUUJxYNxadxgvdFzAwMYK15YtxX+1yGAB6xoZwYegGAGBv/xWsLK3G0sLSpD3XllRjRWUDjvacw7vXx6WmqegUDnWdxn9+6yfRMdiDPe3HEgWkY7AX/SPXcU/jZgDAwOggpqNR1JRU21yVZAyOD2Nf5wn0Dg1gecVS3N+0DZFwHqZjURzuPoNVVctQU1IFAJiITuFYTwtWzjs3Pj2JE73nsKF2NUrzi9Olmgf2fDi/6CrQAxt7PhZCuXS1ANaitktki+cjZpr43M9asPfyDWxuKEfMNHGqewiVxRF8/6PbURwJIzoTs+fSDdxeX4b+oUn888FO9N2awCcfaMJ7NqfOPdr6R/CZH58BDGDN4hL8y9VufPPNdvyPpzaioaLQcYOzxeOBJcvxlTsfR2TBTOTTB5/Djup67L56BavKqtA+MoiRqUl867534Z6ZGcnH3vwpvrD1EXxwxe2YiE3jE3ufxdFrPdi2qA5XRgbxf9qO4fiNXvztnY/jsfrVAIChqUm855XvIT+Uh0jIwJcGd+N9TRvw37a9FUev9eClngsAgC+f3oPfbb4DS+vXpLyNnY2bsK/zZOItHe1pwWR0Cnct24S7Gzdj95Vj+OTO3wAAHO46g0g4gu0NGwAA/3D4pxgYu4lvvfvztj/HWey6fARfeOWbKIoUYHlFHf7h8E+xqLgSX3/nn6GubDG++Nq38eDK7fjjez8CANjbcQKffe6/4ze3PIHP3PsMAGB3+1H8xctfx8sf+1+O+ZJ+SBpLV+z5EOPU8qafJZ4Pqxfygub56Lo5jr95oc2S65MPrEB5YR5eb7uG19qu4dtPb8GmujIAQEvfMD763WPY1XYdb1tfg5+f6sObF67j67+xCVsbKjAdi+GLv2pDW/+I5Q6ipok//3kLllcX4W/fux4FeWGMTEbx6R+dxhd/dR7f+MDtad/fvqsd+OyhX2E8OoVnVm9JKR6z2NN/BT9+y4fQVFKBsegU3vvqv+Cf2o4lCsj8BP/YdgxHrvfgBw99AOsqFmMqFsUfHvglps1YEue1iVH8h3UP40Mr43v8ypm9+Pb5w/jjjffhiWVrMTw9ib889ip++NAHLfcEAHc3bsYPTr6A62O3UFVUjt1XjmNj7WqUFRTj3uVb8G+nXsCN0UFUFVfgSHcLtixtRlFegdRjuzfHhvC5F7+Ke5dvxRd/7feRF8pD/8h1fPwnX8AXXvkm/ue7/xMeWrkDe6+cAGZm9vs7TqAgHMGBrtMJnl3tR3Bnw0YUR2yKehpkhXRFEOl1uY6Dc/Z8UCaIQ+LfRE8PXTwfU9MxdA2Oo2twHJ0z/5/9FY3FY3euqMJ3f2tbonhETRMFeSGEQwZujk0BAH51th87V1Zia0NcHgobBn7vPvsnoU73DOHKjXF8bGcjCvLiN/+S/DB+Y3s9jnbewvBENHW38w4+ffA5PLFsDdaUL8KfHHoRg5PWT5M9Vr8aTTOSVWE4gq1VS9E3Zl3UftHZiifqm7GuYjEAIBIK4w/X70yJi4RCeKpp7imsB5Y0IWaa6B0btn2/C3FHwwaEQyEc720FAOxtP4Z7lsdnUTsaNiAcCmN/1ykAwJHus/HXJD0fu9qPYHRqHJ+652nkhfIAmKgpqcJHtr0Th7rOoH/kBh5acQcu3ehC7/A1AMC+jhN474ZHceHaFdwcG0LMNLH7ynE8vPIOwXfGng85zqBIV/acOg7O/fB8WEFMwtJ6cJ6MFYuK8bWnNqXlKo6EMRmN4W9ebMP5qyNouzaKPAOIxcxEkekaHMdDaxbFeWYG57VlBSiKWNfcrpnHh//sZ2eTPhSzfB03R7F+SZntvt/XtAF/ueVhtN66hve//q/40yMv4ht3vzPlh1k7M3+YfW9lkQJMmtYD6Csjg3h8gdy0urQqJW5pUSkiobn3VTgzd0l0KgI/lNL8YqyvWYVjPeewvmYl2q534PPLPwEAKI4UYsvStTje04qtdevQPdSfmH/IoGeoHwXhfNSV1yRtalX1ssTrW5fehorCUuzrOIGdyzahY7APz2x9Ej9reRWHuk9jaekiDI7fwkMrdognZs+HIIIkXbHnQ+QF5wKiqefDaUU6rn2Xb+KzPz6NO5sq8PaNtdhSX45Vi4vx4N/tSawrL8zD6ETyjTkaMzE5bc1clh+/lJ9/ezNqygpSXl9eVZTWcf4fN92HkGFgXcVifGrdPfjS6TfxzxeO4bdWb02KCxvifwN/RaQAI9HJpIDh6amUZWk5JbCz8XYc7jqDlVX1qCwsw/raVYnX7l2+FS9f3I9jPS2oKq7A2kUrpPnLC0oQNaOIxmLIm1fwxqYmAABF4QLkhcK4d/lW7O04AdM0sWZRI5aUVmNb/Xoc6j6DivxSbFrSjEXFlQIZ2fMhmUhL6UoeQZKuVHxLmYPnO0fmpCt7Tif6Z0/1obGqEF/59U14amsdmmtL0H1rHFHTxFQ0/q1749IyHO0cTBwDwOHOQURtHuNdXh1/mufW+DTW1ZYmfg2OTeMXp/oQm7/MYYO/3bwNd9c04kund+P0zavp3mpabKlegn39nUkPau/tl/StmHMFJpbmEWYTwM5lm9DSfwkHO09j57LbkwrTPY2bca6/Hfs7TmJnwyaEXHz7aqpqwHQsipN9rUnnj/a0oCAcwbLK+IMND63YgYNdp7C/8yTuWhbvRu9s2ISDHaew68oRPLxCRL7Sf3BORR506Yo9Hy6XCyB9AdFaurJeMTg2jVdaByx/HWi/CQAozQ9jYGQSHTfHAMTlp//yy/MAgPGpeMF45q5lGBiZxOd/eQ7Hu27h5XMD+OKv2ixzAsDyqkLsbKrE13e148CVm4jGTLRcHcZfvdCGS9fGUJJvPRS3Qsgw8Dc7HkVRKA9/dPB5jFh0DSKX4xNr78S5wQH8xdGXcORaD37a0YK/Orkr3RJLzuqCIgDAC91t6BtPnYvM8mxe2gwAePnCftzTlCxRra1pQnlhCZ5v3ZNWvkq3pzsbNmJV1TJ88bVv41z/ZUxFp/DShX34/vHn8J71b4kP5QHc27gFo1PjePXSIdzZEJ/t7Fy2Ce2DPWgdaMdDq+IFZDo2jb96/dt4oW2vyGWgA3s+fAN7PjzyOCSwl7Cy1PPRcXMMn3u2xXJVc20J/vmZbfj4vctx7uowPvAPh1GaH0Z+XgiffHAlSgrDOHc1foNsqCjE3753A/7+jcv41I9Oo7GqCJ98oAlf+GUrCiPWxeC/Pnkb/vqFNvzRj84gapowANy3qhqfe1uz7dbtUFdUhi9sfQSfOfg8vnDsVXzpjsfEFs7Dxspa/P3OJ/GVM3vw845WNFdU44823os/P/KSozlxPrZULUVTaSU+c+h5/E7zdnx2w30WUWb80dz6ddhz5URKkTBg4O5lm/Fc65u4u/F2i/XOlyYvFMbX3vmn+MuXv4Gn/+3PAACFefl438ZH8Qc7P5SIK8kvwo76DTjUdQbb6+OPCq9Z1IjqogpUFpahqSLu7I+ZMfz4zMvID+fjsTX3pO6EPR8ULNJgz4cY/PZ8WO3AGB4dI1Sh/PJ8WBcQWZ6rw5MwYyaWlKfOLC5dG0VhxMDSsrlHPbsGx/HUdw7j7963ETub7DX0oYlpXBuZwuKSfJQWhOf2lbJBuR3bRtu80HprABX5hVhSWJI4d+JGHz7w+g/wo4c/iA2VNcLJoqaJW1PjKI8UIjzvG5T0lEDyySu7iBujg7g5MYz68loUhCI2UW5gWv3PM1LrRua7D8cdCG2RfnAuXUBUDc4VFBBl3YeHZ3jdN6+GjYSVJZ4PlwQJ1JbmWxYP0zTxausAPvbd4xgYjg+hozET//dQN4oj4cTjv3YoK8jDiuqi5OLhEbLFAwB+ePkMfvONH+LmzCPBk9Eo/nfbUSwqLMbaikVS+cOGgar8oqTiIbQJwTDZ61RVXIGVVQ0pxYMSWSFdEUR6Xa7j4FzH4kEJD/XCRQL7AOsORNvuw754UP5hN00TwxNR/OEPT+PitRE0VBbi+sgkpmMm/vLta3H/KrG/ciPdU1equw8AGBgfwUf2/ATdI7ewrLgCV8eHEQ6F8ZW7HsddixpcJLMLc613SqQT+wDp3314+9PuS/chWRGoCkhmB+fWFUPHwTmldOXu4zP3YmoBUTH7UCxdueOyyTDvSSPTBFquDqP31gSK8sPY1lCWMAkKcYkdyPFI0ZiImSZO3uhD7/gwyiMF2F5dj/xwmvegong4hMlIV+lOe/8MmIqLR9Jv3HM5Ujnn8F5AWLqSyuCLdGV5QoxHisKugKganFu8rGPxAED2t+0q7z5EH6GSzSpVD/ySrsQ+QFTdh46Dc8uV4ifFIyQqQsalK5IC4o90lTXdh+RgTMoHQildeUKuFw9Fqwjqgcdg9wSU0hUVlGrnLskppSsqZFa6UssD0HYfc6SOJ+SWu8RcAVF8oxc4LU9ECH/+iVo5uJeuXCxRJV15Skn2ARJGVgzOPUhXVMhQrSFOZd99UCFIng+rgHgBUSVdkcAf6YoKlN2HcwKxAPrr5Jd05TmN+GpNpStKBL378JQ5q5+68mPHqTkMCEpYlNIV2bCbiAdQ1H1kRLpyCRXSlWf4/9QVFUjlD2FyD09dCYN+cO5yC76k8ops/nc+RBHy865AOTinAmXxUF4cc737yHXpiiDS6/KMD85VrMjq7vlqCPYAAB0QSURBVIM6gVjA7BnHDiRzg3OWrjzsQDyrz4NzypG4/t0H8Z92HpzTI9efuvK4iuwflErA/7mna/gzOCeSrnx8yME+LIPXS0UzSlxDKEceeg3OgyRdqb9eQfh3PkS50hYQqsE5pXSlZSGyPVCRQCyApSsxwqBLVzTdh57SlTyCJF2p+JbiHLDwjG0ByZx0Zc+p4+CcUrpytyOX78Nn6YqSQH/pihgsXblZJQwdpatkUscTcssJQSdhkUlX6nsM9nzI8ni/Xs4M/mufWdF9ZFS6kszk49d4ysE5FYLu+bBaYllAqKQreQRJuiLYca5LV+Rcc90H5Z6MxH+SfpNRBL378JQ516UruR2kzZpSQCilK+WPtbrhYs8HZRgR/Bic6y9dUXUflM//BGNwrh654PmwAv1TWDOgHJxTgT0fsgjS4FwhtWaDc6rlOg7OKaUrLQuR7YGKBGIB6ZYkFZDMDc5ZuvKwA/GsPg/OKUfi+ncfxH/aeXBOD0XFI1c8H1bw1oH4P/d0DfZ8yIZl8HqpaEaJawjlyEOvwXmQpCv11yuXPB9WSBQQqsE5pXSlZSGyPVCRQCyApSsxwqBLVzTdh57SlTyCJF2p+JbiHCCSNQRkUrqy59RxcE4pXbnbkcv34bN0RUmgv3RFDJau3KwSho7SVTKp4wm55SphuJWwyKQr9T0Gez5kebxfL2cG/7XPrOg+MipdSWby8U5FOTinQi56PqwQopKu5BEk6Ypgx7kuXZFzzXUflHsyEv9J+k1GEfTuw1PmXJeu5HYgnnUmyKIDcSddKX+s1Q0Xez4ow4jgx+Bcf+mKqvugfP4nGINz9chVz4cVJ4kPhHJwTgX2fMgiSINzhdSaDc6plus4OKeUrrQsRLYHKhKIBchuY0EBYc/HQrDnQyyYPR9k5DTLck66sufUcXBOKV252xHNh068A2HPx8IsNNHs+RCJoswoDcqRh16D8yBJV+qvV657PqwC5hUQ9nwsBHs+xML0ka7UDM4BaCdd0XQfekpX8giSdKXiW4pzgNusMwWEPR8pPLYHlifEuRSvYs+HJ5IUKL0BsXTlZpUwdJSukkkdT8gtVwmbZM4SFns+PIE9H+z5sFyZUelKMpOPdyrKwTkV2PNhjxB7PlLBng+xMH3mFez5cH7RVaAHNj8G5yxdediBeNY0Qek7EPZ8OJ2QW64S7PkgBan8IUyePivl8z/BGJyrB3s+0r8s7QNhz4dHnlzvPnJduiKI9Lpcx8E5pXSlZSGyPVCRQCyAYhv2BYQ9H+le9WMH4lnZ80EKI80RMTnNspyTruw5dRycU0pX7nak4kMXh3UBYc/Hwiw00ez5EImizCgNypGHXoPzIElX6q8Xez7EeIQlLPZ8UCYQC2DpSoCQPR+EmcQDqaQreQRJulLxLcU5gPI6pRYQ9nyke1WOS/Eq9nx4IkmB0hsQS1duVglDR+kqmdTxhNxylRBMZmBhAWHPhyew54M9H5YrMypdSWby8U5FOTinAns+5EDyt/EmI0jSFXs+JBm8phFfzZ4PChZpZG5wztKVhx2IZ5XoPoD5BYQ9H04n5JarBHs+SEEqfwiTp89K+fxPMAbn6sGeD9kwI30Hwp4Pjzy53n3kunRFEOl1uY6Dc0rpSstCZHugIoFYAP024ozxAsKej3Sv+rED8azs+SCFkeaImJxmWc5JV/acOg7OKaUrdztS8aGzDwux5yMlC000ez5EolylYs+HE4IkXam/Xuz5kOWZ+52lhMWeD8oEYgEsXYkRBl26ouk+9JSu5BEk6UrFtxTnAFXS1Szon8Jiz4eSVez58ESSAqU3IJau3KwSho7SVTKp4wm55SrhUrqaRUoBYc+HGNjzwZ4Py5UZla4kM/l4p6IcnFOBPR+ySGX02IEESbpiz4ckg9c04qvZ80HBIo3MDc5ZuvKwA/GsHrsPYEEBYc+Hy+UqwZ4PUpDKH8Lk6bNSPv8TjMG5erDnQzbMekGigLDnwyNPrncfuS5dEUR6Xa7j4JxSutKyENkeqEggFuCHdDULlxIWS1cediCelT0fpDDSHBGT0yzLOenKnlPHwTmldOVuRyo+dHJhIUDTmz57PiTD2PORDpQjD70G50GSrtRfL/Z8yPKkXxBizwdlArEAlq7ECLNbuvLIleXSlTyCJF2p+JbiHOCndDULb09hsedDySr2fHgiSYHSG5CKwXkApCvlj7W64WLPB2UYAOkCwp4PsRdccElysudDEiq6j4xKV5KZfLxTUQ7OqcCeD1mIMUoUkCBJV+z5kGTwmkZ8NXs+KFikkbnBOUtXHnYgnlVB9wGD4K8y0VG6SiZ1PCG3XCXY80EKpfMKFdKVMII0OFcP9nzIholvQrCAsOdDLkHAu49cl64IIr0u13FwTildaVmIbA9UJBALyJR0NRsmUEBYuvKwA/Gs7PkghZHmiJicZlnOSVf2nDoOzimlK3c7UvGhc8k+L1jBv4kuD/Z8yIax5yMdKEceeg3OgyRdqb9e7PmQ5ZHfhEMBCVL3QZ1ALIClKzHC7JauPHJluXQljyBJVyq+pTgHZFq6moV4B8KeDyWr2PPhiSQFSm9AKgbnAZCuqHamo3SVTOp4Qm65SqiQriyQpoCw50PsBRdckpzs+ZCEiu4jo9KVZCYf71SUg3MqsOdDFu6rjU0BCZJ0xZ4PSQavacRXs+eDgkUamRucs3TlYQfiWRUPzudDaoiuo3SVTOp4Qm65SrDngxRK5xUqpCthBGlwrh7s+ZAN87YJiwLCng+5BAHvPnJduiKI9Lpcx8E5pXSlZSGyPVCRQCxAJ+lqFgsKCEtXHnYgnpU9H6Qw0hwRk9Msyznpyp5Tx8E5pXTlbkcqPnQu2R2CffeBsOdDNow9H+lAOfLQa3AeJOlK/fViz4csj/frZSCpgASp+6BOIBbA0pUYYXZLVx65sly6kkeQpCsV31KcA3SUrmZfsu5A2POhZBV7PjyRpEDpDUjF4DwA0hXVznSUrpJJHU/ILVcJFdKVIGYKCHs+xF5wwSXJyZ4PSajoPjIqXUlm8vFORTk4pwJ7PmRB130AQChY0hV7PiQZvKYRX82eDwoWaWRucM7SlYcdiGf1eXC+8CXbIbqO0lUyqeMJueUqwZ4PUiidV6iQroQRpMG5erDnQzaMfhPJBYQ9H9IrA9V95Lp0RRDpdbmOg3NK6UrLQmR7oCKBWIDu0tUs5gpIrktXcjsQz8qeD1IYaY6IyWmW5Zx0Zc+p4+CcUrpytyMVHzqX7C62otQHwp4P2TD2fKQD5chDr8F5kKQr9deLPR+yPN6vlx1DvIBkdfdBnUAsgKUrMcKgS1c03Yee0pU8giRdqfiW4hyQLdLVLELs+VCzij0fnkhSoPQGxNKVm1XC0FG6SiZ1PCG3XCVUSFceoETCYs+HLA97PoSgovvIqHQlmcnHOxXl4JwK7PmQhdruA5hXQPS75bPnQzSMPR/+I+jdh6fMuS5dye1APKvPg3MRnhCgp3SVTOp4Qm65SrDngxSk8ocwefqslM//BGNwrh7s+ZAN8+d6kUpY7PmQRZAG5wqpNRucUy3XcXBOKV1pWYhsD1QkEAvIRulqFqGclK7kdiCelT0fpDDSHBGT0yzLOenKnlPHwTmldOVuRyo+dC7ZPV/SOAFZB8KeD9kw9nykA+XIQ6/BeZCkK/XXiz0fsjzer5czw1yE7/+glBPY8yEWpo90xZ4PyURaSlfyCJJ0peJbinNANktXsyApIOz5UMDOng81YOnKzSph6ChdJZM6npBbrhIqpCvPSM7muYCw50OWhz0fQlDRfWRUupLM5ONdgXJwTgX2fMjC/+4D0EjCYs+HWBh7PvxH0LsPT5lzXbqS24F4Vp8H52I8qVGeCgh7PkjDiMCeD0sul18fKZ//CcbgXD3Y8yEblrnr5bqAsOdDFkEanCuk1mxwTrVcx8E5pXSlZSGyPVCRQCwgKNLV7MKMS1js+RALZs8HGTnNspyTruw5dRycU0pX7nak4kPnkt3zJbUncFVA2PMhG8aej3SgHHnoNTgPknSl/nqx50OWx/v1cmZI/wHKaAfCng+xMH2kK/Z8SCbSUrqSR5CkKxXfUpwDAiVdzYN0AWHPhwJ29nyoAUtXblYJQ0fpKpnU8YTccpVQIV15hvMHSKqAsOdDloc9H0JQ0X1kVLqSzOTjXYFycE4F9nzIIrOD8/nIiITFng+xMPZ8+I+gdx+eMue6dCW3A/GsPg/OxXjEooQLCHs+SMOIwJ4PSy6XXx8pn/8JxuBcPdjzIRuWwetl8X1CqICw50MWQRqcK6TWbHBOtVzHwTmldKVlIbI9UJFALCDI0tUsfJWw2PMhFsyeDzJymmU5J13Zc+o4OKeUrtztSMWHziW750sqJ3A5FhD2fMiGsecjHShHHnoNzoMkXam/Xuz5kOXxfr2cGeQ/QL51IOz5EAvTR7piz4dkIi2lK3kESbpS8S3FOSBQ0pUDV9oCwp4PBezs+VADlq7crBKGjtJVMqnjCbnlKqFCuvIM8cH5fNgWEPZ8yPKw50MIKrqPjEpXkpl8vCtQDs6pwJ4PWeg3OJ8P5RIWez7Ewtjz4T+C3n14ypzr0pXcDsSz+jw4lxuJy0dZFhD2fJCGEYE9H5ZcLr8+Uj7/E4zBuXqw50M2LIPXS7AZTSkg7PmQRZAG5wqpNRucUy3XcXBOKV1pWYhsD1QkEAvINelqFsokLPZ8iAWz54OMnGZZzklX9pw6Ds4ppSt3O1LxoXPJ7vmSehe4kgoIez5kw9jzkQ6UIw+9BudBkq7UXy/2fMjyeL9ezgw0HyAlHQh7PsTC9JGu2PMhmUhL6UoeQZKuVHxLcQ4IlHTlgitRQNjzoYCdPR9qwNKVm1XC0FG6SiZ1PCG3XCVUSFee4W1wPh8hgD0f7PlQRK2i+8iodCWZyce7AuXgnArs+ZBFdgzO54NUwmLPh1gYez78R9C7D0+Zc126ktuBeFafB+feR+KyUUCIPR+kYURgz4cll8uvj5TP/wRjcK4e7PmQDcvg9fLQjJJ1IOz5EAvTZ3CukFqzwTnVch0H55TSlZaFyPZARQKxAJau5kBSQNjzIRbMng8ycpplOSdd2XPqODinlK7c7UjFh84lu+dLSitdzULx34XFng85sOfDkiKjg/MgSVfqrxd7PmR5vF8vZwZ12qfnAsKeD7EwfaQr9nxIJtJSupJHkKQrFd9SnAMCJV0RcXkqIOz5cBvsnkB/6YoYLF25WSUMP6Qr0zRTfomTOp6QW64SC5LZvU+ve7K7htb5jJTXTNP0NDifjzyX60jBng/2fFiuzKh0JZnJxzsV5eCcCnbFIxaLIRqNJt3ADMOAYRgIhUIIhVK/wyovjgTdh2maiMViME0T4XA45f3HYjHEYrHE+0y9Pu66D9M0E9czZBiJ3LPnAaTsZ/ZnMHvdTZgwTLt9ycF1AWHPh1gYez78R9C7D0+ZfZauotEovvyNf0TMjCUyFkTyUFRchDu2bMQdWzclFRHl0pUjxKQr0zSx79BxvLbnIB65/y7ce9e2pNdjsRi+/d0f4tqNQXz6E8+gpLjYlktiK4jFYjh19jyefeE1GIaBj33wvWioq4VpmvjHf/0pevoG8I5HH8T2zRsAxAvLxMQkvvbt72Jyahq/8+Gn8Mbeg2i90I73PvkoNt62xtNV9T5EZ8+HR7Dnw5LL5ddHyud/gjE4V49032Lndx5rV61A86rlqK6uws3BW3jpjX04f7E9KXb2m/vst/vZ86aZKsOkO8Y8rqTzRvo8VucX7i8ajSIajSJmxmNMqy+ziT0DsdhMt5LgNJI6mIXvwU76ml1z/Exr/IugaeLoybPxt2UYWL9mFWACZ1svYpYiFovhYnsHJqamULdkMRZVVyA2s2fTND1/nlx1IOz5EAvTZ3CukFqzwTnVch0H55TSld+FyICBdzz2IAry8xGNRvHia3tw7HQLzl9sx9rVK+I37WgUnT29uHFjCOUVpWioq0VhQQFisRgud3QjP5KPxoaliMViuDpwDSOjY1haW4PiokKMT0ygp7cfxcWFqF28CGYshu6+fly/cROVZWVoqF+CSH4EZszE9RuDuDE4iCU1i9HdexUxM4bmlU0wjBCuX7+Jrr6rKCosQGP90njnYBiJwtHZ3YfBoSEsrV0Em/v8ApiYnp7GhUtXMDo2jqZl9agoL0M0GsXljm6EQgZWNTUmZKjeq/0YG59E3ZLFKC4uSmYy43vv7OpFVVU5hoZHcKb1Ah596G4UFhRg47o1eG3PAVzu6MLI6ChKiothmibOXbgEAwY2rm8mfkrOkC8g7PkQC2bPBxk5zbKck67sOf0YnC+ECRPmzE04FoshPz8CwEgcj4yM4se/eBE9fQPxDZpASUkRfv3JX0NdbQ1e230QA9dv4lO/+2Hk5YXx/MtvoruvHw/eewfu2bEFFy5dwbMvvI67d9yO6ooKPPfKLpxpvTiT3ETNoip86H3vQFFhAU6cOYe9B4+jcVkdOrt7kR+J4N9/tAEnzrbitd0HEIvF/7AUFRTg/e96G5bVL0E0GsUvXnoDp1vaACO+xZpF1Q4XM64X/+SXL6O3rx8mgEheBO95/BGsXrkcL+/aj4Hr1/HbH/p1LK1djOnpafzw2RcwMjqGP/idD6ewxWIxnDzTChMmtm5ch96rA2g5fwmnW9qwY8tGlJWWoLGhHu2d3TjbehHbN2/A1NQU2i51IBQysHHtmuSfndBPzg7x1YQ+EPZ8yMFHzwcxF+XIQ6/BeZCkK/XXS6p4mMCBI6ewa99h/PKlN3Do2GkYhoGVy5fBNE28uns/evoGsH7tKnz0g+/BIw/cidHRcfz8hdcwNTWNtauaEnLM2Pg4eq8OADBxpaMb0WgUbZeuAADWrGzCyZbzOHPuAtasaMTv/db78ZYHdqL/2g28sedQkuR0deAa3vbIfXjskfswODSEV3ftR3lZKX776ffiA+9+G6amp/DcK7sQjUZxsb0Dp1raUFVZjo8//T58+Kl3YmhkxOkKAYaByrJS/P7Hn8bb33I/Jqem8KvX9iAWi2Hz+jWACbS0XkQsFkNPXz9uDY9gxfJlKC0tTr6GponpaBSnWtpgGAY23rYat6+PF4Sjp1ricpRhYNO6ZgDA2dYLM/vuxOTkFFYsb0jhpIBUAWHPh1iYPtKVmsE5AO2kK5ruQ0/pSh76SFfxnAYMA9h7+Dj2HzmJlrbLCOeFcdf227FpfTNi0Shazl9GOBzG2x99AHVLanDn1tuxrH4JbtwcQm//AJpXNwGmiQuXOtDZ3YuYaaK8rBRdvX2YnJxCe0c3ystKUFe7GJ1dvQCAutoaXLsxiOqqCoTzwmjv6knsBwawaV0ztm/egI23rUFnV5yzrrYGQ8MjgGli8aIqDFy7gZHRMXR2XwUAbN+8AUtqFqGhbgnWr13l/N4N4P67d6CstBSbN9yGmupK3Boexq2hEWxc14xQKIQzbRcRjUbR0haXmjZvXJvCE4vFcPHSFQyNjKCxfgmKiwrR2FCH4uIC9PYNoLs3vr+1q5sQycvDla5eDN4aQsv5SwCAjeuSOSm6DxgSMxD2fLgNdk+gv3RFDJau3KwSRiakq/nZn37fO5AfiaCwoAAlJUXIj0QAAJNTU4jGoigtKUZ+JJIYJJeXlQLow+jYGBrrl6KyshyXO7oQiYQRMgzs3LEZL762F8dOncXo2DjuXBd/omt4ZBQAsP/oCYTC8e/IkUhe4lHWWRQXFSXey/DoGACg7VI7LnV0Ja5VYWEBxsbHMTYxDgAoKixMdDFFRckzCkuYQFFhQeKwqLgIxo1BTExMoKqyHKtXNKL1Yju6eq6ite0y8gvysXbVimSK+cNzAN29/fjad74HE8Dk5BRMmDh6sgX1S5egqLAQq1csx9nzF3G6pQ0X2jsQyc/DuuYVifdOVTyADPhA2PPBng/LlRmVriQz+fg1nnJwTgU3g1gDwNLaxSjIz085X1RYiKKCQoyOjuPa9ZuorIgPmeMyFbC4qgqhUAjNK5fjwNGTON16EfV1tVi7agVeen0v9h89BRgGbluzCqFQCGVlJQCAJ976AJpXN2F6Oor+azdQu6gqKXNRYQEMIwTARFlZCQwAWzetwyP33QXTNNHTN4CqynKUlhSjsqwMADAwcD3uw4CJgYHrju/bhInuvn6sbirE9HQUN2/eAgBUVJQhFArh9vXNaL1wGW/uP4zB4WFs27QekUjybdk0TQwPj+LS5Q5EInlYXl+X4I7FYmjv6MGZ1gt464PxYfqmdatx9vxF7DtyElPTU9h425qU604BA4IFhD0fYmH6zCvY8+H8oqtAD2x+DM71kq6AmWJjU3Bmz4bDYWy7fR32Hj6OH/38BWxavxYd3X24dmMQy5fVYUntYpimibWrV+Lg0VNxTb+xAaUlxahdvAhX+6+hpKQYy+qWwDAMbF7fjNPnLuD1vYcwHYviUnsnzrRexIa1q/HOtz08Y6gDQkYosccNa1fj9d2HcOLMeVSWl2N8cgK79x9FZWU5PvHM+7Fh3Rq8eeAoDh4/jbz8MCYnp9F68XKcy+Lqzs/x/Cu7cefWTejuvYrhkVGsalqG0pJ4kVuzqgklJUVo7+qJzzDWr0nhgmniVMt5mDCwoXk13vX4I4kiHo1G8U8/+H/o7unH2dYL2L55I1avWI7iokKMjY3DCCVLYqEZMyFm/y/300z+wUF2iM6eD49gz4cll8vug2ZPQRqcq4fsTSccjstNoTQ3LMMw4k9T3bEFI6Pj2LXvMK509mDzhma8/8nHEjHL6pegtLQEoVAIK5Y3IBwOY9WKRoRCIaxbvRLhcNxZvbKpEY8+sBNj4xP4xYtvoOX8ZTSvWoHHH7kv7n4Ph2AYIRihuf2UFBfjPU+8FUWF+Xh51z7s3n8UNYur8dSTjyEcDqO6sgLvfvwRRPIj2H3gGM5fasc9O7bO8KTeRvPCYYRCIRTk52PHlg3Ytf8wWi+2Y1n9Ejzx6EMAkHCTb1i7GoZhoKqiHI0NdZbX5/S5CwiF4gVm/nUMh8PYtmkDjJCB46dbYRgGIpEINt62GqFwCKUlxVi1YnmcB5hx/4cRMkJ2dT09FtQQ4+at4bS3Gqruw3fPh1QB8av7sIgSOyUBvbsPy5XiJ8UjJCpCxgfnFi9TSleZnX3Y8NgcRKNRDI+Oo7S4COFwWJ5r3slYLIZbwyMozM9H4bw5hN0qA/Gb+tDwCMLhUMI9Ph8x08TY+Jjla6nsczkmJqcwPTWFkpK5ddFoFNPT03jxjb04dqoF9+/cjofvu8v5vdlkc3FKAnOVYz5PWgmLPR9iwez5ICOnWZZz0pU9ZzYVDwAIh/NQUVbqjmsBQqEQKsvLpFYZhjEzvLdeFjIMweKRjIL8CAryI4lj0zRx7FQLLl7pxPmLl5GXlzfz14/IwnWJkc9hQeJyiM6eDzmw58OSIqOD8yBJV+qvF/87H7I8DvKrYWA6Oo3O7l7ULl6MB+/ZkVK4XPfgCn9UC6ltJSzlj+2ydOWSyyEHS1eC0FO6EkxnH53F3YfHdy5IYS1duUtmFyZdbVymE/sAqZCuZmE5RGfPh9tg9wT6S1fEYOnKzSph6Fg8kkkdT8gtVwnv9UAB/C0edlD6T9qy54M9H5YrMypdSWby8a5AOTinAmXxUF4cVXUfUvCr+6Bc6J46pYCw50MsTJ95hd7SFSWC3n14yqxIuqICpXRFsAPxrCq6D1XSlasoh9UOJPYdCHs+PII9H5ZcLr8+UirwwRicq4c/g3Mi6crHn5V9WAavl4pmVKCGJBUQqvuQ754PKWSw+8h16Yog0uvyjA/OVazI6u6DOoFYAEtXYoRO1IkCwp4PsWD2fJCR0yzLOenKnlPHwTmldOVuRyo+dC7ZPV9SfaSrWQgM0dnzIQcfPR/ENYRy5KHX4DxI0pX668WeD1ke79fLmcF/7VOE+v8DZZsxGKvWDhUAAAAASUVORK5CYII=</v>
+      </c>
+      <c r="E825" t="str">
+        <v>20-09-2026 08:32:24 pm</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="str">
+        <v>6aaff5866cd0b6ebbbbe8475</v>
+      </c>
+      <c r="B826" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C826" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D826" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E826" t="str">
+        <v>20-09-2026 08:32:30 pm</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="str">
+        <v>6aaff5a66cd0b6ebbbbe85c2</v>
+      </c>
+      <c r="B827" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C827" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D827" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E827" t="str">
+        <v>20-09-2026 08:33:02 pm</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="str">
+        <v>6aaff58d6cd0b6ebbbbe8591</v>
+      </c>
+      <c r="B828" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C828" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D828" t="str">
+        <v>Started Playing game and Debited "10" and Balance "60"</v>
+      </c>
+      <c r="E828" t="str">
+        <v>20-09-2026 08:32:37 pm</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="str">
+        <v>6aaff5a66cd0b6ebbbbe85c5</v>
+      </c>
+      <c r="B829" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C829" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D829" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E829" t="str">
+        <v>20-09-2026 08:33:02 pm</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="str">
+        <v>6aaff5fde709d2c1778f4b82</v>
+      </c>
+      <c r="B830" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C830" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D830" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E830" t="str">
+        <v>20-09-2026 08:34:29 pm</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="str">
+        <v>6aaff5e3e709d2c1778f4b51</v>
+      </c>
+      <c r="B831" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C831" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D831" t="str">
+        <v>Started Playing game and Debited "10" and Balance "50"</v>
+      </c>
+      <c r="E831" t="str">
+        <v>20-09-2026 08:34:03 pm</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="str">
+        <v>6aaff5fde709d2c1778f4b85</v>
+      </c>
+      <c r="B832" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C832" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D832" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E832" t="str">
+        <v>20-09-2026 08:34:29 pm</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="str">
+        <v>6aaff6472302aaa0245d03f5</v>
+      </c>
+      <c r="B833" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C833" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D833" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E833" t="str">
+        <v>20-09-2026 08:35:43 pm</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="str">
+        <v>6aaff62d2302aaa0245d03c3</v>
+      </c>
+      <c r="B834" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C834" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D834" t="str">
+        <v>Started Playing game and Debited "10" and Balance "40"</v>
+      </c>
+      <c r="E834" t="str">
+        <v>20-09-2026 08:35:17 pm</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="str">
+        <v>6aaff6472302aaa0245d03f7</v>
+      </c>
+      <c r="B835" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C835" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D835" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E835" t="str">
+        <v>20-09-2026 08:35:43 pm</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="str">
+        <v>6aaff69172ddae76ecda88bb</v>
+      </c>
+      <c r="B836" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C836" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D836" t="str">
+        <v>Started Playing game and Debited "10" and Balance "30"</v>
+      </c>
+      <c r="E836" t="str">
+        <v>20-09-2026 08:36:57 pm</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="str">
+        <v>6aaff6a472ddae76ecda890b</v>
+      </c>
+      <c r="B837" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C837" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D837" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aaff6a372ddae76ecda88fb , Question : How many times do the letters N, Q appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E837" t="str">
+        <v>20-09-2026 08:37:16 pm</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="str">
+        <v>6aaff6a172ddae76ecda88e7</v>
+      </c>
+      <c r="B838" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C838" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D838" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaff69372ddae76ecda88c6, Reward : 10, Qst No : 2 ,Question : How many times do the letters C, N appear in the paragraph?</v>
+      </c>
+      <c r="E838" t="str">
+        <v>20-09-2026 08:37:13 pm</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="str">
+        <v>6aaff6a472ddae76ecda890d</v>
+      </c>
+      <c r="B839" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C839" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D839" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6aaff6a372ddae76ecda88fb , Question : How many times do the letters N, Q appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E839" t="str">
+        <v>20-09-2026 08:37:16 pm</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="str">
+        <v>6aaff6b372ddae76ecda8944</v>
+      </c>
+      <c r="B840" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C840" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D840" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6aaff6b272ddae76ecda8934 , Question : How many times do the letters F, Z appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E840" t="str">
+        <v>20-09-2026 08:37:31 pm</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="str">
+        <v>6aaff6b072ddae76ecda8920</v>
+      </c>
+      <c r="B841" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C841" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D841" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaff6a372ddae76ecda88fb, Reward : 40, Qst No : 3 ,Question : How many times do the letters N, Q appear in the paragraph?</v>
+      </c>
+      <c r="E841" t="str">
+        <v>20-09-2026 08:37:28 pm</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="str">
+        <v>6aaff6b372ddae76ecda8946</v>
+      </c>
+      <c r="B842" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C842" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D842" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6aaff6b272ddae76ecda8934 , Question : How many times do the letters F, Z appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E842" t="str">
+        <v>20-09-2026 08:37:31 pm</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="str">
+        <v>6aaff6c072ddae76ecda897d</v>
+      </c>
+      <c r="B843" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C843" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D843" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6aaff6c072ddae76ecda896d , Question : How many times do the letters Z, D appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E843" t="str">
+        <v>20-09-2026 08:37:44 pm</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="str">
+        <v>6aaff6bd72ddae76ecda8959</v>
+      </c>
+      <c r="B844" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C844" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D844" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaff6b272ddae76ecda8934, Reward : 30, Qst No : 4 ,Question : How many times do the letters F, Z appear in the paragraph?</v>
+      </c>
+      <c r="E844" t="str">
+        <v>20-09-2026 08:37:41 pm</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="str">
+        <v>6aaff6c072ddae76ecda897f</v>
+      </c>
+      <c r="B845" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C845" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D845" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6aaff6c072ddae76ecda896d , Question : How many times do the letters Z, D appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E845" t="str">
+        <v>20-09-2026 08:37:44 pm</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="str">
+        <v>6aaff6cc72ddae76ecda8992</v>
+      </c>
+      <c r="B846" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C846" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D846" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaff6c072ddae76ecda896d, Reward : 40, Qst No : 5 ,Question : How many times do the letters Z, D appear in the paragraph?</v>
+      </c>
+      <c r="E846" t="str">
+        <v>20-09-2026 08:37:56 pm</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="str">
+        <v>6aaff6cf72ddae76ecda89b5</v>
+      </c>
+      <c r="B847" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C847" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D847" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6aaff6cf72ddae76ecda89a6 , Question : How many times do the letters J, F appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E847" t="str">
+        <v>20-09-2026 08:37:59 pm</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="str">
+        <v>6aaff6cf72ddae76ecda89b8</v>
+      </c>
+      <c r="B848" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C848" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D848" t="str">
+        <v xml:space="preserve">Created Question Number : 4, Rupees : 50, Qst ID : 6aaff6cf72ddae76ecda89a6 , Question : How many times do the letters J, F appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E848" t="str">
+        <v>20-09-2026 08:37:59 pm</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="str">
+        <v>6aaff6e572ddae76ecda89f3</v>
+      </c>
+      <c r="B849" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C849" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D849" t="str">
+        <v xml:space="preserve">Created Question Number : 5, Rupees : 80, Qst ID : 6aaff6e572ddae76ecda89e3 , Question : How many times do the letters W, B appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E849" t="str">
+        <v>20-09-2026 08:38:21 pm</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="str">
+        <v>6aaff6df72ddae76ecda89cb</v>
+      </c>
+      <c r="B850" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C850" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D850" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaff6cf72ddae76ecda89a6, Reward : 50, Qst No : 6 ,Question : How many times do the letters J, F appear in the paragraph?</v>
+      </c>
+      <c r="E850" t="str">
+        <v>20-09-2026 08:38:15 pm</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="str">
+        <v>6aaff6e572ddae76ecda89f5</v>
+      </c>
+      <c r="B851" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C851" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D851" t="str">
+        <v xml:space="preserve">Created Question Number : 5, Rupees : 80, Qst ID : 6aaff6e572ddae76ecda89e3 , Question : How many times do the letters W, B appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E851" t="str">
+        <v>20-09-2026 08:38:21 pm</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="str">
+        <v>6aaff6f672ddae76ecda8a30</v>
+      </c>
+      <c r="B852" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C852" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D852" t="str">
+        <v xml:space="preserve">Created Question Number : 6, Rupees : 110, Qst ID : 6aaff6f672ddae76ecda8a20 , Question : How many times do the letters H, J appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E852" t="str">
+        <v>20-09-2026 08:38:38 pm</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="str">
+        <v>6aaff6f072ddae76ecda8a08</v>
+      </c>
+      <c r="B853" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C853" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D853" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaff6e572ddae76ecda89e3, Reward : 80, Qst No : 7 ,Question : How many times do the letters W, B appear in the paragraph?</v>
+      </c>
+      <c r="E853" t="str">
+        <v>20-09-2026 08:38:32 pm</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="str">
+        <v>6aaff6f672ddae76ecda8a32</v>
+      </c>
+      <c r="B854" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C854" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D854" t="str">
+        <v xml:space="preserve">Created Question Number : 6, Rupees : 110, Qst ID : 6aaff6f672ddae76ecda8a20 , Question : How many times do the letters H, J appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E854" t="str">
+        <v>20-09-2026 08:38:38 pm</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="str">
+        <v>6aaff70a72ddae76ecda8a6d</v>
+      </c>
+      <c r="B855" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C855" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D855" t="str">
+        <v xml:space="preserve">Created Question Number : 7, Rupees : 140, Qst ID : 6aaff70a72ddae76ecda8a5d , Question : How many times do the letters L, R appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E855" t="str">
+        <v>20-09-2026 08:38:58 pm</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="str">
+        <v>6aaff70372ddae76ecda8a45</v>
+      </c>
+      <c r="B856" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C856" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D856" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaff6f672ddae76ecda8a20, Reward : 110, Qst No : 8 ,Question : How many times do the letters H, J appear in the paragraph?</v>
+      </c>
+      <c r="E856" t="str">
+        <v>20-09-2026 08:38:51 pm</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="str">
+        <v>6aaff70a72ddae76ecda8a6f</v>
+      </c>
+      <c r="B857" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C857" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D857" t="str">
+        <v xml:space="preserve">Created Question Number : 7, Rupees : 140, Qst ID : 6aaff70a72ddae76ecda8a5d , Question : How many times do the letters L, R appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E857" t="str">
+        <v>20-09-2026 08:38:58 pm</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="str">
+        <v>6aaff72372ddae76ecda8aaa</v>
+      </c>
+      <c r="B858" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C858" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D858" t="str">
+        <v xml:space="preserve">Created Question Number : 8, Rupees : 170, Qst ID : 6aaff72272ddae76ecda8a9a , Question : How many times do the letters F, D appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E858" t="str">
+        <v>20-09-2026 08:39:23 pm</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="str">
+        <v>6aaff71d72ddae76ecda8a82</v>
+      </c>
+      <c r="B859" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C859" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D859" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaff70a72ddae76ecda8a5d, Reward : 140, Qst No : 9 ,Question : How many times do the letters L, R appear in the paragraph?</v>
+      </c>
+      <c r="E859" t="str">
+        <v>20-09-2026 08:39:17 pm</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="str">
+        <v>6aaff72372ddae76ecda8aac</v>
+      </c>
+      <c r="B860" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C860" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D860" t="str">
+        <v xml:space="preserve">Created Question Number : 8, Rupees : 170, Qst ID : 6aaff72272ddae76ecda8a9a , Question : How many times do the letters F, D appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E860" t="str">
+        <v>20-09-2026 08:39:23 pm</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="str">
+        <v>6aaff73672ddae76ecda8ae7</v>
+      </c>
+      <c r="B861" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C861" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D861" t="str">
+        <v xml:space="preserve">Created Question Number : 9, Rupees : 200, Qst ID : 6aaff73672ddae76ecda8ad7 , Question : How many times do the letters P, J appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E861" t="str">
+        <v>20-09-2026 08:39:42 pm</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="str">
+        <v>6aaff73172ddae76ecda8abf</v>
+      </c>
+      <c r="B862" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C862" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D862" t="str">
+        <v>Answerd Correctly to Qst ID : 6aaff72272ddae76ecda8a9a, Reward : 170, Qst No : 10 ,Question : How many times do the letters F, D appear in the paragraph?</v>
+      </c>
+      <c r="E862" t="str">
+        <v>20-09-2026 08:39:37 pm</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="str">
+        <v>6aaff73672ddae76ecda8ae9</v>
+      </c>
+      <c r="B863" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C863" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D863" t="str">
+        <v xml:space="preserve">Created Question Number : 9, Rupees : 200, Qst ID : 6aaff73672ddae76ecda8ad7 , Question : How many times do the letters P, J appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E863" t="str">
+        <v>20-09-2026 08:39:42 pm</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="str">
+        <v>6aaff84072ddae76ecda8b30</v>
+      </c>
+      <c r="B864" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C864" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D864" t="str">
+        <v>Payment Request Sent, Amount: ₹20₹</v>
+      </c>
+      <c r="E864" t="str">
+        <v>20-09-2026 08:44:08 pm</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="str">
+        <v>6aaff84e72ddae76ecda8b3e</v>
+      </c>
+      <c r="B865" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C865" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D865" t="str">
+        <v>Payment Request Sent, Amount: ₹20₹</v>
+      </c>
+      <c r="E865" t="str">
+        <v>20-09-2026 08:44:22 pm</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="str">
+        <v>6aaff95872ddae76ecda8b54</v>
+      </c>
+      <c r="B866" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C866" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D866" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E866" t="str">
+        <v>20-09-2026 08:48:48 pm</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="str">
+        <v>6aaff95872ddae76ecda8b58</v>
+      </c>
+      <c r="B867" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C867" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D867" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E867" t="str">
+        <v>20-09-2026 08:48:48 pm</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="str">
+        <v>6aaff95d72ddae76ecda8c78</v>
+      </c>
+      <c r="B868" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C868" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D868" t="str">
+        <v>Started Playing game and Debited "10" and Balance "20"</v>
+      </c>
+      <c r="E868" t="str">
+        <v>20-09-2026 08:48:53 pm</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="str">
+        <v>6aaff97672ddae76ecda8cac</v>
+      </c>
+      <c r="B869" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C869" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D869" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E869" t="str">
+        <v>20-09-2026 08:49:18 pm</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="str">
+        <v>6aaff95e72ddae76ecda8c7e</v>
+      </c>
+      <c r="B870" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C870" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D870" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E870" t="str">
+        <v>20-09-2026 08:48:54 pm</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="str">
+        <v>6aaff97672ddae76ecda8cae</v>
+      </c>
+      <c r="B871" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C871" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D871" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E871" t="str">
+        <v>20-09-2026 08:49:18 pm</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="str">
+        <v>6aafff4885167c5cbad91904</v>
+      </c>
+      <c r="B872" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C872" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D872" t="str">
+        <v>Started Playing game and Debited "10" and Balance "10"</v>
+      </c>
+      <c r="E872" t="str">
+        <v>20-09-2026 09:14:08 pm</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="str">
+        <v>6aafff5785167c5cbad91934</v>
+      </c>
+      <c r="B873" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C873" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D873" t="str">
+        <v>Answerd Correctly to Qst ID : 6aafff4a85167c5cbad91916, Reward : 10, Qst No : 2 ,Question : How many times do the letters Q, F appear in the paragraph?</v>
+      </c>
+      <c r="E873" t="str">
+        <v>20-09-2026 09:14:23 pm</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="str">
+        <v>6ab087321e53c09ddd129690</v>
+      </c>
+      <c r="B874" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C874" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D874" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E874" t="str">
+        <v>21-09-2026 06:54:02 am</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="str">
+        <v>6ab087331e53c09ddd129697</v>
+      </c>
+      <c r="B875" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C875" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D875" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E875" t="str">
+        <v>21-09-2026 06:54:03 am</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="str">
+        <v>6ab087451e53c09ddd1297b7</v>
+      </c>
+      <c r="B876" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C876" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D876" t="str">
+        <v>Started Playing game and Debited "10" and Balance "0"</v>
+      </c>
+      <c r="E876" t="str">
+        <v>21-09-2026 06:54:21 am</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="str">
+        <v>6ab087461e53c09ddd1297bd</v>
+      </c>
+      <c r="B877" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C877" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D877" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E877" t="str">
+        <v>21-09-2026 06:54:22 am</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="str">
+        <v>6ab0878f1e53c09ddd12981f</v>
+      </c>
+      <c r="B878" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C878" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D878" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab0878e1e53c09ddd129811 , Question : How many times does the letter sequence 'fun' appear in the given words?, Type :  </v>
+      </c>
+      <c r="E878" t="str">
+        <v>21-09-2026 06:55:35 am</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="str">
+        <v>6ab087711e53c09ddd1297fb</v>
+      </c>
+      <c r="B879" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C879" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D879" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab087481e53c09ddd1297da, Reward : 10, Qst No : 2 ,Question : How many times does the letter sequence 'fly' appear in the given words?</v>
+      </c>
+      <c r="E879" t="str">
+        <v>21-09-2026 06:55:05 am</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="str">
+        <v>6ab0878f1e53c09ddd129821</v>
+      </c>
+      <c r="B880" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C880" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D880" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab0878e1e53c09ddd129811 , Question : How many times does the letter sequence 'fun' appear in the given words?, Type :  </v>
+      </c>
+      <c r="E880" t="str">
+        <v>21-09-2026 06:55:35 am</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="str">
+        <v>6ab087aa1e53c09ddd129847</v>
+      </c>
+      <c r="B881" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C881" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D881" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E881" t="str">
+        <v>21-09-2026 06:56:02 am</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="str">
+        <v>6ab087aa1e53c09ddd12984f</v>
+      </c>
+      <c r="B882" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C882" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D882" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E882" t="str">
+        <v>21-09-2026 06:56:02 am</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="str">
+        <v>6ab08e832210846610faf34f</v>
+      </c>
+      <c r="B883" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C883" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D883" t="str">
+        <v>Started Playing game and Debited "10" and Balance "990"</v>
+      </c>
+      <c r="E883" t="str">
+        <v>21-09-2026 07:25:15 am</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="str">
+        <v>6ab08e9c2210846610faf3b1</v>
+      </c>
+      <c r="B884" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C884" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D884" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab08e9b2210846610faf3a1 , Question : What is the alphabetical arrangement of these random letters: "kol"?, Type :  </v>
+      </c>
+      <c r="E884" t="str">
+        <v>21-09-2026 07:25:40 am</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="str">
+        <v>6ab08e972210846610faf38d</v>
+      </c>
+      <c r="B885" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C885" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D885" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab08e852210846610faf36c, Reward : 10, Qst No : 2 ,Question : What is the alphabetical arrangement of these random letters: "fj"?</v>
+      </c>
+      <c r="E885" t="str">
+        <v>21-09-2026 07:25:35 am</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="str">
+        <v>6ab08e9c2210846610faf3b3</v>
+      </c>
+      <c r="B886" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C886" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D886" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab08e9b2210846610faf3a1 , Question : What is the alphabetical arrangement of these random letters: "kol"?, Type :  </v>
+      </c>
+      <c r="E886" t="str">
+        <v>21-09-2026 07:25:40 am</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E815"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E886"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E886"/>
+  <dimension ref="A1:E900"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15461,9 +15461,247 @@
         <v>21-09-2026 07:25:40 am</v>
       </c>
     </row>
+    <row r="887">
+      <c r="A887" t="str">
+        <v>6ab08eab2210846610faf3c6</v>
+      </c>
+      <c r="B887" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C887" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D887" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab08e9b2210846610faf3a1, Reward : 40, Qst No : 3 ,Question : What is the alphabetical arrangement of these random letters: "kol"?</v>
+      </c>
+      <c r="E887" t="str">
+        <v>21-09-2026 07:25:55 am</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="str">
+        <v>6ab10cb9a6eb8ad793c02e48</v>
+      </c>
+      <c r="B888" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C888" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D888" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E888" t="str">
+        <v>21-09-2026 04:23:45 pm</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="str">
+        <v>6ab10cb9a6eb8ad793c02e4f</v>
+      </c>
+      <c r="B889" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C889" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D889" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E889" t="str">
+        <v>21-09-2026 04:23:45 pm</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="str">
+        <v>6ab10cc3a6eb8ad793c02f71</v>
+      </c>
+      <c r="B890" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C890" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D890" t="str">
+        <v>Started Playing game and Debited "10" and Balance "980"</v>
+      </c>
+      <c r="E890" t="str">
+        <v>21-09-2026 04:23:55 pm</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="str">
+        <v>6ab10cd7a6eb8ad793c02fa1</v>
+      </c>
+      <c r="B891" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C891" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D891" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E891" t="str">
+        <v>21-09-2026 04:24:15 pm</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="str">
+        <v>6ab10cc4a6eb8ad793c02f77</v>
+      </c>
+      <c r="B892" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C892" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D892" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E892" t="str">
+        <v>21-09-2026 04:23:56 pm</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="str">
+        <v>6ab10cd7a6eb8ad793c02fa3</v>
+      </c>
+      <c r="B893" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C893" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D893" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E893" t="str">
+        <v>21-09-2026 04:24:15 pm</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="str">
+        <v>6ab10cdfa6eb8ad793c030c8</v>
+      </c>
+      <c r="B894" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C894" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D894" t="str">
+        <v>Started Playing game and Debited "10" and Balance "970"</v>
+      </c>
+      <c r="E894" t="str">
+        <v>21-09-2026 04:24:23 pm</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="str">
+        <v>6ab10ce0a6eb8ad793c030ce</v>
+      </c>
+      <c r="B895" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C895" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D895" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E895" t="str">
+        <v>21-09-2026 04:24:24 pm</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="str">
+        <v>6ab10d1da6eb8ad793c0311e</v>
+      </c>
+      <c r="B896" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C896" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D896" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab10ce1a6eb8ad793c03100, Reward : 10, Qst No : 2 ,Question : Decode "VG" using cipher key</v>
+      </c>
+      <c r="E896" t="str">
+        <v>21-09-2026 04:25:25 pm</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="str">
+        <v>6ab1144c8fc177cd47e17d98</v>
+      </c>
+      <c r="B897" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C897" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D897" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab1144b8fc177cd47e17d90 , Question : Decode "JHL" using cipher key, Type :  </v>
+      </c>
+      <c r="E897" t="str">
+        <v>21-09-2026 04:56:04 pm</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="str">
+        <v>6ab114528fc177cd47e17dad</v>
+      </c>
+      <c r="B898" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C898" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D898" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E898" t="str">
+        <v>21-09-2026 04:56:10 pm</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="str">
+        <v>6ab114538fc177cd47e17db4</v>
+      </c>
+      <c r="B899" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C899" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D899" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E899" t="str">
+        <v>21-09-2026 04:56:11 pm</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="str">
+        <v>6ab1145a8fc177cd47e17ed7</v>
+      </c>
+      <c r="B900" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C900" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D900" t="str">
+        <v>Started Playing game and Debited "10" and Balance "960"</v>
+      </c>
+      <c r="E900" t="str">
+        <v>21-09-2026 04:56:18 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E886"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E900"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E900"/>
+  <dimension ref="A1:E937"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15699,9 +15699,638 @@
         <v>21-09-2026 04:56:18 pm</v>
       </c>
     </row>
+    <row r="901">
+      <c r="A901" t="str">
+        <v>6ab1146c8fc177cd47e17f25</v>
+      </c>
+      <c r="B901" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C901" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D901" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab1145c8fc177cd47e17f07, Reward : 10, Qst No : 2 ,Question : Decode "ZK" using cipher key</v>
+      </c>
+      <c r="E901" t="str">
+        <v>21-09-2026 04:56:36 pm</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="str">
+        <v>6ab15032880c2005162d2e5c</v>
+      </c>
+      <c r="B902" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C902" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D902" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E902" t="str">
+        <v>21-09-2026 09:11:38 pm</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="str">
+        <v>6ab15033880c2005162d2e62</v>
+      </c>
+      <c r="B903" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C903" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D903" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E903" t="str">
+        <v>21-09-2026 09:11:39 pm</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="str">
+        <v>6ab1503d880c2005162d2f87</v>
+      </c>
+      <c r="B904" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C904" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D904" t="str">
+        <v>Started Playing game and Debited "10" and Balance "950"</v>
+      </c>
+      <c r="E904" t="str">
+        <v>21-09-2026 09:11:49 pm</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="str">
+        <v>6ab1503d880c2005162d2f8d</v>
+      </c>
+      <c r="B905" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C905" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D905" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E905" t="str">
+        <v>21-09-2026 09:11:49 pm</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="str">
+        <v>6ab15071b7b22755f3779e87</v>
+      </c>
+      <c r="B906" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C906" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D906" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E906" t="str">
+        <v>21-09-2026 09:12:41 pm</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="str">
+        <v>6ab15071b7b22755f3779e89</v>
+      </c>
+      <c r="B907" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C907" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D907" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E907" t="str">
+        <v>21-09-2026 09:12:41 pm</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="str">
+        <v>6ab1507bb7b22755f3779fb1</v>
+      </c>
+      <c r="B908" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C908" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D908" t="str">
+        <v>Started Playing game and Debited "10" and Balance "940"</v>
+      </c>
+      <c r="E908" t="str">
+        <v>21-09-2026 09:12:51 pm</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="str">
+        <v>6ab150a0b7b22755f377a004</v>
+      </c>
+      <c r="B909" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C909" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D909" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab1509fb7b22755f3779ff4 , Question : Arrange these letters based on the alphabet series:, Type :  </v>
+      </c>
+      <c r="E909" t="str">
+        <v>21-09-2026 09:13:28 pm</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="str">
+        <v>6ab1509ab7b22755f3779fe1</v>
+      </c>
+      <c r="B910" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C910" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D910" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab1507db7b22755f3779fc3, Reward : 10, Qst No : 2 ,Question : Arrange these letters based on the alphabet series:</v>
+      </c>
+      <c r="E910" t="str">
+        <v>21-09-2026 09:13:22 pm</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="str">
+        <v>6ab150a0b7b22755f377a006</v>
+      </c>
+      <c r="B911" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C911" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D911" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab1509fb7b22755f3779ff4 , Question : Arrange these letters based on the alphabet series:, Type :  </v>
+      </c>
+      <c r="E911" t="str">
+        <v>21-09-2026 09:13:28 pm</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="str">
+        <v>6ab150aab7b22755f377a03d</v>
+      </c>
+      <c r="B912" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C912" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D912" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6ab150a9b7b22755f377a02d , Question : Arrange these letters based on the alphabet series:, Type :  </v>
+      </c>
+      <c r="E912" t="str">
+        <v>21-09-2026 09:13:38 pm</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="str">
+        <v>6ab150a5b7b22755f377a019</v>
+      </c>
+      <c r="B913" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C913" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D913" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab1509fb7b22755f3779ff4, Reward : 40, Qst No : 3 ,Question : Arrange these letters based on the alphabet series:</v>
+      </c>
+      <c r="E913" t="str">
+        <v>21-09-2026 09:13:33 pm</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="str">
+        <v>6ab150aab7b22755f377a03f</v>
+      </c>
+      <c r="B914" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C914" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D914" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6ab150a9b7b22755f377a02d , Question : Arrange these letters based on the alphabet series:, Type :  </v>
+      </c>
+      <c r="E914" t="str">
+        <v>21-09-2026 09:13:38 pm</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="str">
+        <v>6ab1e897b7b22755f377a077</v>
+      </c>
+      <c r="B915" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C915" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D915" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6ab1e897b7b22755f377a067 , Question : Arrange these letters based on the alphabet series:, Type :  </v>
+      </c>
+      <c r="E915" t="str">
+        <v>22-09-2026 08:01:51 am</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="str">
+        <v>6ab150b7b7b22755f377a052</v>
+      </c>
+      <c r="B916" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C916" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D916" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab150a9b7b22755f377a02d, Reward : 30, Qst No : 4 ,Question : Arrange these letters based on the alphabet series:</v>
+      </c>
+      <c r="E916" t="str">
+        <v>21-09-2026 09:13:51 pm</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="str">
+        <v>6ab1e897b7b22755f377a079</v>
+      </c>
+      <c r="B917" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C917" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D917" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6ab1e897b7b22755f377a067 , Question : Arrange these letters based on the alphabet series:, Type :  </v>
+      </c>
+      <c r="E917" t="str">
+        <v>22-09-2026 08:01:51 am</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="str">
+        <v>6ab1e8a6b7b22755f377a08c</v>
+      </c>
+      <c r="B918" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C918" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D918" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab1e897b7b22755f377a067, Reward : 40, Qst No : 5 ,Question : Arrange these letters based on the alphabet series:</v>
+      </c>
+      <c r="E918" t="str">
+        <v>22-09-2026 08:02:06 am</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="str">
+        <v>6ab1f8e496e1b53d01b024ee</v>
+      </c>
+      <c r="B919" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C919" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D919" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E919" t="str">
+        <v>22-09-2026 09:11:24 am</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="str">
+        <v>6ab1f8e596e1b53d01b024f4</v>
+      </c>
+      <c r="B920" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C920" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D920" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E920" t="str">
+        <v>22-09-2026 09:11:25 am</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="str">
+        <v>6ab1f91796e1b53d01b0265a</v>
+      </c>
+      <c r="B921" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C921" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D921" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E921" t="str">
+        <v>22-09-2026 09:12:15 am</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="str">
+        <v>6ab1f8f096e1b53d01b0261b</v>
+      </c>
+      <c r="B922" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C922" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D922" t="str">
+        <v>Started Playing game and Debited "10" and Balance "930"</v>
+      </c>
+      <c r="E922" t="str">
+        <v>22-09-2026 09:11:36 am</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="str">
+        <v>6ab1f91796e1b53d01b0265d</v>
+      </c>
+      <c r="B923" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C923" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D923" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E923" t="str">
+        <v>22-09-2026 09:12:15 am</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="str">
+        <v>6ab22336afdc9c28501de3c9</v>
+      </c>
+      <c r="B924" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C924" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D924" t="str">
+        <v xml:space="preserve">Created Question Number : 0, Rupees : 10, Qst ID : 6ab22335afdc9c28501de3b9 , Question : How many words have the correct ratio when grouped by 2 letters?, Type :  </v>
+      </c>
+      <c r="E924" t="str">
+        <v>22-09-2026 12:11:58 pm</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="str">
+        <v>6ab22234d402a55847dc4a76</v>
+      </c>
+      <c r="B925" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C925" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D925" t="str">
+        <v>Started Playing game and Debited "10" and Balance "920"</v>
+      </c>
+      <c r="E925" t="str">
+        <v>22-09-2026 12:07:40 pm</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="str">
+        <v>6ab2233cafdc9c28501de3e4</v>
+      </c>
+      <c r="B926" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C926" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D926" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E926" t="str">
+        <v>22-09-2026 12:12:04 pm</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="str">
+        <v>6ab22336afdc9c28501de3cb</v>
+      </c>
+      <c r="B927" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C927" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D927" t="str">
+        <v xml:space="preserve">Created Question Number : 0, Rupees : 10, Qst ID : 6ab22335afdc9c28501de3b9 , Question : How many words have the correct ratio when grouped by 2 letters?, Type :  </v>
+      </c>
+      <c r="E927" t="str">
+        <v>22-09-2026 12:11:58 pm</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="str">
+        <v>6ab2233cafdc9c28501de3e6</v>
+      </c>
+      <c r="B928" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C928" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D928" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E928" t="str">
+        <v>22-09-2026 12:12:04 pm</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="str">
+        <v>6ab22348afdc9c28501de511</v>
+      </c>
+      <c r="B929" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C929" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D929" t="str">
+        <v>Started Playing game and Debited "10" and Balance "910"</v>
+      </c>
+      <c r="E929" t="str">
+        <v>22-09-2026 12:12:16 pm</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="str">
+        <v>6ab2235dafdc9c28501de541</v>
+      </c>
+      <c r="B930" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C930" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D930" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab2234aafdc9c28501de523, Reward : 10, Qst No : 2 ,Question : How many words have the correct ratio when grouped by 2 letters?</v>
+      </c>
+      <c r="E930" t="str">
+        <v>22-09-2026 12:12:37 pm</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="str">
+        <v>6ab234a4afdc9c28501de558</v>
+      </c>
+      <c r="B931" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C931" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D931" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab234a3afdc9c28501de550 , Question : How many words have the correct ratio when grouped by 2 letters?, Type :  </v>
+      </c>
+      <c r="E931" t="str">
+        <v>22-09-2026 01:26:20 pm</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="str">
+        <v>6ab234b3afdc9c28501de591</v>
+      </c>
+      <c r="B932" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C932" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D932" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6ab234b2afdc9c28501de581 , Question : How many words have the correct ratio when grouped by 2 letters?, Type :  </v>
+      </c>
+      <c r="E932" t="str">
+        <v>22-09-2026 01:26:35 pm</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="str">
+        <v>6ab234afafdc9c28501de56d</v>
+      </c>
+      <c r="B933" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C933" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D933" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab234a3afdc9c28501de550, Reward : 40, Qst No : 3 ,Question : How many words have the correct ratio when grouped by 2 letters?</v>
+      </c>
+      <c r="E933" t="str">
+        <v>22-09-2026 01:26:31 pm</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="str">
+        <v>6ab234b3afdc9c28501de593</v>
+      </c>
+      <c r="B934" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C934" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D934" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6ab234b2afdc9c28501de581 , Question : How many words have the correct ratio when grouped by 2 letters?, Type :  </v>
+      </c>
+      <c r="E934" t="str">
+        <v>22-09-2026 01:26:35 pm</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="str">
+        <v>6ab234c1afdc9c28501de5ca</v>
+      </c>
+      <c r="B935" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C935" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D935" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6ab234c0afdc9c28501de5ba , Question : How many words have the correct ratio when grouped by 2 letters?, Type :  </v>
+      </c>
+      <c r="E935" t="str">
+        <v>22-09-2026 01:26:49 pm</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="str">
+        <v>6ab234bcafdc9c28501de5a6</v>
+      </c>
+      <c r="B936" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C936" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D936" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab234b2afdc9c28501de581, Reward : 30, Qst No : 4 ,Question : How many words have the correct ratio when grouped by 2 letters?</v>
+      </c>
+      <c r="E936" t="str">
+        <v>22-09-2026 01:26:44 pm</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="str">
+        <v>6ab234c1afdc9c28501de5cc</v>
+      </c>
+      <c r="B937" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C937" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D937" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6ab234c0afdc9c28501de5ba , Question : How many words have the correct ratio when grouped by 2 letters?, Type :  </v>
+      </c>
+      <c r="E937" t="str">
+        <v>22-09-2026 01:26:49 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E900"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E937"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E937"/>
+  <dimension ref="A1:E957"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16328,9 +16328,349 @@
         <v>22-09-2026 01:26:49 pm</v>
       </c>
     </row>
+    <row r="938">
+      <c r="A938" t="str">
+        <v>6ab234cfafdc9c28501de5df</v>
+      </c>
+      <c r="B938" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C938" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D938" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab234c0afdc9c28501de5ba, Reward : 40, Qst No : 5 ,Question : How many words have the correct ratio when grouped by 2 letters?</v>
+      </c>
+      <c r="E938" t="str">
+        <v>22-09-2026 01:27:03 pm</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="str">
+        <v>6ab27252d8c7f60839bb4514</v>
+      </c>
+      <c r="B939" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C939" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D939" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E939" t="str">
+        <v>22-09-2026 05:49:30 pm</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="str">
+        <v>6ab27253d8c7f60839bb451d</v>
+      </c>
+      <c r="B940" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C940" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D940" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E940" t="str">
+        <v>22-09-2026 05:49:31 pm</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="str">
+        <v>6ab2725ad8c7f60839bb4645</v>
+      </c>
+      <c r="B941" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C941" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D941" t="str">
+        <v>Started Playing game and Debited "10" and Balance "900"</v>
+      </c>
+      <c r="E941" t="str">
+        <v>22-09-2026 05:49:38 pm</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="str">
+        <v>6ab2725ad8c7f60839bb464b</v>
+      </c>
+      <c r="B942" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C942" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D942" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E942" t="str">
+        <v>22-09-2026 05:49:38 pm</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="str">
+        <v>6ab276b4d8c7f60839bb469c</v>
+      </c>
+      <c r="B943" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C943" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D943" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E943" t="str">
+        <v>22-09-2026 06:08:12 pm</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="str">
+        <v>6ab276b5d8c7f60839bb46a2</v>
+      </c>
+      <c r="B944" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C944" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D944" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E944" t="str">
+        <v>22-09-2026 06:08:13 pm</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="str">
+        <v>6ab278ef5ef74336414811c9</v>
+      </c>
+      <c r="B945" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C945" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D945" t="str">
+        <v>Started Playing game and Debited "10" and Balance "890"</v>
+      </c>
+      <c r="E945" t="str">
+        <v>22-09-2026 06:17:43 pm</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="str">
+        <v>6ab278f05ef74336414811cf</v>
+      </c>
+      <c r="B946" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C946" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D946" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E946" t="str">
+        <v>22-09-2026 06:17:44 pm</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="str">
+        <v>6ab279205ef7433641481241</v>
+      </c>
+      <c r="B947" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C947" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D947" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab2791f5ef7433641481231 , Question : How many words have the correct ratio when grouped by 2 letters?, Type :  </v>
+      </c>
+      <c r="E947" t="str">
+        <v>22-09-2026 06:18:32 pm</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="str">
+        <v>6ab2791b5ef743364148121d</v>
+      </c>
+      <c r="B948" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C948" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D948" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab278f25ef74336414811ff, Reward : 10, Qst No : 2 ,Question : Decode "NN" using cipher key</v>
+      </c>
+      <c r="E948" t="str">
+        <v>22-09-2026 06:18:27 pm</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="str">
+        <v>6ab279205ef7433641481243</v>
+      </c>
+      <c r="B949" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C949" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D949" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab2791f5ef7433641481231 , Question : How many words have the correct ratio when grouped by 2 letters?, Type :  </v>
+      </c>
+      <c r="E949" t="str">
+        <v>22-09-2026 06:18:32 pm</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="str">
+        <v>6ab279325ef743364148127a</v>
+      </c>
+      <c r="B950" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C950" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D950" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6ab279315ef743364148126a , Question : What is the alphabetical arrangement of these random letters: "emba"?, Type :  </v>
+      </c>
+      <c r="E950" t="str">
+        <v>22-09-2026 06:18:50 pm</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="str">
+        <v>6ab2792d5ef7433641481256</v>
+      </c>
+      <c r="B951" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C951" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D951" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab2791f5ef7433641481231, Reward : 40, Qst No : 3 ,Question : How many words have the correct ratio when grouped by 2 letters?</v>
+      </c>
+      <c r="E951" t="str">
+        <v>22-09-2026 06:18:45 pm</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="str">
+        <v>6ab279325ef743364148127c</v>
+      </c>
+      <c r="B952" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C952" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D952" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6ab279315ef743364148126a , Question : What is the alphabetical arrangement of these random letters: "emba"?, Type :  </v>
+      </c>
+      <c r="E952" t="str">
+        <v>22-09-2026 06:18:50 pm</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="str">
+        <v>6ab2794a5ef74336414812b3</v>
+      </c>
+      <c r="B953" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C953" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D953" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6ab279495ef74336414812a3 , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E953" t="str">
+        <v>22-09-2026 06:19:14 pm</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="str">
+        <v>6ab279455ef743364148128f</v>
+      </c>
+      <c r="B954" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C954" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D954" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab279315ef743364148126a, Reward : 30, Qst No : 4 ,Question : What is the alphabetical arrangement of these random letters: "emba"?</v>
+      </c>
+      <c r="E954" t="str">
+        <v>22-09-2026 06:19:09 pm</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="str">
+        <v>6ab2795a5ef74336414812ce</v>
+      </c>
+      <c r="B955" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C955" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D955" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E955" t="str">
+        <v>22-09-2026 06:19:30 pm</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="str">
+        <v>6ab2794a5ef74336414812b5</v>
+      </c>
+      <c r="B956" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C956" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D956" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6ab279495ef74336414812a3 , Question : How many boxes are unbroken in total?, Type : Total Boxes [Comp] </v>
+      </c>
+      <c r="E956" t="str">
+        <v>22-09-2026 06:19:14 pm</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="str">
+        <v>6ab2795a5ef74336414812d0</v>
+      </c>
+      <c r="B957" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C957" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D957" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E957" t="str">
+        <v>22-09-2026 06:19:30 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E937"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E957"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E957"/>
+  <dimension ref="A1:E965"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16668,9 +16668,145 @@
         <v>22-09-2026 06:19:30 pm</v>
       </c>
     </row>
+    <row r="958">
+      <c r="A958" t="str">
+        <v>6ab2797c5ef74336414813fe</v>
+      </c>
+      <c r="B958" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C958" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D958" t="str">
+        <v>Started Playing game and Debited "10" and Balance "880"</v>
+      </c>
+      <c r="E958" t="str">
+        <v>22-09-2026 06:20:04 pm</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="str">
+        <v>6ab2aca3427da79cc03127fa</v>
+      </c>
+      <c r="B959" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C959" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D959" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E959" t="str">
+        <v>22-09-2026 09:58:19 pm</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="str">
+        <v>6ab2aca4427da79cc0312801</v>
+      </c>
+      <c r="B960" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C960" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D960" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E960" t="str">
+        <v>22-09-2026 09:58:20 pm</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="str">
+        <v>6ab2b1bcb4ee6e3293a61346</v>
+      </c>
+      <c r="B961" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C961" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D961" t="str">
+        <v>Started Playing game and Debited "10" and Balance "870"</v>
+      </c>
+      <c r="E961" t="str">
+        <v>22-09-2026 10:20:04 pm</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="str">
+        <v>6ab2b1bcb4ee6e3293a6134c</v>
+      </c>
+      <c r="B962" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C962" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D962" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E962" t="str">
+        <v>22-09-2026 10:20:04 pm</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="str">
+        <v>6ab2b8195e1ec027a5c56ad1</v>
+      </c>
+      <c r="B963" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C963" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D963" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E963" t="str">
+        <v>22-09-2026 10:47:13 pm</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="str">
+        <v>6ab2b81a5e1ec027a5c56ad7</v>
+      </c>
+      <c r="B964" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C964" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D964" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E964" t="str">
+        <v>22-09-2026 10:47:14 pm</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="str">
+        <v>6ab2b8225e1ec027a5c56c05</v>
+      </c>
+      <c r="B965" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C965" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D965" t="str">
+        <v>Started Playing game and Debited "10" and Balance "860"</v>
+      </c>
+      <c r="E965" t="str">
+        <v>22-09-2026 10:47:22 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E957"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E965"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E965"/>
+  <dimension ref="A1:E989"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16804,9 +16804,417 @@
         <v>22-09-2026 10:47:22 pm</v>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" t="str">
+        <v>6ab329c01995f3c9fbbd78e6</v>
+      </c>
+      <c r="B966" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C966" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D966" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E966" t="str">
+        <v>23-09-2026 06:52:08 am</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="str">
+        <v>6ab329cd1995f3c9fbbd7a17</v>
+      </c>
+      <c r="B967" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C967" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D967" t="str">
+        <v>Started Playing game and Debited "10" and Balance "850"</v>
+      </c>
+      <c r="E967" t="str">
+        <v>23-09-2026 06:52:21 am</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="str">
+        <v>6ab32bb71995f3c9fbbd7a3d</v>
+      </c>
+      <c r="B968" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C968" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D968" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E968" t="str">
+        <v>23-09-2026 07:00:31 am</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="str">
+        <v>6ab32bb81995f3c9fbbd7a45</v>
+      </c>
+      <c r="B969" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C969" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D969" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E969" t="str">
+        <v>23-09-2026 07:00:32 am</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="str">
+        <v>6ab32bc01995f3c9fbbd7b75</v>
+      </c>
+      <c r="B970" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C970" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D970" t="str">
+        <v>Started Playing game and Debited "10" and Balance "840"</v>
+      </c>
+      <c r="E970" t="str">
+        <v>23-09-2026 07:00:40 am</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="str">
+        <v>6ab32be31995f3c9fbbd7b99</v>
+      </c>
+      <c r="B971" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C971" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D971" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E971" t="str">
+        <v>23-09-2026 07:01:15 am</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="str">
+        <v>6ab32be41995f3c9fbbd7ba1</v>
+      </c>
+      <c r="B972" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C972" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D972" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E972" t="str">
+        <v>23-09-2026 07:01:16 am</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="str">
+        <v>6ab32bea1995f3c9fbbd7cd0</v>
+      </c>
+      <c r="B973" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C973" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D973" t="str">
+        <v>Started Playing game and Debited "10" and Balance "830"</v>
+      </c>
+      <c r="E973" t="str">
+        <v>23-09-2026 07:01:22 am</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="str">
+        <v>6ab32beb1995f3c9fbbd7cd6</v>
+      </c>
+      <c r="B974" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C974" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D974" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E974" t="str">
+        <v>23-09-2026 07:01:23 am</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="str">
+        <v>6ab32c001995f3c9fbbd7d20</v>
+      </c>
+      <c r="B975" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C975" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D975" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab32bed1995f3c9fbbd7cff, Reward : 10, Qst No : 2 ,Question : How many boxes are 1:2?</v>
+      </c>
+      <c r="E975" t="str">
+        <v>23-09-2026 07:01:44 am</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="str">
+        <v>6ab32c041995f3c9fbbd7d43</v>
+      </c>
+      <c r="B976" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C976" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D976" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab32c041995f3c9fbbd7d34 , Question : How many boxes are 2:3?, Type :  </v>
+      </c>
+      <c r="E976" t="str">
+        <v>23-09-2026 07:01:48 am</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="str">
+        <v>6ab32c051995f3c9fbbd7d47</v>
+      </c>
+      <c r="B977" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C977" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D977" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab32c041995f3c9fbbd7d34 , Question : How many boxes are 2:3?, Type :  </v>
+      </c>
+      <c r="E977" t="str">
+        <v>23-09-2026 07:01:49 am</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="str">
+        <v>6ab32c0e1995f3c9fbbd7d59</v>
+      </c>
+      <c r="B978" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C978" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D978" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab32c041995f3c9fbbd7d34, Reward : 40, Qst No : 3 ,Question : How many boxes are 2:3?</v>
+      </c>
+      <c r="E978" t="str">
+        <v>23-09-2026 07:01:58 am</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="str">
+        <v>6ab32c141995f3c9fbbd7d7c</v>
+      </c>
+      <c r="B979" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C979" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D979" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6ab32c141995f3c9fbbd7d6d , Question : How many boxes are 2:3?, Type :  </v>
+      </c>
+      <c r="E979" t="str">
+        <v>23-09-2026 07:02:04 am</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="str">
+        <v>6ab32c151995f3c9fbbd7d7f</v>
+      </c>
+      <c r="B980" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C980" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D980" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6ab32c141995f3c9fbbd7d6d , Question : How many boxes are 2:3?, Type :  </v>
+      </c>
+      <c r="E980" t="str">
+        <v>23-09-2026 07:02:05 am</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="str">
+        <v>6ab32c241995f3c9fbbd7db5</v>
+      </c>
+      <c r="B981" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C981" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D981" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6ab32c231995f3c9fbbd7da6 , Question : How many boxes are 2:3?, Type :  </v>
+      </c>
+      <c r="E981" t="str">
+        <v>23-09-2026 07:02:20 am</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="str">
+        <v>6ab32c1e1995f3c9fbbd7d92</v>
+      </c>
+      <c r="B982" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C982" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D982" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab32c141995f3c9fbbd7d6d, Reward : 30, Qst No : 4 ,Question : How many boxes are 2:3?</v>
+      </c>
+      <c r="E982" t="str">
+        <v>23-09-2026 07:02:14 am</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="str">
+        <v>6ab32c241995f3c9fbbd7db8</v>
+      </c>
+      <c r="B983" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C983" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D983" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6ab32c231995f3c9fbbd7da6 , Question : How many boxes are 2:3?, Type :  </v>
+      </c>
+      <c r="E983" t="str">
+        <v>23-09-2026 07:02:20 am</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="str">
+        <v>6ab33473c2b18a7f13cb8ea9</v>
+      </c>
+      <c r="B984" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C984" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D984" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E984" t="str">
+        <v>23-09-2026 07:37:47 am</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="str">
+        <v>6ab33474c2b18a7f13cb8eaf</v>
+      </c>
+      <c r="B985" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C985" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D985" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E985" t="str">
+        <v>23-09-2026 07:37:48 am</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="str">
+        <v>6ab3347dc2b18a7f13cb8fe1</v>
+      </c>
+      <c r="B986" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C986" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D986" t="str">
+        <v>Started Playing game and Debited "10" and Balance "820"</v>
+      </c>
+      <c r="E986" t="str">
+        <v>23-09-2026 07:37:57 am</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="str">
+        <v>6ab334a0c2b18a7f13cb9024</v>
+      </c>
+      <c r="B987" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C987" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D987" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E987" t="str">
+        <v>23-09-2026 07:38:32 am</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="str">
+        <v>6ab334a1c2b18a7f13cb902a</v>
+      </c>
+      <c r="B988" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C988" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D988" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E988" t="str">
+        <v>23-09-2026 07:38:33 am</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="str">
+        <v>6ab334aac2b18a7f13cb915d</v>
+      </c>
+      <c r="B989" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C989" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D989" t="str">
+        <v>Started Playing game and Debited "10" and Balance "810"</v>
+      </c>
+      <c r="E989" t="str">
+        <v>23-09-2026 07:38:42 am</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E965"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E989"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E989"/>
+  <dimension ref="A1:E993"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -17212,9 +17212,77 @@
         <v>23-09-2026 07:38:42 am</v>
       </c>
     </row>
+    <row r="990">
+      <c r="A990" t="str">
+        <v>6ab34864ede13d77e4a6ec75</v>
+      </c>
+      <c r="B990" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C990" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D990" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E990" t="str">
+        <v>23-09-2026 09:02:52 am</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="str">
+        <v>6ab34864ede13d77e4a6ec7c</v>
+      </c>
+      <c r="B991" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C991" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D991" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E991" t="str">
+        <v>23-09-2026 09:02:52 am</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="str">
+        <v>6ab3486bede13d77e4a6edb0</v>
+      </c>
+      <c r="B992" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C992" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D992" t="str">
+        <v>Started Playing game and Debited "10" and Balance "800"</v>
+      </c>
+      <c r="E992" t="str">
+        <v>23-09-2026 09:02:59 am</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="str">
+        <v>6ab3486cede13d77e4a6edb6</v>
+      </c>
+      <c r="B993" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C993" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D993" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E993" t="str">
+        <v>23-09-2026 09:03:00 am</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E989"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E993"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E993"/>
+  <dimension ref="A1:E1000"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -17280,9 +17280,128 @@
         <v>23-09-2026 09:03:00 am</v>
       </c>
     </row>
+    <row r="994">
+      <c r="A994" t="str">
+        <v>6ab3f191842fa99ee20ee1cf</v>
+      </c>
+      <c r="B994" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C994" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D994" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E994" t="str">
+        <v>23-09-2026 09:04:41 pm</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="str">
+        <v>6ab3f192842fa99ee20ee1d5</v>
+      </c>
+      <c r="B995" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C995" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D995" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E995" t="str">
+        <v>23-09-2026 09:04:42 pm</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="str">
+        <v>6ab3f19c842fa99ee20ee30a</v>
+      </c>
+      <c r="B996" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C996" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D996" t="str">
+        <v>Started Playing game and Debited "10" and Balance "790"</v>
+      </c>
+      <c r="E996" t="str">
+        <v>23-09-2026 09:04:52 pm</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="str">
+        <v>6ab3f19c842fa99ee20ee310</v>
+      </c>
+      <c r="B997" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C997" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D997" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E997" t="str">
+        <v>23-09-2026 09:04:52 pm</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="str">
+        <v>6ab3f1ae842fa99ee20ee33c</v>
+      </c>
+      <c r="B998" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C998" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D998" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab3f19e842fa99ee20ee31b, Reward : 10, Qst No : 2 ,Question : Find the final code from the given code.  #9 code.</v>
+      </c>
+      <c r="E998" t="str">
+        <v>23-09-2026 09:05:10 pm</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="str">
+        <v>6ab3f1b8842fa99ee20ee35f</v>
+      </c>
+      <c r="B999" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C999" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D999" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab3f1b7842fa99ee20ee350 , Question : Find the final code from the given code.  #8 code., Type :  </v>
+      </c>
+      <c r="E999" t="str">
+        <v>23-09-2026 09:05:20 pm</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="str">
+        <v>6ab3f1b8842fa99ee20ee362</v>
+      </c>
+      <c r="B1000" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1000" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1000" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab3f1b7842fa99ee20ee350 , Question : Find the final code from the given code.  #8 code., Type :  </v>
+      </c>
+      <c r="E1000" t="str">
+        <v>23-09-2026 09:05:20 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E993"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1000"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1000"/>
+  <dimension ref="A1:E1035"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -17399,9 +17399,604 @@
         <v>23-09-2026 09:05:20 pm</v>
       </c>
     </row>
+    <row r="1001">
+      <c r="A1001" t="str">
+        <v>6ab50c818ec8d7cfd614e9c9</v>
+      </c>
+      <c r="B1001" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1001" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1001" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1001" t="str">
+        <v>24-09-2026 05:11:53 pm</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="str">
+        <v>6ab50c828ec8d7cfd614e9d5</v>
+      </c>
+      <c r="B1002" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1002" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1002" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1002" t="str">
+        <v>24-09-2026 05:11:54 pm</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="str">
+        <v>6ab50c978ec8d7cfd614e9e6</v>
+      </c>
+      <c r="B1003" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1003" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1003" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1003" t="str">
+        <v>24-09-2026 05:12:15 pm</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="str">
+        <v>6ab50c978ec8d7cfd614e9ed</v>
+      </c>
+      <c r="B1004" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1004" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1004" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1004" t="str">
+        <v>24-09-2026 05:12:15 pm</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="str">
+        <v>6ab50ca28ec8d7cfd614eb23</v>
+      </c>
+      <c r="B1005" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1005" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1005" t="str">
+        <v>Started Playing game and Debited "10" and Balance "780"</v>
+      </c>
+      <c r="E1005" t="str">
+        <v>24-09-2026 05:12:26 pm</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="str">
+        <v>6ab50ca28ec8d7cfd614eb29</v>
+      </c>
+      <c r="B1006" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1006" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1006" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1006" t="str">
+        <v>24-09-2026 05:12:26 pm</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="str">
+        <v>6ab50d3f8ec8d7cfd614eb7b</v>
+      </c>
+      <c r="B1007" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1007" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1007" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1007" t="str">
+        <v>24-09-2026 05:15:03 pm</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="str">
+        <v>6ab50d408ec8d7cfd614eb81</v>
+      </c>
+      <c r="B1008" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1008" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1008" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1008" t="str">
+        <v>24-09-2026 05:15:04 pm</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="str">
+        <v>6ab50d468ec8d7cfd614eb94</v>
+      </c>
+      <c r="B1009" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1009" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1009" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1009" t="str">
+        <v>24-09-2026 05:15:10 pm</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="str">
+        <v>6ab50d468ec8d7cfd614eb9a</v>
+      </c>
+      <c r="B1010" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1010" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1010" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1010" t="str">
+        <v>24-09-2026 05:15:10 pm</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="str">
+        <v>6ab50d4d8ec8d7cfd614ecd1</v>
+      </c>
+      <c r="B1011" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1011" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1011" t="str">
+        <v>Started Playing game and Debited "10" and Balance "770"</v>
+      </c>
+      <c r="E1011" t="str">
+        <v>24-09-2026 05:15:17 pm</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="str">
+        <v>6ab50d4d8ec8d7cfd614ecd7</v>
+      </c>
+      <c r="B1012" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1012" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1012" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1012" t="str">
+        <v>24-09-2026 05:15:17 pm</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="str">
+        <v>6ab50d668ec8d7cfd614ed09</v>
+      </c>
+      <c r="B1013" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1013" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1013" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1013" t="str">
+        <v>24-09-2026 05:15:42 pm</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="str">
+        <v>6ab50d678ec8d7cfd614ed11</v>
+      </c>
+      <c r="B1014" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1014" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1014" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1014" t="str">
+        <v>24-09-2026 05:15:43 pm</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="str">
+        <v>6ab50d718ec8d7cfd614ee49</v>
+      </c>
+      <c r="B1015" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1015" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1015" t="str">
+        <v>Started Playing game and Debited "10" and Balance "760"</v>
+      </c>
+      <c r="E1015" t="str">
+        <v>24-09-2026 05:15:53 pm</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="str">
+        <v>6ab50d718ec8d7cfd614ee4f</v>
+      </c>
+      <c r="B1016" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1016" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1016" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1016" t="str">
+        <v>24-09-2026 05:15:53 pm</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="str">
+        <v>6ab50da68ec8d7cfd614ee89</v>
+      </c>
+      <c r="B1017" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1017" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1017" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1017" t="str">
+        <v>24-09-2026 05:16:46 pm</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="str">
+        <v>6ab50da78ec8d7cfd614ee94</v>
+      </c>
+      <c r="B1018" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1018" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1018" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1018" t="str">
+        <v>24-09-2026 05:16:47 pm</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="str">
+        <v>6ab50dad8ec8d7cfd614efcd</v>
+      </c>
+      <c r="B1019" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1019" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1019" t="str">
+        <v>Started Playing game and Debited "10" and Balance "750"</v>
+      </c>
+      <c r="E1019" t="str">
+        <v>24-09-2026 05:16:53 pm</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="str">
+        <v>6ab50dae8ec8d7cfd614efd3</v>
+      </c>
+      <c r="B1020" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1020" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1020" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1020" t="str">
+        <v>24-09-2026 05:16:54 pm</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="str">
+        <v>6ab50df98ec8d7cfd614efff</v>
+      </c>
+      <c r="B1021" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1021" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1021" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab50dae8ec8d7cfd614efde, Reward : 10, Qst No : 2 ,Question : How many colour names match their text colour out of 4?</v>
+      </c>
+      <c r="E1021" t="str">
+        <v>24-09-2026 05:18:09 pm</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="str">
+        <v>6ab50e4c8ec8d7cfd614f017</v>
+      </c>
+      <c r="B1022" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1022" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1022" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab50e4c8ec8d7cfd614f00f , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E1022" t="str">
+        <v>24-09-2026 05:19:32 pm</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="str">
+        <v>6ab50e5c8ec8d7cfd614f02d</v>
+      </c>
+      <c r="B1023" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1023" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1023" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab50e4c8ec8d7cfd614f00f, Reward : 40, Qst No : 3 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E1023" t="str">
+        <v>24-09-2026 05:19:48 pm</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="str">
+        <v>6ab50ec08ec8d7cfd614f045</v>
+      </c>
+      <c r="B1024" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1024" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1024" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6ab50ec08ec8d7cfd614f03d , Question : What is the alphabetical arrangement of these random letters: "idmz"?, Type :  </v>
+      </c>
+      <c r="E1024" t="str">
+        <v>24-09-2026 05:21:28 pm</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="str">
+        <v>6ab50ed68ec8d7cfd614f059</v>
+      </c>
+      <c r="B1025" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1025" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1025" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1025" t="str">
+        <v>24-09-2026 05:21:50 pm</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="str">
+        <v>6ab50ed78ec8d7cfd614f061</v>
+      </c>
+      <c r="B1026" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1026" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1026" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1026" t="str">
+        <v>24-09-2026 05:21:51 pm</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="str">
+        <v>6ab50f158ec8d7cfd614f19c</v>
+      </c>
+      <c r="B1027" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1027" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1027" t="str">
+        <v>Started Playing game and Debited "10" and Balance "740"</v>
+      </c>
+      <c r="E1027" t="str">
+        <v>24-09-2026 05:22:53 pm</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="str">
+        <v>6ab50f168ec8d7cfd614f1a2</v>
+      </c>
+      <c r="B1028" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1028" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1028" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1028" t="str">
+        <v>24-09-2026 05:22:54 pm</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="str">
+        <v>6ab50f578ec8d7cfd614f1c3</v>
+      </c>
+      <c r="B1029" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1029" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1029" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1029" t="str">
+        <v>24-09-2026 05:23:59 pm</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="str">
+        <v>6ab50f588ec8d7cfd614f1c9</v>
+      </c>
+      <c r="B1030" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1030" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1030" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1030" t="str">
+        <v>24-09-2026 05:24:00 pm</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="str">
+        <v>6ab510a38ec8d7cfd614f1e1</v>
+      </c>
+      <c r="B1031" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1031" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1031" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1031" t="str">
+        <v>24-09-2026 05:29:31 pm</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="str">
+        <v>6ab510a48ec8d7cfd614f1ec</v>
+      </c>
+      <c r="B1032" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1032" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1032" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1032" t="str">
+        <v>24-09-2026 05:29:32 pm</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="str">
+        <v>6ab510a98ec8d7cfd614f325</v>
+      </c>
+      <c r="B1033" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1033" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1033" t="str">
+        <v>Started Playing game and Debited "10" and Balance "730"</v>
+      </c>
+      <c r="E1033" t="str">
+        <v>24-09-2026 05:29:37 pm</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="str">
+        <v>6ab510aa8ec8d7cfd614f32b</v>
+      </c>
+      <c r="B1034" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1034" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1034" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1034" t="str">
+        <v>24-09-2026 05:29:38 pm</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="str">
+        <v>6ab5dcab569d6c1412da6686</v>
+      </c>
+      <c r="B1035" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1035" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1035" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1035" t="str">
+        <v>25-09-2026 08:00:03 am</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1000"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1035"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1035"/>
+  <dimension ref="A1:E1040"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -17994,9 +17994,94 @@
         <v>25-09-2026 08:00:03 am</v>
       </c>
     </row>
+    <row r="1036">
+      <c r="A1036" t="str">
+        <v>6ab5dcab569d6c1412da668c</v>
+      </c>
+      <c r="B1036" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1036" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1036" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1036" t="str">
+        <v>25-09-2026 08:00:03 am</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="str">
+        <v>6ab73fb1c42fdc3354a39304</v>
+      </c>
+      <c r="B1037" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1037" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1037" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1037" t="str">
+        <v>26-09-2026 09:14:49 am</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="str">
+        <v>6ab73fb2c42fdc3354a3930a</v>
+      </c>
+      <c r="B1038" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1038" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1038" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1038" t="str">
+        <v>26-09-2026 09:14:50 am</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="str">
+        <v>6ab73fbec42fdc3354a39448</v>
+      </c>
+      <c r="B1039" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1039" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1039" t="str">
+        <v>Started Playing game and Debited "10" and Balance "720"</v>
+      </c>
+      <c r="E1039" t="str">
+        <v>26-09-2026 09:15:02 am</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="str">
+        <v>6ab73fbec42fdc3354a3944e</v>
+      </c>
+      <c r="B1040" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1040" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1040" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1040" t="str">
+        <v>26-09-2026 09:15:02 am</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1035"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1040"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1040"/>
+  <dimension ref="A1:E1042"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -18079,9 +18079,43 @@
         <v>26-09-2026 09:15:02 am</v>
       </c>
     </row>
+    <row r="1041">
+      <c r="A1041" t="str">
+        <v>6ab741f7c42fdc3354a3947d</v>
+      </c>
+      <c r="B1041" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1041" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1041" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab73fc0c42fdc3354a39460, Reward : 10, Qst No : 2 ,Question : How many of the 2 numbers are correct?</v>
+      </c>
+      <c r="E1041" t="str">
+        <v>26-09-2026 09:24:31 am</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="str">
+        <v>6ab8abfeb832a973e8da83b7</v>
+      </c>
+      <c r="B1042" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1042" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1042" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1042" t="str">
+        <v>27-09-2026 11:09:10 am</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1040"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1042"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1042"/>
+  <dimension ref="A1:E1076"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -18113,9 +18113,587 @@
         <v>27-09-2026 11:09:10 am</v>
       </c>
     </row>
+    <row r="1043">
+      <c r="A1043" t="str">
+        <v>6ab8abffb832a973e8da83be</v>
+      </c>
+      <c r="B1043" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1043" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1043" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1043" t="str">
+        <v>27-09-2026 11:09:11 am</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="str">
+        <v>6ab8b17e22e26900c1c1c9ce</v>
+      </c>
+      <c r="B1044" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1044" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1044" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1044" t="str">
+        <v>27-09-2026 11:32:38 am</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="str">
+        <v>6ab8b17f22e26900c1c1c9d5</v>
+      </c>
+      <c r="B1045" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1045" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1045" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1045" t="str">
+        <v>27-09-2026 11:32:39 am</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="str">
+        <v>6ab8b18722e26900c1c1cb12</v>
+      </c>
+      <c r="B1046" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1046" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1046" t="str">
+        <v>Started Playing game and Debited "10" and Balance "710"</v>
+      </c>
+      <c r="E1046" t="str">
+        <v>27-09-2026 11:32:47 am</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="str">
+        <v>6ab8b18822e26900c1c1cb18</v>
+      </c>
+      <c r="B1047" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1047" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1047" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1047" t="str">
+        <v>27-09-2026 11:32:48 am</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="str">
+        <v>6ab8b22622e26900c1c1cb58</v>
+      </c>
+      <c r="B1048" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1048" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1048" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1048" t="str">
+        <v>27-09-2026 11:35:26 am</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="str">
+        <v>6ab8b22722e26900c1c1cb5f</v>
+      </c>
+      <c r="B1049" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1049" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1049" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1049" t="str">
+        <v>27-09-2026 11:35:27 am</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="str">
+        <v>6ab8b22e22e26900c1c1cc9d</v>
+      </c>
+      <c r="B1050" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1050" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1050" t="str">
+        <v>Started Playing game and Debited "10" and Balance "700"</v>
+      </c>
+      <c r="E1050" t="str">
+        <v>27-09-2026 11:35:34 am</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="str">
+        <v>6ab8b22e22e26900c1c1cca3</v>
+      </c>
+      <c r="B1051" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1051" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1051" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1051" t="str">
+        <v>27-09-2026 11:35:34 am</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="str">
+        <v>6ab8b36f22e26900c1c1ccd3</v>
+      </c>
+      <c r="B1052" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1052" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1052" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab8b22f22e26900c1c1ccae, Reward : 10, Qst No : 2 ,Question : How many words have the correct Vowel:Consonant ratio?</v>
+      </c>
+      <c r="E1052" t="str">
+        <v>27-09-2026 11:40:55 am</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="str">
+        <v>6ab8b37622e26900c1c1ccea</v>
+      </c>
+      <c r="B1053" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1053" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1053" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab8b37622e26900c1c1cce2 , Question : How many words are scrambled?, Type :  </v>
+      </c>
+      <c r="E1053" t="str">
+        <v>27-09-2026 11:41:02 am</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="str">
+        <v>6ab8b38b22e26900c1c1cd16</v>
+      </c>
+      <c r="B1054" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1054" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1054" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab8b38b22e26900c1c1cd0e , Question : How many words are scrambled?, Type :  </v>
+      </c>
+      <c r="E1054" t="str">
+        <v>27-09-2026 11:41:23 am</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="str">
+        <v>6ab8b38f22e26900c1c1cd28</v>
+      </c>
+      <c r="B1055" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1055" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1055" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1055" t="str">
+        <v>27-09-2026 11:41:27 am</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="str">
+        <v>6ab8b38f22e26900c1c1cd2e</v>
+      </c>
+      <c r="B1056" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1056" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1056" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1056" t="str">
+        <v>27-09-2026 11:41:27 am</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="str">
+        <v>6ab8b39622e26900c1c1ce6d</v>
+      </c>
+      <c r="B1057" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1057" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1057" t="str">
+        <v>Started Playing game and Debited "10" and Balance "690"</v>
+      </c>
+      <c r="E1057" t="str">
+        <v>27-09-2026 11:41:34 am</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="str">
+        <v>6ab8b39622e26900c1c1ce73</v>
+      </c>
+      <c r="B1058" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1058" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1058" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1058" t="str">
+        <v>27-09-2026 11:41:34 am</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="str">
+        <v>6ab8b4cd22e26900c1c1cea2</v>
+      </c>
+      <c r="B1059" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1059" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1059" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab8b39722e26900c1c1ce7e, Reward : 10, Qst No : 2 ,Question : Decode "MQ" using cipher key</v>
+      </c>
+      <c r="E1059" t="str">
+        <v>27-09-2026 11:46:45 am</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="str">
+        <v>6ab8b4d922e26900c1c1ceb9</v>
+      </c>
+      <c r="B1060" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1060" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1060" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab8b4d822e26900c1c1ceb1 , Question : How many times do the letters L, B appear in the paragraph?, Type :  </v>
+      </c>
+      <c r="E1060" t="str">
+        <v>27-09-2026 11:46:57 am</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="str">
+        <v>6ab8b4ea22e26900c1c1cece</v>
+      </c>
+      <c r="B1061" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1061" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1061" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab8b4d822e26900c1c1ceb1, Reward : 40, Qst No : 3 ,Question : How many times do the letters L, B appear in the paragraph?</v>
+      </c>
+      <c r="E1061" t="str">
+        <v>27-09-2026 11:47:14 am</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="str">
+        <v>6ab8b5b022e26900c1c1cee9</v>
+      </c>
+      <c r="B1062" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1062" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1062" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6ab8b5af22e26900c1c1cee1 , Question : How many times does the letter sequence 'fly' appear in the given words?, Type :  </v>
+      </c>
+      <c r="E1062" t="str">
+        <v>27-09-2026 11:50:32 am</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="str">
+        <v>6ab8b5be22e26900c1c1cefe</v>
+      </c>
+      <c r="B1063" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1063" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1063" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab8b5af22e26900c1c1cee1, Reward : 30, Qst No : 4 ,Question : How many times does the letter sequence 'fly' appear in the given words?</v>
+      </c>
+      <c r="E1063" t="str">
+        <v>27-09-2026 11:50:46 am</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="str">
+        <v>6ab8b5c822e26900c1c1cf15</v>
+      </c>
+      <c r="B1064" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1064" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1064" t="str">
+        <v xml:space="preserve">Created Question Number : 3, Rupees : 40, Qst ID : 6ab8b5c722e26900c1c1cf0d , Question : How many words are scrambled?, Type :  </v>
+      </c>
+      <c r="E1064" t="str">
+        <v>27-09-2026 11:50:56 am</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="str">
+        <v>6ab8b5d222e26900c1c1cf2a</v>
+      </c>
+      <c r="B1065" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1065" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1065" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1065" t="str">
+        <v>27-09-2026 11:51:06 am</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="str">
+        <v>6ab8b5d322e26900c1c1cf32</v>
+      </c>
+      <c r="B1066" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1066" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1066" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1066" t="str">
+        <v>27-09-2026 11:51:07 am</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="str">
+        <v>6ab8b5d922e26900c1c1d070</v>
+      </c>
+      <c r="B1067" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1067" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1067" t="str">
+        <v>Started Playing game and Debited "10" and Balance "680"</v>
+      </c>
+      <c r="E1067" t="str">
+        <v>27-09-2026 11:51:13 am</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="str">
+        <v>6ab8b5d922e26900c1c1d076</v>
+      </c>
+      <c r="B1068" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1068" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1068" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1068" t="str">
+        <v>27-09-2026 11:51:13 am</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="str">
+        <v>6ab8b6a222e26900c1c1d0a5</v>
+      </c>
+      <c r="B1069" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1069" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1069" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab8b5da22e26900c1c1d081, Reward : 10, Qst No : 2 ,Question : How many times do the letters B, K appear in the paragraph?</v>
+      </c>
+      <c r="E1069" t="str">
+        <v>27-09-2026 11:54:34 am</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="str">
+        <v>6ab8b78522e26900c1c1d0be</v>
+      </c>
+      <c r="B1070" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1070" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1070" t="str">
+        <v xml:space="preserve">Created Question Number : 1, Rupees : 20, Qst ID : 6ab8b78422e26900c1c1d0b6 , Question : How many broken boxes are there?, Type : Total Boxes [Broken] </v>
+      </c>
+      <c r="E1070" t="str">
+        <v>27-09-2026 11:58:21 am</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="str">
+        <v>6ab8b79522e26900c1c1d0d3</v>
+      </c>
+      <c r="B1071" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1071" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1071" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab8b78422e26900c1c1d0b6, Reward : 40, Qst No : 3 ,Question : How many broken boxes are there?</v>
+      </c>
+      <c r="E1071" t="str">
+        <v>27-09-2026 11:58:37 am</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="str">
+        <v>6ab8b82b22e26900c1c1d0ed</v>
+      </c>
+      <c r="B1072" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1072" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1072" t="str">
+        <v xml:space="preserve">Created Question Number : 2, Rupees : 30, Qst ID : 6ab8b82922e26900c1c1d0e5 , Question : How many puzzle pieces contain 2 or more MALE connectors (outward tabs)?, Type :  </v>
+      </c>
+      <c r="E1072" t="str">
+        <v>27-09-2026 12:01:07 pm</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="str">
+        <v>6ab8b83722e26900c1c1d107</v>
+      </c>
+      <c r="B1073" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1073" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1073" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1073" t="str">
+        <v>27-09-2026 12:01:19 pm</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="str">
+        <v>6ab8b83822e26900c1c1d10e</v>
+      </c>
+      <c r="B1074" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1074" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1074" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1074" t="str">
+        <v>27-09-2026 12:01:20 pm</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="str">
+        <v>6ab8b8a422e26900c1c1d251</v>
+      </c>
+      <c r="B1075" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1075" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1075" t="str">
+        <v>Started Playing game and Debited "10" and Balance "670"</v>
+      </c>
+      <c r="E1075" t="str">
+        <v>27-09-2026 12:03:08 pm</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="str">
+        <v>6ab8b8a522e26900c1c1d257</v>
+      </c>
+      <c r="B1076" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1076" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1076" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1076" t="str">
+        <v>27-09-2026 12:03:09 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1042"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1076"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1076"/>
+  <dimension ref="A1:E1080"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -18691,9 +18691,77 @@
         <v>27-09-2026 12:03:09 pm</v>
       </c>
     </row>
+    <row r="1077">
+      <c r="A1077" t="str">
+        <v>6ab8b96c22e26900c1c1d285</v>
+      </c>
+      <c r="B1077" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1077" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1077" t="str">
+        <v>Answerd Correctly to Qst ID : 6ab8b8a622e26900c1c1d262, Reward : 10, Qst No : 2 ,Question : What is the correct alphabetical order of these words?</v>
+      </c>
+      <c r="E1077" t="str">
+        <v>27-09-2026 12:06:28 pm</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="str">
+        <v>6abb57ac7f6f8e40dd624c74</v>
+      </c>
+      <c r="B1078" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1078" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1078" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1078" t="str">
+        <v>29-09-2026 11:46:12 am</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="str">
+        <v>6abb57ac7f6f8e40dd624c7a</v>
+      </c>
+      <c r="B1079" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1079" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1079" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1079" t="str">
+        <v>29-09-2026 11:46:12 am</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="str">
+        <v>6abb57b67f6f8e40dd624dbc</v>
+      </c>
+      <c r="B1080" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1080" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1080" t="str">
+        <v>Started Playing game and Debited "10" and Balance "660"</v>
+      </c>
+      <c r="E1080" t="str">
+        <v>29-09-2026 11:46:22 am</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1076"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1080"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1080"/>
+  <dimension ref="A1:E1099"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -18759,9 +18759,332 @@
         <v>29-09-2026 11:46:22 am</v>
       </c>
     </row>
+    <row r="1081">
+      <c r="A1081" t="str">
+        <v>6abb57b67f6f8e40dd624dc2</v>
+      </c>
+      <c r="B1081" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1081" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1081" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1081" t="str">
+        <v>29-09-2026 11:46:22 am</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="str">
+        <v>6abd39d1e6e4c2ee84a6b295</v>
+      </c>
+      <c r="B1082" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1082" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1082" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1082" t="str">
+        <v>30-09-2026 10:03:21 pm</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="str">
+        <v>6abd39d2e6e4c2ee84a6b29b</v>
+      </c>
+      <c r="B1083" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1083" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1083" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1083" t="str">
+        <v>30-09-2026 10:03:22 pm</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="str">
+        <v>6abd3a38e6e4c2ee84a6b40e</v>
+      </c>
+      <c r="B1084" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1084" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1084" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1084" t="str">
+        <v>30-09-2026 10:05:04 pm</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="str">
+        <v>6abd39d9e6e4c2ee84a6b3de</v>
+      </c>
+      <c r="B1085" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1085" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1085" t="str">
+        <v>Started Playing game and Debited "10" and Balance "650"</v>
+      </c>
+      <c r="E1085" t="str">
+        <v>30-09-2026 10:03:29 pm</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="str">
+        <v>6abd3a38e6e4c2ee84a6b410</v>
+      </c>
+      <c r="B1086" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1086" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1086" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1086" t="str">
+        <v>30-09-2026 10:05:04 pm</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="str">
+        <v>6abd3a44e6e4c2ee84a6b556</v>
+      </c>
+      <c r="B1087" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1087" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1087" t="str">
+        <v>Started Playing game and Debited "10" and Balance "640"</v>
+      </c>
+      <c r="E1087" t="str">
+        <v>30-09-2026 10:05:16 pm</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="str">
+        <v>6abd3a5fe6e4c2ee84a6b581</v>
+      </c>
+      <c r="B1088" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1088" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1088" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1088" t="str">
+        <v>30-09-2026 10:05:43 pm</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="str">
+        <v>6abd3a5fe6e4c2ee84a6b588</v>
+      </c>
+      <c r="B1089" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1089" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1089" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1089" t="str">
+        <v>30-09-2026 10:05:43 pm</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="str">
+        <v>6abd3a67e6e4c2ee84a6b6cd</v>
+      </c>
+      <c r="B1090" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1090" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1090" t="str">
+        <v>Started Playing game and Debited "10" and Balance "630"</v>
+      </c>
+      <c r="E1090" t="str">
+        <v>30-09-2026 10:05:51 pm</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="str">
+        <v>6abd3a68e6e4c2ee84a6b6d3</v>
+      </c>
+      <c r="B1091" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1091" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1091" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1091" t="str">
+        <v>30-09-2026 10:05:52 pm</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="str">
+        <v>6abd3abae6e4c2ee84a6b6fa</v>
+      </c>
+      <c r="B1092" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1092" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1092" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1092" t="str">
+        <v>30-09-2026 10:07:14 pm</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="str">
+        <v>6abd3abae6e4c2ee84a6b6fe</v>
+      </c>
+      <c r="B1093" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1093" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1093" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1093" t="str">
+        <v>30-09-2026 10:07:14 pm</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="str">
+        <v>6abd3acde6e4c2ee84a6b846</v>
+      </c>
+      <c r="B1094" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1094" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1094" t="str">
+        <v>Started Playing game and Debited "10" and Balance "620"</v>
+      </c>
+      <c r="E1094" t="str">
+        <v>30-09-2026 10:07:33 pm</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="str">
+        <v>6abd3d88e6e4c2ee84a6b8c4</v>
+      </c>
+      <c r="B1095" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1095" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1095" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1095" t="str">
+        <v>30-09-2026 10:19:12 pm</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="str">
+        <v>6abd3d89e6e4c2ee84a6b8cb</v>
+      </c>
+      <c r="B1096" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1096" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1096" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1096" t="str">
+        <v>30-09-2026 10:19:13 pm</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="str">
+        <v>6abd3e17e6e9cb1e707570de</v>
+      </c>
+      <c r="B1097" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1097" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1097" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1097" t="str">
+        <v>30-09-2026 10:21:35 pm</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="str">
+        <v>6abd3d90e6e4c2ee84a6ba12</v>
+      </c>
+      <c r="B1098" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1098" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1098" t="str">
+        <v>Started Playing game and Debited "10" and Balance "610"</v>
+      </c>
+      <c r="E1098" t="str">
+        <v>30-09-2026 10:19:20 pm</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="str">
+        <v>6abd3e17e6e9cb1e707570e0</v>
+      </c>
+      <c r="B1099" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1099" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1099" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1099" t="str">
+        <v>30-09-2026 10:21:35 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1080"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1099"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/live-history.xlsx
+++ b/live-history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1099"/>
+  <dimension ref="A1:E1121"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -19082,9 +19082,383 @@
         <v>30-09-2026 10:21:35 pm</v>
       </c>
     </row>
+    <row r="1100">
+      <c r="A1100" t="str">
+        <v>6abd3e20e6e9cb1e7075722a</v>
+      </c>
+      <c r="B1100" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1100" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1100" t="str">
+        <v>Started Playing game and Debited "10" and Balance "600"</v>
+      </c>
+      <c r="E1100" t="str">
+        <v>30-09-2026 10:21:44 pm</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="str">
+        <v>6abe6a545c0087cbd83335de</v>
+      </c>
+      <c r="B1101" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1101" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1101" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1101" t="str">
+        <v>01-10-2026 07:42:36 pm</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="str">
+        <v>6abe6a555c0087cbd83335e5</v>
+      </c>
+      <c r="B1102" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1102" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1102" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1102" t="str">
+        <v>01-10-2026 07:42:37 pm</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="str">
+        <v>6abe6bc35c0087cbd83335f8</v>
+      </c>
+      <c r="B1103" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1103" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1103" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1103" t="str">
+        <v>01-10-2026 07:48:43 pm</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="str">
+        <v>6abe6bc45c0087cbd83335fe</v>
+      </c>
+      <c r="B1104" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1104" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1104" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1104" t="str">
+        <v>01-10-2026 07:48:44 pm</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="str">
+        <v>6abe6c805c0087cbd8333610</v>
+      </c>
+      <c r="B1105" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1105" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1105" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1105" t="str">
+        <v>01-10-2026 07:51:52 pm</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="str">
+        <v>6abe6d055c0087cbd833362b</v>
+      </c>
+      <c r="B1106" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1106" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1106" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1106" t="str">
+        <v>01-10-2026 07:54:05 pm</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="str">
+        <v>6abe6c815c0087cbd8333617</v>
+      </c>
+      <c r="B1107" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1107" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1107" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1107" t="str">
+        <v>01-10-2026 07:51:53 pm</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="str">
+        <v>6abe6d055c0087cbd833362d</v>
+      </c>
+      <c r="B1108" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1108" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1108" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1108" t="str">
+        <v>01-10-2026 07:54:05 pm</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="str">
+        <v>6abe6dcc5c0087cbd8333643</v>
+      </c>
+      <c r="B1109" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1109" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1109" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1109" t="str">
+        <v>01-10-2026 07:57:24 pm</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="str">
+        <v>6abe6dcc5c0087cbd8333647</v>
+      </c>
+      <c r="B1110" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1110" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1110" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1110" t="str">
+        <v>01-10-2026 07:57:24 pm</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="str">
+        <v>6abe6e155c0087cbd833365d</v>
+      </c>
+      <c r="B1111" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1111" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1111" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1111" t="str">
+        <v>01-10-2026 07:58:37 pm</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="str">
+        <v>6abe6e635c0087cbd8333676</v>
+      </c>
+      <c r="B1112" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1112" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1112" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1112" t="str">
+        <v>01-10-2026 07:59:55 pm</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="str">
+        <v>6abe6e155c0087cbd8333660</v>
+      </c>
+      <c r="B1113" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1113" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1113" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1113" t="str">
+        <v>01-10-2026 07:58:37 pm</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="str">
+        <v>6abe6e635c0087cbd8333679</v>
+      </c>
+      <c r="B1114" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1114" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1114" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1114" t="str">
+        <v>01-10-2026 07:59:55 pm</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="str">
+        <v>6abe74685c0087cbd833368e</v>
+      </c>
+      <c r="B1115" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1115" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1115" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1115" t="str">
+        <v>01-10-2026 08:25:36 pm</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="str">
+        <v>6abe747d5c0087cbd83336a9</v>
+      </c>
+      <c r="B1116" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1116" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1116" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1116" t="str">
+        <v>01-10-2026 08:25:57 pm</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="str">
+        <v>6abe74685c0087cbd8333694</v>
+      </c>
+      <c r="B1117" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1117" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1117" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1117" t="str">
+        <v>01-10-2026 08:25:36 pm</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="str">
+        <v>6abe74895c0087cbd83336bf</v>
+      </c>
+      <c r="B1118" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1118" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1118" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1118" t="str">
+        <v>01-10-2026 08:26:09 pm</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="str">
+        <v>6abe747d5c0087cbd83336ab</v>
+      </c>
+      <c r="B1119" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1119" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1119" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1119" t="str">
+        <v>01-10-2026 08:25:57 pm</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="str">
+        <v>6abe74895c0087cbd83336c5</v>
+      </c>
+      <c r="B1120" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1120" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1120" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1120" t="str">
+        <v>01-10-2026 08:26:09 pm</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="str">
+        <v>6abe77c15c0087cbd83336d8</v>
+      </c>
+      <c r="B1121" t="str">
+        <v>686e24d32f21c9417882f777</v>
+      </c>
+      <c r="C1121" t="str">
+        <v>Unknown Error</v>
+      </c>
+      <c r="D1121" t="str">
+        <v>Checking Account Balance</v>
+      </c>
+      <c r="E1121" t="str">
+        <v>01-10-2026 08:39:53 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1099"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1121"/>
   </ignoredErrors>
 </worksheet>
 </file>